--- a/languages/de/packs/de/books/德语B2.xlsx
+++ b/languages/de/packs/de/books/德语B2.xlsx
@@ -435,7 +435,7 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>[ɛlfən] 仙女；精灵；仙女的〈n.〉</t>
+          <t>[ɛlfən] 精灵；小仙子（复数）〈n.〉</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
@@ -445,7 +445,7 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>仙女；精灵；仙女的</t>
+          <t>精灵；小仙子（复数）</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
@@ -691,7 +691,7 @@
       </c>
       <c r="B9" s="1" t="inlineStr">
         <is>
-          <t>[ɛʁfɔlɡʁaɪçɐ] 交易者〈adv.〉</t>
+          <t>[ɛʁfɔlɡʁaɪçɐ] 更成功的；成功的〈adv.〉</t>
         </is>
       </c>
       <c r="C9" s="1" t="inlineStr">
@@ -701,7 +701,7 @@
       </c>
       <c r="D9" s="1" t="inlineStr">
         <is>
-          <t>交易者</t>
+          <t>更成功的；成功的</t>
         </is>
       </c>
       <c r="E9" s="1" t="inlineStr">
@@ -819,7 +819,7 @@
       </c>
       <c r="B13" s="1" t="inlineStr">
         <is>
-          <t>[aʊstɐn] 真实的；正确的；忠诚的〈n.〉</t>
+          <t>[aʊstɐn] 牡蛎〈n.〉</t>
         </is>
       </c>
       <c r="C13" s="1" t="inlineStr">
@@ -829,7 +829,7 @@
       </c>
       <c r="D13" s="1" t="inlineStr">
         <is>
-          <t>真实的；正确的；忠诚的</t>
+          <t>牡蛎</t>
         </is>
       </c>
       <c r="E13" s="1" t="inlineStr">
@@ -883,7 +883,7 @@
       </c>
       <c r="B15" s="1" t="inlineStr">
         <is>
-          <t>[muːzɪkaːl] 音乐片；声音美妙的〈n.〉</t>
+          <t>[muːzɪkaːl] 音乐剧〈n.〉</t>
         </is>
       </c>
       <c r="C15" s="1" t="inlineStr">
@@ -893,7 +893,7 @@
       </c>
       <c r="D15" s="1" t="inlineStr">
         <is>
-          <t>音乐片；声音美妙的</t>
+          <t>音乐剧</t>
         </is>
       </c>
       <c r="E15" s="1" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="B38" s="1" t="inlineStr">
         <is>
-          <t>[faːfɔʁiːt] 宠爱的〈n.m.〉</t>
+          <t>[faːfɔʁiːt] 夺冠热门；受宠者；心腹〈n.m.〉</t>
         </is>
       </c>
       <c r="C38" s="1" t="inlineStr">
@@ -1629,7 +1629,7 @@
       </c>
       <c r="D38" s="1" t="inlineStr">
         <is>
-          <t>宠爱的</t>
+          <t>夺冠热门；受宠者；心腹</t>
         </is>
       </c>
       <c r="E38" s="1" t="inlineStr">
@@ -1715,7 +1715,7 @@
       </c>
       <c r="B41" s="1" t="inlineStr">
         <is>
-          <t>[banɐ] 旗帜；显著的；特别好的〈n.〉</t>
+          <t>[banɐ] 横幅；旗帜；标语牌〈n.〉</t>
         </is>
       </c>
       <c r="C41" s="1" t="inlineStr">
@@ -1725,7 +1725,7 @@
       </c>
       <c r="D41" s="1" t="inlineStr">
         <is>
-          <t>旗帜；显著的；特别好的</t>
+          <t>横幅；旗帜；标语牌</t>
         </is>
       </c>
       <c r="E41" s="1" t="inlineStr">
@@ -2419,7 +2419,7 @@
       </c>
       <c r="B63" s="1" t="inlineStr">
         <is>
-          <t>[ʁʏkəndəkʊnk] 后面；背后；后方；后面的〈n.f.〉</t>
+          <t>[ʁʏkəndəkʊnk] 后盾；支援；掩护〈n.f.〉</t>
         </is>
       </c>
       <c r="C63" s="1" t="inlineStr">
@@ -2429,7 +2429,7 @@
       </c>
       <c r="D63" s="1" t="inlineStr">
         <is>
-          <t>后面；背后；后方；后面的</t>
+          <t>后盾；支援；掩护</t>
         </is>
       </c>
       <c r="E63" s="1" t="inlineStr">
@@ -2867,7 +2867,7 @@
       </c>
       <c r="B77" s="1" t="inlineStr">
         <is>
-          <t>[ɛʁt͡stlɪçə] 药物治疗；药物处理；医药；药疗法〈adv.〉</t>
+          <t>[ɛʁt͡stlɪçə] 医生的；医疗的〈adv.〉</t>
         </is>
       </c>
       <c r="C77" s="1" t="inlineStr">
@@ -2877,7 +2877,7 @@
       </c>
       <c r="D77" s="1" t="inlineStr">
         <is>
-          <t>药物治疗；药物处理；医药；药疗法</t>
+          <t>医生的；医疗的</t>
         </is>
       </c>
       <c r="E77" s="1" t="inlineStr">
@@ -3443,7 +3443,7 @@
       </c>
       <c r="B95" s="1" t="inlineStr">
         <is>
-          <t>[yːbəʁzeː] 在海洋彼岸的；横越海洋的〈n.〉</t>
+          <t>[yːbəʁzeː] 海外；海外地区〈n.〉</t>
         </is>
       </c>
       <c r="C95" s="1" t="inlineStr">
@@ -3453,7 +3453,7 @@
       </c>
       <c r="D95" s="1" t="inlineStr">
         <is>
-          <t>在海洋彼岸的；横越海洋的</t>
+          <t>海外；海外地区</t>
         </is>
       </c>
       <c r="E95" s="1" t="inlineStr">
@@ -3667,7 +3667,7 @@
       </c>
       <c r="B102" s="1" t="inlineStr">
         <is>
-          <t>[kʁøːtən] 真实的；正确的；忠诚的〈n.〉</t>
+          <t>[kʁøːtən] 蟾蜍；癞蛤蟆〈n.〉</t>
         </is>
       </c>
       <c r="C102" s="1" t="inlineStr">
@@ -3677,7 +3677,7 @@
       </c>
       <c r="D102" s="1" t="inlineStr">
         <is>
-          <t>真实的；正确的；忠诚的</t>
+          <t>蟾蜍；癞蛤蟆</t>
         </is>
       </c>
       <c r="E102" s="1" t="inlineStr">
@@ -4275,7 +4275,7 @@
       </c>
       <c r="B121" s="1" t="inlineStr">
         <is>
-          <t>[noːtaːɐ] 市民的；公民的；有礼貌的〈n.m.〉</t>
+          <t>[noːtaːɐ] 公证人〈n.m.〉</t>
         </is>
       </c>
       <c r="C121" s="1" t="inlineStr">
@@ -4285,7 +4285,7 @@
       </c>
       <c r="D121" s="1" t="inlineStr">
         <is>
-          <t>市民的；公民的；有礼貌的</t>
+          <t>公证人</t>
         </is>
       </c>
       <c r="E121" s="1" t="inlineStr">
@@ -5139,7 +5139,7 @@
       </c>
       <c r="B148" s="1" t="inlineStr">
         <is>
-          <t>[tʁaɪp] 推进的〈n.〉</t>
+          <t>[tʁaɪp] 驱使；推动；漂移〈n.〉</t>
         </is>
       </c>
       <c r="C148" s="1" t="inlineStr">
@@ -5149,7 +5149,7 @@
       </c>
       <c r="D148" s="1" t="inlineStr">
         <is>
-          <t>推进的</t>
+          <t>驱使；推动；漂移</t>
         </is>
       </c>
       <c r="E148" s="1" t="inlineStr">
@@ -5203,7 +5203,7 @@
       </c>
       <c r="B150" s="1" t="inlineStr">
         <is>
-          <t>[pzʏçoːlɔɡɪʃə] 思想；愿望；智力〈adv.〉</t>
+          <t>[pzʏçoːlɔɡɪʃə] 心理学的；心理上的〈adv.〉</t>
         </is>
       </c>
       <c r="C150" s="1" t="inlineStr">
@@ -5213,7 +5213,7 @@
       </c>
       <c r="D150" s="1" t="inlineStr">
         <is>
-          <t>思想；愿望；智力</t>
+          <t>心理学的；心理上的</t>
         </is>
       </c>
       <c r="E150" s="1" t="inlineStr">
@@ -5619,7 +5619,7 @@
       </c>
       <c r="B163" s="1" t="inlineStr">
         <is>
-          <t>[altaːk] 每天的；日常的；平常的〈n.m.〉</t>
+          <t>[altaːk] 日常生活；平日〈n.m.〉</t>
         </is>
       </c>
       <c r="C163" s="1" t="inlineStr">
@@ -5629,7 +5629,7 @@
       </c>
       <c r="D163" s="1" t="inlineStr">
         <is>
-          <t>每天的；日常的；平常的</t>
+          <t>日常生活；平日</t>
         </is>
       </c>
       <c r="E163" s="1" t="inlineStr">
@@ -7187,7 +7187,7 @@
       </c>
       <c r="B212" s="1" t="inlineStr">
         <is>
-          <t>[bɛkvəmɐ] 游手好闲的人；懒人；懒汉鞋；无业游民〈adv.〉</t>
+          <t>[bɛkvəmɐ] 更舒适的；更安逸的〈adv.〉</t>
         </is>
       </c>
       <c r="C212" s="1" t="inlineStr">
@@ -7197,7 +7197,7 @@
       </c>
       <c r="D212" s="1" t="inlineStr">
         <is>
-          <t>游手好闲的人；懒人；懒汉鞋；无业游民</t>
+          <t>更舒适的；更安逸的</t>
         </is>
       </c>
       <c r="E212" s="1" t="inlineStr">
@@ -8531,7 +8531,7 @@
       </c>
       <c r="B254" s="1" t="inlineStr">
         <is>
-          <t>[handlanɡɐ] 抚恤金的；领取抚恤金的；依靠抚恤金生活的〈n.m.〉</t>
+          <t>[handlanɡɐ] 帮凶；爪牙；打杂工〈n.m.〉</t>
         </is>
       </c>
       <c r="C254" s="1" t="inlineStr">
@@ -8541,7 +8541,7 @@
       </c>
       <c r="D254" s="1" t="inlineStr">
         <is>
-          <t>抚恤金的；领取抚恤金的；依靠抚恤金生活的</t>
+          <t>帮凶；爪牙；打杂工</t>
         </is>
       </c>
       <c r="E254" s="1" t="inlineStr">
@@ -8787,7 +8787,7 @@
       </c>
       <c r="B262" s="1" t="inlineStr">
         <is>
-          <t>[paːt͡sɪfiːk] 太平洋沿岸的；爱好和平的〈n.m.〉</t>
+          <t>[paːt͡sɪfiːk] 太平洋〈n.m.〉</t>
         </is>
       </c>
       <c r="C262" s="1" t="inlineStr">
@@ -8797,7 +8797,7 @@
       </c>
       <c r="D262" s="1" t="inlineStr">
         <is>
-          <t>太平洋沿岸的；爱好和平的</t>
+          <t>太平洋</t>
         </is>
       </c>
       <c r="E262" s="1" t="inlineStr">
@@ -8851,7 +8851,7 @@
       </c>
       <c r="B264" s="1" t="inlineStr">
         <is>
-          <t>[dɛnkmaːl] 纪念物；记忆的〈n.〉</t>
+          <t>[dɛnkmaːl] 纪念碑；历史古迹〈n.〉</t>
         </is>
       </c>
       <c r="C264" s="1" t="inlineStr">
@@ -8861,7 +8861,7 @@
       </c>
       <c r="D264" s="1" t="inlineStr">
         <is>
-          <t>纪念物；记忆的</t>
+          <t>纪念碑；历史古迹</t>
         </is>
       </c>
       <c r="E264" s="1" t="inlineStr">
@@ -9107,7 +9107,7 @@
       </c>
       <c r="B272" s="1" t="inlineStr">
         <is>
-          <t>[ʃtʁøːmʊnk] 涌流；趋势；流；流通的〈n.f.〉</t>
+          <t>[ʃtʁøːmʊnk] 水流；气流；思潮；潮流〈n.f.〉</t>
         </is>
       </c>
       <c r="C272" s="1" t="inlineStr">
@@ -9117,7 +9117,7 @@
       </c>
       <c r="D272" s="1" t="inlineStr">
         <is>
-          <t>涌流；趋势；流；流通的</t>
+          <t>水流；气流；思潮；潮流</t>
         </is>
       </c>
       <c r="E272" s="1" t="inlineStr">
@@ -9747,7 +9747,7 @@
       </c>
       <c r="B292" s="1" t="inlineStr">
         <is>
-          <t>[høːən] 高空的〈n.〉</t>
+          <t>[høːən] 高度；高空；高峰（复数）〈n.〉</t>
         </is>
       </c>
       <c r="C292" s="1" t="inlineStr">
@@ -9757,7 +9757,7 @@
       </c>
       <c r="D292" s="1" t="inlineStr">
         <is>
-          <t>高空的</t>
+          <t>高度；高空；高峰（复数）</t>
         </is>
       </c>
       <c r="E292" s="1" t="inlineStr">
@@ -10131,7 +10131,7 @@
       </c>
       <c r="B304" s="1" t="inlineStr">
         <is>
-          <t>[fɛʁkəl] 年轻的；无经验的〈n.〉</t>
+          <t>[fɛʁkəl] 小猪；小猪仔；邋遢鬼〈n.〉</t>
         </is>
       </c>
       <c r="C304" s="1" t="inlineStr">
@@ -10141,7 +10141,7 @@
       </c>
       <c r="D304" s="1" t="inlineStr">
         <is>
-          <t>年轻的；无经验的</t>
+          <t>小猪；小猪仔；邋遢鬼</t>
         </is>
       </c>
       <c r="E304" s="1" t="inlineStr">
@@ -10291,7 +10291,7 @@
       </c>
       <c r="B309" s="1" t="inlineStr">
         <is>
-          <t>[ɛfɪt͡siːnt] 生效；能胜任；有能力〈adv.〉</t>
+          <t>[ɛfɪt͡siːnt] 高效的；有成效的〈adv.〉</t>
         </is>
       </c>
       <c r="C309" s="1" t="inlineStr">
@@ -10301,7 +10301,7 @@
       </c>
       <c r="D309" s="1" t="inlineStr">
         <is>
-          <t>生效；能胜任；有能力</t>
+          <t>高效的；有成效的</t>
         </is>
       </c>
       <c r="E309" s="1" t="inlineStr">
@@ -10995,7 +10995,7 @@
       </c>
       <c r="B331" s="1" t="inlineStr">
         <is>
-          <t>[eːʁənhaft] 值得尊敬的；荣耀的；高贵的〈n.f.〉</t>
+          <t>[eːʁənhaft] 体面；正直；光荣行为〈n.f.〉</t>
         </is>
       </c>
       <c r="C331" s="1" t="inlineStr">
@@ -11005,7 +11005,7 @@
       </c>
       <c r="D331" s="1" t="inlineStr">
         <is>
-          <t>值得尊敬的；荣耀的；高贵的</t>
+          <t>体面；正直；光荣行为</t>
         </is>
       </c>
       <c r="E331" s="1" t="inlineStr">
@@ -11251,7 +11251,7 @@
       </c>
       <c r="B339" s="1" t="inlineStr">
         <is>
-          <t>[ʊnɡlʏklɪçə] 不幸的；不合适的；不吉利的〈n.〉</t>
+          <t>[ʊnɡlʏklɪçə] 不幸者；可怜人〈n.〉</t>
         </is>
       </c>
       <c r="C339" s="1" t="inlineStr">
@@ -11261,7 +11261,7 @@
       </c>
       <c r="D339" s="1" t="inlineStr">
         <is>
-          <t>不幸的；不合适的；不吉利的</t>
+          <t>不幸者；可怜人</t>
         </is>
       </c>
       <c r="E339" s="1" t="inlineStr">
@@ -12083,7 +12083,7 @@
       </c>
       <c r="B365" s="1" t="inlineStr">
         <is>
-          <t>[pʁeːmiːɐ] 总理；首相；首位的；最初的〈n.m.〉</t>
+          <t>[pʁeːmiːɐ] 总理；首相〈n.m.〉</t>
         </is>
       </c>
       <c r="C365" s="1" t="inlineStr">
@@ -12093,7 +12093,7 @@
       </c>
       <c r="D365" s="1" t="inlineStr">
         <is>
-          <t>总理；首相；首位的；最初的</t>
+          <t>总理；首相</t>
         </is>
       </c>
       <c r="E365" s="1" t="inlineStr">
@@ -12595,7 +12595,7 @@
       </c>
       <c r="B381" s="1" t="inlineStr">
         <is>
-          <t>[ɔbdaxlɔzə] 无家的；无养主的〈n.〉</t>
+          <t>[ɔbdaxlɔzə] 无家可归者；流浪者〈n.〉</t>
         </is>
       </c>
       <c r="C381" s="1" t="inlineStr">
@@ -12605,7 +12605,7 @@
       </c>
       <c r="D381" s="1" t="inlineStr">
         <is>
-          <t>无家的；无养主的</t>
+          <t>无家可归者；流浪者</t>
         </is>
       </c>
       <c r="E381" s="1" t="inlineStr">
@@ -12819,7 +12819,7 @@
       </c>
       <c r="B388" s="1" t="inlineStr">
         <is>
-          <t>[naːtʊʁtalənt] 白痴；自然的；自然界的；本能的〈n.〉</t>
+          <t>[naːtʊʁtalənt] 天生奇才；天赋型人才〈n.〉</t>
         </is>
       </c>
       <c r="C388" s="1" t="inlineStr">
@@ -12829,7 +12829,7 @@
       </c>
       <c r="D388" s="1" t="inlineStr">
         <is>
-          <t>白痴；自然的；自然界的；本能的</t>
+          <t>天生奇才；天赋型人才</t>
         </is>
       </c>
       <c r="E388" s="1" t="inlineStr">
@@ -13203,7 +13203,7 @@
       </c>
       <c r="B400" s="1" t="inlineStr">
         <is>
-          <t>[kʁyːməl] 小的；少的；小型的〈n.m.〉</t>
+          <t>[kʁyːməl] 面包屑；碎屑〈n.m.〉</t>
         </is>
       </c>
       <c r="C400" s="1" t="inlineStr">
@@ -13213,7 +13213,7 @@
       </c>
       <c r="D400" s="1" t="inlineStr">
         <is>
-          <t>小的；少的；小型的</t>
+          <t>面包屑；碎屑</t>
         </is>
       </c>
       <c r="E400" s="1" t="inlineStr">
@@ -14835,7 +14835,7 @@
       </c>
       <c r="B451" s="1" t="inlineStr">
         <is>
-          <t>[vyːtəndɐ] 闪耀光〈adv.〉</t>
+          <t>[vyːtəndɐ] 更愤怒的〈adv.〉</t>
         </is>
       </c>
       <c r="C451" s="1" t="inlineStr">
@@ -14845,7 +14845,7 @@
       </c>
       <c r="D451" s="1" t="inlineStr">
         <is>
-          <t>闪耀光</t>
+          <t>更愤怒的</t>
         </is>
       </c>
       <c r="E451" s="1" t="inlineStr">
@@ -14963,7 +14963,7 @@
       </c>
       <c r="B455" s="1" t="inlineStr">
         <is>
-          <t>[çiːnəzɪʃəs] 中文；中国话〈adv.〉</t>
+          <t>[çiːnəzɪʃəs] 中国的；汉语的〈adv.〉</t>
         </is>
       </c>
       <c r="C455" s="1" t="inlineStr">
@@ -14973,7 +14973,7 @@
       </c>
       <c r="D455" s="1" t="inlineStr">
         <is>
-          <t>中文；中国话</t>
+          <t>中国的；汉语的</t>
         </is>
       </c>
       <c r="E455" s="1" t="inlineStr">
@@ -17107,7 +17107,7 @@
       </c>
       <c r="B522" s="1" t="inlineStr">
         <is>
-          <t>[bɔʏʁtaɪlʊnk] 机密的；获他人信赖的〈n.f.〉</t>
+          <t>[bɔʏʁtaɪlʊnk] 评估；评判；鉴定〈n.f.〉</t>
         </is>
       </c>
       <c r="C522" s="1" t="inlineStr">
@@ -17117,7 +17117,7 @@
       </c>
       <c r="D522" s="1" t="inlineStr">
         <is>
-          <t>机密的；获他人信赖的</t>
+          <t>评估；评判；鉴定</t>
         </is>
       </c>
       <c r="E522" s="1" t="inlineStr">
@@ -17299,7 +17299,7 @@
       </c>
       <c r="B528" s="1" t="inlineStr">
         <is>
-          <t>[hɛk] 尾部；船尾；臀；严厉的〈n.〉</t>
+          <t>[hɛk] 车尾；船尾〈n.〉</t>
         </is>
       </c>
       <c r="C528" s="1" t="inlineStr">
@@ -17309,7 +17309,7 @@
       </c>
       <c r="D528" s="1" t="inlineStr">
         <is>
-          <t>尾部；船尾；臀；严厉的</t>
+          <t>车尾；船尾</t>
         </is>
       </c>
       <c r="E528" s="1" t="inlineStr">
@@ -18643,7 +18643,7 @@
       </c>
       <c r="B570" s="1" t="inlineStr">
         <is>
-          <t>[tøːtʊnk] 谋杀；杀戮；杀害的；疲惫的〈n.f.〉</t>
+          <t>[tøːtʊnk] 杀害；杀戮；致死〈n.f.〉</t>
         </is>
       </c>
       <c r="C570" s="1" t="inlineStr">
@@ -18653,7 +18653,7 @@
       </c>
       <c r="D570" s="1" t="inlineStr">
         <is>
-          <t>谋杀；杀戮；杀害的；疲惫的</t>
+          <t>杀害；杀戮；致死</t>
         </is>
       </c>
       <c r="E570" s="1" t="inlineStr">
@@ -19283,7 +19283,7 @@
       </c>
       <c r="B590" s="1" t="inlineStr">
         <is>
-          <t>[feːɡəfɔʏɐ] 涤罪；炼狱；涤罪的〈n.〉</t>
+          <t>[feːɡəfɔʏɐ] 炼狱〈n.〉</t>
         </is>
       </c>
       <c r="C590" s="1" t="inlineStr">
@@ -19293,7 +19293,7 @@
       </c>
       <c r="D590" s="1" t="inlineStr">
         <is>
-          <t>涤罪；炼狱；涤罪的</t>
+          <t>炼狱</t>
         </is>
       </c>
       <c r="E590" s="1" t="inlineStr">
@@ -20787,7 +20787,7 @@
       </c>
       <c r="B637" s="1" t="inlineStr">
         <is>
-          <t>[miːnɪmuːm] 最小的〈n.〉</t>
+          <t>[miːnɪmuːm] 最小值；最低限度〈n.〉</t>
         </is>
       </c>
       <c r="C637" s="1" t="inlineStr">
@@ -20797,7 +20797,7 @@
       </c>
       <c r="D637" s="1" t="inlineStr">
         <is>
-          <t>最小的</t>
+          <t>最小值；最低限度</t>
         </is>
       </c>
       <c r="E637" s="1" t="inlineStr">
@@ -22803,7 +22803,7 @@
       </c>
       <c r="B700" s="1" t="inlineStr">
         <is>
-          <t>[ɛndstat͡sjoːn] 最后的；末尾的〈n.f.〉</t>
+          <t>[ɛndstat͡sjoːn] 终点站；最后结局〈n.f.〉</t>
         </is>
       </c>
       <c r="C700" s="1" t="inlineStr">
@@ -22813,7 +22813,7 @@
       </c>
       <c r="D700" s="1" t="inlineStr">
         <is>
-          <t>最后的；末尾的</t>
+          <t>终点站；最后结局</t>
         </is>
       </c>
       <c r="E700" s="1" t="inlineStr">
@@ -22867,7 +22867,7 @@
       </c>
       <c r="B702" s="1" t="inlineStr">
         <is>
-          <t>[aːlaʁmbəʁaɪt͡ʃaft] 警觉的；灵敏的〈n.f.〉</t>
+          <t>[aːlaʁmbəʁaɪt͡ʃaft] 戒备状态；警戒就绪〈n.f.〉</t>
         </is>
       </c>
       <c r="C702" s="1" t="inlineStr">
@@ -22877,7 +22877,7 @@
       </c>
       <c r="D702" s="1" t="inlineStr">
         <is>
-          <t>警觉的；灵敏的</t>
+          <t>戒备状态；警戒就绪</t>
         </is>
       </c>
       <c r="E702" s="1" t="inlineStr">
@@ -24019,7 +24019,7 @@
       </c>
       <c r="B738" s="1" t="inlineStr">
         <is>
-          <t>[handʏnʊmɐ] 移动的；易变的〈n.f.〉</t>
+          <t>[handʏnʊmɐ] 手机号码〈n.f.〉</t>
         </is>
       </c>
       <c r="C738" s="1" t="inlineStr">
@@ -24029,7 +24029,7 @@
       </c>
       <c r="D738" s="1" t="inlineStr">
         <is>
-          <t>移动的；易变的</t>
+          <t>手机号码</t>
         </is>
       </c>
       <c r="E738" s="1" t="inlineStr">
@@ -24339,7 +24339,7 @@
       </c>
       <c r="B748" s="1" t="inlineStr">
         <is>
-          <t>[ʃɛʁbən] 坏掉的；打破的〈n.〉</t>
+          <t>[ʃɛʁbən] 碎片；破瓷片（复数）〈n.〉</t>
         </is>
       </c>
       <c r="C748" s="1" t="inlineStr">
@@ -24349,7 +24349,7 @@
       </c>
       <c r="D748" s="1" t="inlineStr">
         <is>
-          <t>坏掉的；打破的</t>
+          <t>碎片；破瓷片（复数）</t>
         </is>
       </c>
       <c r="E748" s="1" t="inlineStr">
@@ -24819,7 +24819,7 @@
       </c>
       <c r="B763" s="1" t="inlineStr">
         <is>
-          <t>[eːdəl] 宝贵的；珍贵的；过于精致的〈n.〉</t>
+          <t>[eːdəl] 贵族；高尚人士〈n.〉</t>
         </is>
       </c>
       <c r="C763" s="1" t="inlineStr">
@@ -24829,7 +24829,7 @@
       </c>
       <c r="D763" s="1" t="inlineStr">
         <is>
-          <t>宝贵的；珍贵的；过于精致的</t>
+          <t>贵族；高尚人士</t>
         </is>
       </c>
       <c r="E763" s="1" t="inlineStr">
@@ -25523,7 +25523,7 @@
       </c>
       <c r="B785" s="1" t="inlineStr">
         <is>
-          <t>[ʃveːfəl] 硫的〈n.〉</t>
+          <t>[ʃveːfəl] 硫磺；硫〈n.〉</t>
         </is>
       </c>
       <c r="C785" s="1" t="inlineStr">
@@ -25533,7 +25533,7 @@
       </c>
       <c r="D785" s="1" t="inlineStr">
         <is>
-          <t>硫的</t>
+          <t>硫磺；硫</t>
         </is>
       </c>
       <c r="E785" s="1" t="inlineStr">
@@ -25555,7 +25555,7 @@
       </c>
       <c r="B786" s="1" t="inlineStr">
         <is>
-          <t>[anɡəstʁənɡt] 同等的人；匹敌；贵族；凝视〈adv.〉</t>
+          <t>[anɡəstʁənɡt] 紧张的；费力的；竭力的〈adv.〉</t>
         </is>
       </c>
       <c r="C786" s="1" t="inlineStr">
@@ -25565,7 +25565,7 @@
       </c>
       <c r="D786" s="1" t="inlineStr">
         <is>
-          <t>同等的人；匹敌；贵族；凝视</t>
+          <t>紧张的；费力的；竭力的</t>
         </is>
       </c>
       <c r="E786" s="1" t="inlineStr">
@@ -25683,7 +25683,7 @@
       </c>
       <c r="B790" s="1" t="inlineStr">
         <is>
-          <t>[ablasən] 皱眉的；愠怒的；昏暗的〈n.〉</t>
+          <t>[ablasən] 排放；放气；放出；停止〈n.〉</t>
         </is>
       </c>
       <c r="C790" s="1" t="inlineStr">
@@ -25693,7 +25693,7 @@
       </c>
       <c r="D790" s="1" t="inlineStr">
         <is>
-          <t>皱眉的；愠怒的；昏暗的</t>
+          <t>排放；放气；放出；停止</t>
         </is>
       </c>
       <c r="E790" s="1" t="inlineStr">
@@ -25843,7 +25843,7 @@
       </c>
       <c r="B795" s="1" t="inlineStr">
         <is>
-          <t>[aːməʁɪkanɪʃəs] 美洲的〈n.〉</t>
+          <t>[aːməʁɪkanɪʃəs] 美洲事物；美国风格〈n.〉</t>
         </is>
       </c>
       <c r="C795" s="1" t="inlineStr">
@@ -25853,7 +25853,7 @@
       </c>
       <c r="D795" s="1" t="inlineStr">
         <is>
-          <t>美洲的</t>
+          <t>美洲事物；美国风格</t>
         </is>
       </c>
       <c r="E795" s="1" t="inlineStr">
@@ -26323,7 +26323,7 @@
       </c>
       <c r="B810" s="1" t="inlineStr">
         <is>
-          <t>[aʊfbaʊ] 组合的；合成的〈n.m.〉</t>
+          <t>[aʊfbaʊ] 建设；搭建；结构；布局〈n.m.〉</t>
         </is>
       </c>
       <c r="C810" s="1" t="inlineStr">
@@ -26333,7 +26333,7 @@
       </c>
       <c r="D810" s="1" t="inlineStr">
         <is>
-          <t>组合的；合成的</t>
+          <t>建设；搭建；结构；布局</t>
         </is>
       </c>
       <c r="E810" s="1" t="inlineStr">
@@ -26387,7 +26387,7 @@
       </c>
       <c r="B812" s="1" t="inlineStr">
         <is>
-          <t>[aɪnvandəʁɐ] 移民；移入的；移民的〈n.m.〉</t>
+          <t>[aɪnvandəʁɐ] 移民；迁入者〈n.m.〉</t>
         </is>
       </c>
       <c r="C812" s="1" t="inlineStr">
@@ -26397,7 +26397,7 @@
       </c>
       <c r="D812" s="1" t="inlineStr">
         <is>
-          <t>移民；移入的；移民的</t>
+          <t>移民；迁入者</t>
         </is>
       </c>
       <c r="E812" s="1" t="inlineStr">
@@ -26579,7 +26579,7 @@
       </c>
       <c r="B818" s="1" t="inlineStr">
         <is>
-          <t>[kɔmpləksə] 综合体；情结〈adv.〉</t>
+          <t>[kɔmpləksə] 复杂的；综合的〈adv.〉</t>
         </is>
       </c>
       <c r="C818" s="1" t="inlineStr">
@@ -26589,7 +26589,7 @@
       </c>
       <c r="D818" s="1" t="inlineStr">
         <is>
-          <t>综合体；情结</t>
+          <t>复杂的；综合的</t>
         </is>
       </c>
       <c r="E818" s="1" t="inlineStr">
@@ -27827,7 +27827,7 @@
       </c>
       <c r="B857" s="1" t="inlineStr">
         <is>
-          <t>[baʊksçməʁt͡sən] 腹部的；有腹鳍的；腹的〈n.〉</t>
+          <t>[baʊksçməʁt͡sən] 腹痛；肚子疼〈n.〉</t>
         </is>
       </c>
       <c r="C857" s="1" t="inlineStr">
@@ -27837,7 +27837,7 @@
       </c>
       <c r="D857" s="1" t="inlineStr">
         <is>
-          <t>腹部的；有腹鳍的；腹的</t>
+          <t>腹痛；肚子疼</t>
         </is>
       </c>
       <c r="E857" s="1" t="inlineStr">
@@ -27891,7 +27891,7 @@
       </c>
       <c r="B859" s="1" t="inlineStr">
         <is>
-          <t>[kaːʁɪbiːk] 加勒比人的〈n.f.〉</t>
+          <t>[kaːʁɪbiːk] 加勒比海；加勒比地区〈n.f.〉</t>
         </is>
       </c>
       <c r="C859" s="1" t="inlineStr">
@@ -27901,7 +27901,7 @@
       </c>
       <c r="D859" s="1" t="inlineStr">
         <is>
-          <t>加勒比人的</t>
+          <t>加勒比海；加勒比地区</t>
         </is>
       </c>
       <c r="E859" s="1" t="inlineStr">
@@ -28627,7 +28627,7 @@
       </c>
       <c r="B882" s="1" t="inlineStr">
         <is>
-          <t>[aktəntaʃə] 摘要；简报；简短的〈n.f.〉</t>
+          <t>[aktəntaʃə] 公文包；公事包〈n.f.〉</t>
         </is>
       </c>
       <c r="C882" s="1" t="inlineStr">
@@ -28637,7 +28637,7 @@
       </c>
       <c r="D882" s="1" t="inlineStr">
         <is>
-          <t>摘要；简报；简短的</t>
+          <t>公文包；公事包</t>
         </is>
       </c>
       <c r="E882" s="1" t="inlineStr">
@@ -28883,7 +28883,7 @@
       </c>
       <c r="B890" s="1" t="inlineStr">
         <is>
-          <t>[t͡saʊbəʁtʁank] 魔术；魔法；魔术的；有魔力的〈n.m.〉</t>
+          <t>[t͡saʊbəʁtʁank] 魔药；魔法药水〈n.m.〉</t>
         </is>
       </c>
       <c r="C890" s="1" t="inlineStr">
@@ -28893,7 +28893,7 @@
       </c>
       <c r="D890" s="1" t="inlineStr">
         <is>
-          <t>魔术；魔法；魔术的；有魔力的</t>
+          <t>魔药；魔法药水</t>
         </is>
       </c>
       <c r="E890" s="1" t="inlineStr">
@@ -28979,7 +28979,7 @@
       </c>
       <c r="B893" s="1" t="inlineStr">
         <is>
-          <t>[ʊnfəʁantvɔʁtliːç] 罪犯；犯人〈adj.〉</t>
+          <t>[ʊnfəʁantvɔʁtliːç] 不负责任的〈adj.〉</t>
         </is>
       </c>
       <c r="C893" s="1" t="inlineStr">
@@ -28989,7 +28989,7 @@
       </c>
       <c r="D893" s="1" t="inlineStr">
         <is>
-          <t>罪犯；犯人</t>
+          <t>不负责任的</t>
         </is>
       </c>
       <c r="E893" s="1" t="inlineStr">
@@ -29203,7 +29203,7 @@
       </c>
       <c r="B900" s="1" t="inlineStr">
         <is>
-          <t>[ʃtʁaːsənʁant] 路旁；路边；路边的〈n.m.〉</t>
+          <t>[ʃtʁaːsənʁant] 路旁；路边〈n.m.〉</t>
         </is>
       </c>
       <c r="C900" s="1" t="inlineStr">
@@ -29213,7 +29213,7 @@
       </c>
       <c r="D900" s="1" t="inlineStr">
         <is>
-          <t>路旁；路边；路边的</t>
+          <t>路旁；路边</t>
         </is>
       </c>
       <c r="E900" s="1" t="inlineStr">
@@ -29523,7 +29523,7 @@
       </c>
       <c r="B910" s="1" t="inlineStr">
         <is>
-          <t>[meːdɪt͡sɪnɐ] 医生；内科的〈n.m.〉</t>
+          <t>[meːdɪt͡sɪnɐ] 医生；医学工作者〈n.m.〉</t>
         </is>
       </c>
       <c r="C910" s="1" t="inlineStr">
@@ -29533,7 +29533,7 @@
       </c>
       <c r="D910" s="1" t="inlineStr">
         <is>
-          <t>医生；内科的</t>
+          <t>医生；医学工作者</t>
         </is>
       </c>
       <c r="E910" s="1" t="inlineStr">
@@ -30899,7 +30899,7 @@
       </c>
       <c r="B953" s="1" t="inlineStr">
         <is>
-          <t>[dʊʁçlaʊxt] 宁静的；沉着的；安详的〈n.f.〉</t>
+          <t>[dʊʁçlaʊxt] 殿下；阁下（贵族尊称）〈n.f.〉</t>
         </is>
       </c>
       <c r="C953" s="1" t="inlineStr">
@@ -30909,7 +30909,7 @@
       </c>
       <c r="D953" s="1" t="inlineStr">
         <is>
-          <t>宁静的；沉着的；安详的</t>
+          <t>殿下；阁下（贵族尊称）</t>
         </is>
       </c>
       <c r="E953" s="1" t="inlineStr">
@@ -31123,7 +31123,7 @@
       </c>
       <c r="B960" s="1" t="inlineStr">
         <is>
-          <t>[baːʁakə] 木制的；呆笨的；木然的〈n.f.〉</t>
+          <t>[baːʁakə] 简易营房；工棚；兵营〈n.f.〉</t>
         </is>
       </c>
       <c r="C960" s="1" t="inlineStr">
@@ -31133,7 +31133,7 @@
       </c>
       <c r="D960" s="1" t="inlineStr">
         <is>
-          <t>木制的；呆笨的；木然的</t>
+          <t>简易营房；工棚；兵营</t>
         </is>
       </c>
       <c r="E960" s="1" t="inlineStr">
@@ -31219,7 +31219,7 @@
       </c>
       <c r="B963" s="1" t="inlineStr">
         <is>
-          <t>[mɪtbʏʁɡɐ] 男人；朋友；同事；同伴的〈n.m.〉</t>
+          <t>[mɪtbʏʁɡɐ] 同胞；公民；市民〈n.m.〉</t>
         </is>
       </c>
       <c r="C963" s="1" t="inlineStr">
@@ -31229,7 +31229,7 @@
       </c>
       <c r="D963" s="1" t="inlineStr">
         <is>
-          <t>男人；朋友；同事；同伴的</t>
+          <t>同胞；公民；市民</t>
         </is>
       </c>
       <c r="E963" s="1" t="inlineStr">
@@ -31411,7 +31411,7 @@
       </c>
       <c r="B969" s="1" t="inlineStr">
         <is>
-          <t>[poːlɪtɪʃəs] 政体；国体；政治组织；政府〈adv.〉</t>
+          <t>[poːlɪtɪʃəs] 政治的〈adv.〉</t>
         </is>
       </c>
       <c r="C969" s="1" t="inlineStr">
@@ -31421,7 +31421,7 @@
       </c>
       <c r="D969" s="1" t="inlineStr">
         <is>
-          <t>政体；国体；政治组织；政府</t>
+          <t>政治的</t>
         </is>
       </c>
       <c r="E969" s="1" t="inlineStr">
@@ -31667,7 +31667,7 @@
       </c>
       <c r="B977" s="1" t="inlineStr">
         <is>
-          <t>[ʊntəʁə] 妖怪；可怕的人；转向架〈adv.〉</t>
+          <t>[ʊntəʁə] 下面的；底部的〈adv.〉</t>
         </is>
       </c>
       <c r="C977" s="1" t="inlineStr">
@@ -31677,7 +31677,7 @@
       </c>
       <c r="D977" s="1" t="inlineStr">
         <is>
-          <t>妖怪；可怕的人；转向架</t>
+          <t>下面的；底部的</t>
         </is>
       </c>
       <c r="E977" s="1" t="inlineStr">
@@ -32755,7 +32755,7 @@
       </c>
       <c r="B1011" s="1" t="inlineStr">
         <is>
-          <t>[fɛʁzʊks] 暂时的〈n.〉</t>
+          <t>[fɛʁzʊks] 试验；尝试（构词成分）〈n.〉</t>
         </is>
       </c>
       <c r="C1011" s="1" t="inlineStr">
@@ -32765,7 +32765,7 @@
       </c>
       <c r="D1011" s="1" t="inlineStr">
         <is>
-          <t>暂时的</t>
+          <t>试验；尝试（构词成分）</t>
         </is>
       </c>
       <c r="E1011" s="1" t="inlineStr">
@@ -33107,7 +33107,7 @@
       </c>
       <c r="B1022" s="1" t="inlineStr">
         <is>
-          <t>[mɪtmənʃən] 男人；朋友；同事；同伴的〈n.〉</t>
+          <t>[mɪtmənʃən] 同胞；周围的人；同仁〈n.〉</t>
         </is>
       </c>
       <c r="C1022" s="1" t="inlineStr">
@@ -33117,7 +33117,7 @@
       </c>
       <c r="D1022" s="1" t="inlineStr">
         <is>
-          <t>男人；朋友；同事；同伴的</t>
+          <t>同胞；周围的人；同仁</t>
         </is>
       </c>
       <c r="E1022" s="1" t="inlineStr">
@@ -33747,7 +33747,7 @@
       </c>
       <c r="B1042" s="1" t="inlineStr">
         <is>
-          <t>[ɡlɛnt͡sən] 有光泽的〈n.m.〉</t>
+          <t>[ɡlɛnt͡sən] 闪烁；发光；光彩夺目〈n.m.〉</t>
         </is>
       </c>
       <c r="C1042" s="1" t="inlineStr">
@@ -33757,7 +33757,7 @@
       </c>
       <c r="D1042" s="1" t="inlineStr">
         <is>
-          <t>有光泽的</t>
+          <t>闪烁；发光；光彩夺目</t>
         </is>
       </c>
       <c r="E1042" s="1" t="inlineStr">
@@ -34163,7 +34163,7 @@
       </c>
       <c r="B1055" s="1" t="inlineStr">
         <is>
-          <t>[leːʁlɪnk] 学徒；无经验的〈n.m.〉</t>
+          <t>[leːʁlɪnk] 学徒；徒弟；见习生〈n.m.〉</t>
         </is>
       </c>
       <c r="C1055" s="1" t="inlineStr">
@@ -34173,7 +34173,7 @@
       </c>
       <c r="D1055" s="1" t="inlineStr">
         <is>
-          <t>学徒；无经验的</t>
+          <t>学徒；徒弟；见习生</t>
         </is>
       </c>
       <c r="E1055" s="1" t="inlineStr">
@@ -34483,7 +34483,7 @@
       </c>
       <c r="B1065" s="1" t="inlineStr">
         <is>
-          <t>[tiːʁɪʃ] 动物〈adj.〉</t>
+          <t>[tiːʁɪʃ] 兽类的；残忍的；野性的〈adj.〉</t>
         </is>
       </c>
       <c r="C1065" s="1" t="inlineStr">
@@ -34493,7 +34493,7 @@
       </c>
       <c r="D1065" s="1" t="inlineStr">
         <is>
-          <t>动物</t>
+          <t>兽类的；残忍的；野性的</t>
         </is>
       </c>
       <c r="E1065" s="1" t="inlineStr">
@@ -34771,7 +34771,7 @@
       </c>
       <c r="B1074" s="1" t="inlineStr">
         <is>
-          <t>[liːblɪnɡzəsən] 宠爱的〈n.〉</t>
+          <t>[liːblɪnɡzəsən] 最喜欢的食物；最爱吃的菜〈n.〉</t>
         </is>
       </c>
       <c r="C1074" s="1" t="inlineStr">
@@ -34781,7 +34781,7 @@
       </c>
       <c r="D1074" s="1" t="inlineStr">
         <is>
-          <t>宠爱的</t>
+          <t>最喜欢的食物；最爱吃的菜</t>
         </is>
       </c>
       <c r="E1074" s="1" t="inlineStr">
@@ -36659,7 +36659,7 @@
       </c>
       <c r="B1133" s="1" t="inlineStr">
         <is>
-          <t>[naxvʊks] 年轻的；无经验的〈n.m.〉</t>
+          <t>[naxvʊks] 后代；新生力量；后备人才〈n.m.〉</t>
         </is>
       </c>
       <c r="C1133" s="1" t="inlineStr">
@@ -36669,7 +36669,7 @@
       </c>
       <c r="D1133" s="1" t="inlineStr">
         <is>
-          <t>年轻的；无经验的</t>
+          <t>后代；新生力量；后备人才</t>
         </is>
       </c>
       <c r="E1133" s="1" t="inlineStr">
@@ -36787,7 +36787,7 @@
       </c>
       <c r="B1137" s="1" t="inlineStr">
         <is>
-          <t>[ɡɛfʁaɪtɐ] 私人的；秘密的；私立的〈n.m.〉</t>
+          <t>[ɡɛfʁaɪtɐ] 一等兵；列兵〈n.m.〉</t>
         </is>
       </c>
       <c r="C1137" s="1" t="inlineStr">
@@ -36797,7 +36797,7 @@
       </c>
       <c r="D1137" s="1" t="inlineStr">
         <is>
-          <t>私人的；秘密的；私立的</t>
+          <t>一等兵；列兵</t>
         </is>
       </c>
       <c r="E1137" s="1" t="inlineStr">
@@ -37043,7 +37043,7 @@
       </c>
       <c r="B1145" s="1" t="inlineStr">
         <is>
-          <t>[toːniːk] 补药；声调的〈n.〉</t>
+          <t>[toːniːk] 汤力水；滋补饮料〈n.〉</t>
         </is>
       </c>
       <c r="C1145" s="1" t="inlineStr">
@@ -37053,7 +37053,7 @@
       </c>
       <c r="D1145" s="1" t="inlineStr">
         <is>
-          <t>补药；声调的</t>
+          <t>汤力水；滋补饮料</t>
         </is>
       </c>
       <c r="E1145" s="1" t="inlineStr">
@@ -37747,7 +37747,7 @@
       </c>
       <c r="B1167" s="1" t="inlineStr">
         <is>
-          <t>[faːnatɪkɐ] 狂热者；盲信；狂热的；盲信的〈n.m.〉</t>
+          <t>[faːnatɪkɐ] 狂热分子；狂热崇拜者〈n.m.〉</t>
         </is>
       </c>
       <c r="C1167" s="1" t="inlineStr">
@@ -37757,7 +37757,7 @@
       </c>
       <c r="D1167" s="1" t="inlineStr">
         <is>
-          <t>狂热者；盲信；狂热的；盲信的</t>
+          <t>狂热分子；狂热崇拜者</t>
         </is>
       </c>
       <c r="E1167" s="1" t="inlineStr">
@@ -38387,7 +38387,7 @@
       </c>
       <c r="B1187" s="1" t="inlineStr">
         <is>
-          <t>[zanftɐ] 安乐死；安死术〈adv.〉</t>
+          <t>[zanftɐ] 更温和的；更柔和的〈adv.〉</t>
         </is>
       </c>
       <c r="C1187" s="1" t="inlineStr">
@@ -38397,7 +38397,7 @@
       </c>
       <c r="D1187" s="1" t="inlineStr">
         <is>
-          <t>安乐死；安死术</t>
+          <t>更温和的；更柔和的</t>
         </is>
       </c>
       <c r="E1187" s="1" t="inlineStr">
@@ -38419,7 +38419,7 @@
       </c>
       <c r="B1188" s="1" t="inlineStr">
         <is>
-          <t>[ʁaʃəln] 时髦的〈n.〉</t>
+          <t>[ʁaʃəln] 沙沙声；悉索声〈n.〉</t>
         </is>
       </c>
       <c r="C1188" s="1" t="inlineStr">
@@ -38429,7 +38429,7 @@
       </c>
       <c r="D1188" s="1" t="inlineStr">
         <is>
-          <t>时髦的</t>
+          <t>沙沙声；悉索声</t>
         </is>
       </c>
       <c r="E1188" s="1" t="inlineStr">
@@ -38739,7 +38739,7 @@
       </c>
       <c r="B1198" s="1" t="inlineStr">
         <is>
-          <t>[aɪzəʁnə] 否定；否定语；负数〈adv.〉</t>
+          <t>[aɪzəʁnə] 铁的；坚强的；刚毅的〈adv.〉</t>
         </is>
       </c>
       <c r="C1198" s="1" t="inlineStr">
@@ -38749,7 +38749,7 @@
       </c>
       <c r="D1198" s="1" t="inlineStr">
         <is>
-          <t>否定；否定语；负数</t>
+          <t>铁的；坚强的；刚毅的</t>
         </is>
       </c>
       <c r="E1198" s="1" t="inlineStr">
@@ -38899,7 +38899,7 @@
       </c>
       <c r="B1203" s="1" t="inlineStr">
         <is>
-          <t>[ʁaɪt͡st] 刺激的；使愤怒的；气人的〈n.〉</t>
+          <t>[ʁaɪt͡st] 刺激；激怒（动词现在时）〈n.〉</t>
         </is>
       </c>
       <c r="C1203" s="1" t="inlineStr">
@@ -38909,7 +38909,7 @@
       </c>
       <c r="D1203" s="1" t="inlineStr">
         <is>
-          <t>刺激的；使愤怒的；气人的</t>
+          <t>刺激；激怒（动词现在时）</t>
         </is>
       </c>
       <c r="E1203" s="1" t="inlineStr">
@@ -38963,7 +38963,7 @@
       </c>
       <c r="B1205" s="1" t="inlineStr">
         <is>
-          <t>[beːlaɪdɪɡʊnɡən] 恶言谩骂的；被滥用的；腐败的〈n.〉</t>
+          <t>[beːlaɪdɪɡʊnɡən] 侮辱；冒犯（复数）〈n.〉</t>
         </is>
       </c>
       <c r="C1205" s="1" t="inlineStr">
@@ -38973,7 +38973,7 @@
       </c>
       <c r="D1205" s="1" t="inlineStr">
         <is>
-          <t>恶言谩骂的；被滥用的；腐败的</t>
+          <t>侮辱；冒犯（复数）</t>
         </is>
       </c>
       <c r="E1205" s="1" t="inlineStr">
@@ -39091,7 +39091,7 @@
       </c>
       <c r="B1209" s="1" t="inlineStr">
         <is>
-          <t>[uːnabhɛnɡɪɡə] 独立自主者；有主见的〈n.〉</t>
+          <t>[uːnabhɛnɡɪɡə] 独立候选人；无党派人士〈n.〉</t>
         </is>
       </c>
       <c r="C1209" s="1" t="inlineStr">
@@ -39101,7 +39101,7 @@
       </c>
       <c r="D1209" s="1" t="inlineStr">
         <is>
-          <t>独立自主者；有主见的</t>
+          <t>独立候选人；无党派人士</t>
         </is>
       </c>
       <c r="E1209" s="1" t="inlineStr">
@@ -39251,7 +39251,7 @@
       </c>
       <c r="B1214" s="1" t="inlineStr">
         <is>
-          <t>[naːt͡sjoːnalɡaʁdə] 国家的；国立的；全国性的〈n.f.〉</t>
+          <t>[naːt͡sjoːnalɡaʁdə] 国民警卫队〈n.f.〉</t>
         </is>
       </c>
       <c r="C1214" s="1" t="inlineStr">
@@ -39261,7 +39261,7 @@
       </c>
       <c r="D1214" s="1" t="inlineStr">
         <is>
-          <t>国家的；国立的；全国性的</t>
+          <t>国民警卫队</t>
         </is>
       </c>
       <c r="E1214" s="1" t="inlineStr">
@@ -39347,7 +39347,7 @@
       </c>
       <c r="B1217" s="1" t="inlineStr">
         <is>
-          <t>[bʁuːtalɐ] 杀人者；凶手；屠宰者〈adv.〉</t>
+          <t>[bʁuːtalɐ] 更残暴的；更凶狠的〈adv.〉</t>
         </is>
       </c>
       <c r="C1217" s="1" t="inlineStr">
@@ -39357,7 +39357,7 @@
       </c>
       <c r="D1217" s="1" t="inlineStr">
         <is>
-          <t>杀人者；凶手；屠宰者</t>
+          <t>更残暴的；更凶狠的</t>
         </is>
       </c>
       <c r="E1217" s="1" t="inlineStr">
@@ -39443,7 +39443,7 @@
       </c>
       <c r="B1220" s="1" t="inlineStr">
         <is>
-          <t>[ɡɔʊfəʁnɔʏʁs] 州长的；统治者的〈n.〉</t>
+          <t>[ɡɔʊfəʁnɔʏʁs] 州长；省长（属格/复数）〈n.〉</t>
         </is>
       </c>
       <c r="C1220" s="1" t="inlineStr">
@@ -39453,7 +39453,7 @@
       </c>
       <c r="D1220" s="1" t="inlineStr">
         <is>
-          <t>州长的；统治者的</t>
+          <t>州长；省长（属格/复数）</t>
         </is>
       </c>
       <c r="E1220" s="1" t="inlineStr">
@@ -39539,7 +39539,7 @@
       </c>
       <c r="B1223" s="1" t="inlineStr">
         <is>
-          <t>[mɪtləʁə] 平均；平均数；一般水平〈adv.〉</t>
+          <t>[mɪtləʁə] 中部的；中等的；中间的〈adv.〉</t>
         </is>
       </c>
       <c r="C1223" s="1" t="inlineStr">
@@ -39549,7 +39549,7 @@
       </c>
       <c r="D1223" s="1" t="inlineStr">
         <is>
-          <t>平均；平均数；一般水平</t>
+          <t>中部的；中等的；中间的</t>
         </is>
       </c>
       <c r="E1223" s="1" t="inlineStr">
@@ -39795,7 +39795,7 @@
       </c>
       <c r="B1231" s="1" t="inlineStr">
         <is>
-          <t>[ɛnɡlɪʃɐ] 管理人；保管人；监护人〈adv.〉</t>
+          <t>[ɛnɡlɪʃɐ] 英国的；英格兰的〈adv.〉</t>
         </is>
       </c>
       <c r="C1231" s="1" t="inlineStr">
@@ -39805,7 +39805,7 @@
       </c>
       <c r="D1231" s="1" t="inlineStr">
         <is>
-          <t>管理人；保管人；监护人</t>
+          <t>英国的；英格兰的</t>
         </is>
       </c>
       <c r="E1231" s="1" t="inlineStr">
@@ -41107,7 +41107,7 @@
       </c>
       <c r="B1272" s="1" t="inlineStr">
         <is>
-          <t>[faːʁəʁflʊxt] 打了人后即逃跑的〈n.f.〉</t>
+          <t>[faːʁəʁflʊxt] 交通肇事逃逸〈n.f.〉</t>
         </is>
       </c>
       <c r="C1272" s="1" t="inlineStr">
@@ -41117,7 +41117,7 @@
       </c>
       <c r="D1272" s="1" t="inlineStr">
         <is>
-          <t>打了人后即逃跑的</t>
+          <t>交通肇事逃逸</t>
         </is>
       </c>
       <c r="E1272" s="1" t="inlineStr">
@@ -41939,7 +41939,7 @@
       </c>
       <c r="B1298" s="1" t="inlineStr">
         <is>
-          <t>[fɔuːl] 污秽的；邪恶的；恶臭的〈n.〉</t>
+          <t>[fɔuːl] 犯规（体育）〈n.〉</t>
         </is>
       </c>
       <c r="C1298" s="1" t="inlineStr">
@@ -41949,7 +41949,7 @@
       </c>
       <c r="D1298" s="1" t="inlineStr">
         <is>
-          <t>污秽的；邪恶的；恶臭的</t>
+          <t>犯规（体育）</t>
         </is>
       </c>
       <c r="E1298" s="1" t="inlineStr">
@@ -43219,7 +43219,7 @@
       </c>
       <c r="B1338" s="1" t="inlineStr">
         <is>
-          <t>[aʊsənmɪnɪstɐ] 外国的；外交的；外省的〈n.m.〉</t>
+          <t>[aʊsənmɪnɪstɐ] 外交部长；外长〈n.m.〉</t>
         </is>
       </c>
       <c r="C1338" s="1" t="inlineStr">
@@ -43229,7 +43229,7 @@
       </c>
       <c r="D1338" s="1" t="inlineStr">
         <is>
-          <t>外国的；外交的；外省的</t>
+          <t>外交部长；外长</t>
         </is>
       </c>
       <c r="E1338" s="1" t="inlineStr">
@@ -44275,7 +44275,7 @@
       </c>
       <c r="B1371" s="1" t="inlineStr">
         <is>
-          <t>[oːbəndʁaɪn] 在上面；成功；领先〈adv.〉</t>
+          <t>[oːbəndʁaɪn] 此外；而且；加之〈adv.〉</t>
         </is>
       </c>
       <c r="C1371" s="1" t="inlineStr">
@@ -44285,7 +44285,7 @@
       </c>
       <c r="D1371" s="1" t="inlineStr">
         <is>
-          <t>在上面；成功；领先</t>
+          <t>此外；而且；加之</t>
         </is>
       </c>
       <c r="E1371" s="1" t="inlineStr">
@@ -44435,7 +44435,7 @@
       </c>
       <c r="B1376" s="1" t="inlineStr">
         <is>
-          <t>[nɔʏtʁaːl] 中立者；中立国；非彩色〈adv.〉</t>
+          <t>[nɔʏtʁaːl] 中立的；中性的〈adv.〉</t>
         </is>
       </c>
       <c r="C1376" s="1" t="inlineStr">
@@ -44445,7 +44445,7 @@
       </c>
       <c r="D1376" s="1" t="inlineStr">
         <is>
-          <t>中立者；中立国；非彩色</t>
+          <t>中立的；中性的</t>
         </is>
       </c>
       <c r="E1376" s="1" t="inlineStr">
@@ -45107,7 +45107,7 @@
       </c>
       <c r="B1397" s="1" t="inlineStr">
         <is>
-          <t>[nɪt͡st͡sa] 美好的；和蔼的；正派的〈n.〉</t>
+          <t>[nɪt͡st͡sa] 尼斯（法国城市）〈n.〉</t>
         </is>
       </c>
       <c r="C1397" s="1" t="inlineStr">
@@ -45117,7 +45117,7 @@
       </c>
       <c r="D1397" s="1" t="inlineStr">
         <is>
-          <t>美好的；和蔼的；正派的</t>
+          <t>尼斯（法国城市）</t>
         </is>
       </c>
       <c r="E1397" s="1" t="inlineStr">
@@ -45363,7 +45363,7 @@
       </c>
       <c r="B1405" s="1" t="inlineStr">
         <is>
-          <t>[mɔndlɪçt] 月夜的〈n.〉</t>
+          <t>[mɔndlɪçt] 月光〈n.〉</t>
         </is>
       </c>
       <c r="C1405" s="1" t="inlineStr">
@@ -45373,7 +45373,7 @@
       </c>
       <c r="D1405" s="1" t="inlineStr">
         <is>
-          <t>月夜的</t>
+          <t>月光</t>
         </is>
       </c>
       <c r="E1405" s="1" t="inlineStr">
@@ -45619,7 +45619,7 @@
       </c>
       <c r="B1413" s="1" t="inlineStr">
         <is>
-          <t>[zɔnən] 太阳的；日光的〈n.〉</t>
+          <t>[zɔnən] 太阳（复数）；晒太阳〈n.〉</t>
         </is>
       </c>
       <c r="C1413" s="1" t="inlineStr">
@@ -45629,7 +45629,7 @@
       </c>
       <c r="D1413" s="1" t="inlineStr">
         <is>
-          <t>太阳的；日光的</t>
+          <t>太阳（复数）；晒太阳</t>
         </is>
       </c>
       <c r="E1413" s="1" t="inlineStr">
@@ -45971,7 +45971,7 @@
       </c>
       <c r="B1424" s="1" t="inlineStr">
         <is>
-          <t>[kɛstçən] 小的；少的；小型的〈n.〉</t>
+          <t>[kɛstçən] 小盒子；小箱；小方格〈n.〉</t>
         </is>
       </c>
       <c r="C1424" s="1" t="inlineStr">
@@ -45981,7 +45981,7 @@
       </c>
       <c r="D1424" s="1" t="inlineStr">
         <is>
-          <t>小的；少的；小型的</t>
+          <t>小盒子；小箱；小方格</t>
         </is>
       </c>
       <c r="E1424" s="1" t="inlineStr">
@@ -46003,7 +46003,7 @@
       </c>
       <c r="B1425" s="1" t="inlineStr">
         <is>
-          <t>[maksɪmuːm] 极点；最大量；极大；最高的〈n.〉</t>
+          <t>[maksɪmuːm] 最大值；最高限度〈n.〉</t>
         </is>
       </c>
       <c r="C1425" s="1" t="inlineStr">
@@ -46013,7 +46013,7 @@
       </c>
       <c r="D1425" s="1" t="inlineStr">
         <is>
-          <t>极点；最大量；极大；最高的</t>
+          <t>最大值；最高限度</t>
         </is>
       </c>
       <c r="E1425" s="1" t="inlineStr">
@@ -46067,7 +46067,7 @@
       </c>
       <c r="B1427" s="1" t="inlineStr">
         <is>
-          <t>[ablənkʊnɡsmanœfɐ] 转换注意力的；牵制的〈n.〉</t>
+          <t>[ablənkʊnɡsmanœfɐ] 转移注意力策略；声东击西手段；牵制行动〈n.〉</t>
         </is>
       </c>
       <c r="C1427" s="1" t="inlineStr">
@@ -46077,7 +46077,7 @@
       </c>
       <c r="D1427" s="1" t="inlineStr">
         <is>
-          <t>转换注意力的；牵制的</t>
+          <t>转移注意力策略；声东击西手段；牵制行动</t>
         </is>
       </c>
       <c r="E1427" s="1" t="inlineStr">
@@ -46419,7 +46419,7 @@
       </c>
       <c r="B1438" s="1" t="inlineStr">
         <is>
-          <t>[lanɡvaɪlɐ] 沉闷的；冗长乏味的〈n.m.〉</t>
+          <t>[lanɡvaɪlɐ] 乏味的人；令人厌烦的人〈n.m.〉</t>
         </is>
       </c>
       <c r="C1438" s="1" t="inlineStr">
@@ -46429,7 +46429,7 @@
       </c>
       <c r="D1438" s="1" t="inlineStr">
         <is>
-          <t>沉闷的；冗长乏味的</t>
+          <t>乏味的人；令人厌烦的人</t>
         </is>
       </c>
       <c r="E1438" s="1" t="inlineStr">
@@ -46483,7 +46483,7 @@
       </c>
       <c r="B1440" s="1" t="inlineStr">
         <is>
-          <t>[blɪkvɪnkəl] 有角的；消瘦的；有尖角的〈n.m.〉</t>
+          <t>[blɪkvɪnkəl] 视角；观察角度〈n.m.〉</t>
         </is>
       </c>
       <c r="C1440" s="1" t="inlineStr">
@@ -46493,7 +46493,7 @@
       </c>
       <c r="D1440" s="1" t="inlineStr">
         <is>
-          <t>有角的；消瘦的；有尖角的</t>
+          <t>视角；观察角度</t>
         </is>
       </c>
       <c r="E1440" s="1" t="inlineStr">
@@ -46931,7 +46931,7 @@
       </c>
       <c r="B1454" s="1" t="inlineStr">
         <is>
-          <t>[ʃpɔʁtvaɡən] 喜好运动的；运动用的；冒险性的〈n.m.〉</t>
+          <t>[ʃpɔʁtvaɡən] 跑车；运动汽车〈n.m.〉</t>
         </is>
       </c>
       <c r="C1454" s="1" t="inlineStr">
@@ -46941,7 +46941,7 @@
       </c>
       <c r="D1454" s="1" t="inlineStr">
         <is>
-          <t>喜好运动的；运动用的；冒险性的</t>
+          <t>跑车；运动汽车</t>
         </is>
       </c>
       <c r="E1454" s="1" t="inlineStr">
@@ -47187,7 +47187,7 @@
       </c>
       <c r="B1462" s="1" t="inlineStr">
         <is>
-          <t>[hɔxfəʁaːt] 高度；高处；高的；高级的〈n.m.〉</t>
+          <t>[hɔxfəʁaːt] 叛国罪；大逆不道罪〈n.m.〉</t>
         </is>
       </c>
       <c r="C1462" s="1" t="inlineStr">
@@ -47197,7 +47197,7 @@
       </c>
       <c r="D1462" s="1" t="inlineStr">
         <is>
-          <t>高度；高处；高的；高级的</t>
+          <t>叛国罪；大逆不道罪</t>
         </is>
       </c>
       <c r="E1462" s="1" t="inlineStr">
@@ -48147,7 +48147,7 @@
       </c>
       <c r="B1492" s="1" t="inlineStr">
         <is>
-          <t>[pɔʁt͡səlaːn] 瓷器；瓷；瓷制的〈n.〉</t>
+          <t>[pɔʁt͡səlaːn] 瓷器；瓷〈n.〉</t>
         </is>
       </c>
       <c r="C1492" s="1" t="inlineStr">
@@ -48157,7 +48157,7 @@
       </c>
       <c r="D1492" s="1" t="inlineStr">
         <is>
-          <t>瓷器；瓷；瓷制的</t>
+          <t>瓷器；瓷</t>
         </is>
       </c>
       <c r="E1492" s="1" t="inlineStr">
@@ -48563,7 +48563,7 @@
       </c>
       <c r="B1505" s="1" t="inlineStr">
         <is>
-          <t>[fɔʁzɪçtsmasnaːmə] 预先警戒的；预防的；留心的〈n.f.〉</t>
+          <t>[fɔʁzɪçtsmasnaːmə] 预防措施；防范对策〈n.f.〉</t>
         </is>
       </c>
       <c r="C1505" s="1" t="inlineStr">
@@ -48573,7 +48573,7 @@
       </c>
       <c r="D1505" s="1" t="inlineStr">
         <is>
-          <t>预先警戒的；预防的；留心的</t>
+          <t>预防措施；防范对策</t>
         </is>
       </c>
       <c r="E1505" s="1" t="inlineStr">
@@ -49555,7 +49555,7 @@
       </c>
       <c r="B1536" s="1" t="inlineStr">
         <is>
-          <t>[ʁoːmantɪkɐ] 浪漫的；风流的；传奇性的〈n.m.〉</t>
+          <t>[ʁoːmantɪkɐ] 浪漫主义者；浪漫的人〈n.m.〉</t>
         </is>
       </c>
       <c r="C1536" s="1" t="inlineStr">
@@ -49565,7 +49565,7 @@
       </c>
       <c r="D1536" s="1" t="inlineStr">
         <is>
-          <t>浪漫的；风流的；传奇性的</t>
+          <t>浪漫主义者；浪漫的人</t>
         </is>
       </c>
       <c r="E1536" s="1" t="inlineStr">
@@ -49907,7 +49907,7 @@
       </c>
       <c r="B1547" s="1" t="inlineStr">
         <is>
-          <t>[ʁeːɡənʃɪʁm] 伞；雨伞；保护伞；伞的〈n.m.〉</t>
+          <t>[ʁeːɡənʃɪʁm] 雨伞〈n.m.〉</t>
         </is>
       </c>
       <c r="C1547" s="1" t="inlineStr">
@@ -49917,7 +49917,7 @@
       </c>
       <c r="D1547" s="1" t="inlineStr">
         <is>
-          <t>伞；雨伞；保护伞；伞的</t>
+          <t>雨伞</t>
         </is>
       </c>
       <c r="E1547" s="1" t="inlineStr">
@@ -51763,7 +51763,7 @@
       </c>
       <c r="B1605" s="1" t="inlineStr">
         <is>
-          <t>[bʁaɪtən] 纬度的〈n.〉</t>
+          <t>[bʁaɪtən] 纬度（复数）〈n.〉</t>
         </is>
       </c>
       <c r="C1605" s="1" t="inlineStr">
@@ -51773,7 +51773,7 @@
       </c>
       <c r="D1605" s="1" t="inlineStr">
         <is>
-          <t>纬度的</t>
+          <t>纬度（复数）</t>
         </is>
       </c>
       <c r="E1605" s="1" t="inlineStr">
@@ -51891,7 +51891,7 @@
       </c>
       <c r="B1609" s="1" t="inlineStr">
         <is>
-          <t>[ɡʁɔsstadt] 大的；大量的；宽大的〈n.f.〉</t>
+          <t>[ɡʁɔsstadt] 大城市；大都会〈n.f.〉</t>
         </is>
       </c>
       <c r="C1609" s="1" t="inlineStr">
@@ -51901,7 +51901,7 @@
       </c>
       <c r="D1609" s="1" t="inlineStr">
         <is>
-          <t>大的；大量的；宽大的</t>
+          <t>大城市；大都会</t>
         </is>
       </c>
       <c r="E1609" s="1" t="inlineStr">
@@ -52403,7 +52403,7 @@
       </c>
       <c r="B1625" s="1" t="inlineStr">
         <is>
-          <t>[kaːnadiːɐ] 加拿大的〈n.m.〉</t>
+          <t>[kaːnadiːɐ] 加拿大人〈n.m.〉</t>
         </is>
       </c>
       <c r="C1625" s="1" t="inlineStr">
@@ -52413,7 +52413,7 @@
       </c>
       <c r="D1625" s="1" t="inlineStr">
         <is>
-          <t>加拿大的</t>
+          <t>加拿大人</t>
         </is>
       </c>
       <c r="E1625" s="1" t="inlineStr">
@@ -52499,7 +52499,7 @@
       </c>
       <c r="B1628" s="1" t="inlineStr">
         <is>
-          <t>[dʊmpfɐ] 砰的一声；嘭的一声〈adv.〉</t>
+          <t>[dʊmpfɐ] 更低沉的；更沉闷的〈adv.〉</t>
         </is>
       </c>
       <c r="C1628" s="1" t="inlineStr">
@@ -52509,7 +52509,7 @@
       </c>
       <c r="D1628" s="1" t="inlineStr">
         <is>
-          <t>砰的一声；嘭的一声</t>
+          <t>更低沉的；更沉闷的</t>
         </is>
       </c>
       <c r="E1628" s="1" t="inlineStr">
@@ -53011,7 +53011,7 @@
       </c>
       <c r="B1644" s="1" t="inlineStr">
         <is>
-          <t>[ʁaːzənt] 在；向；对；地址转换器〈adv.〉</t>
+          <t>[ʁaːzənt] 疯狂的；飞快的〈adv.〉</t>
         </is>
       </c>
       <c r="C1644" s="1" t="inlineStr">
@@ -53021,7 +53021,7 @@
       </c>
       <c r="D1644" s="1" t="inlineStr">
         <is>
-          <t>在；向；对；地址转换器</t>
+          <t>疯狂的；飞快的</t>
         </is>
       </c>
       <c r="E1644" s="1" t="inlineStr">
@@ -53523,7 +53523,7 @@
       </c>
       <c r="B1660" s="1" t="inlineStr">
         <is>
-          <t>[ʁʏkfal] 复归的〈n.〉</t>
+          <t>[ʁʏkfal] 旧病复发；倒退；重新犯罪〈n.〉</t>
         </is>
       </c>
       <c r="C1660" s="1" t="inlineStr">
@@ -53533,7 +53533,7 @@
       </c>
       <c r="D1660" s="1" t="inlineStr">
         <is>
-          <t>复归的</t>
+          <t>旧病复发；倒退；重新犯罪</t>
         </is>
       </c>
       <c r="E1660" s="1" t="inlineStr">
@@ -53555,7 +53555,7 @@
       </c>
       <c r="B1661" s="1" t="inlineStr">
         <is>
-          <t>[astəʁɔɪdən] 星状的〈n.〉</t>
+          <t>[astəʁɔɪdən] 小行星（复数）〈n.〉</t>
         </is>
       </c>
       <c r="C1661" s="1" t="inlineStr">
@@ -53565,7 +53565,7 @@
       </c>
       <c r="D1661" s="1" t="inlineStr">
         <is>
-          <t>星状的</t>
+          <t>小行星（复数）</t>
         </is>
       </c>
       <c r="E1661" s="1" t="inlineStr">
@@ -54099,7 +54099,7 @@
       </c>
       <c r="B1678" s="1" t="inlineStr">
         <is>
-          <t>[diːɡɪtaːl] 数字显示的〈n.〉</t>
+          <t>[diːɡɪtaːl] 数字显示屏；数码产品〈n.〉</t>
         </is>
       </c>
       <c r="C1678" s="1" t="inlineStr">
@@ -54109,7 +54109,7 @@
       </c>
       <c r="D1678" s="1" t="inlineStr">
         <is>
-          <t>数字显示的</t>
+          <t>数字显示屏；数码产品</t>
         </is>
       </c>
       <c r="E1678" s="1" t="inlineStr">
@@ -54131,7 +54131,7 @@
       </c>
       <c r="B1679" s="1" t="inlineStr">
         <is>
-          <t>[ʃpaɪçɐn] 存款；挽救；节约；搭救的〈n.〉</t>
+          <t>[ʃpaɪçɐn] 存储；储存；保全〈n.〉</t>
         </is>
       </c>
       <c r="C1679" s="1" t="inlineStr">
@@ -54141,7 +54141,7 @@
       </c>
       <c r="D1679" s="1" t="inlineStr">
         <is>
-          <t>存款；挽救；节约；搭救的</t>
+          <t>存储；储存；保全</t>
         </is>
       </c>
       <c r="E1679" s="1" t="inlineStr">
@@ -54387,7 +54387,7 @@
       </c>
       <c r="B1687" s="1" t="inlineStr">
         <is>
-          <t>[kʁabən] 真实的；正确的；忠诚的〈n.〉</t>
+          <t>[kʁabən] 螃蟹；小虾〈n.〉</t>
         </is>
       </c>
       <c r="C1687" s="1" t="inlineStr">
@@ -54397,7 +54397,7 @@
       </c>
       <c r="D1687" s="1" t="inlineStr">
         <is>
-          <t>真实的；正确的；忠诚的</t>
+          <t>螃蟹；小虾</t>
         </is>
       </c>
       <c r="E1687" s="1" t="inlineStr">
@@ -54963,7 +54963,7 @@
       </c>
       <c r="B1705" s="1" t="inlineStr">
         <is>
-          <t>[kabʁɪɔ] 可改变的〈n.〉</t>
+          <t>[kabʁɪɔ] 敞篷汽车；敞篷车〈n.〉</t>
         </is>
       </c>
       <c r="C1705" s="1" t="inlineStr">
@@ -54973,7 +54973,7 @@
       </c>
       <c r="D1705" s="1" t="inlineStr">
         <is>
-          <t>可改变的</t>
+          <t>敞篷汽车；敞篷车</t>
         </is>
       </c>
       <c r="E1705" s="1" t="inlineStr">
@@ -55443,7 +55443,7 @@
       </c>
       <c r="B1720" s="1" t="inlineStr">
         <is>
-          <t>[juːɡəndlɪçɐ] 青春期的〈n.m.〉</t>
+          <t>[juːɡəndlɪçɐ] 青少年；少年〈n.m.〉</t>
         </is>
       </c>
       <c r="C1720" s="1" t="inlineStr">
@@ -55453,7 +55453,7 @@
       </c>
       <c r="D1720" s="1" t="inlineStr">
         <is>
-          <t>青春期的</t>
+          <t>青少年；少年</t>
         </is>
       </c>
       <c r="E1720" s="1" t="inlineStr">
@@ -55603,7 +55603,7 @@
       </c>
       <c r="B1725" s="1" t="inlineStr">
         <is>
-          <t>[ʊmzət͡sən] 动人的；令人感动的；鼓动的〈n.〉</t>
+          <t>[ʊmzət͡sən] 实施；执行；转换〈n.〉</t>
         </is>
       </c>
       <c r="C1725" s="1" t="inlineStr">
@@ -55613,7 +55613,7 @@
       </c>
       <c r="D1725" s="1" t="inlineStr">
         <is>
-          <t>动人的；令人感动的；鼓动的</t>
+          <t>实施；执行；转换</t>
         </is>
       </c>
       <c r="E1725" s="1" t="inlineStr">
@@ -56307,7 +56307,7 @@
       </c>
       <c r="B1747" s="1" t="inlineStr">
         <is>
-          <t>[dɔvntoːn] 当顿的〈n.〉</t>
+          <t>[dɔvntoːn] 唐顿（地名/庄园名）〈n.〉</t>
         </is>
       </c>
       <c r="C1747" s="1" t="inlineStr">
@@ -56317,7 +56317,7 @@
       </c>
       <c r="D1747" s="1" t="inlineStr">
         <is>
-          <t>当顿的</t>
+          <t>唐顿（地名/庄园名）</t>
         </is>
       </c>
       <c r="E1747" s="1" t="inlineStr">
@@ -56819,7 +56819,7 @@
       </c>
       <c r="B1763" s="1" t="inlineStr">
         <is>
-          <t>[ɛtlɪçə] 数；数字；数目〈adv.〉</t>
+          <t>[ɛtlɪçə] 若干的；好些；相当多的〈adv.〉</t>
         </is>
       </c>
       <c r="C1763" s="1" t="inlineStr">
@@ -56829,7 +56829,7 @@
       </c>
       <c r="D1763" s="1" t="inlineStr">
         <is>
-          <t>数；数字；数目</t>
+          <t>若干的；好些；相当多的</t>
         </is>
       </c>
       <c r="E1763" s="1" t="inlineStr">
@@ -56883,7 +56883,7 @@
       </c>
       <c r="B1765" s="1" t="inlineStr">
         <is>
-          <t>[ɡɛvøːnlɪçəs] 通常的；共同的；通俗的〈n.〉</t>
+          <t>[ɡɛvøːnlɪçəs] 寻常事；平常事〈n.〉</t>
         </is>
       </c>
       <c r="C1765" s="1" t="inlineStr">
@@ -56893,7 +56893,7 @@
       </c>
       <c r="D1765" s="1" t="inlineStr">
         <is>
-          <t>通常的；共同的；通俗的</t>
+          <t>寻常事；平常事</t>
         </is>
       </c>
       <c r="E1765" s="1" t="inlineStr">
@@ -57011,7 +57011,7 @@
       </c>
       <c r="B1769" s="1" t="inlineStr">
         <is>
-          <t>[zeːnatɔʁən] 参议院的〈n.〉</t>
+          <t>[zeːnatɔʁən] 参议员（复数）〈n.〉</t>
         </is>
       </c>
       <c r="C1769" s="1" t="inlineStr">
@@ -57021,7 +57021,7 @@
       </c>
       <c r="D1769" s="1" t="inlineStr">
         <is>
-          <t>参议院的</t>
+          <t>参议员（复数）</t>
         </is>
       </c>
       <c r="E1769" s="1" t="inlineStr">
@@ -57235,7 +57235,7 @@
       </c>
       <c r="B1776" s="1" t="inlineStr">
         <is>
-          <t>[koːʁɛanɐ] 朝鲜人；朝鲜语的〈n.m.〉</t>
+          <t>[koːʁɛanɐ] 韩国人；朝鲜人〈n.m.〉</t>
         </is>
       </c>
       <c r="C1776" s="1" t="inlineStr">
@@ -57245,7 +57245,7 @@
       </c>
       <c r="D1776" s="1" t="inlineStr">
         <is>
-          <t>朝鲜人；朝鲜语的</t>
+          <t>韩国人；朝鲜人</t>
         </is>
       </c>
       <c r="E1776" s="1" t="inlineStr">
@@ -57715,7 +57715,7 @@
       </c>
       <c r="B1791" s="1" t="inlineStr">
         <is>
-          <t>[hoːzəntaʃə] 裤子的〈n.f.〉</t>
+          <t>[hoːzəntaʃə] 裤兜；裤袋〈n.f.〉</t>
         </is>
       </c>
       <c r="C1791" s="1" t="inlineStr">
@@ -57725,7 +57725,7 @@
       </c>
       <c r="D1791" s="1" t="inlineStr">
         <is>
-          <t>裤子的</t>
+          <t>裤兜；裤袋</t>
         </is>
       </c>
       <c r="E1791" s="1" t="inlineStr">
@@ -58995,7 +58995,7 @@
       </c>
       <c r="B1831" s="1" t="inlineStr">
         <is>
-          <t>[leːbənsvaɪzə] 生活；生计；生存；活的〈n.f.〉</t>
+          <t>[leːbənsvaɪzə] 生活方式；生存习性〈n.f.〉</t>
         </is>
       </c>
       <c r="C1831" s="1" t="inlineStr">
@@ -59005,7 +59005,7 @@
       </c>
       <c r="D1831" s="1" t="inlineStr">
         <is>
-          <t>生活；生计；生存；活的</t>
+          <t>生活方式；生存习性</t>
         </is>
       </c>
       <c r="E1831" s="1" t="inlineStr">
@@ -59315,7 +59315,7 @@
       </c>
       <c r="B1841" s="1" t="inlineStr">
         <is>
-          <t>[faxman] 专家；行家；老练的；内行的〈n.m.〉</t>
+          <t>[faxman] 专家；内行；行家〈n.m.〉</t>
         </is>
       </c>
       <c r="C1841" s="1" t="inlineStr">
@@ -59325,7 +59325,7 @@
       </c>
       <c r="D1841" s="1" t="inlineStr">
         <is>
-          <t>专家；行家；老练的；内行的</t>
+          <t>专家；内行；行家</t>
         </is>
       </c>
       <c r="E1841" s="1" t="inlineStr">
@@ -59379,7 +59379,7 @@
       </c>
       <c r="B1843" s="1" t="inlineStr">
         <is>
-          <t>[hɪntəʁə] 列；线；绳〈adv.〉</t>
+          <t>[hɪntəʁə] 后面的；后部的〈adv.〉</t>
         </is>
       </c>
       <c r="C1843" s="1" t="inlineStr">
@@ -59389,7 +59389,7 @@
       </c>
       <c r="D1843" s="1" t="inlineStr">
         <is>
-          <t>列；线；绳</t>
+          <t>后面的；后部的</t>
         </is>
       </c>
       <c r="E1843" s="1" t="inlineStr">
@@ -59411,7 +59411,7 @@
       </c>
       <c r="B1844" s="1" t="inlineStr">
         <is>
-          <t>[ʃtɛʁblɪçə] 生物；人类的〈n.〉</t>
+          <t>[ʃtɛʁblɪçə] 凡人；会死的人类〈n.〉</t>
         </is>
       </c>
       <c r="C1844" s="1" t="inlineStr">
@@ -59421,7 +59421,7 @@
       </c>
       <c r="D1844" s="1" t="inlineStr">
         <is>
-          <t>生物；人类的</t>
+          <t>凡人；会死的人类</t>
         </is>
       </c>
       <c r="E1844" s="1" t="inlineStr">
@@ -59507,7 +59507,7 @@
       </c>
       <c r="B1847" s="1" t="inlineStr">
         <is>
-          <t>[hʊndəʁtɐ] 百；百个；一百的〈n.m.〉</t>
+          <t>[hʊndəʁtɐ] 百位数；一百元纸币〈n.m.〉</t>
         </is>
       </c>
       <c r="C1847" s="1" t="inlineStr">
@@ -59517,7 +59517,7 @@
       </c>
       <c r="D1847" s="1" t="inlineStr">
         <is>
-          <t>百；百个；一百的</t>
+          <t>百位数；一百元纸币</t>
         </is>
       </c>
       <c r="E1847" s="1" t="inlineStr">
@@ -60915,7 +60915,7 @@
       </c>
       <c r="B1891" s="1" t="inlineStr">
         <is>
-          <t>[afʁɪkanɪʃə] 非洲人的〈n.〉</t>
+          <t>[afʁɪkanɪʃə] 非洲事物；非洲风格〈n.〉</t>
         </is>
       </c>
       <c r="C1891" s="1" t="inlineStr">
@@ -60925,7 +60925,7 @@
       </c>
       <c r="D1891" s="1" t="inlineStr">
         <is>
-          <t>非洲人的</t>
+          <t>非洲事物；非洲风格</t>
         </is>
       </c>
       <c r="E1891" s="1" t="inlineStr">
@@ -60979,7 +60979,7 @@
       </c>
       <c r="B1893" s="1" t="inlineStr">
         <is>
-          <t>[leːbənst͡saɪt] 一生；终生；一生的；终生的〈n.f.〉</t>
+          <t>[leːbənst͡saɪt] 一生；终身；寿命〈n.f.〉</t>
         </is>
       </c>
       <c r="C1893" s="1" t="inlineStr">
@@ -60989,7 +60989,7 @@
       </c>
       <c r="D1893" s="1" t="inlineStr">
         <is>
-          <t>一生；终生；一生的；终生的</t>
+          <t>一生；终身；寿命</t>
         </is>
       </c>
       <c r="E1893" s="1" t="inlineStr">
@@ -61331,7 +61331,7 @@
       </c>
       <c r="B1904" s="1" t="inlineStr">
         <is>
-          <t>[taʊfən] 洗礼的〈n.〉</t>
+          <t>[taʊfən] 施洗；受洗礼〈n.〉</t>
         </is>
       </c>
       <c r="C1904" s="1" t="inlineStr">
@@ -61341,7 +61341,7 @@
       </c>
       <c r="D1904" s="1" t="inlineStr">
         <is>
-          <t>洗礼的</t>
+          <t>施洗；受洗礼</t>
         </is>
       </c>
       <c r="E1904" s="1" t="inlineStr">
@@ -61907,7 +61907,7 @@
       </c>
       <c r="B1922" s="1" t="inlineStr">
         <is>
-          <t>[liːblɪnɡsfaʁbə] 宠爱的〈n.f.〉</t>
+          <t>[liːblɪnɡsfaʁbə] 最喜欢的颜色〈n.f.〉</t>
         </is>
       </c>
       <c r="C1922" s="1" t="inlineStr">
@@ -61917,7 +61917,7 @@
       </c>
       <c r="D1922" s="1" t="inlineStr">
         <is>
-          <t>宠爱的</t>
+          <t>最喜欢的颜色</t>
         </is>
       </c>
       <c r="E1922" s="1" t="inlineStr">
@@ -62131,7 +62131,7 @@
       </c>
       <c r="B1929" s="1" t="inlineStr">
         <is>
-          <t>[ʃtaxəldʁaːt] 有倒刺的〈n.m.〉</t>
+          <t>[ʃtaxəldʁaːt] 铁丝网；带刺铁丝〈n.m.〉</t>
         </is>
       </c>
       <c r="C1929" s="1" t="inlineStr">
@@ -62141,7 +62141,7 @@
       </c>
       <c r="D1929" s="1" t="inlineStr">
         <is>
-          <t>有倒刺的</t>
+          <t>铁丝网；带刺铁丝</t>
         </is>
       </c>
       <c r="E1929" s="1" t="inlineStr">
@@ -62675,7 +62675,7 @@
       </c>
       <c r="B1946" s="1" t="inlineStr">
         <is>
-          <t>[bloːsə] 暗黄色；暗黄色皮革〈adv.〉</t>
+          <t>[bloːsə] 单纯的；仅仅的；赤裸的〈adv.〉</t>
         </is>
       </c>
       <c r="C1946" s="1" t="inlineStr">
@@ -62685,7 +62685,7 @@
       </c>
       <c r="D1946" s="1" t="inlineStr">
         <is>
-          <t>暗黄色；暗黄色皮革</t>
+          <t>单纯的；仅仅的；赤裸的</t>
         </is>
       </c>
       <c r="E1946" s="1" t="inlineStr">
@@ -63187,7 +63187,7 @@
       </c>
       <c r="B1962" s="1" t="inlineStr">
         <is>
-          <t>[ɡʁɔst͡sʏɡɪɡə] 慷慨；宽大；礼物；奖励金〈adv.〉</t>
+          <t>[ɡʁɔst͡sʏɡɪɡə] 慷慨的；大方的；宽宏大量的〈adv.〉</t>
         </is>
       </c>
       <c r="C1962" s="1" t="inlineStr">
@@ -63197,7 +63197,7 @@
       </c>
       <c r="D1962" s="1" t="inlineStr">
         <is>
-          <t>慷慨；宽大；礼物；奖励金</t>
+          <t>慷慨的；大方的；宽宏大量的</t>
         </is>
       </c>
       <c r="E1962" s="1" t="inlineStr">
@@ -63379,7 +63379,7 @@
       </c>
       <c r="B1968" s="1" t="inlineStr">
         <is>
-          <t>[aːdɐ] 隔热的；绝缘的〈n.f.〉</t>
+          <t>[aːdɐ] 血管；静脉；矿脉〈n.f.〉</t>
         </is>
       </c>
       <c r="C1968" s="1" t="inlineStr">
@@ -63389,7 +63389,7 @@
       </c>
       <c r="D1968" s="1" t="inlineStr">
         <is>
-          <t>隔热的；绝缘的</t>
+          <t>血管；静脉；矿脉</t>
         </is>
       </c>
       <c r="E1968" s="1" t="inlineStr">
@@ -63411,7 +63411,7 @@
       </c>
       <c r="B1969" s="1" t="inlineStr">
         <is>
-          <t>[ʃlɔʏdɐn] 脱离；一碰就散开；脱落的〈n.〉</t>
+          <t>[ʃlɔʏdɐn] 打滑甩尾；脱水甩干；抛掷〈n.〉</t>
         </is>
       </c>
       <c r="C1969" s="1" t="inlineStr">
@@ -63421,7 +63421,7 @@
       </c>
       <c r="D1969" s="1" t="inlineStr">
         <is>
-          <t>脱离；一碰就散开；脱落的</t>
+          <t>打滑甩尾；脱水甩干；抛掷</t>
         </is>
       </c>
       <c r="E1969" s="1" t="inlineStr">
@@ -64755,7 +64755,7 @@
       </c>
       <c r="B2011" s="1" t="inlineStr">
         <is>
-          <t>[dɪaləkt] 方言的；乡音的〈n.〉</t>
+          <t>[dɪaləkt] 方言；地方话〈n.〉</t>
         </is>
       </c>
       <c r="C2011" s="1" t="inlineStr">
@@ -64765,7 +64765,7 @@
       </c>
       <c r="D2011" s="1" t="inlineStr">
         <is>
-          <t>方言的；乡音的</t>
+          <t>方言；地方话</t>
         </is>
       </c>
       <c r="E2011" s="1" t="inlineStr">
@@ -64883,7 +64883,7 @@
       </c>
       <c r="B2015" s="1" t="inlineStr">
         <is>
-          <t>[aʊfpasɐ] 私人的；涉及隐私的；有人性的〈n.m.〉</t>
+          <t>[aʊfpasɐ] 看守人；监护者；监工〈n.m.〉</t>
         </is>
       </c>
       <c r="C2015" s="1" t="inlineStr">
@@ -64893,7 +64893,7 @@
       </c>
       <c r="D2015" s="1" t="inlineStr">
         <is>
-          <t>私人的；涉及隐私的；有人性的</t>
+          <t>看守人；监护者；监工</t>
         </is>
       </c>
       <c r="E2015" s="1" t="inlineStr">
@@ -65107,7 +65107,7 @@
       </c>
       <c r="B2022" s="1" t="inlineStr">
         <is>
-          <t>[bɛʁnstaɪn] 琥珀；琥珀似的〈n.m.〉</t>
+          <t>[bɛʁnstaɪn] 琥珀〈n.m.〉</t>
         </is>
       </c>
       <c r="C2022" s="1" t="inlineStr">
@@ -65117,7 +65117,7 @@
       </c>
       <c r="D2022" s="1" t="inlineStr">
         <is>
-          <t>琥珀；琥珀似的</t>
+          <t>琥珀</t>
         </is>
       </c>
       <c r="E2022" s="1" t="inlineStr">
@@ -65235,7 +65235,7 @@
       </c>
       <c r="B2026" s="1" t="inlineStr">
         <is>
-          <t>[almɛçtɪɡə] 万能的；全能的〈n.m.〉</t>
+          <t>[almɛçtɪɡə] 全能者；上帝〈n.m.〉</t>
         </is>
       </c>
       <c r="C2026" s="1" t="inlineStr">
@@ -65245,7 +65245,7 @@
       </c>
       <c r="D2026" s="1" t="inlineStr">
         <is>
-          <t>万能的；全能的</t>
+          <t>全能者；上帝</t>
         </is>
       </c>
       <c r="E2026" s="1" t="inlineStr">
@@ -67539,7 +67539,7 @@
       </c>
       <c r="B2098" s="1" t="inlineStr">
         <is>
-          <t>[aːs] 死肉；腐肉；腐肉的；似腐肉的〈n.〉</t>
+          <t>[aːs] 死肉；腐肉〈n.〉</t>
         </is>
       </c>
       <c r="C2098" s="1" t="inlineStr">
@@ -67549,7 +67549,7 @@
       </c>
       <c r="D2098" s="1" t="inlineStr">
         <is>
-          <t>死肉；腐肉；腐肉的；似腐肉的</t>
+          <t>死肉；腐肉</t>
         </is>
       </c>
       <c r="E2098" s="1" t="inlineStr">
@@ -67667,7 +67667,7 @@
       </c>
       <c r="B2102" s="1" t="inlineStr">
         <is>
-          <t>[aktɪfə] 活跃的；起作用的；积极的〈n.〉</t>
+          <t>[aktɪfə] 积极分子；在役人员〈n.〉</t>
         </is>
       </c>
       <c r="C2102" s="1" t="inlineStr">
@@ -67677,7 +67677,7 @@
       </c>
       <c r="D2102" s="1" t="inlineStr">
         <is>
-          <t>活跃的；起作用的；积极的</t>
+          <t>积极分子；在役人员</t>
         </is>
       </c>
       <c r="E2102" s="1" t="inlineStr">
@@ -67827,7 +67827,7 @@
       </c>
       <c r="B2107" s="1" t="inlineStr">
         <is>
-          <t>[blɪndaʁm] 蒙蔽物；窗帘；盲目的；瞎的〈n.m.〉</t>
+          <t>[blɪndaʁm] 阑尾；盲肠〈n.m.〉</t>
         </is>
       </c>
       <c r="C2107" s="1" t="inlineStr">
@@ -67837,7 +67837,7 @@
       </c>
       <c r="D2107" s="1" t="inlineStr">
         <is>
-          <t>蒙蔽物；窗帘；盲目的；瞎的</t>
+          <t>阑尾；盲肠</t>
         </is>
       </c>
       <c r="E2107" s="1" t="inlineStr">
@@ -68435,7 +68435,7 @@
       </c>
       <c r="B2126" s="1" t="inlineStr">
         <is>
-          <t>[knakɐ] 裂解；分解；敏捷的〈n.m.〉</t>
+          <t>[knakɐ] 脆皮小香肠；老朽〈n.m.〉</t>
         </is>
       </c>
       <c r="C2126" s="1" t="inlineStr">
@@ -68445,7 +68445,7 @@
       </c>
       <c r="D2126" s="1" t="inlineStr">
         <is>
-          <t>裂解；分解；敏捷的</t>
+          <t>脆皮小香肠；老朽</t>
         </is>
       </c>
       <c r="E2126" s="1" t="inlineStr">
@@ -69043,7 +69043,7 @@
       </c>
       <c r="B2145" s="1" t="inlineStr">
         <is>
-          <t>[kapən] 极好的；主要的〈n.〉</t>
+          <t>[kapən] 护盖；帽子 / 截短；切除〈n.〉</t>
         </is>
       </c>
       <c r="C2145" s="1" t="inlineStr">
@@ -69053,7 +69053,7 @@
       </c>
       <c r="D2145" s="1" t="inlineStr">
         <is>
-          <t>极好的；主要的</t>
+          <t>护盖；帽子 / 截短；切除</t>
         </is>
       </c>
       <c r="E2145" s="1" t="inlineStr">
@@ -69747,7 +69747,7 @@
       </c>
       <c r="B2167" s="1" t="inlineStr">
         <is>
-          <t>[naxtɪʃ] 床边；床边的；临床的〈n.m.〉</t>
+          <t>[naxtɪʃ] 床头柜；床边桌〈n.m.〉</t>
         </is>
       </c>
       <c r="C2167" s="1" t="inlineStr">
@@ -69757,7 +69757,7 @@
       </c>
       <c r="D2167" s="1" t="inlineStr">
         <is>
-          <t>床边；床边的；临床的</t>
+          <t>床头柜；床边桌</t>
         </is>
       </c>
       <c r="E2167" s="1" t="inlineStr">
@@ -69939,7 +69939,7 @@
       </c>
       <c r="B2173" s="1" t="inlineStr">
         <is>
-          <t>[kɔləktiːf] 集体的；聚集的；共同的〈n.〉</t>
+          <t>[kɔləktiːf] 集体；集体组织〈n.〉</t>
         </is>
       </c>
       <c r="C2173" s="1" t="inlineStr">
@@ -69949,7 +69949,7 @@
       </c>
       <c r="D2173" s="1" t="inlineStr">
         <is>
-          <t>集体的；聚集的；共同的</t>
+          <t>集体；集体组织</t>
         </is>
       </c>
       <c r="E2173" s="1" t="inlineStr">

--- a/languages/de/packs/de/books/德语B2.xlsx
+++ b/languages/de/packs/de/books/德语B2.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="词汇表" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="词汇表" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -915,7 +915,7 @@
       </c>
       <c r="B16" s="1" t="inlineStr">
         <is>
-          <t>[viːnɐ] 维也纳〈adj.〉</t>
+          <t>[viːnɐ] 维也纳的；维也纳人〈adj.〉</t>
         </is>
       </c>
       <c r="C16" s="1" t="inlineStr">
@@ -925,7 +925,7 @@
       </c>
       <c r="D16" s="1" t="inlineStr">
         <is>
-          <t>维也纳</t>
+          <t>维也纳的；维也纳人</t>
         </is>
       </c>
       <c r="E16" s="1" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="B20" s="1" t="inlineStr">
         <is>
-          <t>[ɛnt͡ʃɛdɪɡʊnk] 补偿；赔偿金；工资；代偿〈n.f.〉</t>
+          <t>[ɛnt͡ʃɛdɪɡʊŋ] 补偿；赔偿金；工资；代偿〈n.f.〉</t>
         </is>
       </c>
       <c r="C20" s="1" t="inlineStr">
         <is>
-          <t>ɛnt͡ʃɛdɪɡʊnk</t>
+          <t>ɛnt͡ʃɛdɪɡʊŋ</t>
         </is>
       </c>
       <c r="D20" s="1" t="inlineStr">
@@ -1139,7 +1139,7 @@
       </c>
       <c r="B23" s="1" t="inlineStr">
         <is>
-          <t>[vɛltmaɪstɐ] 世界；地球；宇宙〈n.m.〉</t>
+          <t>[vɛltmaɪstɐ] 世界冠军〈n.m.〉</t>
         </is>
       </c>
       <c r="C23" s="1" t="inlineStr">
@@ -1149,7 +1149,7 @@
       </c>
       <c r="D23" s="1" t="inlineStr">
         <is>
-          <t>世界；地球；宇宙</t>
+          <t>世界冠军</t>
         </is>
       </c>
       <c r="E23" s="1" t="inlineStr">
@@ -1171,7 +1171,7 @@
       </c>
       <c r="B24" s="1" t="inlineStr">
         <is>
-          <t>[veːzəntlɪçə] 形势；情况；环境〈n.〉</t>
+          <t>[veːzəntlɪçə] 本质的东西；要点；实质〈n.〉〈n.〉</t>
         </is>
       </c>
       <c r="C24" s="1" t="inlineStr">
@@ -1181,7 +1181,7 @@
       </c>
       <c r="D24" s="1" t="inlineStr">
         <is>
-          <t>形势；情况；环境</t>
+          <t>本质的东西；要点；实质〈n.〉</t>
         </is>
       </c>
       <c r="E24" s="1" t="inlineStr">
@@ -1203,7 +1203,7 @@
       </c>
       <c r="B25" s="1" t="inlineStr">
         <is>
-          <t>[ɡeːmɪʃt] 混合的；形形色色的；弄糊涂的〈adj.〉</t>
+          <t>[ɡeːmɪʃt] 混合的；形形色色的〈adj.〉</t>
         </is>
       </c>
       <c r="C25" s="1" t="inlineStr">
@@ -1213,7 +1213,7 @@
       </c>
       <c r="D25" s="1" t="inlineStr">
         <is>
-          <t>混合的；形形色色的；弄糊涂的</t>
+          <t>混合的；形形色色的</t>
         </is>
       </c>
       <c r="E25" s="1" t="inlineStr">
@@ -1459,7 +1459,7 @@
       </c>
       <c r="B33" s="1" t="inlineStr">
         <is>
-          <t>[faːkʊltɛːt] 才能；能力；全体教员〈n.f.〉</t>
+          <t>[faːkʊltɛːt] （大学的）学院、系；才能；能力；全体教员〈n.f.〉〈n.f.〉</t>
         </is>
       </c>
       <c r="C33" s="1" t="inlineStr">
@@ -1469,7 +1469,7 @@
       </c>
       <c r="D33" s="1" t="inlineStr">
         <is>
-          <t>才能；能力；全体教员</t>
+          <t>（大学的）学院、系；才能；能力；全体教员〈n.f.〉</t>
         </is>
       </c>
       <c r="E33" s="1" t="inlineStr">
@@ -1491,7 +1491,7 @@
       </c>
       <c r="B34" s="1" t="inlineStr">
         <is>
-          <t>[mœpzə] 乳房〈n.〉</t>
+          <t>[mœpzə] 哈巴狗；巴哥犬〈n.〉</t>
         </is>
       </c>
       <c r="C34" s="1" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="D34" s="1" t="inlineStr">
         <is>
-          <t>乳房</t>
+          <t>哈巴狗；巴哥犬</t>
         </is>
       </c>
       <c r="E34" s="1" t="inlineStr">
@@ -1555,7 +1555,7 @@
       </c>
       <c r="B36" s="1" t="inlineStr">
         <is>
-          <t>[ʃlaɡt͡saɪlə] 捕捉；陷阱；捕捉之物〈n.f.〉</t>
+          <t>[ʃlaɡt͡saɪlə] （报纸）大字标题；头条新闻〈n.f.〉</t>
         </is>
       </c>
       <c r="C36" s="1" t="inlineStr">
@@ -1565,7 +1565,7 @@
       </c>
       <c r="D36" s="1" t="inlineStr">
         <is>
-          <t>捕捉；陷阱；捕捉之物</t>
+          <t>（报纸）大字标题；头条新闻</t>
         </is>
       </c>
       <c r="E36" s="1" t="inlineStr">
@@ -1811,7 +1811,7 @@
       </c>
       <c r="B44" s="1" t="inlineStr">
         <is>
-          <t>[ʃnɛlstəns] 明白地；清楚地；特意地〈adv.〉</t>
+          <t>[ʃnɛlstəns] 尽快地；火速地〈adv.〉</t>
         </is>
       </c>
       <c r="C44" s="1" t="inlineStr">
@@ -1821,7 +1821,7 @@
       </c>
       <c r="D44" s="1" t="inlineStr">
         <is>
-          <t>明白地；清楚地；特意地</t>
+          <t>尽快地；火速地</t>
         </is>
       </c>
       <c r="E44" s="1" t="inlineStr">
@@ -1843,7 +1843,7 @@
       </c>
       <c r="B45" s="1" t="inlineStr">
         <is>
-          <t>[t͡suːʁəçtkɔmən] 竞争；应付；长袍〈v.〉</t>
+          <t>[t͡suːʁəçtkɔmən] 应付；处理；适应〈v.〉</t>
         </is>
       </c>
       <c r="C45" s="1" t="inlineStr">
@@ -1853,7 +1853,7 @@
       </c>
       <c r="D45" s="1" t="inlineStr">
         <is>
-          <t>竞争；应付；长袍</t>
+          <t>应付；处理；适应</t>
         </is>
       </c>
       <c r="E45" s="1" t="inlineStr">
@@ -1971,7 +1971,7 @@
       </c>
       <c r="B49" s="1" t="inlineStr">
         <is>
-          <t>[ʊntəʁbʁɪnɡən] 住所；住宅；定居〈v.〉</t>
+          <t>[ʊntəʁbʁɪnɡən] 安置；安顿；使住宿〈v.〉</t>
         </is>
       </c>
       <c r="C49" s="1" t="inlineStr">
@@ -1981,7 +1981,7 @@
       </c>
       <c r="D49" s="1" t="inlineStr">
         <is>
-          <t>住所；住宅；定居</t>
+          <t>安置；安顿；使住宿</t>
         </is>
       </c>
       <c r="E49" s="1" t="inlineStr">
@@ -2067,7 +2067,7 @@
       </c>
       <c r="B52" s="1" t="inlineStr">
         <is>
-          <t>[kantɪnə] 全体人员；工作班子；棍棒〈n.f.〉</t>
+          <t>[kantɪnə] 食堂；餐厅〈n.f.〉</t>
         </is>
       </c>
       <c r="C52" s="1" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="D52" s="1" t="inlineStr">
         <is>
-          <t>全体人员；工作班子；棍棒</t>
+          <t>食堂；餐厅</t>
         </is>
       </c>
       <c r="E52" s="1" t="inlineStr">
@@ -2099,7 +2099,7 @@
       </c>
       <c r="B53" s="1" t="inlineStr">
         <is>
-          <t>[aʊfɡəvəkt] 眼睛晶莹的〈adv.〉</t>
+          <t>[aʊfɡəvəkt] 机敏的；聪明的；机灵的〈adv.〉</t>
         </is>
       </c>
       <c r="C53" s="1" t="inlineStr">
@@ -2109,7 +2109,7 @@
       </c>
       <c r="D53" s="1" t="inlineStr">
         <is>
-          <t>眼睛晶莹的</t>
+          <t>机敏的；聪明的；机灵的</t>
         </is>
       </c>
       <c r="E53" s="1" t="inlineStr">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="B72" s="1" t="inlineStr">
         <is>
-          <t>[ɡeːaltzəʁhøːʊnk] 上升；增加；上涨〈n.f.〉</t>
+          <t>[ɡeːaltzəʁhøːʊŋ] 上升；增加；上涨〈n.f.〉</t>
         </is>
       </c>
       <c r="C72" s="1" t="inlineStr">
         <is>
-          <t>ɡeːaltzəʁhøːʊnk</t>
+          <t>ɡeːaltzəʁhøːʊŋ</t>
         </is>
       </c>
       <c r="D72" s="1" t="inlineStr">
@@ -2803,7 +2803,7 @@
       </c>
       <c r="B75" s="1" t="inlineStr">
         <is>
-          <t>[ɛʁbzən] 豌豆〈n.〉</t>
+          <t>[ɛʁbzən] 豌豆（Erbse 的复数）〈n.f.〉〈n.〉</t>
         </is>
       </c>
       <c r="C75" s="1" t="inlineStr">
@@ -2813,7 +2813,7 @@
       </c>
       <c r="D75" s="1" t="inlineStr">
         <is>
-          <t>豌豆</t>
+          <t>豌豆（Erbse 的复数）〈n.f.〉</t>
         </is>
       </c>
       <c r="E75" s="1" t="inlineStr">
@@ -2835,7 +2835,7 @@
       </c>
       <c r="B76" s="1" t="inlineStr">
         <is>
-          <t>[kloːn] 无性系；代用件〈n.m.〉</t>
+          <t>[kloːn] 克隆；无性繁殖系〈m.〉〈n.m.〉</t>
         </is>
       </c>
       <c r="C76" s="1" t="inlineStr">
@@ -2845,7 +2845,7 @@
       </c>
       <c r="D76" s="1" t="inlineStr">
         <is>
-          <t>无性系；代用件</t>
+          <t>克隆；无性繁殖系〈m.〉</t>
         </is>
       </c>
       <c r="E76" s="1" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B79" s="1" t="inlineStr">
         <is>
-          <t>[hoːməlant] 黑色〈n.〉</t>
+          <t>[hoːməlant] 祖国；家园〈n.〉</t>
         </is>
       </c>
       <c r="C79" s="1" t="inlineStr">
@@ -2941,7 +2941,7 @@
       </c>
       <c r="D79" s="1" t="inlineStr">
         <is>
-          <t>黑色</t>
+          <t>祖国；家园</t>
         </is>
       </c>
       <c r="E79" s="1" t="inlineStr">
@@ -3027,7 +3027,7 @@
       </c>
       <c r="B82" s="1" t="inlineStr">
         <is>
-          <t>[aʊfbʁɪnɡən] 联系；交际；熟人〈n.〉</t>
+          <t>[aʊfbʁɪnɡən] 涂上；施加；筹集；使恼怒〈n.〉</t>
         </is>
       </c>
       <c r="C82" s="1" t="inlineStr">
@@ -3037,7 +3037,7 @@
       </c>
       <c r="D82" s="1" t="inlineStr">
         <is>
-          <t>联系；交际；熟人</t>
+          <t>涂上；施加；筹集；使恼怒</t>
         </is>
       </c>
       <c r="E82" s="1" t="inlineStr">
@@ -3059,7 +3059,7 @@
       </c>
       <c r="B83" s="1" t="inlineStr">
         <is>
-          <t>[t͡sɪmɐn] 做；进行；完成〈v.〉</t>
+          <t>[t͡sɪmɐn] 做木工；建造〈v.〉</t>
         </is>
       </c>
       <c r="C83" s="1" t="inlineStr">
@@ -3069,7 +3069,7 @@
       </c>
       <c r="D83" s="1" t="inlineStr">
         <is>
-          <t>做；进行；完成</t>
+          <t>做木工；建造</t>
         </is>
       </c>
       <c r="E83" s="1" t="inlineStr">
@@ -3091,7 +3091,7 @@
       </c>
       <c r="B84" s="1" t="inlineStr">
         <is>
-          <t>[katɔlɪʃ] 普遍的；广泛的〈adj.〉</t>
+          <t>[katɔlɪʃ] 天主教的〈adj.〉</t>
         </is>
       </c>
       <c r="C84" s="1" t="inlineStr">
@@ -3101,7 +3101,7 @@
       </c>
       <c r="D84" s="1" t="inlineStr">
         <is>
-          <t>普遍的；广泛的</t>
+          <t>天主教的</t>
         </is>
       </c>
       <c r="E84" s="1" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="B88" s="1" t="inlineStr">
         <is>
-          <t>[bɔvlɪnk] 保龄球戏〈n.〉</t>
+          <t>[bɔvlɪŋ] 保龄球戏〈n.〉</t>
         </is>
       </c>
       <c r="C88" s="1" t="inlineStr">
         <is>
-          <t>bɔvlɪnk</t>
+          <t>bɔvlɪŋ</t>
         </is>
       </c>
       <c r="D88" s="1" t="inlineStr">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="B89" s="1" t="inlineStr">
         <is>
-          <t>[eːkəl] 爬；徐行；蠕动〈n.〉</t>
+          <t>[eːkəl] 厌恶；恶心〈n.〉</t>
         </is>
       </c>
       <c r="C89" s="1" t="inlineStr">
@@ -3261,7 +3261,7 @@
       </c>
       <c r="D89" s="1" t="inlineStr">
         <is>
-          <t>爬；徐行；蠕动</t>
+          <t>厌恶；恶心</t>
         </is>
       </c>
       <c r="E89" s="1" t="inlineStr">
@@ -3283,7 +3283,7 @@
       </c>
       <c r="B90" s="1" t="inlineStr">
         <is>
-          <t>[fʏzɪʃ] 按自然规律；完全地；实际上〈adv.〉</t>
+          <t>[fʏzɪʃ] 物理的；身体的；物质的〈adv.〉</t>
         </is>
       </c>
       <c r="C90" s="1" t="inlineStr">
@@ -3293,7 +3293,7 @@
       </c>
       <c r="D90" s="1" t="inlineStr">
         <is>
-          <t>按自然规律；完全地；实际上</t>
+          <t>物理的；身体的；物质的</t>
         </is>
       </c>
       <c r="E90" s="1" t="inlineStr">
@@ -3315,7 +3315,7 @@
       </c>
       <c r="B91" s="1" t="inlineStr">
         <is>
-          <t>[maːsə] 韵律学；韵律特色〈n.〉</t>
+          <t>[maːsə] 尺寸；度量；规格（Maß 的复数）〈n.〉</t>
         </is>
       </c>
       <c r="C91" s="1" t="inlineStr">
@@ -3325,7 +3325,7 @@
       </c>
       <c r="D91" s="1" t="inlineStr">
         <is>
-          <t>韵律学；韵律特色</t>
+          <t>尺寸；度量；规格（Maß 的复数）</t>
         </is>
       </c>
       <c r="E91" s="1" t="inlineStr">
@@ -3667,7 +3667,7 @@
       </c>
       <c r="B102" s="1" t="inlineStr">
         <is>
-          <t>[kʁøːtən] 蟾蜍；癞蛤蟆〈n.〉</t>
+          <t>[kʁøːtən] 蟾蜍；癞蛤蟆〈n.f.〉（单数 Kröte，Kröten 为复数）〈n.〉</t>
         </is>
       </c>
       <c r="C102" s="1" t="inlineStr">
@@ -3677,7 +3677,7 @@
       </c>
       <c r="D102" s="1" t="inlineStr">
         <is>
-          <t>蟾蜍；癞蛤蟆</t>
+          <t>蟾蜍；癞蛤蟆〈n.f.〉（单数 Kröte，Kröten 为复数）</t>
         </is>
       </c>
       <c r="E102" s="1" t="inlineStr">
@@ -4115,7 +4115,7 @@
       </c>
       <c r="B116" s="1" t="inlineStr">
         <is>
-          <t>[plœt͡slɪçə] 喷射；迸发〈adv.〉</t>
+          <t>[plœt͡slɪçə] 突然的；意外的〈adv.〉</t>
         </is>
       </c>
       <c r="C116" s="1" t="inlineStr">
@@ -4125,7 +4125,7 @@
       </c>
       <c r="D116" s="1" t="inlineStr">
         <is>
-          <t>喷射；迸发</t>
+          <t>突然的；意外的</t>
         </is>
       </c>
       <c r="E116" s="1" t="inlineStr">
@@ -4339,7 +4339,7 @@
       </c>
       <c r="B123" s="1" t="inlineStr">
         <is>
-          <t>[ʃtʁʏmpfə] 尼龙长袜〈n.〉</t>
+          <t>[ʃtʁʏmpfə] 长袜（Strumpf的复数）〈n.m.〉〈n.〉</t>
         </is>
       </c>
       <c r="C123" s="1" t="inlineStr">
@@ -4349,7 +4349,7 @@
       </c>
       <c r="D123" s="1" t="inlineStr">
         <is>
-          <t>尼龙长袜</t>
+          <t>长袜（Strumpf的复数）〈n.m.〉</t>
         </is>
       </c>
       <c r="E123" s="1" t="inlineStr">
@@ -4499,12 +4499,12 @@
       </c>
       <c r="B128" s="1" t="inlineStr">
         <is>
-          <t>[abfɪndʊnk] 偿清〈n.f.〉</t>
+          <t>[abfɪndʊŋ] 偿清〈n.f.〉</t>
         </is>
       </c>
       <c r="C128" s="1" t="inlineStr">
         <is>
-          <t>abfɪndʊnk</t>
+          <t>abfɪndʊŋ</t>
         </is>
       </c>
       <c r="D128" s="1" t="inlineStr">
@@ -4659,7 +4659,7 @@
       </c>
       <c r="B133" s="1" t="inlineStr">
         <is>
-          <t>[abzaɪts] 小声说的话；离开〈n.〉</t>
+          <t>[abzaɪts] 越位；偏僻处〈n.〉</t>
         </is>
       </c>
       <c r="C133" s="1" t="inlineStr">
@@ -4669,7 +4669,7 @@
       </c>
       <c r="D133" s="1" t="inlineStr">
         <is>
-          <t>小声说的话；离开</t>
+          <t>越位；偏僻处</t>
         </is>
       </c>
       <c r="E133" s="1" t="inlineStr">
@@ -4819,7 +4819,7 @@
       </c>
       <c r="B138" s="1" t="inlineStr">
         <is>
-          <t>[nɪpəl] 乳头；奶头；奶嘴；螺纹接口〈n.〉</t>
+          <t>[nɪpəl] 乳头；奶嘴；螺纹接口〈n.m.〉〈n.〉</t>
         </is>
       </c>
       <c r="C138" s="1" t="inlineStr">
@@ -4829,7 +4829,7 @@
       </c>
       <c r="D138" s="1" t="inlineStr">
         <is>
-          <t>乳头；奶头；奶嘴；螺纹接口</t>
+          <t>乳头；奶嘴；螺纹接口〈n.m.〉</t>
         </is>
       </c>
       <c r="E138" s="1" t="inlineStr">
@@ -4915,7 +4915,7 @@
       </c>
       <c r="B141" s="1" t="inlineStr">
         <is>
-          <t>[akɐ] 英亩〈n.m.〉</t>
+          <t>[akɐ] 田地；耕地〈n.m.〉</t>
         </is>
       </c>
       <c r="C141" s="1" t="inlineStr">
@@ -4925,7 +4925,7 @@
       </c>
       <c r="D141" s="1" t="inlineStr">
         <is>
-          <t>英亩</t>
+          <t>田地；耕地</t>
         </is>
       </c>
       <c r="E141" s="1" t="inlineStr">
@@ -4947,7 +4947,7 @@
       </c>
       <c r="B142" s="1" t="inlineStr">
         <is>
-          <t>[meːdɪt͡sɪnɪʃ] 医生；内科的〈adj.〉</t>
+          <t>[meːdɪt͡sɪnɪʃ] 医学的；医疗的〈adj.〉</t>
         </is>
       </c>
       <c r="C142" s="1" t="inlineStr">
@@ -4957,7 +4957,7 @@
       </c>
       <c r="D142" s="1" t="inlineStr">
         <is>
-          <t>医生；内科的</t>
+          <t>医学的；医疗的</t>
         </is>
       </c>
       <c r="E142" s="1" t="inlineStr">
@@ -4979,7 +4979,7 @@
       </c>
       <c r="B143" s="1" t="inlineStr">
         <is>
-          <t>[takt] 条；棒；酒吧〈n.m.〉</t>
+          <t>[takt] 节拍；节奏；分寸〈n.m.〉</t>
         </is>
       </c>
       <c r="C143" s="1" t="inlineStr">
@@ -4989,7 +4989,7 @@
       </c>
       <c r="D143" s="1" t="inlineStr">
         <is>
-          <t>条；棒；酒吧</t>
+          <t>节拍；节奏；分寸</t>
         </is>
       </c>
       <c r="E143" s="1" t="inlineStr">
@@ -5011,7 +5011,7 @@
       </c>
       <c r="B144" s="1" t="inlineStr">
         <is>
-          <t>[meːnʏ] 日落；同伙；组合〈n.〉</t>
+          <t>[meːnʏ] 套餐；菜单；（电脑）菜单〈n.〉</t>
         </is>
       </c>
       <c r="C144" s="1" t="inlineStr">
@@ -5021,7 +5021,7 @@
       </c>
       <c r="D144" s="1" t="inlineStr">
         <is>
-          <t>日落；同伙；组合</t>
+          <t>套餐；菜单；（电脑）菜单</t>
         </is>
       </c>
       <c r="E144" s="1" t="inlineStr">
@@ -5363,7 +5363,7 @@
       </c>
       <c r="B155" s="1" t="inlineStr">
         <is>
-          <t>[ɪndɐ] 印度河；印第安座〈n.m.〉</t>
+          <t>[ɪndɐ] 印度人〈n.m.〉</t>
         </is>
       </c>
       <c r="C155" s="1" t="inlineStr">
@@ -5373,7 +5373,7 @@
       </c>
       <c r="D155" s="1" t="inlineStr">
         <is>
-          <t>印度河；印第安座</t>
+          <t>印度人</t>
         </is>
       </c>
       <c r="E155" s="1" t="inlineStr">
@@ -5395,7 +5395,7 @@
       </c>
       <c r="B156" s="1" t="inlineStr">
         <is>
-          <t>[fɔʁtɔʏʃən] 锉；琢磨；锉屑；编档〈n.〉</t>
+          <t>[fɔʁtɔʏʃən] 假装；伪装；佯装〈n.〉</t>
         </is>
       </c>
       <c r="C156" s="1" t="inlineStr">
@@ -5405,7 +5405,7 @@
       </c>
       <c r="D156" s="1" t="inlineStr">
         <is>
-          <t>锉；琢磨；锉屑；编档</t>
+          <t>假装；伪装；佯装</t>
         </is>
       </c>
       <c r="E156" s="1" t="inlineStr">
@@ -5747,7 +5747,7 @@
       </c>
       <c r="B167" s="1" t="inlineStr">
         <is>
-          <t>[fɪtnəsstʊdɪɔ] 适合；合宜；合理〈n.〉</t>
+          <t>[fɪtnəsstʊdɪɔ] 健身房〈n.〉</t>
         </is>
       </c>
       <c r="C167" s="1" t="inlineStr">
@@ -5757,7 +5757,7 @@
       </c>
       <c r="D167" s="1" t="inlineStr">
         <is>
-          <t>适合；合宜；合理</t>
+          <t>健身房</t>
         </is>
       </c>
       <c r="E167" s="1" t="inlineStr">
@@ -6131,12 +6131,12 @@
       </c>
       <c r="B179" s="1" t="inlineStr">
         <is>
-          <t>[ankʏndɪɡʊnk] 注意；布告；通知〈n.f.〉</t>
+          <t>[aŋʏndɪɡʊŋ] 注意；布告；通知〈n.f.〉</t>
         </is>
       </c>
       <c r="C179" s="1" t="inlineStr">
         <is>
-          <t>ankʏndɪɡʊnk</t>
+          <t>aŋʏndɪɡʊŋ</t>
         </is>
       </c>
       <c r="D179" s="1" t="inlineStr">
@@ -6195,7 +6195,7 @@
       </c>
       <c r="B181" s="1" t="inlineStr">
         <is>
-          <t>[piːpɪ] 便士；小便〈n.〉</t>
+          <t>[piːpɪ] 小便；尿尿〈n.〉</t>
         </is>
       </c>
       <c r="C181" s="1" t="inlineStr">
@@ -6205,7 +6205,7 @@
       </c>
       <c r="D181" s="1" t="inlineStr">
         <is>
-          <t>便士；小便</t>
+          <t>小便；尿尿</t>
         </is>
       </c>
       <c r="E181" s="1" t="inlineStr">
@@ -6259,12 +6259,12 @@
       </c>
       <c r="B183" s="1" t="inlineStr">
         <is>
-          <t>[daʁstəlʊnk] 表示法；表现；陈述〈n.f.〉</t>
+          <t>[daʁstəlʊŋ] 表示法；表现；陈述〈n.f.〉</t>
         </is>
       </c>
       <c r="C183" s="1" t="inlineStr">
         <is>
-          <t>daʁstəlʊnk</t>
+          <t>daʁstəlʊŋ</t>
         </is>
       </c>
       <c r="D183" s="1" t="inlineStr">
@@ -6611,7 +6611,7 @@
       </c>
       <c r="B194" s="1" t="inlineStr">
         <is>
-          <t>[abʃlaɡən] 屑片；薄片；碎片；削〈v.〉</t>
+          <t>[abʃlaɡən] 敲落；砍下；拒绝〈v.〉</t>
         </is>
       </c>
       <c r="C194" s="1" t="inlineStr">
@@ -6621,7 +6621,7 @@
       </c>
       <c r="D194" s="1" t="inlineStr">
         <is>
-          <t>屑片；薄片；碎片；削</t>
+          <t>敲落；砍下；拒绝</t>
         </is>
       </c>
       <c r="E194" s="1" t="inlineStr">
@@ -6867,7 +6867,7 @@
       </c>
       <c r="B202" s="1" t="inlineStr">
         <is>
-          <t>[fɔʁɡɛnɡɐ] 前任；先辈；前身；初牙〈n.m.〉</t>
+          <t>[fɔʁɡɛnɡɐ] 前任；前辈；前身〈n.m.〉〈n.m.〉</t>
         </is>
       </c>
       <c r="C202" s="1" t="inlineStr">
@@ -6877,7 +6877,7 @@
       </c>
       <c r="D202" s="1" t="inlineStr">
         <is>
-          <t>前任；先辈；前身；初牙</t>
+          <t>前任；前辈；前身〈n.m.〉</t>
         </is>
       </c>
       <c r="E202" s="1" t="inlineStr">
@@ -6899,7 +6899,7 @@
       </c>
       <c r="B203" s="1" t="inlineStr">
         <is>
-          <t>[landstʁaɪçɐ] 窃贼；撬窃保险箱的盗贼；恶棍；罪犯〈n.m.〉</t>
+          <t>[landstʁaɪçɐ] 流浪汉；流浪者〈n.m.〉</t>
         </is>
       </c>
       <c r="C203" s="1" t="inlineStr">
@@ -6909,7 +6909,7 @@
       </c>
       <c r="D203" s="1" t="inlineStr">
         <is>
-          <t>窃贼；撬窃保险箱的盗贼；恶棍；罪犯</t>
+          <t>流浪汉；流浪者</t>
         </is>
       </c>
       <c r="E203" s="1" t="inlineStr">
@@ -6963,17 +6963,17 @@
       </c>
       <c r="B205" s="1" t="inlineStr">
         <is>
-          <t>[masɪfə] 沉重；巨大；大块〈n.〉</t>
+          <t>[masiːvə] 山体；山脉；大块岩石〈n.〉</t>
         </is>
       </c>
       <c r="C205" s="1" t="inlineStr">
         <is>
-          <t>masɪfə</t>
+          <t>masiːvə</t>
         </is>
       </c>
       <c r="D205" s="1" t="inlineStr">
         <is>
-          <t>沉重；巨大；大块</t>
+          <t>山体；山脉；大块岩石</t>
         </is>
       </c>
       <c r="E205" s="1" t="inlineStr">
@@ -7059,7 +7059,7 @@
       </c>
       <c r="B208" s="1" t="inlineStr">
         <is>
-          <t>[ʃɐ] 去；走；达到〈n.〉</t>
+          <t>[ʃɐ] 剪刀（Schere 的误拼）〈n.〉</t>
         </is>
       </c>
       <c r="C208" s="1" t="inlineStr">
@@ -7069,7 +7069,7 @@
       </c>
       <c r="D208" s="1" t="inlineStr">
         <is>
-          <t>去；走；达到</t>
+          <t>剪刀（Schere 的误拼）</t>
         </is>
       </c>
       <c r="E208" s="1" t="inlineStr">
@@ -7283,7 +7283,7 @@
       </c>
       <c r="B215" s="1" t="inlineStr">
         <is>
-          <t>[aʊfdʁɪnɡliːç] 似黄铜的〈adj.〉</t>
+          <t>[aʊfdʁɪnɡliːç] 强求的；纠缠不休的；唐突的〈adj.〉</t>
         </is>
       </c>
       <c r="C215" s="1" t="inlineStr">
@@ -7293,7 +7293,7 @@
       </c>
       <c r="D215" s="1" t="inlineStr">
         <is>
-          <t>似黄铜的</t>
+          <t>强求的；纠缠不休的；唐突的</t>
         </is>
       </c>
       <c r="E215" s="1" t="inlineStr">
@@ -7315,7 +7315,7 @@
       </c>
       <c r="B216" s="1" t="inlineStr">
         <is>
-          <t>[abstɔsənt] 放；摆；安置〈adv.〉</t>
+          <t>[abstɔsənt] 令人厌恶的；排斥的〈adv.〉</t>
         </is>
       </c>
       <c r="C216" s="1" t="inlineStr">
@@ -7325,7 +7325,7 @@
       </c>
       <c r="D216" s="1" t="inlineStr">
         <is>
-          <t>放；摆；安置</t>
+          <t>令人厌恶的；排斥的</t>
         </is>
       </c>
       <c r="E216" s="1" t="inlineStr">
@@ -7379,12 +7379,12 @@
       </c>
       <c r="B218" s="1" t="inlineStr">
         <is>
-          <t>[eːnəʁɡiːkvələ] 能源〈n.f.〉</t>
+          <t>[ɛnəʁɡiːkvɛlə] 能源〈n.f.〉</t>
         </is>
       </c>
       <c r="C218" s="1" t="inlineStr">
         <is>
-          <t>eːnəʁɡiːkvələ</t>
+          <t>ɛnəʁɡiːkvɛlə</t>
         </is>
       </c>
       <c r="D218" s="1" t="inlineStr">
@@ -7635,7 +7635,7 @@
       </c>
       <c r="B226" s="1" t="inlineStr">
         <is>
-          <t>[ʃpyːlə] 藏垢的场所；沟渠〈n.f.〉</t>
+          <t>[ʃpyːlə] 水槽；洗碗槽〈n.f.〉</t>
         </is>
       </c>
       <c r="C226" s="1" t="inlineStr">
@@ -7645,7 +7645,7 @@
       </c>
       <c r="D226" s="1" t="inlineStr">
         <is>
-          <t>藏垢的场所；沟渠</t>
+          <t>水槽；洗碗槽</t>
         </is>
       </c>
       <c r="E226" s="1" t="inlineStr">
@@ -7667,7 +7667,7 @@
       </c>
       <c r="B227" s="1" t="inlineStr">
         <is>
-          <t>[naksɪt͡sən] 阻止；监禁；拘留；隔离〈n.〉</t>
+          <t>[naksɪt͡sən] 留堂；课后留校〈n.〉</t>
         </is>
       </c>
       <c r="C227" s="1" t="inlineStr">
@@ -7677,7 +7677,7 @@
       </c>
       <c r="D227" s="1" t="inlineStr">
         <is>
-          <t>阻止；监禁；拘留；隔离</t>
+          <t>留堂；课后留校</t>
         </is>
       </c>
       <c r="E227" s="1" t="inlineStr">
@@ -7731,7 +7731,7 @@
       </c>
       <c r="B229" s="1" t="inlineStr">
         <is>
-          <t>[yːbəʁɡeːən] 等级；年级；阶段〈v.〉</t>
+          <t>[yːbəʁɡeːən] 过渡；转入；转向；忽视〈v.〉</t>
         </is>
       </c>
       <c r="C229" s="1" t="inlineStr">
@@ -7741,7 +7741,7 @@
       </c>
       <c r="D229" s="1" t="inlineStr">
         <is>
-          <t>等级；年级；阶段</t>
+          <t>过渡；转入；转向；忽视</t>
         </is>
       </c>
       <c r="E229" s="1" t="inlineStr">
@@ -8051,7 +8051,7 @@
       </c>
       <c r="B239" s="1" t="inlineStr">
         <is>
-          <t>[abfanɡən] 列；线；绳〈n.〉</t>
+          <t>[abfanɡən] 拦截；截获；缓冲〈n.〉</t>
         </is>
       </c>
       <c r="C239" s="1" t="inlineStr">
@@ -8061,7 +8061,7 @@
       </c>
       <c r="D239" s="1" t="inlineStr">
         <is>
-          <t>列；线；绳</t>
+          <t>拦截；截获；缓冲</t>
         </is>
       </c>
       <c r="E239" s="1" t="inlineStr">
@@ -8179,7 +8179,7 @@
       </c>
       <c r="B243" s="1" t="inlineStr">
         <is>
-          <t>[oːdʏsɔʏs] 也〈n.m.〉</t>
+          <t>[oːdʏsɔʏs] 奥德修斯〈n.m.〉</t>
         </is>
       </c>
       <c r="C243" s="1" t="inlineStr">
@@ -8189,7 +8189,7 @@
       </c>
       <c r="D243" s="1" t="inlineStr">
         <is>
-          <t>也</t>
+          <t>奥德修斯</t>
         </is>
       </c>
       <c r="E243" s="1" t="inlineStr">
@@ -8275,7 +8275,7 @@
       </c>
       <c r="B246" s="1" t="inlineStr">
         <is>
-          <t>[ɛʁlœzə] 保持；保有；留住〈n.〉</t>
+          <t>[ɛʁlœzə] 收入；收益；销售所得〈n.〉</t>
         </is>
       </c>
       <c r="C246" s="1" t="inlineStr">
@@ -8285,7 +8285,7 @@
       </c>
       <c r="D246" s="1" t="inlineStr">
         <is>
-          <t>保持；保有；留住</t>
+          <t>收入；收益；销售所得</t>
         </is>
       </c>
       <c r="E246" s="1" t="inlineStr">
@@ -8307,12 +8307,12 @@
       </c>
       <c r="B247" s="1" t="inlineStr">
         <is>
-          <t>[anlaɪtʊnk] 指令；教导；命令〈n.f.〉</t>
+          <t>[anlaɪtʊŋ] 指令；教导；命令〈n.f.〉</t>
         </is>
       </c>
       <c r="C247" s="1" t="inlineStr">
         <is>
-          <t>anlaɪtʊnk</t>
+          <t>anlaɪtʊŋ</t>
         </is>
       </c>
       <c r="D247" s="1" t="inlineStr">
@@ -8499,12 +8499,12 @@
       </c>
       <c r="B253" s="1" t="inlineStr">
         <is>
-          <t>[mʊstank] 野马；军官〈n.m.〉</t>
+          <t>[mʊstaŋ] 野马；军官〈n.m.〉</t>
         </is>
       </c>
       <c r="C253" s="1" t="inlineStr">
         <is>
-          <t>mʊstank</t>
+          <t>mʊstaŋ</t>
         </is>
       </c>
       <c r="D253" s="1" t="inlineStr">
@@ -8723,7 +8723,7 @@
       </c>
       <c r="B260" s="1" t="inlineStr">
         <is>
-          <t>[ɡeːbɛʁən] 熊；忍受；支承；产生〈v.〉</t>
+          <t>[ɡeːbɛʁən] 分娩；生育；生产〈v.〉</t>
         </is>
       </c>
       <c r="C260" s="1" t="inlineStr">
@@ -8733,7 +8733,7 @@
       </c>
       <c r="D260" s="1" t="inlineStr">
         <is>
-          <t>熊；忍受；支承；产生</t>
+          <t>分娩；生育；生产</t>
         </is>
       </c>
       <c r="E260" s="1" t="inlineStr">
@@ -8915,7 +8915,7 @@
       </c>
       <c r="B266" s="1" t="inlineStr">
         <is>
-          <t>[tɪkən] 滴答声；一瞬间；壁虱〈n.〉</t>
+          <t>[tɪkən] 条纹布料；〈口〉（某人的）怪癖、路数（动词 ticken：滴答作响）〈n.〉</t>
         </is>
       </c>
       <c r="C266" s="1" t="inlineStr">
@@ -8925,7 +8925,7 @@
       </c>
       <c r="D266" s="1" t="inlineStr">
         <is>
-          <t>滴答声；一瞬间；壁虱</t>
+          <t>条纹布料；〈口〉（某人的）怪癖、路数（动词 ticken：滴答作响）</t>
         </is>
       </c>
       <c r="E266" s="1" t="inlineStr">
@@ -9139,7 +9139,7 @@
       </c>
       <c r="B273" s="1" t="inlineStr">
         <is>
-          <t>[pɛtʁʊs] 逐渐消失；逐渐减少〈n.m.〉</t>
+          <t>[pɛtʁʊs] 彼得〈n.m.〉</t>
         </is>
       </c>
       <c r="C273" s="1" t="inlineStr">
@@ -9149,7 +9149,7 @@
       </c>
       <c r="D273" s="1" t="inlineStr">
         <is>
-          <t>逐渐消失；逐渐减少</t>
+          <t>彼得</t>
         </is>
       </c>
       <c r="E273" s="1" t="inlineStr">
@@ -9267,7 +9267,7 @@
       </c>
       <c r="B277" s="1" t="inlineStr">
         <is>
-          <t>[vɪt͡sɪɡə] 妙语；遁辞〈adv.〉</t>
+          <t>[vɪt͡sɪɡə] 诙谐的；风趣的〈adv.〉</t>
         </is>
       </c>
       <c r="C277" s="1" t="inlineStr">
@@ -9277,7 +9277,7 @@
       </c>
       <c r="D277" s="1" t="inlineStr">
         <is>
-          <t>妙语；遁辞</t>
+          <t>诙谐的；风趣的</t>
         </is>
       </c>
       <c r="E277" s="1" t="inlineStr">
@@ -9331,7 +9331,7 @@
       </c>
       <c r="B279" s="1" t="inlineStr">
         <is>
-          <t>[hɛftɪɡə] 憎恶；讨厌；臭名〈adv.〉</t>
+          <t>[hɛftɪɡə] 猛烈的；激烈的〈adj.〉〈adv.〉</t>
         </is>
       </c>
       <c r="C279" s="1" t="inlineStr">
@@ -9341,7 +9341,7 @@
       </c>
       <c r="D279" s="1" t="inlineStr">
         <is>
-          <t>憎恶；讨厌；臭名</t>
+          <t>猛烈的；激烈的〈adj.〉</t>
         </is>
       </c>
       <c r="E279" s="1" t="inlineStr">
@@ -9427,7 +9427,7 @@
       </c>
       <c r="B282" s="1" t="inlineStr">
         <is>
-          <t>[aʁtɪç] 善行；好处；利益；好的〈adj.〉</t>
+          <t>[aʁtɪç] 乖的；听话的；有礼貌的〈adj.〉</t>
         </is>
       </c>
       <c r="C282" s="1" t="inlineStr">
@@ -9437,7 +9437,7 @@
       </c>
       <c r="D282" s="1" t="inlineStr">
         <is>
-          <t>善行；好处；利益；好的</t>
+          <t>乖的；听话的；有礼貌的</t>
         </is>
       </c>
       <c r="E282" s="1" t="inlineStr">
@@ -9459,7 +9459,7 @@
       </c>
       <c r="B283" s="1" t="inlineStr">
         <is>
-          <t>[pʊblɪkɪtʏ] 大肆宣传；皮下注射〈n.〉</t>
+          <t>[pʊblɪkɪtʏ] 宣传；公众关注〈n.〉</t>
         </is>
       </c>
       <c r="C283" s="1" t="inlineStr">
@@ -9469,7 +9469,7 @@
       </c>
       <c r="D283" s="1" t="inlineStr">
         <is>
-          <t>大肆宣传；皮下注射</t>
+          <t>宣传；公众关注</t>
         </is>
       </c>
       <c r="E283" s="1" t="inlineStr">
@@ -9619,12 +9619,12 @@
       </c>
       <c r="B288" s="1" t="inlineStr">
         <is>
-          <t>[deːmʏtɪɡʊnk] 侮辱；侮辱的言行；无礼；有伤尊严〈n.f.〉</t>
+          <t>[deːmʏtɪɡʊŋ] 侮辱；侮辱的言行；无礼；有伤尊严〈n.f.〉</t>
         </is>
       </c>
       <c r="C288" s="1" t="inlineStr">
         <is>
-          <t>deːmʏtɪɡʊnk</t>
+          <t>deːmʏtɪɡʊŋ</t>
         </is>
       </c>
       <c r="D288" s="1" t="inlineStr">
@@ -9843,7 +9843,7 @@
       </c>
       <c r="B295" s="1" t="inlineStr">
         <is>
-          <t>[ʊnɡət͡siːfɐ] 熏制；熏烟〈n.〉</t>
+          <t>[ʊnɡət͡siːfɐ] 害虫；寄生虫〈n.〉</t>
         </is>
       </c>
       <c r="C295" s="1" t="inlineStr">
@@ -9853,7 +9853,7 @@
       </c>
       <c r="D295" s="1" t="inlineStr">
         <is>
-          <t>熏制；熏烟</t>
+          <t>害虫；寄生虫</t>
         </is>
       </c>
       <c r="E295" s="1" t="inlineStr">
@@ -9971,7 +9971,7 @@
       </c>
       <c r="B299" s="1" t="inlineStr">
         <is>
-          <t>[bʁɛnəndən] 使湿透；弄湿〈n.〉</t>
+          <t>[bʁɛnəndən] 燃烧；燃烧的（名词化形容词）〈n.〉</t>
         </is>
       </c>
       <c r="C299" s="1" t="inlineStr">
@@ -9981,7 +9981,7 @@
       </c>
       <c r="D299" s="1" t="inlineStr">
         <is>
-          <t>使湿透；弄湿</t>
+          <t>燃烧；燃烧的（名词化形容词）</t>
         </is>
       </c>
       <c r="E299" s="1" t="inlineStr">
@@ -10067,7 +10067,7 @@
       </c>
       <c r="B302" s="1" t="inlineStr">
         <is>
-          <t>[beːtɔnən] 给文章加标点；加强〈v.〉</t>
+          <t>[beːtɔnən] 强调；着重〈v.〉</t>
         </is>
       </c>
       <c r="C302" s="1" t="inlineStr">
@@ -10077,7 +10077,7 @@
       </c>
       <c r="D302" s="1" t="inlineStr">
         <is>
-          <t>给文章加标点；加强</t>
+          <t>强调；着重</t>
         </is>
       </c>
       <c r="E302" s="1" t="inlineStr">
@@ -10259,7 +10259,7 @@
       </c>
       <c r="B308" s="1" t="inlineStr">
         <is>
-          <t>[fɛʁvøːnən] 款待；佳肴〈v.〉</t>
+          <t>[fɛʁvøːnən] 娇惯；宠坏〈v.〉</t>
         </is>
       </c>
       <c r="C308" s="1" t="inlineStr">
@@ -10269,7 +10269,7 @@
       </c>
       <c r="D308" s="1" t="inlineStr">
         <is>
-          <t>款待；佳肴</t>
+          <t>娇惯；宠坏</t>
         </is>
       </c>
       <c r="E308" s="1" t="inlineStr">
@@ -10451,7 +10451,7 @@
       </c>
       <c r="B314" s="1" t="inlineStr">
         <is>
-          <t>[fɛʁzət͡sʊnk] 退休；隐居；撤退〈n.f.〉</t>
+          <t>[fɛʁzət͡sʊnk] 调职；调动；位移〈n.f.〉</t>
         </is>
       </c>
       <c r="C314" s="1" t="inlineStr">
@@ -10461,7 +10461,7 @@
       </c>
       <c r="D314" s="1" t="inlineStr">
         <is>
-          <t>退休；隐居；撤退</t>
+          <t>调职；调动；位移</t>
         </is>
       </c>
       <c r="E314" s="1" t="inlineStr">
@@ -10515,7 +10515,7 @@
       </c>
       <c r="B316" s="1" t="inlineStr">
         <is>
-          <t>[jaːʁmaʁkt] 展览会；市集〈n.m.〉</t>
+          <t>[jaːʁmaʁkt] （有游乐表演的）年市；庙会；游乐集市〈n.m.〉〈n.m.〉</t>
         </is>
       </c>
       <c r="C316" s="1" t="inlineStr">
@@ -10525,7 +10525,7 @@
       </c>
       <c r="D316" s="1" t="inlineStr">
         <is>
-          <t>展览会；市集</t>
+          <t>（有游乐表演的）年市；庙会；游乐集市〈n.m.〉</t>
         </is>
       </c>
       <c r="E316" s="1" t="inlineStr">
@@ -10579,7 +10579,7 @@
       </c>
       <c r="B318" s="1" t="inlineStr">
         <is>
-          <t>[knalɐ] 少量；马嚼子〈n.m.〉</t>
+          <t>[knalɐ] 爆竹；巨响；轰动的事物〈n.m.〉</t>
         </is>
       </c>
       <c r="C318" s="1" t="inlineStr">
@@ -10589,7 +10589,7 @@
       </c>
       <c r="D318" s="1" t="inlineStr">
         <is>
-          <t>少量；马嚼子</t>
+          <t>爆竹；巨响；轰动的事物</t>
         </is>
       </c>
       <c r="E318" s="1" t="inlineStr">
@@ -10643,17 +10643,17 @@
       </c>
       <c r="B320" s="1" t="inlineStr">
         <is>
-          <t>[ʁeːzəʁfiːʁən] 储备品；贮量；后备军〈v.〉</t>
+          <t>[ʁezɛʁviːʁən] 预订；保留〈v.〉</t>
         </is>
       </c>
       <c r="C320" s="1" t="inlineStr">
         <is>
-          <t>ʁeːzəʁfiːʁən</t>
+          <t>ʁezɛʁviːʁən</t>
         </is>
       </c>
       <c r="D320" s="1" t="inlineStr">
         <is>
-          <t>储备品；贮量；后备军</t>
+          <t>预订；保留</t>
         </is>
       </c>
       <c r="E320" s="1" t="inlineStr">
@@ -10707,7 +10707,7 @@
       </c>
       <c r="B322" s="1" t="inlineStr">
         <is>
-          <t>[ʃtɛndɪɡə] 钥匙；键；解答〈adv.〉</t>
+          <t>[ʃtɛndɪɡə] 持续的；不断的；经常的〈adv.〉</t>
         </is>
       </c>
       <c r="C322" s="1" t="inlineStr">
@@ -10717,7 +10717,7 @@
       </c>
       <c r="D322" s="1" t="inlineStr">
         <is>
-          <t>钥匙；键；解答</t>
+          <t>持续的；不断的；经常的</t>
         </is>
       </c>
       <c r="E322" s="1" t="inlineStr">
@@ -10771,7 +10771,7 @@
       </c>
       <c r="B324" s="1" t="inlineStr">
         <is>
-          <t>[ʃpaːʁə] 浪费；废物；损耗〈n.〉</t>
+          <t>[ʃpaːʁə] 储蓄；节省〈v.〉（原形 sparen）〈n.〉</t>
         </is>
       </c>
       <c r="C324" s="1" t="inlineStr">
@@ -10781,7 +10781,7 @@
       </c>
       <c r="D324" s="1" t="inlineStr">
         <is>
-          <t>浪费；废物；损耗</t>
+          <t>储蓄；节省〈v.〉（原形 sparen）</t>
         </is>
       </c>
       <c r="E324" s="1" t="inlineStr">
@@ -10835,7 +10835,7 @@
       </c>
       <c r="B326" s="1" t="inlineStr">
         <is>
-          <t>[baːdəmantəl] 沐浴；浴室；浴〈n.m.〉</t>
+          <t>[baːdəmantəl] 浴袍；浴衣〈n.m.〉</t>
         </is>
       </c>
       <c r="C326" s="1" t="inlineStr">
@@ -10845,7 +10845,7 @@
       </c>
       <c r="D326" s="1" t="inlineStr">
         <is>
-          <t>沐浴；浴室；浴</t>
+          <t>浴袍；浴衣</t>
         </is>
       </c>
       <c r="E326" s="1" t="inlineStr">
@@ -10867,7 +10867,7 @@
       </c>
       <c r="B327" s="1" t="inlineStr">
         <is>
-          <t>[tʁʊp] 特鲁普〈n.m.〉</t>
+          <t>[tʁʊp] 小队；班组；一群〈n.m.〉</t>
         </is>
       </c>
       <c r="C327" s="1" t="inlineStr">
@@ -10877,7 +10877,7 @@
       </c>
       <c r="D327" s="1" t="inlineStr">
         <is>
-          <t>特鲁普</t>
+          <t>小队；班组；一群</t>
         </is>
       </c>
       <c r="E327" s="1" t="inlineStr">
@@ -10931,7 +10931,7 @@
       </c>
       <c r="B329" s="1" t="inlineStr">
         <is>
-          <t>[hɔxt͡saɪtsɡəʃənk] 婚礼；结婚；结婚周年纪念日〈n.〉</t>
+          <t>[hɔxt͡saɪtsɡəʃənk] 结婚礼物〈n.〉</t>
         </is>
       </c>
       <c r="C329" s="1" t="inlineStr">
@@ -10941,7 +10941,7 @@
       </c>
       <c r="D329" s="1" t="inlineStr">
         <is>
-          <t>婚礼；结婚；结婚周年纪念日</t>
+          <t>结婚礼物</t>
         </is>
       </c>
       <c r="E329" s="1" t="inlineStr">
@@ -11059,7 +11059,7 @@
       </c>
       <c r="B333" s="1" t="inlineStr">
         <is>
-          <t>[aɪntɔpf] 炖；烦恼；热浴〈n.m.〉</t>
+          <t>[aɪntɔpf] 一锅炖菜；什锦炖菜〈n.m.〉</t>
         </is>
       </c>
       <c r="C333" s="1" t="inlineStr">
@@ -11069,7 +11069,7 @@
       </c>
       <c r="D333" s="1" t="inlineStr">
         <is>
-          <t>炖；烦恼；热浴</t>
+          <t>一锅炖菜；什锦炖菜</t>
         </is>
       </c>
       <c r="E333" s="1" t="inlineStr">
@@ -11091,7 +11091,7 @@
       </c>
       <c r="B334" s="1" t="inlineStr">
         <is>
-          <t>[pɪkəl] 碎冰锥〈n.m.〉</t>
+          <t>[pɪkəl] 粉刺；丘疹；镐〈n.m.〉</t>
         </is>
       </c>
       <c r="C334" s="1" t="inlineStr">
@@ -11101,7 +11101,7 @@
       </c>
       <c r="D334" s="1" t="inlineStr">
         <is>
-          <t>碎冰锥</t>
+          <t>粉刺；丘疹；镐</t>
         </is>
       </c>
       <c r="E334" s="1" t="inlineStr">
@@ -11155,7 +11155,7 @@
       </c>
       <c r="B336" s="1" t="inlineStr">
         <is>
-          <t>[beːnənən] 名字；名称；姓名〈v.〉</t>
+          <t>[beːnənən] 命名；取名；指定〈v.〉</t>
         </is>
       </c>
       <c r="C336" s="1" t="inlineStr">
@@ -11165,7 +11165,7 @@
       </c>
       <c r="D336" s="1" t="inlineStr">
         <is>
-          <t>名字；名称；姓名</t>
+          <t>命名；取名；指定</t>
         </is>
       </c>
       <c r="E336" s="1" t="inlineStr">
@@ -11219,7 +11219,7 @@
       </c>
       <c r="B338" s="1" t="inlineStr">
         <is>
-          <t>[anfyːʁən] 矛尖；先锋队〈v.〉</t>
+          <t>[anfyːʁən] 领导；率领；引用〈v.〉</t>
         </is>
       </c>
       <c r="C338" s="1" t="inlineStr">
@@ -11229,7 +11229,7 @@
       </c>
       <c r="D338" s="1" t="inlineStr">
         <is>
-          <t>矛尖；先锋队</t>
+          <t>领导；率领；引用</t>
         </is>
       </c>
       <c r="E338" s="1" t="inlineStr">
@@ -11315,7 +11315,7 @@
       </c>
       <c r="B341" s="1" t="inlineStr">
         <is>
-          <t>[bɛkɐ] 面包师；烤箱〈n.m.〉</t>
+          <t>[bɛkɐ] 面包师；面包店老板〈n.m.〉</t>
         </is>
       </c>
       <c r="C341" s="1" t="inlineStr">
@@ -11325,7 +11325,7 @@
       </c>
       <c r="D341" s="1" t="inlineStr">
         <is>
-          <t>面包师；烤箱</t>
+          <t>面包师；面包店老板</t>
         </is>
       </c>
       <c r="E341" s="1" t="inlineStr">
@@ -11347,7 +11347,7 @@
       </c>
       <c r="B342" s="1" t="inlineStr">
         <is>
-          <t>[fœlɪɡɐ] 缺氧症；缺氧〈adv.〉</t>
+          <t>[fœlɪɡɐ] 更完全的；更彻底的〈adv.〉</t>
         </is>
       </c>
       <c r="C342" s="1" t="inlineStr">
@@ -11357,7 +11357,7 @@
       </c>
       <c r="D342" s="1" t="inlineStr">
         <is>
-          <t>缺氧症；缺氧</t>
+          <t>更完全的；更彻底的</t>
         </is>
       </c>
       <c r="E342" s="1" t="inlineStr">
@@ -11379,12 +11379,12 @@
       </c>
       <c r="B343" s="1" t="inlineStr">
         <is>
-          <t>[pɛʁfəʁzə] 使堕落；使反常；歪曲〈n.〉</t>
+          <t>[pɛʁvɛʁzə] 使堕落；使反常；歪曲〈n.〉</t>
         </is>
       </c>
       <c r="C343" s="1" t="inlineStr">
         <is>
-          <t>pɛʁfəʁzə</t>
+          <t>pɛʁvɛʁzə</t>
         </is>
       </c>
       <c r="D343" s="1" t="inlineStr">
@@ -11507,7 +11507,7 @@
       </c>
       <c r="B347" s="1" t="inlineStr">
         <is>
-          <t>[fɔʁbəstʁaft] 先；先前；以前〈adj.〉</t>
+          <t>[fɔʁbəstʁaft] 有前科的；曾被判刑的〈adj.〉</t>
         </is>
       </c>
       <c r="C347" s="1" t="inlineStr">
@@ -11517,7 +11517,7 @@
       </c>
       <c r="D347" s="1" t="inlineStr">
         <is>
-          <t>先；先前；以前</t>
+          <t>有前科的；曾被判刑的</t>
         </is>
       </c>
       <c r="E347" s="1" t="inlineStr">
@@ -11571,7 +11571,7 @@
       </c>
       <c r="B349" s="1" t="inlineStr">
         <is>
-          <t>[beːbən] 发颤音〈n.〉</t>
+          <t>[beːbən] 地震；颤动〈n.〉</t>
         </is>
       </c>
       <c r="C349" s="1" t="inlineStr">
@@ -11581,7 +11581,7 @@
       </c>
       <c r="D349" s="1" t="inlineStr">
         <is>
-          <t>发颤音</t>
+          <t>地震；颤动</t>
         </is>
       </c>
       <c r="E349" s="1" t="inlineStr">
@@ -11603,7 +11603,7 @@
       </c>
       <c r="B350" s="1" t="inlineStr">
         <is>
-          <t>[kaːnɪstɐ] 装罐；罐头；容器；能；可以；作废字符〈n.m.〉</t>
+          <t>[kaːnɪstɐ] 罐；桶；油桶〈n.m.〉</t>
         </is>
       </c>
       <c r="C350" s="1" t="inlineStr">
@@ -11613,7 +11613,7 @@
       </c>
       <c r="D350" s="1" t="inlineStr">
         <is>
-          <t>装罐；罐头；容器；能；可以；作废字符</t>
+          <t>罐；桶；油桶</t>
         </is>
       </c>
       <c r="E350" s="1" t="inlineStr">
@@ -11891,7 +11891,7 @@
       </c>
       <c r="B359" s="1" t="inlineStr">
         <is>
-          <t>[tɔastɐ] 烤面包器；烤面包炉；祝酒人〈n.m.〉</t>
+          <t>[tɔastɐ] 烤面包器；烤面包炉〈n.m.〉〈n.m.〉</t>
         </is>
       </c>
       <c r="C359" s="1" t="inlineStr">
@@ -11901,7 +11901,7 @@
       </c>
       <c r="D359" s="1" t="inlineStr">
         <is>
-          <t>烤面包器；烤面包炉；祝酒人</t>
+          <t>烤面包器；烤面包炉〈n.m.〉</t>
         </is>
       </c>
       <c r="E359" s="1" t="inlineStr">
@@ -11955,12 +11955,12 @@
       </c>
       <c r="B361" s="1" t="inlineStr">
         <is>
-          <t>[bʁandstɪftʊnk] 纵火；纵火罪；放火〈n.f.〉</t>
+          <t>[bʁandstɪftʊŋ] 纵火；纵火罪；放火〈n.f.〉</t>
         </is>
       </c>
       <c r="C361" s="1" t="inlineStr">
         <is>
-          <t>bʁandstɪftʊnk</t>
+          <t>bʁandstɪftʊŋ</t>
         </is>
       </c>
       <c r="D361" s="1" t="inlineStr">
@@ -11987,7 +11987,7 @@
       </c>
       <c r="B362" s="1" t="inlineStr">
         <is>
-          <t>[ʁeːfəʁənt͡sən] 信任状；国书；文件〈n.〉</t>
+          <t>[ʁeːfəʁənt͡sən] 推荐信；证明书；参考〈n.〉</t>
         </is>
       </c>
       <c r="C362" s="1" t="inlineStr">
@@ -11997,7 +11997,7 @@
       </c>
       <c r="D362" s="1" t="inlineStr">
         <is>
-          <t>信任状；国书；文件</t>
+          <t>推荐信；证明书；参考</t>
         </is>
       </c>
       <c r="E362" s="1" t="inlineStr">
@@ -12147,7 +12147,7 @@
       </c>
       <c r="B367" s="1" t="inlineStr">
         <is>
-          <t>[ʃtaːtlɪçə] 酒鬼〈n.〉</t>
+          <t>[ʃtaːtlɪçə] 国立的；国家的；州立的〈n.〉</t>
         </is>
       </c>
       <c r="C367" s="1" t="inlineStr">
@@ -12157,7 +12157,7 @@
       </c>
       <c r="D367" s="1" t="inlineStr">
         <is>
-          <t>酒鬼</t>
+          <t>国立的；国家的；州立的</t>
         </is>
       </c>
       <c r="E367" s="1" t="inlineStr">
@@ -12307,7 +12307,7 @@
       </c>
       <c r="B372" s="1" t="inlineStr">
         <is>
-          <t>[fɛʁʃlɪnɡən] 咯咯叫〈v.〉</t>
+          <t>[fɛʁʃlɪnɡən] 吞食；狼吞虎咽〈v.〉</t>
         </is>
       </c>
       <c r="C372" s="1" t="inlineStr">
@@ -12317,7 +12317,7 @@
       </c>
       <c r="D372" s="1" t="inlineStr">
         <is>
-          <t>咯咯叫</t>
+          <t>吞食；狼吞虎咽</t>
         </is>
       </c>
       <c r="E372" s="1" t="inlineStr">
@@ -12467,7 +12467,7 @@
       </c>
       <c r="B377" s="1" t="inlineStr">
         <is>
-          <t>[kɔntʁɔlʁaʊm] 控制；管理；克制〈n.m.〉</t>
+          <t>[kɔntʁɔlʁaʊm] 控制室〈n.m.〉</t>
         </is>
       </c>
       <c r="C377" s="1" t="inlineStr">
@@ -12477,7 +12477,7 @@
       </c>
       <c r="D377" s="1" t="inlineStr">
         <is>
-          <t>控制；管理；克制</t>
+          <t>控制室</t>
         </is>
       </c>
       <c r="E377" s="1" t="inlineStr">
@@ -12755,7 +12755,7 @@
       </c>
       <c r="B386" s="1" t="inlineStr">
         <is>
-          <t>[mʊfiːn] 松饼〈n.〉</t>
+          <t>[mʊfiːn] 松饼〈n.m.〉〈n.〉</t>
         </is>
       </c>
       <c r="C386" s="1" t="inlineStr">
@@ -12765,7 +12765,7 @@
       </c>
       <c r="D386" s="1" t="inlineStr">
         <is>
-          <t>松饼</t>
+          <t>松饼〈n.m.〉</t>
         </is>
       </c>
       <c r="E386" s="1" t="inlineStr">
@@ -12851,7 +12851,7 @@
       </c>
       <c r="B389" s="1" t="inlineStr">
         <is>
-          <t>[ʃtʁeːbɐ] 苦读；辛苦工作〈n.m.〉</t>
+          <t>[ʃtʁeːbɐ] 书呆子；死用功的人〈n.m.〉</t>
         </is>
       </c>
       <c r="C389" s="1" t="inlineStr">
@@ -12861,7 +12861,7 @@
       </c>
       <c r="D389" s="1" t="inlineStr">
         <is>
-          <t>苦读；辛苦工作</t>
+          <t>书呆子；死用功的人</t>
         </is>
       </c>
       <c r="E389" s="1" t="inlineStr">
@@ -12883,7 +12883,7 @@
       </c>
       <c r="B390" s="1" t="inlineStr">
         <is>
-          <t>[ʃnʏfəln] 吸食强力胶的习惯〈n.〉</t>
+          <t>[ʃnʏfəln] 嗅；窥探；打探〈v.〉〈n.〉</t>
         </is>
       </c>
       <c r="C390" s="1" t="inlineStr">
@@ -12893,7 +12893,7 @@
       </c>
       <c r="D390" s="1" t="inlineStr">
         <is>
-          <t>吸食强力胶的习惯</t>
+          <t>嗅；窥探；打探〈v.〉</t>
         </is>
       </c>
       <c r="E390" s="1" t="inlineStr">
@@ -12915,7 +12915,7 @@
       </c>
       <c r="B391" s="1" t="inlineStr">
         <is>
-          <t>[vɪnkən] 波；波浪；波动〈v.〉</t>
+          <t>[vɪnkən] 挥手；招手〈v.〉</t>
         </is>
       </c>
       <c r="C391" s="1" t="inlineStr">
@@ -12925,7 +12925,7 @@
       </c>
       <c r="D391" s="1" t="inlineStr">
         <is>
-          <t>波；波浪；波动</t>
+          <t>挥手；招手</t>
         </is>
       </c>
       <c r="E391" s="1" t="inlineStr">
@@ -12947,7 +12947,7 @@
       </c>
       <c r="B392" s="1" t="inlineStr">
         <is>
-          <t>[ɛʁmʊtɪɡt] 兴高采烈地〈adv.〉</t>
+          <t>[ɛʁmʊtɪɡt] 鼓励；鼓舞；受鼓舞的〈adv.〉</t>
         </is>
       </c>
       <c r="C392" s="1" t="inlineStr">
@@ -12957,7 +12957,7 @@
       </c>
       <c r="D392" s="1" t="inlineStr">
         <is>
-          <t>兴高采烈地</t>
+          <t>鼓励；鼓舞；受鼓舞的</t>
         </is>
       </c>
       <c r="E392" s="1" t="inlineStr">
@@ -13043,7 +13043,7 @@
       </c>
       <c r="B395" s="1" t="inlineStr">
         <is>
-          <t>[t͡svɪt͡ʃɐn] 啁啾〈n.〉</t>
+          <t>[t͡svɪt͡ʃɐn] （鸟）啁啾，鸣叫〈v.〉〈n.〉</t>
         </is>
       </c>
       <c r="C395" s="1" t="inlineStr">
@@ -13053,7 +13053,7 @@
       </c>
       <c r="D395" s="1" t="inlineStr">
         <is>
-          <t>啁啾</t>
+          <t>（鸟）啁啾，鸣叫〈v.〉</t>
         </is>
       </c>
       <c r="E395" s="1" t="inlineStr">
@@ -13267,7 +13267,7 @@
       </c>
       <c r="B402" s="1" t="inlineStr">
         <is>
-          <t>[vakəln] 摆动；摇晃；不稳定〈n.〉</t>
+          <t>[vakəln] 摆动；摇晃〈v.〉〈n.〉</t>
         </is>
       </c>
       <c r="C402" s="1" t="inlineStr">
@@ -13277,7 +13277,7 @@
       </c>
       <c r="D402" s="1" t="inlineStr">
         <is>
-          <t>摆动；摇晃；不稳定</t>
+          <t>摆动；摇晃〈v.〉</t>
         </is>
       </c>
       <c r="E402" s="1" t="inlineStr">
@@ -13491,7 +13491,7 @@
       </c>
       <c r="B409" s="1" t="inlineStr">
         <is>
-          <t>[voːʁaʊs] 的；属于〈adv.〉</t>
+          <t>[voːʁaʊs] 从什么中；由什么〈adv.〉</t>
         </is>
       </c>
       <c r="C409" s="1" t="inlineStr">
@@ -13501,7 +13501,7 @@
       </c>
       <c r="D409" s="1" t="inlineStr">
         <is>
-          <t>的；属于</t>
+          <t>从什么中；由什么</t>
         </is>
       </c>
       <c r="E409" s="1" t="inlineStr">
@@ -13715,7 +13715,7 @@
       </c>
       <c r="B416" s="1" t="inlineStr">
         <is>
-          <t>[ɡɛʃɛftlɪçə] 生意；事情；业务〈adv.〉</t>
+          <t>[ɡɛʃɛftlɪçə] 商业的；业务的；公务的〈adv.〉</t>
         </is>
       </c>
       <c r="C416" s="1" t="inlineStr">
@@ -13725,7 +13725,7 @@
       </c>
       <c r="D416" s="1" t="inlineStr">
         <is>
-          <t>生意；事情；业务</t>
+          <t>商业的；业务的；公务的</t>
         </is>
       </c>
       <c r="E416" s="1" t="inlineStr">
@@ -13779,7 +13779,7 @@
       </c>
       <c r="B418" s="1" t="inlineStr">
         <is>
-          <t>[fɛstləɡən] 琢石；擦伤〈n.〉</t>
+          <t>[fɛstləɡən] 确定；规定；固定〈n.〉</t>
         </is>
       </c>
       <c r="C418" s="1" t="inlineStr">
@@ -13789,7 +13789,7 @@
       </c>
       <c r="D418" s="1" t="inlineStr">
         <is>
-          <t>琢石；擦伤</t>
+          <t>确定；规定；固定</t>
         </is>
       </c>
       <c r="E418" s="1" t="inlineStr">
@@ -13875,7 +13875,7 @@
       </c>
       <c r="B421" s="1" t="inlineStr">
         <is>
-          <t>[peːɡazʊs] 诗兴；诗才〈n.m.〉</t>
+          <t>[peːɡazʊs] 飞马；飞马座〈n.m.〉</t>
         </is>
       </c>
       <c r="C421" s="1" t="inlineStr">
@@ -13885,7 +13885,7 @@
       </c>
       <c r="D421" s="1" t="inlineStr">
         <is>
-          <t>诗兴；诗才</t>
+          <t>飞马；飞马座</t>
         </is>
       </c>
       <c r="E421" s="1" t="inlineStr">
@@ -13907,7 +13907,7 @@
       </c>
       <c r="B422" s="1" t="inlineStr">
         <is>
-          <t>[pɔʁt] 港口；埠；舱门〈n.〉</t>
+          <t>[pɔʁt] （计算机）端口；接口〈n.m.〉（“港口”应为 Hafen）〈n.〉</t>
         </is>
       </c>
       <c r="C422" s="1" t="inlineStr">
@@ -13917,7 +13917,7 @@
       </c>
       <c r="D422" s="1" t="inlineStr">
         <is>
-          <t>港口；埠；舱门</t>
+          <t>（计算机）端口；接口〈n.m.〉（“港口”应为 Hafen）</t>
         </is>
       </c>
       <c r="E422" s="1" t="inlineStr">
@@ -13971,7 +13971,7 @@
       </c>
       <c r="B424" s="1" t="inlineStr">
         <is>
-          <t>[mɛksɪkanɪʃə] 玉米粉蒸肉〈adv.〉</t>
+          <t>[mɛksɪkanɪʃə] 墨西哥的〈adv.〉</t>
         </is>
       </c>
       <c r="C424" s="1" t="inlineStr">
@@ -13981,7 +13981,7 @@
       </c>
       <c r="D424" s="1" t="inlineStr">
         <is>
-          <t>玉米粉蒸肉</t>
+          <t>墨西哥的</t>
         </is>
       </c>
       <c r="E424" s="1" t="inlineStr">
@@ -14163,7 +14163,7 @@
       </c>
       <c r="B430" s="1" t="inlineStr">
         <is>
-          <t>[alɡəmaɪnə] 趋势；倾向；走向〈adv.〉</t>
+          <t>[alɡəmaɪnə] 一般的；普遍的；总的〈adv.〉</t>
         </is>
       </c>
       <c r="C430" s="1" t="inlineStr">
@@ -14173,7 +14173,7 @@
       </c>
       <c r="D430" s="1" t="inlineStr">
         <is>
-          <t>趋势；倾向；走向</t>
+          <t>一般的；普遍的；总的</t>
         </is>
       </c>
       <c r="E430" s="1" t="inlineStr">
@@ -14355,7 +14355,7 @@
       </c>
       <c r="B436" s="1" t="inlineStr">
         <is>
-          <t>[puːɐ] 直线；直；直的；笔直的〈adv.〉</t>
+          <t>[puːɐ] 纯的；纯粹的〈adv.〉</t>
         </is>
       </c>
       <c r="C436" s="1" t="inlineStr">
@@ -14365,7 +14365,7 @@
       </c>
       <c r="D436" s="1" t="inlineStr">
         <is>
-          <t>直线；直；直的；笔直的</t>
+          <t>纯的；纯粹的</t>
         </is>
       </c>
       <c r="E436" s="1" t="inlineStr">
@@ -14451,7 +14451,7 @@
       </c>
       <c r="B439" s="1" t="inlineStr">
         <is>
-          <t>[ʊndɔʏtliːç] 连音符；诽谤；玷污〈adj.〉</t>
+          <t>[ʊndɔʏtliːç] 不清楚的；模糊的〈adj.〉</t>
         </is>
       </c>
       <c r="C439" s="1" t="inlineStr">
@@ -14461,7 +14461,7 @@
       </c>
       <c r="D439" s="1" t="inlineStr">
         <is>
-          <t>连音符；诽谤；玷污</t>
+          <t>不清楚的；模糊的</t>
         </is>
       </c>
       <c r="E439" s="1" t="inlineStr">
@@ -14515,7 +14515,7 @@
       </c>
       <c r="B441" s="1" t="inlineStr">
         <is>
-          <t>[ʃtɛlfəʁtʁətəndɐ] 交替的；轮流的；间隔的；轮流〈adv.〉</t>
+          <t>[ʃtɛlfəʁtʁətəndɐ] 代理的；副的；代表的〈adv.〉</t>
         </is>
       </c>
       <c r="C441" s="1" t="inlineStr">
@@ -14525,7 +14525,7 @@
       </c>
       <c r="D441" s="1" t="inlineStr">
         <is>
-          <t>交替的；轮流的；间隔的；轮流</t>
+          <t>代理的；副的；代表的</t>
         </is>
       </c>
       <c r="E441" s="1" t="inlineStr">
@@ -14547,7 +14547,7 @@
       </c>
       <c r="B442" s="1" t="inlineStr">
         <is>
-          <t>[tɛnəseː] 田纳西州〈n.m.〉</t>
+          <t>[tɛnəseː] 田纳西州〈专名，通常无冠词〉〈n.m.〉</t>
         </is>
       </c>
       <c r="C442" s="1" t="inlineStr">
@@ -14557,7 +14557,7 @@
       </c>
       <c r="D442" s="1" t="inlineStr">
         <is>
-          <t>田纳西州</t>
+          <t>田纳西州〈专名，通常无冠词〉</t>
         </is>
       </c>
       <c r="E442" s="1" t="inlineStr">
@@ -14771,7 +14771,7 @@
       </c>
       <c r="B449" s="1" t="inlineStr">
         <is>
-          <t>[tʏçtɪç] 勇敢的；美好的〈adj.〉</t>
+          <t>[tʏçtɪç] 能干的；勤勉的；熟练的〈adj.〉</t>
         </is>
       </c>
       <c r="C449" s="1" t="inlineStr">
@@ -14781,7 +14781,7 @@
       </c>
       <c r="D449" s="1" t="inlineStr">
         <is>
-          <t>勇敢的；美好的</t>
+          <t>能干的；勤勉的；熟练的</t>
         </is>
       </c>
       <c r="E449" s="1" t="inlineStr">
@@ -14803,7 +14803,7 @@
       </c>
       <c r="B450" s="1" t="inlineStr">
         <is>
-          <t>[fɔʁɡank] 活动；行动；活跃〈n.m.〉</t>
+          <t>[fɔʁɡank] 过程；事件；事项〈m.〉〈n.m.〉</t>
         </is>
       </c>
       <c r="C450" s="1" t="inlineStr">
@@ -14813,7 +14813,7 @@
       </c>
       <c r="D450" s="1" t="inlineStr">
         <is>
-          <t>活动；行动；活跃</t>
+          <t>过程；事件；事项〈m.〉</t>
         </is>
       </c>
       <c r="E450" s="1" t="inlineStr">
@@ -14899,7 +14899,7 @@
       </c>
       <c r="B453" s="1" t="inlineStr">
         <is>
-          <t>[ɡeːʁɪnɡɐ] 狭窄部分；隘路；狭窄的；仔细的〈adv.〉</t>
+          <t>[ɡeːʁɪnɡɐ] 较小的；较少的；次要的〈adv.〉</t>
         </is>
       </c>
       <c r="C453" s="1" t="inlineStr">
@@ -14909,7 +14909,7 @@
       </c>
       <c r="D453" s="1" t="inlineStr">
         <is>
-          <t>狭窄部分；隘路；狭窄的；仔细的</t>
+          <t>较小的；较少的；次要的</t>
         </is>
       </c>
       <c r="E453" s="1" t="inlineStr">
@@ -15251,7 +15251,7 @@
       </c>
       <c r="B464" s="1" t="inlineStr">
         <is>
-          <t>[blyːtən] &lt;口&gt;衣服；旧衣；服饰〈n.〉</t>
+          <t>[blyːtən] 花；花朵〈n.〉</t>
         </is>
       </c>
       <c r="C464" s="1" t="inlineStr">
@@ -15261,7 +15261,7 @@
       </c>
       <c r="D464" s="1" t="inlineStr">
         <is>
-          <t>&lt;口&gt;衣服；旧衣；服饰</t>
+          <t>花；花朵</t>
         </is>
       </c>
       <c r="E464" s="1" t="inlineStr">
@@ -15315,7 +15315,7 @@
       </c>
       <c r="B466" s="1" t="inlineStr">
         <is>
-          <t>[ʃʊsvʊndə] 枪弹；射击；炮击〈n.f.〉</t>
+          <t>[ʃʊsvʊndə] 枪伤；枪弹伤〈n.f.〉</t>
         </is>
       </c>
       <c r="C466" s="1" t="inlineStr">
@@ -15325,7 +15325,7 @@
       </c>
       <c r="D466" s="1" t="inlineStr">
         <is>
-          <t>枪弹；射击；炮击</t>
+          <t>枪伤；枪弹伤</t>
         </is>
       </c>
       <c r="E466" s="1" t="inlineStr">
@@ -15347,7 +15347,7 @@
       </c>
       <c r="B467" s="1" t="inlineStr">
         <is>
-          <t>[aʊsfaːʁt] 出口；退场；离去〈n.f.〉</t>
+          <t>[aʊsfaːʁt] （车行）出口；驶出；驾车出游〈n.f.〉〈n.f.〉</t>
         </is>
       </c>
       <c r="C467" s="1" t="inlineStr">
@@ -15357,7 +15357,7 @@
       </c>
       <c r="D467" s="1" t="inlineStr">
         <is>
-          <t>出口；退场；离去</t>
+          <t>（车行）出口；驶出；驾车出游〈n.f.〉</t>
         </is>
       </c>
       <c r="E467" s="1" t="inlineStr">
@@ -15411,7 +15411,7 @@
       </c>
       <c r="B469" s="1" t="inlineStr">
         <is>
-          <t>[faʊlə] 有毒的；中毒的；毒物的〈adv.〉</t>
+          <t>[faʊlə] 懒惰的；腐烂的〈adv.〉</t>
         </is>
       </c>
       <c r="C469" s="1" t="inlineStr">
@@ -15421,7 +15421,7 @@
       </c>
       <c r="D469" s="1" t="inlineStr">
         <is>
-          <t>有毒的；中毒的；毒物的</t>
+          <t>懒惰的；腐烂的</t>
         </is>
       </c>
       <c r="E469" s="1" t="inlineStr">
@@ -15475,7 +15475,7 @@
       </c>
       <c r="B471" s="1" t="inlineStr">
         <is>
-          <t>[mɛnlɪçɐ] 牡鹿〈adv.〉</t>
+          <t>[mɛnlɪçɐ] 男性的；更男性化的〈adv.〉</t>
         </is>
       </c>
       <c r="C471" s="1" t="inlineStr">
@@ -15485,7 +15485,7 @@
       </c>
       <c r="D471" s="1" t="inlineStr">
         <is>
-          <t>牡鹿</t>
+          <t>男性的；更男性化的</t>
         </is>
       </c>
       <c r="E471" s="1" t="inlineStr">
@@ -15827,7 +15827,7 @@
       </c>
       <c r="B482" s="1" t="inlineStr">
         <is>
-          <t>[aʊzaɪnandəʁzət͡sʊnk] 磨损；打架〈n.f.〉</t>
+          <t>[aʊzaɪnandəʁzət͡sʊnk] 争论；争执；辩论〈n.f.〉</t>
         </is>
       </c>
       <c r="C482" s="1" t="inlineStr">
@@ -15837,7 +15837,7 @@
       </c>
       <c r="D482" s="1" t="inlineStr">
         <is>
-          <t>磨损；打架</t>
+          <t>争论；争执；辩论</t>
         </is>
       </c>
       <c r="E482" s="1" t="inlineStr">
@@ -15955,7 +15955,7 @@
       </c>
       <c r="B486" s="1" t="inlineStr">
         <is>
-          <t>[aɪnɡəbən] 行政；管理；政府机关；给药〈n.〉</t>
+          <t>[aɪnɡəbən] 输入；键入〈n.〉</t>
         </is>
       </c>
       <c r="C486" s="1" t="inlineStr">
@@ -15965,7 +15965,7 @@
       </c>
       <c r="D486" s="1" t="inlineStr">
         <is>
-          <t>行政；管理；政府机关；给药</t>
+          <t>输入；键入</t>
         </is>
       </c>
       <c r="E486" s="1" t="inlineStr">
@@ -16115,7 +16115,7 @@
       </c>
       <c r="B491" s="1" t="inlineStr">
         <is>
-          <t>[biːkɪnɪ] 大爆炸；比基尼泳装〈n.m.〉</t>
+          <t>[biːkɪnɪ] 比基尼泳装〈n.m.〉</t>
         </is>
       </c>
       <c r="C491" s="1" t="inlineStr">
@@ -16125,7 +16125,7 @@
       </c>
       <c r="D491" s="1" t="inlineStr">
         <is>
-          <t>大爆炸；比基尼泳装</t>
+          <t>比基尼泳装</t>
         </is>
       </c>
       <c r="E491" s="1" t="inlineStr">
@@ -16179,12 +16179,12 @@
       </c>
       <c r="B493" s="1" t="inlineStr">
         <is>
-          <t>[mançəstɐ] 曼彻斯特〈n.〉</t>
+          <t>[mɛntʃɛstɐ] 曼彻斯特〈n.〉</t>
         </is>
       </c>
       <c r="C493" s="1" t="inlineStr">
         <is>
-          <t>mançəstɐ</t>
+          <t>mɛntʃɛstɐ</t>
         </is>
       </c>
       <c r="D493" s="1" t="inlineStr">
@@ -16499,7 +16499,7 @@
       </c>
       <c r="B503" s="1" t="inlineStr">
         <is>
-          <t>[hiːp] 摇摆舞的；无节制的；乱窜的〈adv.〉</t>
+          <t>[hiːp] 时髦的；新潮的〈adj.〉〈adv.〉</t>
         </is>
       </c>
       <c r="C503" s="1" t="inlineStr">
@@ -16509,7 +16509,7 @@
       </c>
       <c r="D503" s="1" t="inlineStr">
         <is>
-          <t>摇摆舞的；无节制的；乱窜的</t>
+          <t>时髦的；新潮的〈adj.〉</t>
         </is>
       </c>
       <c r="E503" s="1" t="inlineStr">
@@ -16851,7 +16851,7 @@
       </c>
       <c r="B514" s="1" t="inlineStr">
         <is>
-          <t>[jɛɡlɪçɐ] 苍蝇；两翼昆虫；飞行；飞〈adv.〉</t>
+          <t>[jɛɡlɪçɐ] 任何的；一切的〈adj.〉〈adv.〉</t>
         </is>
       </c>
       <c r="C514" s="1" t="inlineStr">
@@ -16861,7 +16861,7 @@
       </c>
       <c r="D514" s="1" t="inlineStr">
         <is>
-          <t>苍蝇；两翼昆虫；飞行；飞</t>
+          <t>任何的；一切的〈adj.〉</t>
         </is>
       </c>
       <c r="E514" s="1" t="inlineStr">
@@ -16979,12 +16979,12 @@
       </c>
       <c r="B518" s="1" t="inlineStr">
         <is>
-          <t>[anstʁənɡʊnk] 努力；成就〈n.f.〉</t>
+          <t>[anstʁənɡʊŋ] 努力；成就〈n.f.〉</t>
         </is>
       </c>
       <c r="C518" s="1" t="inlineStr">
         <is>
-          <t>anstʁənɡʊnk</t>
+          <t>anstʁənɡʊŋ</t>
         </is>
       </c>
       <c r="D518" s="1" t="inlineStr">
@@ -17043,7 +17043,7 @@
       </c>
       <c r="B520" s="1" t="inlineStr">
         <is>
-          <t>[uːnʊntəʁbʁɔxən] 未减轻的；未受救济的〈v.〉</t>
+          <t>[uːnʊntəʁbʁɔxən] 不间断的；连续的〈v.〉</t>
         </is>
       </c>
       <c r="C520" s="1" t="inlineStr">
@@ -17053,7 +17053,7 @@
       </c>
       <c r="D520" s="1" t="inlineStr">
         <is>
-          <t>未减轻的；未受救济的</t>
+          <t>不间断的；连续的</t>
         </is>
       </c>
       <c r="E520" s="1" t="inlineStr">
@@ -17427,7 +17427,7 @@
       </c>
       <c r="B532" s="1" t="inlineStr">
         <is>
-          <t>[bʁaːfə] &lt;口&gt;=〈adv.〉</t>
+          <t>[bʁaːfə] 乖的；听话的；老实的〈adv.〉</t>
         </is>
       </c>
       <c r="C532" s="1" t="inlineStr">
@@ -17437,7 +17437,7 @@
       </c>
       <c r="D532" s="1" t="inlineStr">
         <is>
-          <t>&lt;口&gt;=</t>
+          <t>乖的；听话的；老实的</t>
         </is>
       </c>
       <c r="E532" s="1" t="inlineStr">
@@ -17523,7 +17523,7 @@
       </c>
       <c r="B535" s="1" t="inlineStr">
         <is>
-          <t>[zʊbjəkt] 科目；主题；臣民〈n.〉</t>
+          <t>[zʊbjəkt] 主语；主体〈n.〉〈n.〉</t>
         </is>
       </c>
       <c r="C535" s="1" t="inlineStr">
@@ -17533,7 +17533,7 @@
       </c>
       <c r="D535" s="1" t="inlineStr">
         <is>
-          <t>科目；主题；臣民</t>
+          <t>主语；主体〈n.〉</t>
         </is>
       </c>
       <c r="E535" s="1" t="inlineStr">
@@ -17619,7 +17619,7 @@
       </c>
       <c r="B538" s="1" t="inlineStr">
         <is>
-          <t>[pʊt͡sə] 弹性；适应性；给；授予〈n.〉</t>
+          <t>[pʊt͡sə] 擦洗；打扫是动词 putzen；名词 die Putze 指打扫、清洁（南德用语）〈n.f.〉〈n.〉</t>
         </is>
       </c>
       <c r="C538" s="1" t="inlineStr">
@@ -17629,7 +17629,7 @@
       </c>
       <c r="D538" s="1" t="inlineStr">
         <is>
-          <t>弹性；适应性；给；授予</t>
+          <t>擦洗；打扫是动词 putzen；名词 die Putze 指打扫、清洁（南德用语）〈n.f.〉</t>
         </is>
       </c>
       <c r="E538" s="1" t="inlineStr">
@@ -18035,7 +18035,7 @@
       </c>
       <c r="B551" s="1" t="inlineStr">
         <is>
-          <t>[fɔʁzɪnɡən] 听；听力；试听；审计命令〈v.〉</t>
+          <t>[fɔʁzɪnɡən] 试唱；为…演唱〈v.〉</t>
         </is>
       </c>
       <c r="C551" s="1" t="inlineStr">
@@ -18045,7 +18045,7 @@
       </c>
       <c r="D551" s="1" t="inlineStr">
         <is>
-          <t>听；听力；试听；审计命令</t>
+          <t>试唱；为…演唱</t>
         </is>
       </c>
       <c r="E551" s="1" t="inlineStr">
@@ -18323,7 +18323,7 @@
       </c>
       <c r="B560" s="1" t="inlineStr">
         <is>
-          <t>[fɛʁʃlaɡən] 搭乘〈v.〉</t>
+          <t>[fɛʁʃlaɡən] 使偏离航向；打歪〈v.〉</t>
         </is>
       </c>
       <c r="C560" s="1" t="inlineStr">
@@ -18333,7 +18333,7 @@
       </c>
       <c r="D560" s="1" t="inlineStr">
         <is>
-          <t>搭乘</t>
+          <t>使偏离航向；打歪</t>
         </is>
       </c>
       <c r="E560" s="1" t="inlineStr">
@@ -18419,7 +18419,7 @@
       </c>
       <c r="B563" s="1" t="inlineStr">
         <is>
-          <t>[dɔnəʁɡʁɔlən] 旋转的；波动的；起伏的；旋转〈n.〉</t>
+          <t>[dɔnəʁɡʁɔlən] 雷鸣；隆隆雷声〈n.〉</t>
         </is>
       </c>
       <c r="C563" s="1" t="inlineStr">
@@ -18429,7 +18429,7 @@
       </c>
       <c r="D563" s="1" t="inlineStr">
         <is>
-          <t>旋转的；波动的；起伏的；旋转</t>
+          <t>雷鸣；隆隆雷声</t>
         </is>
       </c>
       <c r="E563" s="1" t="inlineStr">
@@ -18483,7 +18483,7 @@
       </c>
       <c r="B565" s="1" t="inlineStr">
         <is>
-          <t>[ɡɛl] 权利；右边；正义〈adv.〉</t>
+          <t>[ɡɛl] 对吧？是吧？（表示求证的语气词）〈adv.〉</t>
         </is>
       </c>
       <c r="C565" s="1" t="inlineStr">
@@ -18493,7 +18493,7 @@
       </c>
       <c r="D565" s="1" t="inlineStr">
         <is>
-          <t>权利；右边；正义</t>
+          <t>对吧？是吧？（表示求证的语气词）</t>
         </is>
       </c>
       <c r="E565" s="1" t="inlineStr">
@@ -18515,17 +18515,17 @@
       </c>
       <c r="B566" s="1" t="inlineStr">
         <is>
-          <t>[ɛntspanʊnk] 压力；紧迫；强调〈n.f.〉</t>
+          <t>[ɛntspanʊŋ] 放松；松弛；缓和〈n.f.〉</t>
         </is>
       </c>
       <c r="C566" s="1" t="inlineStr">
         <is>
-          <t>ɛntspanʊnk</t>
+          <t>ɛntspanʊŋ</t>
         </is>
       </c>
       <c r="D566" s="1" t="inlineStr">
         <is>
-          <t>压力；紧迫；强调</t>
+          <t>放松；松弛；缓和</t>
         </is>
       </c>
       <c r="E566" s="1" t="inlineStr">
@@ -19059,7 +19059,7 @@
       </c>
       <c r="B583" s="1" t="inlineStr">
         <is>
-          <t>[ʃɔʏ] 象老鼠的；多老鼠的；胆小的〈adv.〉</t>
+          <t>[ʃɔʏ] 胆怯的；易受惊的；羞怯的〈adv.〉</t>
         </is>
       </c>
       <c r="C583" s="1" t="inlineStr">
@@ -19069,7 +19069,7 @@
       </c>
       <c r="D583" s="1" t="inlineStr">
         <is>
-          <t>象老鼠的；多老鼠的；胆小的</t>
+          <t>胆怯的；易受惊的；羞怯的</t>
         </is>
       </c>
       <c r="E583" s="1" t="inlineStr">
@@ -19219,7 +19219,7 @@
       </c>
       <c r="B588" s="1" t="inlineStr">
         <is>
-          <t>[aɪnzɪçt] 感应；感觉；感官〈n.f.〉</t>
+          <t>[aɪnzɪçt] 洞察力；认识；见解〈n.f.〉</t>
         </is>
       </c>
       <c r="C588" s="1" t="inlineStr">
@@ -19229,7 +19229,7 @@
       </c>
       <c r="D588" s="1" t="inlineStr">
         <is>
-          <t>感应；感觉；感官</t>
+          <t>洞察力；认识；见解</t>
         </is>
       </c>
       <c r="E588" s="1" t="inlineStr">
@@ -19315,7 +19315,7 @@
       </c>
       <c r="B591" s="1" t="inlineStr">
         <is>
-          <t>[aɪnfəʁstɛndnɪs] 赞成；批准；核准〈n.〉</t>
+          <t>[aɪnfəʁstɛndnɪs] 同意；赞同；谅解〈n.〉</t>
         </is>
       </c>
       <c r="C591" s="1" t="inlineStr">
@@ -19325,7 +19325,7 @@
       </c>
       <c r="D591" s="1" t="inlineStr">
         <is>
-          <t>赞成；批准；核准</t>
+          <t>同意；赞同；谅解</t>
         </is>
       </c>
       <c r="E591" s="1" t="inlineStr">
@@ -19571,7 +19571,7 @@
       </c>
       <c r="B599" s="1" t="inlineStr">
         <is>
-          <t>[anɡəʃlaɡən] 失败〈v.〉</t>
+          <t>[anɡəʃlaɡən] 被击中的；身体不适的；状况不佳的〈v.〉</t>
         </is>
       </c>
       <c r="C599" s="1" t="inlineStr">
@@ -19581,7 +19581,7 @@
       </c>
       <c r="D599" s="1" t="inlineStr">
         <is>
-          <t>失败</t>
+          <t>被击中的；身体不适的；状况不佳的</t>
         </is>
       </c>
       <c r="E599" s="1" t="inlineStr">
@@ -19667,7 +19667,7 @@
       </c>
       <c r="B602" s="1" t="inlineStr">
         <is>
-          <t>[dɪkəs] 奶昔〈adv.〉</t>
+          <t>[dɪkəs] 厚的；粗的；浓的；胖的〈adv.〉</t>
         </is>
       </c>
       <c r="C602" s="1" t="inlineStr">
@@ -19677,7 +19677,7 @@
       </c>
       <c r="D602" s="1" t="inlineStr">
         <is>
-          <t>奶昔</t>
+          <t>厚的；粗的；浓的；胖的</t>
         </is>
       </c>
       <c r="E602" s="1" t="inlineStr">
@@ -19827,7 +19827,7 @@
       </c>
       <c r="B607" s="1" t="inlineStr">
         <is>
-          <t>[aːnanas] 凤梨；菠萝；失业救济金〈n.f.〉</t>
+          <t>[aːnanas] 菠萝；凤梨〈n.f.〉</t>
         </is>
       </c>
       <c r="C607" s="1" t="inlineStr">
@@ -19837,7 +19837,7 @@
       </c>
       <c r="D607" s="1" t="inlineStr">
         <is>
-          <t>凤梨；菠萝；失业救济金</t>
+          <t>菠萝；凤梨</t>
         </is>
       </c>
       <c r="E607" s="1" t="inlineStr">
@@ -20083,7 +20083,7 @@
       </c>
       <c r="B615" s="1" t="inlineStr">
         <is>
-          <t>[ɛʁvaɪtəʁt] 延续的；伸出的；竭尽全力的〈adj.〉</t>
+          <t>[ɛʁvaɪtəʁt] 扩大的；扩展的；扩充的〈adj.〉</t>
         </is>
       </c>
       <c r="C615" s="1" t="inlineStr">
@@ -20093,7 +20093,7 @@
       </c>
       <c r="D615" s="1" t="inlineStr">
         <is>
-          <t>延续的；伸出的；竭尽全力的</t>
+          <t>扩大的；扩展的；扩充的</t>
         </is>
       </c>
       <c r="E615" s="1" t="inlineStr">
@@ -20147,7 +20147,7 @@
       </c>
       <c r="B617" s="1" t="inlineStr">
         <is>
-          <t>[fiːçɐ] 爬行的昆虫〈n.〉</t>
+          <t>[fiːçɐ] 牲畜；野兽；家伙〈n.〉</t>
         </is>
       </c>
       <c r="C617" s="1" t="inlineStr">
@@ -20157,7 +20157,7 @@
       </c>
       <c r="D617" s="1" t="inlineStr">
         <is>
-          <t>爬行的昆虫</t>
+          <t>牲畜；野兽；家伙</t>
         </is>
       </c>
       <c r="E617" s="1" t="inlineStr">
@@ -20243,7 +20243,7 @@
       </c>
       <c r="B620" s="1" t="inlineStr">
         <is>
-          <t>[fɔʁank] 领先；上席〈n.m.〉</t>
+          <t>[fɔʁank] 优先；优先地位〈m.〉〈n.m.〉</t>
         </is>
       </c>
       <c r="C620" s="1" t="inlineStr">
@@ -20253,7 +20253,7 @@
       </c>
       <c r="D620" s="1" t="inlineStr">
         <is>
-          <t>领先；上席</t>
+          <t>优先；优先地位〈m.〉</t>
         </is>
       </c>
       <c r="E620" s="1" t="inlineStr">
@@ -20307,7 +20307,7 @@
       </c>
       <c r="B622" s="1" t="inlineStr">
         <is>
-          <t>[abhœʁən] 拦截；截断；截住〈n.〉</t>
+          <t>[abhœʁən] 窃听；监听；听诊〈n.〉</t>
         </is>
       </c>
       <c r="C622" s="1" t="inlineStr">
@@ -20317,7 +20317,7 @@
       </c>
       <c r="D622" s="1" t="inlineStr">
         <is>
-          <t>拦截；截断；截住</t>
+          <t>窃听；监听；听诊</t>
         </is>
       </c>
       <c r="E622" s="1" t="inlineStr">
@@ -20403,7 +20403,7 @@
       </c>
       <c r="B625" s="1" t="inlineStr">
         <is>
-          <t>[fɛʁboːt] 禁令；禁止〈n.〉</t>
+          <t>[fɛʁboːt] 禁令；禁止〈n.〉〈n.〉</t>
         </is>
       </c>
       <c r="C625" s="1" t="inlineStr">
@@ -20413,7 +20413,7 @@
       </c>
       <c r="D625" s="1" t="inlineStr">
         <is>
-          <t>禁令；禁止</t>
+          <t>禁令；禁止〈n.〉</t>
         </is>
       </c>
       <c r="E625" s="1" t="inlineStr">
@@ -20531,7 +20531,7 @@
       </c>
       <c r="B629" s="1" t="inlineStr">
         <is>
-          <t>[aspəkt] 旋转；自旋；疾驰〈n.m.〉</t>
+          <t>[aspəkt] 方面；层面；视角〈n.m.〉</t>
         </is>
       </c>
       <c r="C629" s="1" t="inlineStr">
@@ -20541,7 +20541,7 @@
       </c>
       <c r="D629" s="1" t="inlineStr">
         <is>
-          <t>旋转；自旋；疾驰</t>
+          <t>方面；层面；视角</t>
         </is>
       </c>
       <c r="E629" s="1" t="inlineStr">
@@ -20563,7 +20563,7 @@
       </c>
       <c r="B630" s="1" t="inlineStr">
         <is>
-          <t>[beːʁən] 茎；干；柄〈n.〉</t>
+          <t>[beːʁən] 浆果；莓果〈n.〉</t>
         </is>
       </c>
       <c r="C630" s="1" t="inlineStr">
@@ -20573,7 +20573,7 @@
       </c>
       <c r="D630" s="1" t="inlineStr">
         <is>
-          <t>茎；干；柄</t>
+          <t>浆果；莓果</t>
         </is>
       </c>
       <c r="E630" s="1" t="inlineStr">
@@ -20627,7 +20627,7 @@
       </c>
       <c r="B632" s="1" t="inlineStr">
         <is>
-          <t>[pʁiːmə] 最佳部分；初期〈n.f.〉</t>
+          <t>[pʁiːmə] 全盛期；鼎盛时期〈n.f.〉〈n.f.〉</t>
         </is>
       </c>
       <c r="C632" s="1" t="inlineStr">
@@ -20637,7 +20637,7 @@
       </c>
       <c r="D632" s="1" t="inlineStr">
         <is>
-          <t>最佳部分；初期</t>
+          <t>全盛期；鼎盛时期〈n.f.〉</t>
         </is>
       </c>
       <c r="E632" s="1" t="inlineStr">
@@ -21331,7 +21331,7 @@
       </c>
       <c r="B654" s="1" t="inlineStr">
         <is>
-          <t>[dʊʁksət͡sən] 成功；继承；继续〈v.〉</t>
+          <t>[dʊʁksət͡sən] 贯彻；推行；坚持并实现〈v.〉</t>
         </is>
       </c>
       <c r="C654" s="1" t="inlineStr">
@@ -21341,7 +21341,7 @@
       </c>
       <c r="D654" s="1" t="inlineStr">
         <is>
-          <t>成功；继承；继续</t>
+          <t>贯彻；推行；坚持并实现</t>
         </is>
       </c>
       <c r="E654" s="1" t="inlineStr">
@@ -21395,7 +21395,7 @@
       </c>
       <c r="B656" s="1" t="inlineStr">
         <is>
-          <t>[ɛndlɔzə] 结束语；演讲；夸夸其谈〈adv.〉</t>
+          <t>[ɛndlɔzə] 无尽的；无休止的；无穷的〈adv.〉</t>
         </is>
       </c>
       <c r="C656" s="1" t="inlineStr">
@@ -21405,7 +21405,7 @@
       </c>
       <c r="D656" s="1" t="inlineStr">
         <is>
-          <t>结束语；演讲；夸夸其谈</t>
+          <t>无尽的；无休止的；无穷的</t>
         </is>
       </c>
       <c r="E656" s="1" t="inlineStr">
@@ -21459,7 +21459,7 @@
       </c>
       <c r="B658" s="1" t="inlineStr">
         <is>
-          <t>[ɪləɡaləs] 非法交易〈adv.〉</t>
+          <t>[ɪləɡaləs] 非法的〈adj.〉〈adv.〉</t>
         </is>
       </c>
       <c r="C658" s="1" t="inlineStr">
@@ -21469,7 +21469,7 @@
       </c>
       <c r="D658" s="1" t="inlineStr">
         <is>
-          <t>非法交易</t>
+          <t>非法的〈adj.〉</t>
         </is>
       </c>
       <c r="E658" s="1" t="inlineStr">
@@ -21523,7 +21523,7 @@
       </c>
       <c r="B660" s="1" t="inlineStr">
         <is>
-          <t>[aːɡiːʁən] 秘密行动；秘密；鬼祟〈n.〉</t>
+          <t>[aːɡiːʁən] 行动；行事；表演〈n.〉</t>
         </is>
       </c>
       <c r="C660" s="1" t="inlineStr">
@@ -21533,7 +21533,7 @@
       </c>
       <c r="D660" s="1" t="inlineStr">
         <is>
-          <t>秘密行动；秘密；鬼祟</t>
+          <t>行动；行事；表演</t>
         </is>
       </c>
       <c r="E660" s="1" t="inlineStr">
@@ -21555,12 +21555,12 @@
       </c>
       <c r="B661" s="1" t="inlineStr">
         <is>
-          <t>[tɔʊxdɔvn] 触地；触地得分；着地〈n.m.〉</t>
+          <t>[taʊt͡ʃdaʊn] 触地；触地得分；着地〈n.m.〉</t>
         </is>
       </c>
       <c r="C661" s="1" t="inlineStr">
         <is>
-          <t>tɔʊxdɔvn</t>
+          <t>taʊt͡ʃdaʊn</t>
         </is>
       </c>
       <c r="D661" s="1" t="inlineStr">
@@ -21587,7 +21587,7 @@
       </c>
       <c r="B662" s="1" t="inlineStr">
         <is>
-          <t>[paːʁən] 配偶；对手；助手〈v.〉</t>
+          <t>[paːʁən] 交配；配对〈v.〉</t>
         </is>
       </c>
       <c r="C662" s="1" t="inlineStr">
@@ -21597,7 +21597,7 @@
       </c>
       <c r="D662" s="1" t="inlineStr">
         <is>
-          <t>配偶；对手；助手</t>
+          <t>交配；配对</t>
         </is>
       </c>
       <c r="E662" s="1" t="inlineStr">
@@ -21683,7 +21683,7 @@
       </c>
       <c r="B665" s="1" t="inlineStr">
         <is>
-          <t>[ʃʁaʊbə] 门闩；螺钉；筛子〈n.f.〉</t>
+          <t>[ʃʁaʊbə] 螺钉；螺丝〈n.f.〉</t>
         </is>
       </c>
       <c r="C665" s="1" t="inlineStr">
@@ -21693,7 +21693,7 @@
       </c>
       <c r="D665" s="1" t="inlineStr">
         <is>
-          <t>门闩；螺钉；筛子</t>
+          <t>螺钉；螺丝</t>
         </is>
       </c>
       <c r="E665" s="1" t="inlineStr">
@@ -21715,7 +21715,7 @@
       </c>
       <c r="B666" s="1" t="inlineStr">
         <is>
-          <t>[aʊfʃnaɪdən] 吹；打击；殴打〈v.〉</t>
+          <t>[aʊfʃnaɪdən] 切开；吹牛；说大话〈v.〉</t>
         </is>
       </c>
       <c r="C666" s="1" t="inlineStr">
@@ -21725,7 +21725,7 @@
       </c>
       <c r="D666" s="1" t="inlineStr">
         <is>
-          <t>吹；打击；殴打</t>
+          <t>切开；吹牛；说大话</t>
         </is>
       </c>
       <c r="E666" s="1" t="inlineStr">
@@ -22035,7 +22035,7 @@
       </c>
       <c r="B676" s="1" t="inlineStr">
         <is>
-          <t>[fiːzuːm] 签证；签发〈n.〉</t>
+          <t>[fiːzuːm] 签证〈n.〉〈n.〉</t>
         </is>
       </c>
       <c r="C676" s="1" t="inlineStr">
@@ -22045,7 +22045,7 @@
       </c>
       <c r="D676" s="1" t="inlineStr">
         <is>
-          <t>签证；签发</t>
+          <t>签证〈n.〉</t>
         </is>
       </c>
       <c r="E676" s="1" t="inlineStr">
@@ -22067,7 +22067,7 @@
       </c>
       <c r="B677" s="1" t="inlineStr">
         <is>
-          <t>[mʏkən] 蚊；侏儒〈n.〉</t>
+          <t>[mʏkən] 蚊子（Mücke 的复数）〈n.〉</t>
         </is>
       </c>
       <c r="C677" s="1" t="inlineStr">
@@ -22077,7 +22077,7 @@
       </c>
       <c r="D677" s="1" t="inlineStr">
         <is>
-          <t>蚊；侏儒</t>
+          <t>蚊子（Mücke 的复数）</t>
         </is>
       </c>
       <c r="E677" s="1" t="inlineStr">
@@ -22323,7 +22323,7 @@
       </c>
       <c r="B685" s="1" t="inlineStr">
         <is>
-          <t>[fiːnant͡samt] 税；税款；重负〈n.〉</t>
+          <t>[fiːnant͡samt] 税务局〈n.〉</t>
         </is>
       </c>
       <c r="C685" s="1" t="inlineStr">
@@ -22333,7 +22333,7 @@
       </c>
       <c r="D685" s="1" t="inlineStr">
         <is>
-          <t>税；税款；重负</t>
+          <t>税务局</t>
         </is>
       </c>
       <c r="E685" s="1" t="inlineStr">
@@ -23091,12 +23091,12 @@
       </c>
       <c r="B709" s="1" t="inlineStr">
         <is>
-          <t>[flaːt] 弗拉德〈n.〉</t>
+          <t>[vlaːt] 弗拉德〈n.〉</t>
         </is>
       </c>
       <c r="C709" s="1" t="inlineStr">
         <is>
-          <t>flaːt</t>
+          <t>vlaːt</t>
         </is>
       </c>
       <c r="D709" s="1" t="inlineStr">
@@ -23187,7 +23187,7 @@
       </c>
       <c r="B712" s="1" t="inlineStr">
         <is>
-          <t>[dʁeːaʁbaɪtən] 射击；狩猎；芽〈n.〉</t>
+          <t>[dʁeːaʁbaɪtən] （电影）拍摄；摄制〈n.〉</t>
         </is>
       </c>
       <c r="C712" s="1" t="inlineStr">
@@ -23197,7 +23197,7 @@
       </c>
       <c r="D712" s="1" t="inlineStr">
         <is>
-          <t>射击；狩猎；芽</t>
+          <t>（电影）拍摄；摄制</t>
         </is>
       </c>
       <c r="E712" s="1" t="inlineStr">
@@ -23475,7 +23475,7 @@
       </c>
       <c r="B721" s="1" t="inlineStr">
         <is>
-          <t>[muːzə] 沉思；冥想〈n.f.〉</t>
+          <t>[muːzə] 缪斯；灵感女神〈n.f.〉</t>
         </is>
       </c>
       <c r="C721" s="1" t="inlineStr">
@@ -23485,7 +23485,7 @@
       </c>
       <c r="D721" s="1" t="inlineStr">
         <is>
-          <t>沉思；冥想</t>
+          <t>缪斯；灵感女神</t>
         </is>
       </c>
       <c r="E721" s="1" t="inlineStr">
@@ -23507,7 +23507,7 @@
       </c>
       <c r="B722" s="1" t="inlineStr">
         <is>
-          <t>[dʁaɪst] 的变形〈adv.〉</t>
+          <t>[dʁaɪst] 大胆的；放肆的；厚颜无耻的〈adv.〉</t>
         </is>
       </c>
       <c r="C722" s="1" t="inlineStr">
@@ -23517,7 +23517,7 @@
       </c>
       <c r="D722" s="1" t="inlineStr">
         <is>
-          <t>的变形</t>
+          <t>大胆的；放肆的；厚颜无耻的</t>
         </is>
       </c>
       <c r="E722" s="1" t="inlineStr">
@@ -23539,7 +23539,7 @@
       </c>
       <c r="B723" s="1" t="inlineStr">
         <is>
-          <t>[ɛs] 正餐；宴会〈n.〉</t>
+          <t>[ɛs] 吃；食物；一顿饭〈n.〉〈n.〉</t>
         </is>
       </c>
       <c r="C723" s="1" t="inlineStr">
@@ -23549,7 +23549,7 @@
       </c>
       <c r="D723" s="1" t="inlineStr">
         <is>
-          <t>正餐；宴会</t>
+          <t>吃；食物；一顿饭〈n.〉</t>
         </is>
       </c>
       <c r="E723" s="1" t="inlineStr">
@@ -23603,7 +23603,7 @@
       </c>
       <c r="B725" s="1" t="inlineStr">
         <is>
-          <t>[yːbəʁvaxʊnɡskaməʁa] 安全；安全性；防护物〈n.f.〉</t>
+          <t>[yːbəʁvaxʊnɡskaməʁa] 监控摄像头；监视摄像机〈n.f.〉</t>
         </is>
       </c>
       <c r="C725" s="1" t="inlineStr">
@@ -23613,7 +23613,7 @@
       </c>
       <c r="D725" s="1" t="inlineStr">
         <is>
-          <t>安全；安全性；防护物</t>
+          <t>监控摄像头；监视摄像机</t>
         </is>
       </c>
       <c r="E725" s="1" t="inlineStr">
@@ -23699,7 +23699,7 @@
       </c>
       <c r="B728" s="1" t="inlineStr">
         <is>
-          <t>[plaʏbɔʏ] 花花公子；乖巧的人〈n.m.〉</t>
+          <t>[plaʏbɔʏ] 花花公子；纨绔子弟〈n.m.〉</t>
         </is>
       </c>
       <c r="C728" s="1" t="inlineStr">
@@ -23709,7 +23709,7 @@
       </c>
       <c r="D728" s="1" t="inlineStr">
         <is>
-          <t>花花公子；乖巧的人</t>
+          <t>花花公子；纨绔子弟</t>
         </is>
       </c>
       <c r="E728" s="1" t="inlineStr">
@@ -23827,7 +23827,7 @@
       </c>
       <c r="B732" s="1" t="inlineStr">
         <is>
-          <t>[fʏnfmaːl] 五；五个〈adj.〉</t>
+          <t>[fʏnfmaːl] 五次〈adj.〉</t>
         </is>
       </c>
       <c r="C732" s="1" t="inlineStr">
@@ -23837,7 +23837,7 @@
       </c>
       <c r="D732" s="1" t="inlineStr">
         <is>
-          <t>五；五个</t>
+          <t>五次</t>
         </is>
       </c>
       <c r="E732" s="1" t="inlineStr">
@@ -23987,7 +23987,7 @@
       </c>
       <c r="B737" s="1" t="inlineStr">
         <is>
-          <t>[oːʁɪnk] 耳朵；倾听；听觉〈n.m.〉</t>
+          <t>[oːʁɪnk] 耳环〈n.m.〉</t>
         </is>
       </c>
       <c r="C737" s="1" t="inlineStr">
@@ -23997,7 +23997,7 @@
       </c>
       <c r="D737" s="1" t="inlineStr">
         <is>
-          <t>耳朵；倾听；听觉</t>
+          <t>耳环</t>
         </is>
       </c>
       <c r="E737" s="1" t="inlineStr">
@@ -24307,7 +24307,7 @@
       </c>
       <c r="B747" s="1" t="inlineStr">
         <is>
-          <t>[yːbəʁalhiːn] 全部结束；到处；浑身〈adv.〉</t>
+          <t>[yːbəʁalhiːn] 到各处；向四面八方〈adv.〉</t>
         </is>
       </c>
       <c r="C747" s="1" t="inlineStr">
@@ -24317,7 +24317,7 @@
       </c>
       <c r="D747" s="1" t="inlineStr">
         <is>
-          <t>全部结束；到处；浑身</t>
+          <t>到各处；向四面八方</t>
         </is>
       </c>
       <c r="E747" s="1" t="inlineStr">
@@ -24339,7 +24339,7 @@
       </c>
       <c r="B748" s="1" t="inlineStr">
         <is>
-          <t>[ʃɛʁbən] 碎片；破瓷片（复数）〈n.〉</t>
+          <t>[ʃɛʁbən] Scherbe：碎片；破瓷片〈n.f.〉（复数 Scherben）〈n.〉</t>
         </is>
       </c>
       <c r="C748" s="1" t="inlineStr">
@@ -24349,7 +24349,7 @@
       </c>
       <c r="D748" s="1" t="inlineStr">
         <is>
-          <t>碎片；破瓷片（复数）</t>
+          <t>Scherbe：碎片；破瓷片〈n.f.〉（复数 Scherben）</t>
         </is>
       </c>
       <c r="E748" s="1" t="inlineStr">
@@ -24467,7 +24467,7 @@
       </c>
       <c r="B752" s="1" t="inlineStr">
         <is>
-          <t>[ɡeːʁɪçtsmədɪt͡siːn] 法律的；法定的；合法的；法定权利〈n.f.〉</t>
+          <t>[ɡeːʁɪçtsmədɪt͡siːn] 法医学；法医鉴定〈n.f.〉</t>
         </is>
       </c>
       <c r="C752" s="1" t="inlineStr">
@@ -24477,7 +24477,7 @@
       </c>
       <c r="D752" s="1" t="inlineStr">
         <is>
-          <t>法律的；法定的；合法的；法定权利</t>
+          <t>法医学；法医鉴定</t>
         </is>
       </c>
       <c r="E752" s="1" t="inlineStr">
@@ -24691,7 +24691,7 @@
       </c>
       <c r="B759" s="1" t="inlineStr">
         <is>
-          <t>[beːt͡saʊbəʁndə] 妖妇；女巫〈adv.〉</t>
+          <t>[beːt͡saʊbəʁndə] 迷人的；令人着迷的〈adv.〉</t>
         </is>
       </c>
       <c r="C759" s="1" t="inlineStr">
@@ -24701,7 +24701,7 @@
       </c>
       <c r="D759" s="1" t="inlineStr">
         <is>
-          <t>妖妇；女巫</t>
+          <t>迷人的；令人着迷的</t>
         </is>
       </c>
       <c r="E759" s="1" t="inlineStr">
@@ -24723,7 +24723,7 @@
       </c>
       <c r="B760" s="1" t="inlineStr">
         <is>
-          <t>[ɪnstɪtʊt͡sjoːn] 实体；实存物；存在〈n.f.〉</t>
+          <t>[ɪnstɪtʊt͡sjoːn] 机构；制度〈n.f.〉</t>
         </is>
       </c>
       <c r="C760" s="1" t="inlineStr">
@@ -24733,7 +24733,7 @@
       </c>
       <c r="D760" s="1" t="inlineStr">
         <is>
-          <t>实体；实存物；存在</t>
+          <t>机构；制度</t>
         </is>
       </c>
       <c r="E760" s="1" t="inlineStr">
@@ -24755,7 +24755,7 @@
       </c>
       <c r="B761" s="1" t="inlineStr">
         <is>
-          <t>[ɡeːʁɪnɡə] 缺乏〈adv.〉</t>
+          <t>[ɡeːʁɪnɡə] 少量的；轻微的；小的〈adv.〉</t>
         </is>
       </c>
       <c r="C761" s="1" t="inlineStr">
@@ -24765,7 +24765,7 @@
       </c>
       <c r="D761" s="1" t="inlineStr">
         <is>
-          <t>缺乏</t>
+          <t>少量的；轻微的；小的</t>
         </is>
       </c>
       <c r="E761" s="1" t="inlineStr">
@@ -25011,7 +25011,7 @@
       </c>
       <c r="B769" s="1" t="inlineStr">
         <is>
-          <t>[abʃiːdsbʁiːf] 辞别；再见〈n.m.〉</t>
+          <t>[abʃiːdsbʁiːf] 告别信；绝笔〈n.m.〉</t>
         </is>
       </c>
       <c r="C769" s="1" t="inlineStr">
@@ -25021,7 +25021,7 @@
       </c>
       <c r="D769" s="1" t="inlineStr">
         <is>
-          <t>辞别；再见</t>
+          <t>告别信；绝笔</t>
         </is>
       </c>
       <c r="E769" s="1" t="inlineStr">
@@ -25427,7 +25427,7 @@
       </c>
       <c r="B782" s="1" t="inlineStr">
         <is>
-          <t>[ɡeːbʊʁtzʊʁkʊndə] 出生；起源；生产；分娩〈n.f.〉</t>
+          <t>[ɡeːbʊʁtzʊʁkʊndə] 出生证明；出生证〈n.f.〉</t>
         </is>
       </c>
       <c r="C782" s="1" t="inlineStr">
@@ -25437,7 +25437,7 @@
       </c>
       <c r="D782" s="1" t="inlineStr">
         <is>
-          <t>出生；起源；生产；分娩</t>
+          <t>出生证明；出生证</t>
         </is>
       </c>
       <c r="E782" s="1" t="inlineStr">
@@ -25651,7 +25651,7 @@
       </c>
       <c r="B789" s="1" t="inlineStr">
         <is>
-          <t>[mʏltɔnə] 容器；箱子；二进制；商业信息网〈n.f.〉</t>
+          <t>[mʏltɔnə] 垃圾桶；垃圾箱〈n.f.〉</t>
         </is>
       </c>
       <c r="C789" s="1" t="inlineStr">
@@ -25661,7 +25661,7 @@
       </c>
       <c r="D789" s="1" t="inlineStr">
         <is>
-          <t>容器；箱子；二进制；商业信息网</t>
+          <t>垃圾桶；垃圾箱</t>
         </is>
       </c>
       <c r="E789" s="1" t="inlineStr">
@@ -25715,17 +25715,17 @@
       </c>
       <c r="B791" s="1" t="inlineStr">
         <is>
-          <t>[beːɡabʊnk] 职业；天命；天职〈n.f.〉</t>
+          <t>[beːɡabʊŋ] 天赋；才能〈n.f.〉</t>
         </is>
       </c>
       <c r="C791" s="1" t="inlineStr">
         <is>
-          <t>beːɡabʊnk</t>
+          <t>beːɡabʊŋ</t>
         </is>
       </c>
       <c r="D791" s="1" t="inlineStr">
         <is>
-          <t>职业；天命；天职</t>
+          <t>天赋；才能</t>
         </is>
       </c>
       <c r="E791" s="1" t="inlineStr">
@@ -25971,7 +25971,7 @@
       </c>
       <c r="B799" s="1" t="inlineStr">
         <is>
-          <t>[aːnəʁkənən] 荣誉；头衔；信用〈v.〉</t>
+          <t>[aːnəʁkənən] 承认；认可；赞赏〈v.〉</t>
         </is>
       </c>
       <c r="C799" s="1" t="inlineStr">
@@ -25981,7 +25981,7 @@
       </c>
       <c r="D799" s="1" t="inlineStr">
         <is>
-          <t>荣誉；头衔；信用</t>
+          <t>承认；认可；赞赏</t>
         </is>
       </c>
       <c r="E799" s="1" t="inlineStr">
@@ -26067,7 +26067,7 @@
       </c>
       <c r="B802" s="1" t="inlineStr">
         <is>
-          <t>[tʏpɪʃɐ] 潮土油〈adv.〉</t>
+          <t>[tʏpɪʃɐ] 典型的；有代表性的〈adv.〉</t>
         </is>
       </c>
       <c r="C802" s="1" t="inlineStr">
@@ -26077,7 +26077,7 @@
       </c>
       <c r="D802" s="1" t="inlineStr">
         <is>
-          <t>潮土油</t>
+          <t>典型的；有代表性的</t>
         </is>
       </c>
       <c r="E802" s="1" t="inlineStr">
@@ -26355,7 +26355,7 @@
       </c>
       <c r="B811" s="1" t="inlineStr">
         <is>
-          <t>[vaʃlapən] 毛巾；面巾〈n.m.〉</t>
+          <t>[vaʃlapən] 洗脸巾；擦洗布；（口）懦弱的人〈n.m.〉〈n.m.〉</t>
         </is>
       </c>
       <c r="C811" s="1" t="inlineStr">
@@ -26365,7 +26365,7 @@
       </c>
       <c r="D811" s="1" t="inlineStr">
         <is>
-          <t>毛巾；面巾</t>
+          <t>洗脸巾；擦洗布；（口）懦弱的人〈n.m.〉</t>
         </is>
       </c>
       <c r="E811" s="1" t="inlineStr">
@@ -26483,7 +26483,7 @@
       </c>
       <c r="B815" s="1" t="inlineStr">
         <is>
-          <t>[ʊntəʁvəʁfən] 科目；主题；臣民〈v.〉</t>
+          <t>[ʊntəʁvəʁfən] 征服；使服从；使屈服〈v.〉</t>
         </is>
       </c>
       <c r="C815" s="1" t="inlineStr">
@@ -26493,7 +26493,7 @@
       </c>
       <c r="D815" s="1" t="inlineStr">
         <is>
-          <t>科目；主题；臣民</t>
+          <t>征服；使服从；使屈服</t>
         </is>
       </c>
       <c r="E815" s="1" t="inlineStr">
@@ -26675,7 +26675,7 @@
       </c>
       <c r="B821" s="1" t="inlineStr">
         <is>
-          <t>[ɡeːbɛk] 蛋糕〈n.〉</t>
+          <t>[ɡeːbɛk] 糕点；烘焙点心〈n.〉</t>
         </is>
       </c>
       <c r="C821" s="1" t="inlineStr">
@@ -26685,7 +26685,7 @@
       </c>
       <c r="D821" s="1" t="inlineStr">
         <is>
-          <t>蛋糕</t>
+          <t>糕点；烘焙点心</t>
         </is>
       </c>
       <c r="E821" s="1" t="inlineStr">
@@ -26707,7 +26707,7 @@
       </c>
       <c r="B822" s="1" t="inlineStr">
         <is>
-          <t>[mɪtfaːʁɡələɡənhaɪt] 举起；帮助；昂扬〈n.f.〉</t>
+          <t>[mɪtfaːʁɡələɡənhaɪt] 搭车机会；顺风车；拼车〈n.f.〉</t>
         </is>
       </c>
       <c r="C822" s="1" t="inlineStr">
@@ -26717,7 +26717,7 @@
       </c>
       <c r="D822" s="1" t="inlineStr">
         <is>
-          <t>举起；帮助；昂扬</t>
+          <t>搭车机会；顺风车；拼车</t>
         </is>
       </c>
       <c r="E822" s="1" t="inlineStr">
@@ -26771,7 +26771,7 @@
       </c>
       <c r="B824" s="1" t="inlineStr">
         <is>
-          <t>[kandɪdiːʁən] 跑；赛跑；奔跑〈v.〉</t>
+          <t>[kandɪdiːʁən] 竞选；参加竞选〈v.〉〈v.〉</t>
         </is>
       </c>
       <c r="C824" s="1" t="inlineStr">
@@ -26781,7 +26781,7 @@
       </c>
       <c r="D824" s="1" t="inlineStr">
         <is>
-          <t>跑；赛跑；奔跑</t>
+          <t>竞选；参加竞选〈v.〉</t>
         </is>
       </c>
       <c r="E824" s="1" t="inlineStr">
@@ -26899,7 +26899,7 @@
       </c>
       <c r="B828" s="1" t="inlineStr">
         <is>
-          <t>[miːt͡sə] 鸟〈n.f.〉</t>
+          <t>[miːt͡sə] 小猫；猫咪（昵称）〈n.f.〉</t>
         </is>
       </c>
       <c r="C828" s="1" t="inlineStr">
@@ -26909,7 +26909,7 @@
       </c>
       <c r="D828" s="1" t="inlineStr">
         <is>
-          <t>鸟</t>
+          <t>小猫；猫咪（昵称）</t>
         </is>
       </c>
       <c r="E828" s="1" t="inlineStr">
@@ -26931,7 +26931,7 @@
       </c>
       <c r="B829" s="1" t="inlineStr">
         <is>
-          <t>[ʊʁspʁʏnɡlɪçə] 要价；索价〈adv.〉</t>
+          <t>[ʊʁspʁʏnɡlɪçə] 原来的；最初的〈adv.〉</t>
         </is>
       </c>
       <c r="C829" s="1" t="inlineStr">
@@ -26941,7 +26941,7 @@
       </c>
       <c r="D829" s="1" t="inlineStr">
         <is>
-          <t>要价；索价</t>
+          <t>原来的；最初的</t>
         </is>
       </c>
       <c r="E829" s="1" t="inlineStr">
@@ -26963,7 +26963,7 @@
       </c>
       <c r="B830" s="1" t="inlineStr">
         <is>
-          <t>[nɔʏntən] 第九；九分之一〈n.〉</t>
+          <t>[nɔʏntən] 第九（应为 Neunte，der/die/das Neunte）〈n.〉</t>
         </is>
       </c>
       <c r="C830" s="1" t="inlineStr">
@@ -26973,7 +26973,7 @@
       </c>
       <c r="D830" s="1" t="inlineStr">
         <is>
-          <t>第九；九分之一</t>
+          <t>第九（应为 Neunte，der/die/das Neunte）</t>
         </is>
       </c>
       <c r="E830" s="1" t="inlineStr">
@@ -27091,12 +27091,12 @@
       </c>
       <c r="B834" s="1" t="inlineStr">
         <is>
-          <t>[kastɪnk] 投掷；铸成品；角色分配；浇铸〈n.〉</t>
+          <t>[kastɪŋ] 投掷；铸成品；角色分配；浇铸〈n.〉</t>
         </is>
       </c>
       <c r="C834" s="1" t="inlineStr">
         <is>
-          <t>kastɪnk</t>
+          <t>kastɪŋ</t>
         </is>
       </c>
       <c r="D834" s="1" t="inlineStr">
@@ -27155,17 +27155,17 @@
       </c>
       <c r="B836" s="1" t="inlineStr">
         <is>
-          <t>[snaːkə] 蛇；拉〈n.m.〉</t>
+          <t>[sneːk] 蛇（英语借词）；德语应为 Schlange〈f.〉〈n.m.〉</t>
         </is>
       </c>
       <c r="C836" s="1" t="inlineStr">
         <is>
-          <t>snaːkə</t>
+          <t>sneːk</t>
         </is>
       </c>
       <c r="D836" s="1" t="inlineStr">
         <is>
-          <t>蛇；拉</t>
+          <t>蛇（英语借词）；德语应为 Schlange〈f.〉</t>
         </is>
       </c>
       <c r="E836" s="1" t="inlineStr">
@@ -27443,7 +27443,7 @@
       </c>
       <c r="B845" s="1" t="inlineStr">
         <is>
-          <t>[beːʁyːmtaɪt] 的变形〈n.f.〉</t>
+          <t>[beːʁyːmtaɪt] 名声；名人；声望〈n.f.〉</t>
         </is>
       </c>
       <c r="C845" s="1" t="inlineStr">
@@ -27453,7 +27453,7 @@
       </c>
       <c r="D845" s="1" t="inlineStr">
         <is>
-          <t>的变形</t>
+          <t>名声；名人；声望</t>
         </is>
       </c>
       <c r="E845" s="1" t="inlineStr">
@@ -27571,7 +27571,7 @@
       </c>
       <c r="B849" s="1" t="inlineStr">
         <is>
-          <t>[klasəntʁəfən] 班级；阶级；种类〈n.〉</t>
+          <t>[klasəntʁəfən] 同学聚会；班级聚会〈n.〉</t>
         </is>
       </c>
       <c r="C849" s="1" t="inlineStr">
@@ -27581,7 +27581,7 @@
       </c>
       <c r="D849" s="1" t="inlineStr">
         <is>
-          <t>班级；阶级；种类</t>
+          <t>同学聚会；班级聚会</t>
         </is>
       </c>
       <c r="E849" s="1" t="inlineStr">
@@ -27667,7 +27667,7 @@
       </c>
       <c r="B852" s="1" t="inlineStr">
         <is>
-          <t>[bɛʁɡɐ] 伯杰〈n.〉</t>
+          <t>[bɛʁɡɐ] 贝格尔（姓氏）〈n.〉</t>
         </is>
       </c>
       <c r="C852" s="1" t="inlineStr">
@@ -27677,7 +27677,7 @@
       </c>
       <c r="D852" s="1" t="inlineStr">
         <is>
-          <t>伯杰</t>
+          <t>贝格尔（姓氏）</t>
         </is>
       </c>
       <c r="E852" s="1" t="inlineStr">
@@ -27699,7 +27699,7 @@
       </c>
       <c r="B853" s="1" t="inlineStr">
         <is>
-          <t>[miːzəʁabəl] 过粘的；过甜的〈adv.〉</t>
+          <t>[miːzəʁabəl] 悲惨的；糟糕的〈adv.〉</t>
         </is>
       </c>
       <c r="C853" s="1" t="inlineStr">
@@ -27709,7 +27709,7 @@
       </c>
       <c r="D853" s="1" t="inlineStr">
         <is>
-          <t>过粘的；过甜的</t>
+          <t>悲惨的；糟糕的</t>
         </is>
       </c>
       <c r="E853" s="1" t="inlineStr">
@@ -27763,7 +27763,7 @@
       </c>
       <c r="B855" s="1" t="inlineStr">
         <is>
-          <t>[hʊʁlɛʏ] 赫尔利〈n.〉</t>
+          <t>[hʊʁlɛʏ] 曲棍球杆；赫尔利式曲棍球〈n.〉〈n.〉</t>
         </is>
       </c>
       <c r="C855" s="1" t="inlineStr">
@@ -27773,7 +27773,7 @@
       </c>
       <c r="D855" s="1" t="inlineStr">
         <is>
-          <t>赫尔利</t>
+          <t>曲棍球杆；赫尔利式曲棍球〈n.〉</t>
         </is>
       </c>
       <c r="E855" s="1" t="inlineStr">
@@ -28147,7 +28147,7 @@
       </c>
       <c r="B867" s="1" t="inlineStr">
         <is>
-          <t>[maxbaːɐ] 能养活的；有生机的〈adj.〉</t>
+          <t>[maxbaːɐ] 可行的；可做到的〈adj.〉</t>
         </is>
       </c>
       <c r="C867" s="1" t="inlineStr">
@@ -28157,7 +28157,7 @@
       </c>
       <c r="D867" s="1" t="inlineStr">
         <is>
-          <t>能养活的；有生机的</t>
+          <t>可行的；可做到的</t>
         </is>
       </c>
       <c r="E867" s="1" t="inlineStr">
@@ -28243,7 +28243,7 @@
       </c>
       <c r="B870" s="1" t="inlineStr">
         <is>
-          <t>[faʁbɪɡə] 条理；斑纹〈adv.〉</t>
+          <t>[faʁbɪɡə] 彩色的；有色的；有色人种的〈adv.〉</t>
         </is>
       </c>
       <c r="C870" s="1" t="inlineStr">
@@ -28253,7 +28253,7 @@
       </c>
       <c r="D870" s="1" t="inlineStr">
         <is>
-          <t>条理；斑纹</t>
+          <t>彩色的；有色的；有色人种的</t>
         </is>
       </c>
       <c r="E870" s="1" t="inlineStr">
@@ -28307,12 +28307,12 @@
       </c>
       <c r="B872" s="1" t="inlineStr">
         <is>
-          <t>[beːlɔʏxtʊnk] 照明；照明设备；舞台灯光〈n.f.〉</t>
+          <t>[beːlɔʏxtʊŋ] 照明；照明设备；舞台灯光〈n.f.〉</t>
         </is>
       </c>
       <c r="C872" s="1" t="inlineStr">
         <is>
-          <t>beːlɔʏxtʊnk</t>
+          <t>beːlɔʏxtʊŋ</t>
         </is>
       </c>
       <c r="D872" s="1" t="inlineStr">
@@ -28371,7 +28371,7 @@
       </c>
       <c r="B874" s="1" t="inlineStr">
         <is>
-          <t>[ʃvaxəs] 地颤动〈adv.〉</t>
+          <t>[ʃvaxəs] 虚弱的；微弱的〈adv.〉</t>
         </is>
       </c>
       <c r="C874" s="1" t="inlineStr">
@@ -28381,7 +28381,7 @@
       </c>
       <c r="D874" s="1" t="inlineStr">
         <is>
-          <t>地颤动</t>
+          <t>虚弱的；微弱的</t>
         </is>
       </c>
       <c r="E874" s="1" t="inlineStr">
@@ -28467,7 +28467,7 @@
       </c>
       <c r="B877" s="1" t="inlineStr">
         <is>
-          <t>[knalhaʁt] 刀剑搏杀〈adv.〉</t>
+          <t>[knalhaʁt] 强硬的；毫不留情的〈adv.〉</t>
         </is>
       </c>
       <c r="C877" s="1" t="inlineStr">
@@ -28477,7 +28477,7 @@
       </c>
       <c r="D877" s="1" t="inlineStr">
         <is>
-          <t>刀剑搏杀</t>
+          <t>强硬的；毫不留情的</t>
         </is>
       </c>
       <c r="E877" s="1" t="inlineStr">
@@ -28691,7 +28691,7 @@
       </c>
       <c r="B884" s="1" t="inlineStr">
         <is>
-          <t>[blɪnt͡səln] 斜视眼；倾向〈v.〉</t>
+          <t>[blɪnt͡səln] 眨眼；闪烁〈v.〉</t>
         </is>
       </c>
       <c r="C884" s="1" t="inlineStr">
@@ -28701,7 +28701,7 @@
       </c>
       <c r="D884" s="1" t="inlineStr">
         <is>
-          <t>斜视眼；倾向</t>
+          <t>眨眼；闪烁</t>
         </is>
       </c>
       <c r="E884" s="1" t="inlineStr">
@@ -29075,7 +29075,7 @@
       </c>
       <c r="B896" s="1" t="inlineStr">
         <is>
-          <t>[ʃaʁfəs] 制裁；镇压；痛击〈adv.〉</t>
+          <t>[ʃaʁfəs] 锋利的；尖锐的；辛辣的〈adv.〉</t>
         </is>
       </c>
       <c r="C896" s="1" t="inlineStr">
@@ -29085,7 +29085,7 @@
       </c>
       <c r="D896" s="1" t="inlineStr">
         <is>
-          <t>制裁；镇压；痛击</t>
+          <t>锋利的；尖锐的；辛辣的</t>
         </is>
       </c>
       <c r="E896" s="1" t="inlineStr">
@@ -29139,12 +29139,12 @@
       </c>
       <c r="B898" s="1" t="inlineStr">
         <is>
-          <t>[çeːfʏ] 打猎时的叫喊；追赶；追猎〈n.m.〉</t>
+          <t>[ʃɛvi] 打猎时的叫喊；追赶；追猎〈n.m.〉</t>
         </is>
       </c>
       <c r="C898" s="1" t="inlineStr">
         <is>
-          <t>çeːfʏ</t>
+          <t>ʃɛvi</t>
         </is>
       </c>
       <c r="D898" s="1" t="inlineStr">
@@ -29235,7 +29235,7 @@
       </c>
       <c r="B901" s="1" t="inlineStr">
         <is>
-          <t>[atʁaktɪfɐ] 高等级带练低等级〈adv.〉</t>
+          <t>[atʁaktɪfɐ] 有吸引力的；迷人的〈adv.〉</t>
         </is>
       </c>
       <c r="C901" s="1" t="inlineStr">
@@ -29245,7 +29245,7 @@
       </c>
       <c r="D901" s="1" t="inlineStr">
         <is>
-          <t>高等级带练低等级</t>
+          <t>有吸引力的；迷人的</t>
         </is>
       </c>
       <c r="E901" s="1" t="inlineStr">
@@ -29331,7 +29331,7 @@
       </c>
       <c r="B904" s="1" t="inlineStr">
         <is>
-          <t>[uːnanɡəməsən] 内衣；内裙〈v.〉</t>
+          <t>[uːnanɡəməsən] 不适当的；不相称的〈v.〉</t>
         </is>
       </c>
       <c r="C904" s="1" t="inlineStr">
@@ -29341,7 +29341,7 @@
       </c>
       <c r="D904" s="1" t="inlineStr">
         <is>
-          <t>内衣；内裙</t>
+          <t>不适当的；不相称的</t>
         </is>
       </c>
       <c r="E904" s="1" t="inlineStr">
@@ -29555,7 +29555,7 @@
       </c>
       <c r="B911" s="1" t="inlineStr">
         <is>
-          <t>[fɛʁtʁətʊnk] 归还；更换；代替者；复位〈n.f.〉</t>
+          <t>[fɛʁtʁətʊnk] 代表；代理；代表机构〈n.f.〉</t>
         </is>
       </c>
       <c r="C911" s="1" t="inlineStr">
@@ -29565,7 +29565,7 @@
       </c>
       <c r="D911" s="1" t="inlineStr">
         <is>
-          <t>归还；更换；代替者；复位</t>
+          <t>代表；代理；代表机构</t>
         </is>
       </c>
       <c r="E911" s="1" t="inlineStr">
@@ -29619,7 +29619,7 @@
       </c>
       <c r="B913" s="1" t="inlineStr">
         <is>
-          <t>[pʁyːɡəlaɪ] 打；挫败；搏动；打浆〈n.f.〉</t>
+          <t>[pʁyːɡəlaɪ] 斗殴；互殴〈n.f.〉</t>
         </is>
       </c>
       <c r="C913" s="1" t="inlineStr">
@@ -29629,7 +29629,7 @@
       </c>
       <c r="D913" s="1" t="inlineStr">
         <is>
-          <t>打；挫败；搏动；打浆</t>
+          <t>斗殴；互殴</t>
         </is>
       </c>
       <c r="E913" s="1" t="inlineStr">
@@ -29651,7 +29651,7 @@
       </c>
       <c r="B914" s="1" t="inlineStr">
         <is>
-          <t>[t͡suːzamənt͡siːən] 齐心协力〈v.〉</t>
+          <t>[t͡suːzamənt͡siːən] 收缩；聚集；合住〈v.〉</t>
         </is>
       </c>
       <c r="C914" s="1" t="inlineStr">
@@ -29661,7 +29661,7 @@
       </c>
       <c r="D914" s="1" t="inlineStr">
         <is>
-          <t>齐心协力</t>
+          <t>收缩；聚集；合住</t>
         </is>
       </c>
       <c r="E914" s="1" t="inlineStr">
@@ -29779,7 +29779,7 @@
       </c>
       <c r="B918" s="1" t="inlineStr">
         <is>
-          <t>[knɛçt] 农场〈n.m.〉</t>
+          <t>[knɛçt] 仆人；雇农；农奴〈n.m.〉</t>
         </is>
       </c>
       <c r="C918" s="1" t="inlineStr">
@@ -29789,7 +29789,7 @@
       </c>
       <c r="D918" s="1" t="inlineStr">
         <is>
-          <t>农场</t>
+          <t>仆人；雇农；农奴</t>
         </is>
       </c>
       <c r="E918" s="1" t="inlineStr">
@@ -29971,7 +29971,7 @@
       </c>
       <c r="B924" s="1" t="inlineStr">
         <is>
-          <t>[ʃiːbə] 滑行的；变化的；滑动〈n.〉</t>
+          <t>[ʃiːbə] （独立词条应为 Schieber）滑块；滑动件；滑阀〈n.m.〉〈n.〉</t>
         </is>
       </c>
       <c r="C924" s="1" t="inlineStr">
@@ -29981,7 +29981,7 @@
       </c>
       <c r="D924" s="1" t="inlineStr">
         <is>
-          <t>滑行的；变化的；滑动</t>
+          <t>（独立词条应为 Schieber）滑块；滑动件；滑阀〈n.m.〉</t>
         </is>
       </c>
       <c r="E924" s="1" t="inlineStr">
@@ -30035,7 +30035,7 @@
       </c>
       <c r="B926" s="1" t="inlineStr">
         <is>
-          <t>[ʃlʊsfɔlɡəʁʊnk] 结论；结尾；推论；缔结〈n.f.〉</t>
+          <t>[ʃlʊsfɔlɡəʁʊnk] 结论；推论〈n.f.〉</t>
         </is>
       </c>
       <c r="C926" s="1" t="inlineStr">
@@ -30045,7 +30045,7 @@
       </c>
       <c r="D926" s="1" t="inlineStr">
         <is>
-          <t>结论；结尾；推论；缔结</t>
+          <t>结论；推论</t>
         </is>
       </c>
       <c r="E926" s="1" t="inlineStr">
@@ -30227,7 +30227,7 @@
       </c>
       <c r="B932" s="1" t="inlineStr">
         <is>
-          <t>[makənt͡siː] 麦肯齐河〈加拿大河流〉〈n.〉</t>
+          <t>[makənt͡siː] 麦肯齐河（加拿大河流）〈n.〉</t>
         </is>
       </c>
       <c r="C932" s="1" t="inlineStr">
@@ -30237,7 +30237,7 @@
       </c>
       <c r="D932" s="1" t="inlineStr">
         <is>
-          <t>麦肯齐河〈加拿大河流〉</t>
+          <t>麦肯齐河（加拿大河流）</t>
         </is>
       </c>
       <c r="E932" s="1" t="inlineStr">
@@ -30291,7 +30291,7 @@
       </c>
       <c r="B934" s="1" t="inlineStr">
         <is>
-          <t>[aʊfʃlaːk] 翻领〈n.m.〉</t>
+          <t>[aʊfʃlaːk] 加价；附加费；冲击；扣杀〈n.m.〉</t>
         </is>
       </c>
       <c r="C934" s="1" t="inlineStr">
@@ -30301,7 +30301,7 @@
       </c>
       <c r="D934" s="1" t="inlineStr">
         <is>
-          <t>翻领</t>
+          <t>加价；附加费；冲击；扣杀</t>
         </is>
       </c>
       <c r="E934" s="1" t="inlineStr">
@@ -30515,7 +30515,7 @@
       </c>
       <c r="B941" s="1" t="inlineStr">
         <is>
-          <t>[zalt] 盐湖城机场；盐湖城市中心〈n.〉</t>
+          <t>[zalt] 盐湖城（Salt Lake City 的简称）〈n.〉</t>
         </is>
       </c>
       <c r="C941" s="1" t="inlineStr">
@@ -30525,7 +30525,7 @@
       </c>
       <c r="D941" s="1" t="inlineStr">
         <is>
-          <t>盐湖城机场；盐湖城市中心</t>
+          <t>盐湖城（Salt Lake City 的简称）</t>
         </is>
       </c>
       <c r="E941" s="1" t="inlineStr">
@@ -30547,7 +30547,7 @@
       </c>
       <c r="B942" s="1" t="inlineStr">
         <is>
-          <t>[aɪnblɪk] 通路；入口；接近〈n.m.〉</t>
+          <t>[aɪnblɪk] 洞察；了解；见识〈n.m.〉</t>
         </is>
       </c>
       <c r="C942" s="1" t="inlineStr">
@@ -30557,7 +30557,7 @@
       </c>
       <c r="D942" s="1" t="inlineStr">
         <is>
-          <t>通路；入口；接近</t>
+          <t>洞察；了解；见识</t>
         </is>
       </c>
       <c r="E942" s="1" t="inlineStr">
@@ -30579,7 +30579,7 @@
       </c>
       <c r="B943" s="1" t="inlineStr">
         <is>
-          <t>[fɔʁləɡən] 屈服；服从；谦恭〈n.〉</t>
+          <t>[fɔʁləɡən] 提交；出示；提出〈n.〉</t>
         </is>
       </c>
       <c r="C943" s="1" t="inlineStr">
@@ -30589,7 +30589,7 @@
       </c>
       <c r="D943" s="1" t="inlineStr">
         <is>
-          <t>屈服；服从；谦恭</t>
+          <t>提交；出示；提出</t>
         </is>
       </c>
       <c r="E943" s="1" t="inlineStr">
@@ -30771,7 +30771,7 @@
       </c>
       <c r="B949" s="1" t="inlineStr">
         <is>
-          <t>[vɛʁbəspoːt] 广告业〈n.m.〉</t>
+          <t>[vɛʁbəspoːt] 广告短片；电视广告〈n.m.〉</t>
         </is>
       </c>
       <c r="C949" s="1" t="inlineStr">
@@ -30781,7 +30781,7 @@
       </c>
       <c r="D949" s="1" t="inlineStr">
         <is>
-          <t>广告业</t>
+          <t>广告短片；电视广告</t>
         </is>
       </c>
       <c r="E949" s="1" t="inlineStr">
@@ -30835,7 +30835,7 @@
       </c>
       <c r="B951" s="1" t="inlineStr">
         <is>
-          <t>[beːʁuːən] 建立基础〈v.〉</t>
+          <t>[beːʁuːən] 基于；以……为基础〈v.〉</t>
         </is>
       </c>
       <c r="C951" s="1" t="inlineStr">
@@ -30845,7 +30845,7 @@
       </c>
       <c r="D951" s="1" t="inlineStr">
         <is>
-          <t>建立基础</t>
+          <t>基于；以……为基础</t>
         </is>
       </c>
       <c r="E951" s="1" t="inlineStr">
@@ -30899,7 +30899,7 @@
       </c>
       <c r="B953" s="1" t="inlineStr">
         <is>
-          <t>[dʊʁçlaʊxt] 殿下；阁下（贵族尊称）〈n.f.〉</t>
+          <t>[dʊʁçlaʊxt] 殿下；阁下（贵族尊称）〈n.n.〉〈n.f.〉</t>
         </is>
       </c>
       <c r="C953" s="1" t="inlineStr">
@@ -30909,7 +30909,7 @@
       </c>
       <c r="D953" s="1" t="inlineStr">
         <is>
-          <t>殿下；阁下（贵族尊称）</t>
+          <t>殿下；阁下（贵族尊称）〈n.n.〉</t>
         </is>
       </c>
       <c r="E953" s="1" t="inlineStr">
@@ -31059,7 +31059,7 @@
       </c>
       <c r="B958" s="1" t="inlineStr">
         <is>
-          <t>[dɪnɡs] 小装置；小机件〈n.〉</t>
+          <t>[dɪnɡs] （叫不出名字的）东西；那玩意儿〈n.〉</t>
         </is>
       </c>
       <c r="C958" s="1" t="inlineStr">
@@ -31069,7 +31069,7 @@
       </c>
       <c r="D958" s="1" t="inlineStr">
         <is>
-          <t>小装置；小机件</t>
+          <t>（叫不出名字的）东西；那玩意儿</t>
         </is>
       </c>
       <c r="E958" s="1" t="inlineStr">
@@ -31091,12 +31091,12 @@
       </c>
       <c r="B959" s="1" t="inlineStr">
         <is>
-          <t>[ɡʁɪnɡɔ] 外国佬〈n.m.〉</t>
+          <t>[ɡʁɪŋɡo] 外国佬〈n.m.〉</t>
         </is>
       </c>
       <c r="C959" s="1" t="inlineStr">
         <is>
-          <t>ɡʁɪnɡɔ</t>
+          <t>ɡʁɪŋɡo</t>
         </is>
       </c>
       <c r="D959" s="1" t="inlineStr">
@@ -31155,7 +31155,7 @@
       </c>
       <c r="B961" s="1" t="inlineStr">
         <is>
-          <t>[ɡʁʊnt͡sən] 咕哝〈n.〉</t>
+          <t>[ɡʁʊnt͡sən] （猪等）发出呼噜声；哼声〈n.〉〈n.〉</t>
         </is>
       </c>
       <c r="C961" s="1" t="inlineStr">
@@ -31165,7 +31165,7 @@
       </c>
       <c r="D961" s="1" t="inlineStr">
         <is>
-          <t>咕哝</t>
+          <t>（猪等）发出呼噜声；哼声〈n.〉</t>
         </is>
       </c>
       <c r="E961" s="1" t="inlineStr">
@@ -31251,7 +31251,7 @@
       </c>
       <c r="B964" s="1" t="inlineStr">
         <is>
-          <t>[kʁɛftɪɡɐ] 鼻涕虫；刺蛾；懒汉〈adv.〉</t>
+          <t>[kʁɛftɪɡɐ] 更强壮的；更有力的〈adv.〉</t>
         </is>
       </c>
       <c r="C964" s="1" t="inlineStr">
@@ -31261,7 +31261,7 @@
       </c>
       <c r="D964" s="1" t="inlineStr">
         <is>
-          <t>鼻涕虫；刺蛾；懒汉</t>
+          <t>更强壮的；更有力的</t>
         </is>
       </c>
       <c r="E964" s="1" t="inlineStr">
@@ -31443,7 +31443,7 @@
       </c>
       <c r="B970" s="1" t="inlineStr">
         <is>
-          <t>[ɡlɛʃən] 一点点；少许；一会儿〈n.〉</t>
+          <t>[ɡlɛʃən] 小玻璃杯；一小杯（酒等）〈n.〉〈n.〉</t>
         </is>
       </c>
       <c r="C970" s="1" t="inlineStr">
@@ -31453,7 +31453,7 @@
       </c>
       <c r="D970" s="1" t="inlineStr">
         <is>
-          <t>一点点；少许；一会儿</t>
+          <t>小玻璃杯；一小杯（酒等）〈n.〉</t>
         </is>
       </c>
       <c r="E970" s="1" t="inlineStr">
@@ -31699,7 +31699,7 @@
       </c>
       <c r="B978" s="1" t="inlineStr">
         <is>
-          <t>[beːfalən] 抓住；逮捕；捉拿〈adj.〉</t>
+          <t>[beːfalən] 侵袭；蔓延到〈v.〉〈adj.〉</t>
         </is>
       </c>
       <c r="C978" s="1" t="inlineStr">
@@ -31709,7 +31709,7 @@
       </c>
       <c r="D978" s="1" t="inlineStr">
         <is>
-          <t>抓住；逮捕；捉拿</t>
+          <t>侵袭；蔓延到〈v.〉</t>
         </is>
       </c>
       <c r="E978" s="1" t="inlineStr">
@@ -31731,7 +31731,7 @@
       </c>
       <c r="B979" s="1" t="inlineStr">
         <is>
-          <t>[ʃmiːdən] 锻炼；伪造；锻造；锻件〈n.〉</t>
+          <t>[ʃmiːdən] 锻造；打铁〈v.〉〈n.〉</t>
         </is>
       </c>
       <c r="C979" s="1" t="inlineStr">
@@ -31741,7 +31741,7 @@
       </c>
       <c r="D979" s="1" t="inlineStr">
         <is>
-          <t>锻炼；伪造；锻造；锻件</t>
+          <t>锻造；打铁〈v.〉</t>
         </is>
       </c>
       <c r="E979" s="1" t="inlineStr">
@@ -31891,7 +31891,7 @@
       </c>
       <c r="B984" s="1" t="inlineStr">
         <is>
-          <t>[ɡlaɪçʊnk] 相等；等式；平衡；方程式〈n.f.〉</t>
+          <t>[ɡlaɪçʊnk] 等式；方程式〈f.〉〈n.f.〉</t>
         </is>
       </c>
       <c r="C984" s="1" t="inlineStr">
@@ -31901,7 +31901,7 @@
       </c>
       <c r="D984" s="1" t="inlineStr">
         <is>
-          <t>相等；等式；平衡；方程式</t>
+          <t>等式；方程式〈f.〉</t>
         </is>
       </c>
       <c r="E984" s="1" t="inlineStr">
@@ -32019,7 +32019,7 @@
       </c>
       <c r="B988" s="1" t="inlineStr">
         <is>
-          <t>[fɛʁʃlʊnɡən] 全部；完整；充满的；完全的〈v.〉</t>
+          <t>[fɛʁʃlʊnɡən] 吞噬的；缠绕的〈v.〉</t>
         </is>
       </c>
       <c r="C988" s="1" t="inlineStr">
@@ -32029,7 +32029,7 @@
       </c>
       <c r="D988" s="1" t="inlineStr">
         <is>
-          <t>全部；完整；充满的；完全的</t>
+          <t>吞噬的；缠绕的</t>
         </is>
       </c>
       <c r="E988" s="1" t="inlineStr">
@@ -32115,7 +32115,7 @@
       </c>
       <c r="B991" s="1" t="inlineStr">
         <is>
-          <t>[zɪɡnatuːɐ] 签字；识别标志；调号；签名附件〈n.f.〉</t>
+          <t>[zɪɡnatuːɐ] 标记；特征；（图书馆）索书号〈n.f.〉〈n.f.〉</t>
         </is>
       </c>
       <c r="C991" s="1" t="inlineStr">
@@ -32125,7 +32125,7 @@
       </c>
       <c r="D991" s="1" t="inlineStr">
         <is>
-          <t>签字；识别标志；调号；签名附件</t>
+          <t>标记；特征；（图书馆）索书号〈n.f.〉</t>
         </is>
       </c>
       <c r="E991" s="1" t="inlineStr">
@@ -32147,7 +32147,7 @@
       </c>
       <c r="B992" s="1" t="inlineStr">
         <is>
-          <t>[ʊnbədɔʏtənt] 不足取地〈adv.〉</t>
+          <t>[ʊnbədɔʏtənt] 不重要的；无足轻重的；微不足道的〈adv.〉</t>
         </is>
       </c>
       <c r="C992" s="1" t="inlineStr">
@@ -32157,7 +32157,7 @@
       </c>
       <c r="D992" s="1" t="inlineStr">
         <is>
-          <t>不足取地</t>
+          <t>不重要的；无足轻重的；微不足道的</t>
         </is>
       </c>
       <c r="E992" s="1" t="inlineStr">
@@ -32531,7 +32531,7 @@
       </c>
       <c r="B1004" s="1" t="inlineStr">
         <is>
-          <t>[bɪlɪɡəs] 假冒商品；敲去〈adv.〉</t>
+          <t>[bɪlɪɡəs] 便宜的；廉价的〈adv.〉</t>
         </is>
       </c>
       <c r="C1004" s="1" t="inlineStr">
@@ -32541,7 +32541,7 @@
       </c>
       <c r="D1004" s="1" t="inlineStr">
         <is>
-          <t>假冒商品；敲去</t>
+          <t>便宜的；廉价的</t>
         </is>
       </c>
       <c r="E1004" s="1" t="inlineStr">
@@ -32819,7 +32819,7 @@
       </c>
       <c r="B1013" s="1" t="inlineStr">
         <is>
-          <t>[t͡saːltaːk] 季度结帐日〈n.m.〉</t>
+          <t>[t͡saːltaːk] 发薪日〈n.m.〉</t>
         </is>
       </c>
       <c r="C1013" s="1" t="inlineStr">
@@ -32829,7 +32829,7 @@
       </c>
       <c r="D1013" s="1" t="inlineStr">
         <is>
-          <t>季度结帐日</t>
+          <t>发薪日</t>
         </is>
       </c>
       <c r="E1013" s="1" t="inlineStr">
@@ -33075,7 +33075,7 @@
       </c>
       <c r="B1021" s="1" t="inlineStr">
         <is>
-          <t>[ɡɛʃɛftsʁaɪzə] 生意；事情；业务〈n.f.〉</t>
+          <t>[ɡɛʃɛftsʁaɪzə] 出差；商务旅行〈n.f.〉</t>
         </is>
       </c>
       <c r="C1021" s="1" t="inlineStr">
@@ -33085,7 +33085,7 @@
       </c>
       <c r="D1021" s="1" t="inlineStr">
         <is>
-          <t>生意；事情；业务</t>
+          <t>出差；商务旅行</t>
         </is>
       </c>
       <c r="E1021" s="1" t="inlineStr">
@@ -33107,7 +33107,7 @@
       </c>
       <c r="B1022" s="1" t="inlineStr">
         <is>
-          <t>[mɪtmənʃən] 同胞；周围的人；同仁〈n.〉</t>
+          <t>[mɪtmənʃən] 同胞；周围的人；同仁〈n.m.〉〈n.〉</t>
         </is>
       </c>
       <c r="C1022" s="1" t="inlineStr">
@@ -33117,7 +33117,7 @@
       </c>
       <c r="D1022" s="1" t="inlineStr">
         <is>
-          <t>同胞；周围的人；同仁</t>
+          <t>同胞；周围的人；同仁〈n.m.〉</t>
         </is>
       </c>
       <c r="E1022" s="1" t="inlineStr">
@@ -33139,7 +33139,7 @@
       </c>
       <c r="B1023" s="1" t="inlineStr">
         <is>
-          <t>[fɔʁt͡sʏɡliːç] 精巧地；敏锐地〈adv.〉</t>
+          <t>[fɔʁt͡sʏɡliːç] 极好的；卓越的〈adv.〉</t>
         </is>
       </c>
       <c r="C1023" s="1" t="inlineStr">
@@ -33149,7 +33149,7 @@
       </c>
       <c r="D1023" s="1" t="inlineStr">
         <is>
-          <t>精巧地；敏锐地</t>
+          <t>极好的；卓越的</t>
         </is>
       </c>
       <c r="E1023" s="1" t="inlineStr">
@@ -33395,7 +33395,7 @@
       </c>
       <c r="B1031" s="1" t="inlineStr">
         <is>
-          <t>[mɪsbʁaʊxən] 板岩；页岩；提名名单〈v.〉</t>
+          <t>[mɪsbʁaʊxən] 滥用；虐待〈v.〉</t>
         </is>
       </c>
       <c r="C1031" s="1" t="inlineStr">
@@ -33405,7 +33405,7 @@
       </c>
       <c r="D1031" s="1" t="inlineStr">
         <is>
-          <t>板岩；页岩；提名名单</t>
+          <t>滥用；虐待</t>
         </is>
       </c>
       <c r="E1031" s="1" t="inlineStr">
@@ -33491,7 +33491,7 @@
       </c>
       <c r="B1034" s="1" t="inlineStr">
         <is>
-          <t>[ʁɛalə] 在...之后〈adv.〉</t>
+          <t>[ʁɛalə] 真实的；实际的〈adv.〉</t>
         </is>
       </c>
       <c r="C1034" s="1" t="inlineStr">
@@ -33501,7 +33501,7 @@
       </c>
       <c r="D1034" s="1" t="inlineStr">
         <is>
-          <t>在...之后</t>
+          <t>真实的；实际的</t>
         </is>
       </c>
       <c r="E1034" s="1" t="inlineStr">
@@ -33555,7 +33555,7 @@
       </c>
       <c r="B1036" s="1" t="inlineStr">
         <is>
-          <t>[ʃpalt] 裂缝；裂沟；裂开；分裂〈n.m.〉</t>
+          <t>[ʃpalt] 裂缝；裂隙〈n.m.〉〈n.m.〉</t>
         </is>
       </c>
       <c r="C1036" s="1" t="inlineStr">
@@ -33565,7 +33565,7 @@
       </c>
       <c r="D1036" s="1" t="inlineStr">
         <is>
-          <t>裂缝；裂沟；裂开；分裂</t>
+          <t>裂缝；裂隙〈n.m.〉</t>
         </is>
       </c>
       <c r="E1036" s="1" t="inlineStr">
@@ -33651,7 +33651,7 @@
       </c>
       <c r="B1039" s="1" t="inlineStr">
         <is>
-          <t>[ʊntəʁneːmɐ] 路；道路；公路〈n.m.〉</t>
+          <t>[ʊntəʁneːmɐ] 企业家；经营者〈n.m.〉</t>
         </is>
       </c>
       <c r="C1039" s="1" t="inlineStr">
@@ -33661,7 +33661,7 @@
       </c>
       <c r="D1039" s="1" t="inlineStr">
         <is>
-          <t>路；道路；公路</t>
+          <t>企业家；经营者</t>
         </is>
       </c>
       <c r="E1039" s="1" t="inlineStr">
@@ -33747,7 +33747,7 @@
       </c>
       <c r="B1042" s="1" t="inlineStr">
         <is>
-          <t>[ɡlɛnt͡sən] 闪烁；发光；光彩夺目〈n.m.〉</t>
+          <t>[ɡlɛnt͡sən] 发光；闪耀；闪烁〈v.〉〈n.m.〉</t>
         </is>
       </c>
       <c r="C1042" s="1" t="inlineStr">
@@ -33757,7 +33757,7 @@
       </c>
       <c r="D1042" s="1" t="inlineStr">
         <is>
-          <t>闪烁；发光；光彩夺目</t>
+          <t>发光；闪耀；闪烁〈v.〉</t>
         </is>
       </c>
       <c r="E1042" s="1" t="inlineStr">
@@ -33843,7 +33843,7 @@
       </c>
       <c r="B1045" s="1" t="inlineStr">
         <is>
-          <t>[laːdʏʃaft] 贵妇身分；夫人；小姐〈n.f.〉</t>
+          <t>[laːdʏʃaft] 该词非标准德语词（源自英语 Ladyship，阁下、夫人身分）〈n.f.〉</t>
         </is>
       </c>
       <c r="C1045" s="1" t="inlineStr">
@@ -33853,7 +33853,7 @@
       </c>
       <c r="D1045" s="1" t="inlineStr">
         <is>
-          <t>贵妇身分；夫人；小姐</t>
+          <t>该词非标准德语词（源自英语 Ladyship，阁下、夫人身分）</t>
         </is>
       </c>
       <c r="E1045" s="1" t="inlineStr">
@@ -33971,7 +33971,7 @@
       </c>
       <c r="B1049" s="1" t="inlineStr">
         <is>
-          <t>[ɡeːzʊndɐ] 常识〈adv.〉</t>
+          <t>[ɡeːzʊndɐ] 健康的〈adv.〉</t>
         </is>
       </c>
       <c r="C1049" s="1" t="inlineStr">
@@ -33981,7 +33981,7 @@
       </c>
       <c r="D1049" s="1" t="inlineStr">
         <is>
-          <t>常识</t>
+          <t>健康的</t>
         </is>
       </c>
       <c r="E1049" s="1" t="inlineStr">
@@ -34099,7 +34099,7 @@
       </c>
       <c r="B1053" s="1" t="inlineStr">
         <is>
-          <t>[teːkə] 计算器；计算者；柜台〈n.f.〉</t>
+          <t>[teːkə] 柜台；吧台〈n.f.〉</t>
         </is>
       </c>
       <c r="C1053" s="1" t="inlineStr">
@@ -34109,7 +34109,7 @@
       </c>
       <c r="D1053" s="1" t="inlineStr">
         <is>
-          <t>计算器；计算者；柜台</t>
+          <t>柜台；吧台</t>
         </is>
       </c>
       <c r="E1053" s="1" t="inlineStr">
@@ -34227,7 +34227,7 @@
       </c>
       <c r="B1057" s="1" t="inlineStr">
         <is>
-          <t>[fɔʁbaɪɡeːən] 呼叫；访问；打电话〈v.〉</t>
+          <t>[fɔʁbaɪɡeːən] 走过；经过〈v.〉</t>
         </is>
       </c>
       <c r="C1057" s="1" t="inlineStr">
@@ -34237,7 +34237,7 @@
       </c>
       <c r="D1057" s="1" t="inlineStr">
         <is>
-          <t>呼叫；访问；打电话</t>
+          <t>走过；经过</t>
         </is>
       </c>
       <c r="E1057" s="1" t="inlineStr">
@@ -34323,7 +34323,7 @@
       </c>
       <c r="B1060" s="1" t="inlineStr">
         <is>
-          <t>[fʊnkt͡sjoːnən] 连结；连锁；相关〈n.〉</t>
+          <t>[fʊnkt͡sjoːnən] 功能；职能；函数〈n.〉</t>
         </is>
       </c>
       <c r="C1060" s="1" t="inlineStr">
@@ -34333,7 +34333,7 @@
       </c>
       <c r="D1060" s="1" t="inlineStr">
         <is>
-          <t>连结；连锁；相关</t>
+          <t>功能；职能；函数</t>
         </is>
       </c>
       <c r="E1060" s="1" t="inlineStr">
@@ -34611,7 +34611,7 @@
       </c>
       <c r="B1069" s="1" t="inlineStr">
         <is>
-          <t>[kaːpʊtmaxən] 休息；中断；破裂处〈v.〉</t>
+          <t>[kaːpʊtmaxən] 弄坏；损坏；破坏〈v.〉〈v.〉</t>
         </is>
       </c>
       <c r="C1069" s="1" t="inlineStr">
@@ -34621,7 +34621,7 @@
       </c>
       <c r="D1069" s="1" t="inlineStr">
         <is>
-          <t>休息；中断；破裂处</t>
+          <t>弄坏；损坏；破坏〈v.〉</t>
         </is>
       </c>
       <c r="E1069" s="1" t="inlineStr">
@@ -34739,7 +34739,7 @@
       </c>
       <c r="B1073" s="1" t="inlineStr">
         <is>
-          <t>[vɪkəln] 风；气息；气味〈v.〉</t>
+          <t>[vɪkəln] 包裹；缠绕〈v.〉</t>
         </is>
       </c>
       <c r="C1073" s="1" t="inlineStr">
@@ -34749,7 +34749,7 @@
       </c>
       <c r="D1073" s="1" t="inlineStr">
         <is>
-          <t>风；气息；气味</t>
+          <t>包裹；缠绕</t>
         </is>
       </c>
       <c r="E1073" s="1" t="inlineStr">
@@ -34835,7 +34835,7 @@
       </c>
       <c r="B1076" s="1" t="inlineStr">
         <is>
-          <t>[ʃvaxɐ] 昏厥；昏倒；模糊的；微弱的〈adv.〉</t>
+          <t>[ʃvaxɐ] 虚弱的；微弱的〈adv.〉</t>
         </is>
       </c>
       <c r="C1076" s="1" t="inlineStr">
@@ -34845,7 +34845,7 @@
       </c>
       <c r="D1076" s="1" t="inlineStr">
         <is>
-          <t>昏厥；昏倒；模糊的；微弱的</t>
+          <t>虚弱的；微弱的</t>
         </is>
       </c>
       <c r="E1076" s="1" t="inlineStr">
@@ -34963,7 +34963,7 @@
       </c>
       <c r="B1080" s="1" t="inlineStr">
         <is>
-          <t>[maɡt] 女性；女人〈n.f.〉</t>
+          <t>[maɡt] 女仆；侍女；少女〈n.f.〉</t>
         </is>
       </c>
       <c r="C1080" s="1" t="inlineStr">
@@ -34973,7 +34973,7 @@
       </c>
       <c r="D1080" s="1" t="inlineStr">
         <is>
-          <t>女性；女人</t>
+          <t>女仆；侍女；少女</t>
         </is>
       </c>
       <c r="E1080" s="1" t="inlineStr">
@@ -35347,7 +35347,7 @@
       </c>
       <c r="B1092" s="1" t="inlineStr">
         <is>
-          <t>[foːʁaʁbaɪtɐ] 领班；工头；陪审长〈n.m.〉</t>
+          <t>[foːʁaʁbaɪtɐ] 领班；工头〈n.m.〉〈n.m.〉</t>
         </is>
       </c>
       <c r="C1092" s="1" t="inlineStr">
@@ -35357,7 +35357,7 @@
       </c>
       <c r="D1092" s="1" t="inlineStr">
         <is>
-          <t>领班；工头；陪审长</t>
+          <t>领班；工头〈n.m.〉</t>
         </is>
       </c>
       <c r="E1092" s="1" t="inlineStr">
@@ -35379,7 +35379,7 @@
       </c>
       <c r="B1093" s="1" t="inlineStr">
         <is>
-          <t>[ʃʊbs] 刺；戳；袋子〈n.m.〉</t>
+          <t>[ʃʊbs] 推；推撞〈n.m.〉</t>
         </is>
       </c>
       <c r="C1093" s="1" t="inlineStr">
@@ -35389,7 +35389,7 @@
       </c>
       <c r="D1093" s="1" t="inlineStr">
         <is>
-          <t>刺；戳；袋子</t>
+          <t>推；推撞</t>
         </is>
       </c>
       <c r="E1093" s="1" t="inlineStr">
@@ -35411,12 +35411,12 @@
       </c>
       <c r="B1094" s="1" t="inlineStr">
         <is>
-          <t>[naɪɡʊnk] 程度；坡度；顶点〈n.f.〉</t>
+          <t>[naɪɡʊŋ] 程度；坡度；顶点〈n.f.〉</t>
         </is>
       </c>
       <c r="C1094" s="1" t="inlineStr">
         <is>
-          <t>naɪɡʊnk</t>
+          <t>naɪɡʊŋ</t>
         </is>
       </c>
       <c r="D1094" s="1" t="inlineStr">
@@ -35603,12 +35603,12 @@
       </c>
       <c r="B1100" s="1" t="inlineStr">
         <is>
-          <t>[jɪnk] 中国的殷代〈n.〉</t>
+          <t>[jɪŋ] 中国的殷代〈n.〉</t>
         </is>
       </c>
       <c r="C1100" s="1" t="inlineStr">
         <is>
-          <t>jɪnk</t>
+          <t>jɪŋ</t>
         </is>
       </c>
       <c r="D1100" s="1" t="inlineStr">
@@ -35699,7 +35699,7 @@
       </c>
       <c r="B1103" s="1" t="inlineStr">
         <is>
-          <t>[aɪntʁaɡən] 寄存器；记录；登记簿〈v.〉</t>
+          <t>[aɪntʁaɡən] 登记；填入；记入；注册〈v.〉</t>
         </is>
       </c>
       <c r="C1103" s="1" t="inlineStr">
@@ -35709,7 +35709,7 @@
       </c>
       <c r="D1103" s="1" t="inlineStr">
         <is>
-          <t>寄存器；记录；登记簿</t>
+          <t>登记；填入；记入；注册</t>
         </is>
       </c>
       <c r="E1103" s="1" t="inlineStr">
@@ -35731,7 +35731,7 @@
       </c>
       <c r="B1104" s="1" t="inlineStr">
         <is>
-          <t>[kaf] 倾销商品；转出〈n.〉</t>
+          <t>[kaf] 穷乡僻壤；偏僻小村〈n.〉</t>
         </is>
       </c>
       <c r="C1104" s="1" t="inlineStr">
@@ -35741,7 +35741,7 @@
       </c>
       <c r="D1104" s="1" t="inlineStr">
         <is>
-          <t>倾销商品；转出</t>
+          <t>穷乡僻壤；偏僻小村</t>
         </is>
       </c>
       <c r="E1104" s="1" t="inlineStr">
@@ -35859,7 +35859,7 @@
       </c>
       <c r="B1108" s="1" t="inlineStr">
         <is>
-          <t>[aʁtəʁiː] 动脉；干道；要道〈n.f.〉</t>
+          <t>[aʁtəʁiː] 动脉〈n.f.〉〈n.f.〉</t>
         </is>
       </c>
       <c r="C1108" s="1" t="inlineStr">
@@ -35869,7 +35869,7 @@
       </c>
       <c r="D1108" s="1" t="inlineStr">
         <is>
-          <t>动脉；干道；要道</t>
+          <t>动脉〈n.f.〉</t>
         </is>
       </c>
       <c r="E1108" s="1" t="inlineStr">
@@ -35923,7 +35923,7 @@
       </c>
       <c r="B1110" s="1" t="inlineStr">
         <is>
-          <t>[ɡʁoːbə] 瞎猜；瞎估计〈adv.〉</t>
+          <t>[ɡʁoːbə] 粗糙的；粗略的〈adj.〉〈adv.〉</t>
         </is>
       </c>
       <c r="C1110" s="1" t="inlineStr">
@@ -35933,7 +35933,7 @@
       </c>
       <c r="D1110" s="1" t="inlineStr">
         <is>
-          <t>瞎猜；瞎估计</t>
+          <t>粗糙的；粗略的〈adj.〉</t>
         </is>
       </c>
       <c r="E1110" s="1" t="inlineStr">
@@ -35955,7 +35955,7 @@
       </c>
       <c r="B1111" s="1" t="inlineStr">
         <is>
-          <t>[kɔkpiːt] 飞行；射程；逃走〈n.〉</t>
+          <t>[kɔkpiːt] 驾驶舱；座舱〈n.〉</t>
         </is>
       </c>
       <c r="C1111" s="1" t="inlineStr">
@@ -35965,7 +35965,7 @@
       </c>
       <c r="D1111" s="1" t="inlineStr">
         <is>
-          <t>飞行；射程；逃走</t>
+          <t>驾驶舱；座舱</t>
         </is>
       </c>
       <c r="E1111" s="1" t="inlineStr">
@@ -35987,7 +35987,7 @@
       </c>
       <c r="B1112" s="1" t="inlineStr">
         <is>
-          <t>[beːta] 乙种〈n.〉</t>
+          <t>[beːta] 贝塔（希腊字母第二个）；测试版〈n.〉〈n.〉</t>
         </is>
       </c>
       <c r="C1112" s="1" t="inlineStr">
@@ -35997,7 +35997,7 @@
       </c>
       <c r="D1112" s="1" t="inlineStr">
         <is>
-          <t>乙种</t>
+          <t>贝塔（希腊字母第二个）；测试版〈n.〉</t>
         </is>
       </c>
       <c r="E1112" s="1" t="inlineStr">
@@ -36211,7 +36211,7 @@
       </c>
       <c r="B1119" s="1" t="inlineStr">
         <is>
-          <t>[ʃlʏpfən] 阴影；影线；剖面线〈n.〉</t>
+          <t>[ʃlʏpfən] 孵化；钻出；溜进；穿上〈n.〉</t>
         </is>
       </c>
       <c r="C1119" s="1" t="inlineStr">
@@ -36221,7 +36221,7 @@
       </c>
       <c r="D1119" s="1" t="inlineStr">
         <is>
-          <t>阴影；影线；剖面线</t>
+          <t>孵化；钻出；溜进；穿上</t>
         </is>
       </c>
       <c r="E1119" s="1" t="inlineStr">
@@ -36275,12 +36275,12 @@
       </c>
       <c r="B1121" s="1" t="inlineStr">
         <is>
-          <t>[bɛʃɛftɪɡʊnk] 职业；占有；占有期〈n.f.〉</t>
+          <t>[bɛʃɛftɪɡʊŋ] 职业；占有；占有期〈n.f.〉</t>
         </is>
       </c>
       <c r="C1121" s="1" t="inlineStr">
         <is>
-          <t>bɛʃɛftɪɡʊnk</t>
+          <t>bɛʃɛftɪɡʊŋ</t>
         </is>
       </c>
       <c r="D1121" s="1" t="inlineStr">
@@ -36307,7 +36307,7 @@
       </c>
       <c r="B1122" s="1" t="inlineStr">
         <is>
-          <t>[ʃtandhaltən] 站立；站住；停顿〈v.〉</t>
+          <t>[ʃtandhaltən] 经受住；顶住；抵抗〈v.〉</t>
         </is>
       </c>
       <c r="C1122" s="1" t="inlineStr">
@@ -36317,7 +36317,7 @@
       </c>
       <c r="D1122" s="1" t="inlineStr">
         <is>
-          <t>站立；站住；停顿</t>
+          <t>经受住；顶住；抵抗</t>
         </is>
       </c>
       <c r="E1122" s="1" t="inlineStr">
@@ -36371,7 +36371,7 @@
       </c>
       <c r="B1124" s="1" t="inlineStr">
         <is>
-          <t>[ʃnʏʁzənkəl] 长靴；踢；解雇〈n.m.〉</t>
+          <t>[ʃnʏʁzənkəl] 鞋带〈n.m.〉</t>
         </is>
       </c>
       <c r="C1124" s="1" t="inlineStr">
@@ -36381,7 +36381,7 @@
       </c>
       <c r="D1124" s="1" t="inlineStr">
         <is>
-          <t>长靴；踢；解雇</t>
+          <t>鞋带</t>
         </is>
       </c>
       <c r="E1124" s="1" t="inlineStr">
@@ -36467,7 +36467,7 @@
       </c>
       <c r="B1127" s="1" t="inlineStr">
         <is>
-          <t>[ʃaɪtəʁhaʊfən] 葬礼；出殡〈n.m.〉</t>
+          <t>[ʃaɪtəʁhaʊfən] 火葬柴堆；焚尸柴堆〈n.m.〉</t>
         </is>
       </c>
       <c r="C1127" s="1" t="inlineStr">
@@ -36477,7 +36477,7 @@
       </c>
       <c r="D1127" s="1" t="inlineStr">
         <is>
-          <t>葬礼；出殡</t>
+          <t>火葬柴堆；焚尸柴堆</t>
         </is>
       </c>
       <c r="E1127" s="1" t="inlineStr">
@@ -36499,7 +36499,7 @@
       </c>
       <c r="B1128" s="1" t="inlineStr">
         <is>
-          <t>[kuːlɪsən] 变化；移动；轮班〈n.〉</t>
+          <t>[kuːlɪsən] 舞台布景；布景片〈n.〉</t>
         </is>
       </c>
       <c r="C1128" s="1" t="inlineStr">
@@ -36509,7 +36509,7 @@
       </c>
       <c r="D1128" s="1" t="inlineStr">
         <is>
-          <t>变化；移动；轮班</t>
+          <t>舞台布景；布景片</t>
         </is>
       </c>
       <c r="E1128" s="1" t="inlineStr">
@@ -36595,7 +36595,7 @@
       </c>
       <c r="B1131" s="1" t="inlineStr">
         <is>
-          <t>[vɪnk] 点头示意；招手；小河〈n.m.〉</t>
+          <t>[vɪnk] 示意；眼色；暗示〈n.m.〉</t>
         </is>
       </c>
       <c r="C1131" s="1" t="inlineStr">
@@ -36605,7 +36605,7 @@
       </c>
       <c r="D1131" s="1" t="inlineStr">
         <is>
-          <t>点头示意；招手；小河</t>
+          <t>示意；眼色；暗示</t>
         </is>
       </c>
       <c r="E1131" s="1" t="inlineStr">
@@ -36691,7 +36691,7 @@
       </c>
       <c r="B1134" s="1" t="inlineStr">
         <is>
-          <t>[naːtʏʁlɪçɐ] 白痴；自然的；自然界的；本能的〈adv.〉</t>
+          <t>[naːtʏʁlɪçɐ] 更自然的；自然的〈adv.〉</t>
         </is>
       </c>
       <c r="C1134" s="1" t="inlineStr">
@@ -36701,7 +36701,7 @@
       </c>
       <c r="D1134" s="1" t="inlineStr">
         <is>
-          <t>白痴；自然的；自然界的；本能的</t>
+          <t>更自然的；自然的</t>
         </is>
       </c>
       <c r="E1134" s="1" t="inlineStr">
@@ -36723,7 +36723,7 @@
       </c>
       <c r="B1135" s="1" t="inlineStr">
         <is>
-          <t>[ʁɪsə] 形袖章〈n.〉</t>
+          <t>[ʁɪsə] 裂缝；裂纹；裂口〈n.〉</t>
         </is>
       </c>
       <c r="C1135" s="1" t="inlineStr">
@@ -36733,7 +36733,7 @@
       </c>
       <c r="D1135" s="1" t="inlineStr">
         <is>
-          <t>形袖章</t>
+          <t>裂缝；裂纹；裂口</t>
         </is>
       </c>
       <c r="E1135" s="1" t="inlineStr">
@@ -36915,7 +36915,7 @@
       </c>
       <c r="B1141" s="1" t="inlineStr">
         <is>
-          <t>[ʃtɪftən] 消失；不见〈v.〉</t>
+          <t>[ʃtɪftən] 捐赠；创立；缔造〈v.〉</t>
         </is>
       </c>
       <c r="C1141" s="1" t="inlineStr">
@@ -36925,7 +36925,7 @@
       </c>
       <c r="D1141" s="1" t="inlineStr">
         <is>
-          <t>消失；不见</t>
+          <t>捐赠；创立；缔造</t>
         </is>
       </c>
       <c r="E1141" s="1" t="inlineStr">
@@ -36947,7 +36947,7 @@
       </c>
       <c r="B1142" s="1" t="inlineStr">
         <is>
-          <t>[ɛʁhɔbənən] 和...在一起；以；由于〈v.〉</t>
+          <t>[ɛʁhɔbənən] 举起的；抬高的；升起的〈v.〉</t>
         </is>
       </c>
       <c r="C1142" s="1" t="inlineStr">
@@ -36957,7 +36957,7 @@
       </c>
       <c r="D1142" s="1" t="inlineStr">
         <is>
-          <t>和...在一起；以；由于</t>
+          <t>举起的；抬高的；升起的</t>
         </is>
       </c>
       <c r="E1142" s="1" t="inlineStr">
@@ -37203,7 +37203,7 @@
       </c>
       <c r="B1150" s="1" t="inlineStr">
         <is>
-          <t>[pʊəʁtɔ] 波多黎各〈n.〉</t>
+          <t>[pʊəʁtɔ] 港口〈n.〉</t>
         </is>
       </c>
       <c r="C1150" s="1" t="inlineStr">
@@ -37213,7 +37213,7 @@
       </c>
       <c r="D1150" s="1" t="inlineStr">
         <is>
-          <t>波多黎各</t>
+          <t>港口</t>
         </is>
       </c>
       <c r="E1150" s="1" t="inlineStr">
@@ -37299,7 +37299,7 @@
       </c>
       <c r="B1153" s="1" t="inlineStr">
         <is>
-          <t>[ɔfənzɪfə] 令人不快的；侮辱的；攻击性的；攻击的〈adv.〉</t>
+          <t>[ɔfənzɪfə] 攻势；进攻（名词，die Offensive；形容词为 offensiv）〈adv.〉</t>
         </is>
       </c>
       <c r="C1153" s="1" t="inlineStr">
@@ -37309,7 +37309,7 @@
       </c>
       <c r="D1153" s="1" t="inlineStr">
         <is>
-          <t>令人不快的；侮辱的；攻击性的；攻击的</t>
+          <t>攻势；进攻（名词，die Offensive；形容词为 offensiv）</t>
         </is>
       </c>
       <c r="E1153" s="1" t="inlineStr">
@@ -37331,12 +37331,12 @@
       </c>
       <c r="B1154" s="1" t="inlineStr">
         <is>
-          <t>[beːaʊptʊnk] 断言；主张；宣称〈n.f.〉</t>
+          <t>[beːaʊptʊŋ] 断言；主张；宣称〈n.f.〉</t>
         </is>
       </c>
       <c r="C1154" s="1" t="inlineStr">
         <is>
-          <t>beːaʊptʊnk</t>
+          <t>beːaʊptʊŋ</t>
         </is>
       </c>
       <c r="D1154" s="1" t="inlineStr">
@@ -37651,7 +37651,7 @@
       </c>
       <c r="B1164" s="1" t="inlineStr">
         <is>
-          <t>[eːdʊaʁt] 忏悔者爱德华〈n.〉</t>
+          <t>[eːdʊaʁt] 爱德华（人名）〈n.〉</t>
         </is>
       </c>
       <c r="C1164" s="1" t="inlineStr">
@@ -37661,7 +37661,7 @@
       </c>
       <c r="D1164" s="1" t="inlineStr">
         <is>
-          <t>忏悔者爱德华</t>
+          <t>爱德华（人名）</t>
         </is>
       </c>
       <c r="E1164" s="1" t="inlineStr">
@@ -37715,7 +37715,7 @@
       </c>
       <c r="B1166" s="1" t="inlineStr">
         <is>
-          <t>[fɛʁhaʊən] 打；拍击〈v.〉</t>
+          <t>[fɛʁhaʊən] 砍坏；痛打；搞砸（考试等）〈v.〉〈v.〉</t>
         </is>
       </c>
       <c r="C1166" s="1" t="inlineStr">
@@ -37725,7 +37725,7 @@
       </c>
       <c r="D1166" s="1" t="inlineStr">
         <is>
-          <t>打；拍击</t>
+          <t>砍坏；痛打；搞砸（考试等）〈v.〉</t>
         </is>
       </c>
       <c r="E1166" s="1" t="inlineStr">
@@ -37811,7 +37811,7 @@
       </c>
       <c r="B1169" s="1" t="inlineStr">
         <is>
-          <t>[fɛstəs] 干旱地区；旱田；陆地〈adv.〉</t>
+          <t>[fɛstəs] 坚固的；牢固的；坚实的〈adv.〉</t>
         </is>
       </c>
       <c r="C1169" s="1" t="inlineStr">
@@ -37821,7 +37821,7 @@
       </c>
       <c r="D1169" s="1" t="inlineStr">
         <is>
-          <t>干旱地区；旱田；陆地</t>
+          <t>坚固的；牢固的；坚实的</t>
         </is>
       </c>
       <c r="E1169" s="1" t="inlineStr">
@@ -37843,7 +37843,7 @@
       </c>
       <c r="B1170" s="1" t="inlineStr">
         <is>
-          <t>[hakflaɪʃ] 切碎；剁碎；绞碎〈n.〉</t>
+          <t>[hakflaɪʃ] 肉馅；绞碎的肉〈n.〉</t>
         </is>
       </c>
       <c r="C1170" s="1" t="inlineStr">
@@ -37853,7 +37853,7 @@
       </c>
       <c r="D1170" s="1" t="inlineStr">
         <is>
-          <t>切碎；剁碎；绞碎</t>
+          <t>肉馅；绞碎的肉</t>
         </is>
       </c>
       <c r="E1170" s="1" t="inlineStr">
@@ -38067,7 +38067,7 @@
       </c>
       <c r="B1177" s="1" t="inlineStr">
         <is>
-          <t>[aːlaʁmiːʁən] 警觉的；灵敏的〈v.〉</t>
+          <t>[aːlaʁmiːʁən] 报警；使警觉〈v.〉</t>
         </is>
       </c>
       <c r="C1177" s="1" t="inlineStr">
@@ -38077,7 +38077,7 @@
       </c>
       <c r="D1177" s="1" t="inlineStr">
         <is>
-          <t>警觉的；灵敏的</t>
+          <t>报警；使警觉</t>
         </is>
       </c>
       <c r="E1177" s="1" t="inlineStr">
@@ -38291,7 +38291,7 @@
       </c>
       <c r="B1184" s="1" t="inlineStr">
         <is>
-          <t>[loːɡə] 盒子；箱；方框〈n.f.〉</t>
+          <t>[loːɡə] 包厢〈n.f.〉</t>
         </is>
       </c>
       <c r="C1184" s="1" t="inlineStr">
@@ -38301,7 +38301,7 @@
       </c>
       <c r="D1184" s="1" t="inlineStr">
         <is>
-          <t>盒子；箱；方框</t>
+          <t>包厢</t>
         </is>
       </c>
       <c r="E1184" s="1" t="inlineStr">
@@ -38355,12 +38355,12 @@
       </c>
       <c r="B1186" s="1" t="inlineStr">
         <is>
-          <t>[pɪanɔ] 钢琴〈adv.〉</t>
+          <t>[piaːno] 钢琴〈adv.〉</t>
         </is>
       </c>
       <c r="C1186" s="1" t="inlineStr">
         <is>
-          <t>pɪanɔ</t>
+          <t>piaːno</t>
         </is>
       </c>
       <c r="D1186" s="1" t="inlineStr">
@@ -38675,7 +38675,7 @@
       </c>
       <c r="B1196" s="1" t="inlineStr">
         <is>
-          <t>[koːbɔlt] 妖怪；可怕的人；标准〈n.m.〉</t>
+          <t>[koːbɔlt] 小妖精；家神；淘气鬼〈n.m.〉</t>
         </is>
       </c>
       <c r="C1196" s="1" t="inlineStr">
@@ -38685,7 +38685,7 @@
       </c>
       <c r="D1196" s="1" t="inlineStr">
         <is>
-          <t>妖怪；可怕的人；标准</t>
+          <t>小妖精；家神；淘气鬼</t>
         </is>
       </c>
       <c r="E1196" s="1" t="inlineStr">
@@ -38995,7 +38995,7 @@
       </c>
       <c r="B1206" s="1" t="inlineStr">
         <is>
-          <t>[fɔʁspaɪzə] 开端者；在起跑线上的人；参加赛跑的人〈n.f.〉</t>
+          <t>[fɔʁspaɪzə] 前菜；开胃菜〈n.f.〉</t>
         </is>
       </c>
       <c r="C1206" s="1" t="inlineStr">
@@ -39005,7 +39005,7 @@
       </c>
       <c r="D1206" s="1" t="inlineStr">
         <is>
-          <t>开端者；在起跑线上的人；参加赛跑的人</t>
+          <t>前菜；开胃菜</t>
         </is>
       </c>
       <c r="E1206" s="1" t="inlineStr">
@@ -39443,12 +39443,12 @@
       </c>
       <c r="B1220" s="1" t="inlineStr">
         <is>
-          <t>[ɡɔʊfəʁnɔʏʁs] 州长；省长（属格/复数）〈n.〉</t>
+          <t>[ɡuvɛʁnøːʁs] 州长；省长（属格/复数）〈n.〉</t>
         </is>
       </c>
       <c r="C1220" s="1" t="inlineStr">
         <is>
-          <t>ɡɔʊfəʁnɔʏʁs</t>
+          <t>ɡuvɛʁnøːʁs</t>
         </is>
       </c>
       <c r="D1220" s="1" t="inlineStr">
@@ -39635,7 +39635,7 @@
       </c>
       <c r="B1226" s="1" t="inlineStr">
         <is>
-          <t>[fɔʁtʁətən] 站出来；自告奋勇；主动响应〈v.〉</t>
+          <t>[fɔʁtʁətən] 走上前；出列；站到前面来〈v.〉</t>
         </is>
       </c>
       <c r="C1226" s="1" t="inlineStr">
@@ -39645,7 +39645,7 @@
       </c>
       <c r="D1226" s="1" t="inlineStr">
         <is>
-          <t>站出来；自告奋勇；主动响应</t>
+          <t>走上前；出列；站到前面来</t>
         </is>
       </c>
       <c r="E1226" s="1" t="inlineStr">
@@ -39827,7 +39827,7 @@
       </c>
       <c r="B1232" s="1" t="inlineStr">
         <is>
-          <t>[vʊxt] 热烈；激烈〈n.f.〉</t>
+          <t>[vʊxt] 重量；冲击力；威力〈n.f.〉</t>
         </is>
       </c>
       <c r="C1232" s="1" t="inlineStr">
@@ -39837,7 +39837,7 @@
       </c>
       <c r="D1232" s="1" t="inlineStr">
         <is>
-          <t>热烈；激烈</t>
+          <t>重量；冲击力；威力</t>
         </is>
       </c>
       <c r="E1232" s="1" t="inlineStr">
@@ -40083,12 +40083,12 @@
       </c>
       <c r="B1240" s="1" t="inlineStr">
         <is>
-          <t>[pɛakə] 和平；和约；治安〈n.〉</t>
+          <t>[piːs] 和平；和约；治安〈n.〉</t>
         </is>
       </c>
       <c r="C1240" s="1" t="inlineStr">
         <is>
-          <t>pɛakə</t>
+          <t>piːs</t>
         </is>
       </c>
       <c r="D1240" s="1" t="inlineStr">
@@ -40371,7 +40371,7 @@
       </c>
       <c r="B1249" s="1" t="inlineStr">
         <is>
-          <t>[klasɪʃ] 古典作品；杰作〈adj.〉</t>
+          <t>[klasɪʃ] 古典的；经典的〈adj.〉</t>
         </is>
       </c>
       <c r="C1249" s="1" t="inlineStr">
@@ -40381,7 +40381,7 @@
       </c>
       <c r="D1249" s="1" t="inlineStr">
         <is>
-          <t>古典作品；杰作</t>
+          <t>古典的；经典的</t>
         </is>
       </c>
       <c r="E1249" s="1" t="inlineStr">
@@ -40819,7 +40819,7 @@
       </c>
       <c r="B1263" s="1" t="inlineStr">
         <is>
-          <t>[t͡suːʁʏkʃlaɡən] 向后折；倒折〈v.〉</t>
+          <t>[t͡suːʁʏkʃlaɡən] 反击；打回〈v.〉</t>
         </is>
       </c>
       <c r="C1263" s="1" t="inlineStr">
@@ -40829,7 +40829,7 @@
       </c>
       <c r="D1263" s="1" t="inlineStr">
         <is>
-          <t>向后折；倒折</t>
+          <t>反击；打回</t>
         </is>
       </c>
       <c r="E1263" s="1" t="inlineStr">
@@ -40851,7 +40851,7 @@
       </c>
       <c r="B1264" s="1" t="inlineStr">
         <is>
-          <t>[t͡sɪʁkəl] &lt;拉&gt;圆规座〈n.m.〉</t>
+          <t>[t͡sɪʁkəl] 圆规；圈子；小组〈n.m.〉</t>
         </is>
       </c>
       <c r="C1264" s="1" t="inlineStr">
@@ -40861,7 +40861,7 @@
       </c>
       <c r="D1264" s="1" t="inlineStr">
         <is>
-          <t>&lt;拉&gt;圆规座</t>
+          <t>圆规；圈子；小组</t>
         </is>
       </c>
       <c r="E1264" s="1" t="inlineStr">
@@ -41171,7 +41171,7 @@
       </c>
       <c r="B1274" s="1" t="inlineStr">
         <is>
-          <t>[laːbiːl] 无判断力的；分不清方向或目标的〈adj.〉</t>
+          <t>[laːbiːl] 不稳定的；易变的；动摇的〈adj.〉</t>
         </is>
       </c>
       <c r="C1274" s="1" t="inlineStr">
@@ -41181,7 +41181,7 @@
       </c>
       <c r="D1274" s="1" t="inlineStr">
         <is>
-          <t>无判断力的；分不清方向或目标的</t>
+          <t>不稳定的；易变的；动摇的</t>
         </is>
       </c>
       <c r="E1274" s="1" t="inlineStr">
@@ -41267,7 +41267,7 @@
       </c>
       <c r="B1277" s="1" t="inlineStr">
         <is>
-          <t>[blʊfən] 断崖；绝壁〈v.〉</t>
+          <t>[blʊfən] 虚张声势；诈骗；吓唬〈v.〉</t>
         </is>
       </c>
       <c r="C1277" s="1" t="inlineStr">
@@ -41277,7 +41277,7 @@
       </c>
       <c r="D1277" s="1" t="inlineStr">
         <is>
-          <t>断崖；绝壁</t>
+          <t>虚张声势；诈骗；吓唬</t>
         </is>
       </c>
       <c r="E1277" s="1" t="inlineStr">
@@ -41363,7 +41363,7 @@
       </c>
       <c r="B1280" s="1" t="inlineStr">
         <is>
-          <t>[haːlʊnkə] 懦夫〈n.m.〉</t>
+          <t>[haːlʊnkə] 无赖；恶棍；流氓〈n.m.〉</t>
         </is>
       </c>
       <c r="C1280" s="1" t="inlineStr">
@@ -41373,7 +41373,7 @@
       </c>
       <c r="D1280" s="1" t="inlineStr">
         <is>
-          <t>懦夫</t>
+          <t>无赖；恶棍；流氓</t>
         </is>
       </c>
       <c r="E1280" s="1" t="inlineStr">
@@ -41523,7 +41523,7 @@
       </c>
       <c r="B1285" s="1" t="inlineStr">
         <is>
-          <t>[aʊfɡədʁeːt] 勇敢的；精神充沛的；烈性的〈adv.〉</t>
+          <t>[aʊfɡədʁeːt] 兴奋的；亢奋的；活泼的〈adv.〉</t>
         </is>
       </c>
       <c r="C1285" s="1" t="inlineStr">
@@ -41533,7 +41533,7 @@
       </c>
       <c r="D1285" s="1" t="inlineStr">
         <is>
-          <t>勇敢的；精神充沛的；烈性的</t>
+          <t>兴奋的；亢奋的；活泼的</t>
         </is>
       </c>
       <c r="E1285" s="1" t="inlineStr">
@@ -41651,7 +41651,7 @@
       </c>
       <c r="B1289" s="1" t="inlineStr">
         <is>
-          <t>[ʃɪməl] 模子；模制品；松软沃土〈n.m.〉</t>
+          <t>[ʃɪməl] 白马；霉菌〈n.m.〉</t>
         </is>
       </c>
       <c r="C1289" s="1" t="inlineStr">
@@ -41661,7 +41661,7 @@
       </c>
       <c r="D1289" s="1" t="inlineStr">
         <is>
-          <t>模子；模制品；松软沃土</t>
+          <t>白马；霉菌</t>
         </is>
       </c>
       <c r="E1289" s="1" t="inlineStr">
@@ -42291,7 +42291,7 @@
       </c>
       <c r="B1309" s="1" t="inlineStr">
         <is>
-          <t>[aʊsbʁaɪtən] 出发；开始；陈列〈v.〉</t>
+          <t>[aʊsbʁaɪtən] 展开；铺开；传播；蔓延〈v.〉</t>
         </is>
       </c>
       <c r="C1309" s="1" t="inlineStr">
@@ -42301,7 +42301,7 @@
       </c>
       <c r="D1309" s="1" t="inlineStr">
         <is>
-          <t>出发；开始；陈列</t>
+          <t>展开；铺开；传播；蔓延</t>
         </is>
       </c>
       <c r="E1309" s="1" t="inlineStr">
@@ -42579,7 +42579,7 @@
       </c>
       <c r="B1318" s="1" t="inlineStr">
         <is>
-          <t>[zɛɔuːl] 灵魂；心灵；精神〈n.〉</t>
+          <t>[zɛɔuːl] 首尔（韩国首都）〈n.〉</t>
         </is>
       </c>
       <c r="C1318" s="1" t="inlineStr">
@@ -42589,7 +42589,7 @@
       </c>
       <c r="D1318" s="1" t="inlineStr">
         <is>
-          <t>灵魂；心灵；精神</t>
+          <t>首尔（韩国首都）</t>
         </is>
       </c>
       <c r="E1318" s="1" t="inlineStr">
@@ -42675,7 +42675,7 @@
       </c>
       <c r="B1321" s="1" t="inlineStr">
         <is>
-          <t>[kʁɛatɪfə] 区域；面积；范围〈adv.〉</t>
+          <t>[kʁɛatɪfə] 有创造力的；创造性的〈adv.〉</t>
         </is>
       </c>
       <c r="C1321" s="1" t="inlineStr">
@@ -42685,7 +42685,7 @@
       </c>
       <c r="D1321" s="1" t="inlineStr">
         <is>
-          <t>区域；面积；范围</t>
+          <t>有创造力的；创造性的</t>
         </is>
       </c>
       <c r="E1321" s="1" t="inlineStr">
@@ -42771,7 +42771,7 @@
       </c>
       <c r="B1324" s="1" t="inlineStr">
         <is>
-          <t>[ʃnʊpfən] 头；头脑；领袖〈n.m.〉</t>
+          <t>[ʃnʊpfən] 感冒；伤风；鼻塞〈n.m.〉</t>
         </is>
       </c>
       <c r="C1324" s="1" t="inlineStr">
@@ -42781,7 +42781,7 @@
       </c>
       <c r="D1324" s="1" t="inlineStr">
         <is>
-          <t>头；头脑；领袖</t>
+          <t>感冒；伤风；鼻塞</t>
         </is>
       </c>
       <c r="E1324" s="1" t="inlineStr">
@@ -43027,7 +43027,7 @@
       </c>
       <c r="B1332" s="1" t="inlineStr">
         <is>
-          <t>[ʁeːfançə] 回访比赛〈n.f.〉</t>
+          <t>[ʁeːfançə] 报仇；复仇；再赛〈n.f.〉</t>
         </is>
       </c>
       <c r="C1332" s="1" t="inlineStr">
@@ -43037,7 +43037,7 @@
       </c>
       <c r="D1332" s="1" t="inlineStr">
         <is>
-          <t>回访比赛</t>
+          <t>报仇；复仇；再赛</t>
         </is>
       </c>
       <c r="E1332" s="1" t="inlineStr">
@@ -43123,7 +43123,7 @@
       </c>
       <c r="B1335" s="1" t="inlineStr">
         <is>
-          <t>[baʊmvɔlə] 棉花；和谐；有好感；理解〈n.f.〉</t>
+          <t>[baʊmvɔlə] 棉花〈n.f.〉</t>
         </is>
       </c>
       <c r="C1335" s="1" t="inlineStr">
@@ -43133,7 +43133,7 @@
       </c>
       <c r="D1335" s="1" t="inlineStr">
         <is>
-          <t>棉花；和谐；有好感；理解</t>
+          <t>棉花</t>
         </is>
       </c>
       <c r="E1335" s="1" t="inlineStr">
@@ -43155,7 +43155,7 @@
       </c>
       <c r="B1336" s="1" t="inlineStr">
         <is>
-          <t>[foːɡəlɡət͡svɪt͡ʃɐ] 呢喃〈n.〉</t>
+          <t>[foːɡəlɡət͡svɪt͡ʃɐ] 鸟鸣；鸟的啁啾声〈n.〉〈n.〉</t>
         </is>
       </c>
       <c r="C1336" s="1" t="inlineStr">
@@ -43165,7 +43165,7 @@
       </c>
       <c r="D1336" s="1" t="inlineStr">
         <is>
-          <t>呢喃</t>
+          <t>鸟鸣；鸟的啁啾声〈n.〉</t>
         </is>
       </c>
       <c r="E1336" s="1" t="inlineStr">
@@ -43347,7 +43347,7 @@
       </c>
       <c r="B1342" s="1" t="inlineStr">
         <is>
-          <t>[taktɪʃə] 防暴装备〈adv.〉</t>
+          <t>[taktɪʃə] 战术的；策略的〈adv.〉</t>
         </is>
       </c>
       <c r="C1342" s="1" t="inlineStr">
@@ -43357,7 +43357,7 @@
       </c>
       <c r="D1342" s="1" t="inlineStr">
         <is>
-          <t>防暴装备</t>
+          <t>战术的；策略的</t>
         </is>
       </c>
       <c r="E1342" s="1" t="inlineStr">
@@ -43731,7 +43731,7 @@
       </c>
       <c r="B1354" s="1" t="inlineStr">
         <is>
-          <t>[hɪntəʁvɛldlɐ] 未开垦地〈n.m.〉</t>
+          <t>[hɪntəʁvɛldlɐ] 乡巴佬；土包子〈n.m.〉</t>
         </is>
       </c>
       <c r="C1354" s="1" t="inlineStr">
@@ -43741,7 +43741,7 @@
       </c>
       <c r="D1354" s="1" t="inlineStr">
         <is>
-          <t>未开垦地</t>
+          <t>乡巴佬；土包子</t>
         </is>
       </c>
       <c r="E1354" s="1" t="inlineStr">
@@ -43955,7 +43955,7 @@
       </c>
       <c r="B1361" s="1" t="inlineStr">
         <is>
-          <t>[kɔmandɔt͡səntʁalə] 突击队；突击队员；布尔人部队〈n.f.〉</t>
+          <t>[kɔmandɔt͡səntʁalə] 指挥中心；司令部〈n.f.〉</t>
         </is>
       </c>
       <c r="C1361" s="1" t="inlineStr">
@@ -43965,7 +43965,7 @@
       </c>
       <c r="D1361" s="1" t="inlineStr">
         <is>
-          <t>突击队；突击队员；布尔人部队</t>
+          <t>指挥中心；司令部</t>
         </is>
       </c>
       <c r="E1361" s="1" t="inlineStr">
@@ -43987,7 +43987,7 @@
       </c>
       <c r="B1362" s="1" t="inlineStr">
         <is>
-          <t>[fɛʁt͡sœɡɐn] 阻挠议事的活动；掠夺兵；暴兵〈n.〉</t>
+          <t>[fɛʁt͡sœɡɐn] 延迟；推迟；延误〈n.〉</t>
         </is>
       </c>
       <c r="C1362" s="1" t="inlineStr">
@@ -43997,7 +43997,7 @@
       </c>
       <c r="D1362" s="1" t="inlineStr">
         <is>
-          <t>阻挠议事的活动；掠夺兵；暴兵</t>
+          <t>延迟；推迟；延误</t>
         </is>
       </c>
       <c r="E1362" s="1" t="inlineStr">
@@ -44243,7 +44243,7 @@
       </c>
       <c r="B1370" s="1" t="inlineStr">
         <is>
-          <t>[ambɪt͡sjoːnən] 气质；耐力；勇气〈n.〉</t>
+          <t>[ambɪt͡sjoːnən] 雄心；抱负；志向〈n.〉</t>
         </is>
       </c>
       <c r="C1370" s="1" t="inlineStr">
@@ -44253,7 +44253,7 @@
       </c>
       <c r="D1370" s="1" t="inlineStr">
         <is>
-          <t>气质；耐力；勇气</t>
+          <t>雄心；抱负；志向</t>
         </is>
       </c>
       <c r="E1370" s="1" t="inlineStr">
@@ -44307,7 +44307,7 @@
       </c>
       <c r="B1372" s="1" t="inlineStr">
         <is>
-          <t>[hɛftɪɡɐ] 暴风雨；使骚动〈adv.〉</t>
+          <t>[hɛftɪɡɐ] 更猛烈的；更激烈的〈adj.〉〈adv.〉</t>
         </is>
       </c>
       <c r="C1372" s="1" t="inlineStr">
@@ -44317,7 +44317,7 @@
       </c>
       <c r="D1372" s="1" t="inlineStr">
         <is>
-          <t>暴风雨；使骚动</t>
+          <t>更猛烈的；更激烈的〈adj.〉</t>
         </is>
       </c>
       <c r="E1372" s="1" t="inlineStr">
@@ -44371,7 +44371,7 @@
       </c>
       <c r="B1374" s="1" t="inlineStr">
         <is>
-          <t>[hɔtdoːk] 玉米狗〈n.〉</t>
+          <t>[hɔtdoːk] 热狗〈n.〉</t>
         </is>
       </c>
       <c r="C1374" s="1" t="inlineStr">
@@ -44381,7 +44381,7 @@
       </c>
       <c r="D1374" s="1" t="inlineStr">
         <is>
-          <t>玉米狗</t>
+          <t>热狗</t>
         </is>
       </c>
       <c r="E1374" s="1" t="inlineStr">
@@ -44403,7 +44403,7 @@
       </c>
       <c r="B1375" s="1" t="inlineStr">
         <is>
-          <t>[maʁkən] 马尔凯〈n.〉</t>
+          <t>[maʁkən] 品牌；商标；邮票（Marke 的复数）〈n.〉</t>
         </is>
       </c>
       <c r="C1375" s="1" t="inlineStr">
@@ -44413,7 +44413,7 @@
       </c>
       <c r="D1375" s="1" t="inlineStr">
         <is>
-          <t>马尔凯</t>
+          <t>品牌；商标；邮票（Marke 的复数）</t>
         </is>
       </c>
       <c r="E1375" s="1" t="inlineStr">
@@ -44467,12 +44467,12 @@
       </c>
       <c r="B1377" s="1" t="inlineStr">
         <is>
-          <t>[bɛɡnadɪɡʊnk] 授予；授予物；允许〈n.f.〉</t>
+          <t>[bɛɡnadɪɡʊŋ] 授予；授予物；允许〈n.f.〉</t>
         </is>
       </c>
       <c r="C1377" s="1" t="inlineStr">
         <is>
-          <t>bɛɡnadɪɡʊnk</t>
+          <t>bɛɡnadɪɡʊŋ</t>
         </is>
       </c>
       <c r="D1377" s="1" t="inlineStr">
@@ -44531,17 +44531,17 @@
       </c>
       <c r="B1379" s="1" t="inlineStr">
         <is>
-          <t>[kʁankənfəʁzɪçəʁʊnk] 健康；卫生；蓬勃〈n.f.〉</t>
+          <t>[kʁaŋənfəʁzɪçəʁʊŋ] 医疗保险；健康保险〈n.f.〉</t>
         </is>
       </c>
       <c r="C1379" s="1" t="inlineStr">
         <is>
-          <t>kʁankənfəʁzɪçəʁʊnk</t>
+          <t>kʁaŋənfəʁzɪçəʁʊŋ</t>
         </is>
       </c>
       <c r="D1379" s="1" t="inlineStr">
         <is>
-          <t>健康；卫生；蓬勃</t>
+          <t>医疗保险；健康保险</t>
         </is>
       </c>
       <c r="E1379" s="1" t="inlineStr">
@@ -44627,7 +44627,7 @@
       </c>
       <c r="B1382" s="1" t="inlineStr">
         <is>
-          <t>[tʁansfɐ] 贸易；商业；交易〈n.m.〉</t>
+          <t>[tʁansfɐ] 转移；传输；转会；转账〈n.m.〉</t>
         </is>
       </c>
       <c r="C1382" s="1" t="inlineStr">
@@ -44637,7 +44637,7 @@
       </c>
       <c r="D1382" s="1" t="inlineStr">
         <is>
-          <t>贸易；商业；交易</t>
+          <t>转移；传输；转会；转账</t>
         </is>
       </c>
       <c r="E1382" s="1" t="inlineStr">
@@ -45075,7 +45075,7 @@
       </c>
       <c r="B1396" s="1" t="inlineStr">
         <is>
-          <t>[aʊstʁaɡən] 签名登记离开〈v.〉</t>
+          <t>[aʊstʁaɡən] 递送；分发；举办〈v.〉</t>
         </is>
       </c>
       <c r="C1396" s="1" t="inlineStr">
@@ -45085,7 +45085,7 @@
       </c>
       <c r="D1396" s="1" t="inlineStr">
         <is>
-          <t>签名登记离开</t>
+          <t>递送；分发；举办</t>
         </is>
       </c>
       <c r="E1396" s="1" t="inlineStr">
@@ -45139,7 +45139,7 @@
       </c>
       <c r="B1398" s="1" t="inlineStr">
         <is>
-          <t>[miːtfəʁtʁaːk] 租用；租赁；租回〈n.m.〉</t>
+          <t>[miːtfəʁtʁaːk] 租赁合同；租约〈n.m.〉</t>
         </is>
       </c>
       <c r="C1398" s="1" t="inlineStr">
@@ -45149,7 +45149,7 @@
       </c>
       <c r="D1398" s="1" t="inlineStr">
         <is>
-          <t>租用；租赁；租回</t>
+          <t>租赁合同；租约</t>
         </is>
       </c>
       <c r="E1398" s="1" t="inlineStr">
@@ -45203,7 +45203,7 @@
       </c>
       <c r="B1400" s="1" t="inlineStr">
         <is>
-          <t>[vafənhɛndlɐ] 武器；军事行动；军械〈n.m.〉</t>
+          <t>[vafənhɛndlɐ] 军火商；武器贩子〈n.m.〉</t>
         </is>
       </c>
       <c r="C1400" s="1" t="inlineStr">
@@ -45213,7 +45213,7 @@
       </c>
       <c r="D1400" s="1" t="inlineStr">
         <is>
-          <t>武器；军事行动；军械</t>
+          <t>军火商；武器贩子</t>
         </is>
       </c>
       <c r="E1400" s="1" t="inlineStr">
@@ -45331,7 +45331,7 @@
       </c>
       <c r="B1404" s="1" t="inlineStr">
         <is>
-          <t>[ʃʊslɪniː] 发射线〈n.f.〉</t>
+          <t>[ʃʊslɪniː] 射击线；弹道〈n.f.〉〈n.f.〉</t>
         </is>
       </c>
       <c r="C1404" s="1" t="inlineStr">
@@ -45341,7 +45341,7 @@
       </c>
       <c r="D1404" s="1" t="inlineStr">
         <is>
-          <t>发射线</t>
+          <t>射击线；弹道〈n.f.〉</t>
         </is>
       </c>
       <c r="E1404" s="1" t="inlineStr">
@@ -45395,7 +45395,7 @@
       </c>
       <c r="B1406" s="1" t="inlineStr">
         <is>
-          <t>[tɛatəʁstʏk] 阶段；舞台；场所〈n.〉</t>
+          <t>[tɛatəʁstʏk] 剧本；戏剧；话剧〈n.〉</t>
         </is>
       </c>
       <c r="C1406" s="1" t="inlineStr">
@@ -45405,7 +45405,7 @@
       </c>
       <c r="D1406" s="1" t="inlineStr">
         <is>
-          <t>阶段；舞台；场所</t>
+          <t>剧本；戏剧；话剧</t>
         </is>
       </c>
       <c r="E1406" s="1" t="inlineStr">
@@ -45427,12 +45427,12 @@
       </c>
       <c r="B1407" s="1" t="inlineStr">
         <is>
-          <t>[beːlaɡəʁʊnk] 围困；围攻〈n.f.〉</t>
+          <t>[beːlaɡəʁʊŋ] 围困；围攻〈n.f.〉</t>
         </is>
       </c>
       <c r="C1407" s="1" t="inlineStr">
         <is>
-          <t>beːlaɡəʁʊnk</t>
+          <t>beːlaɡəʁʊŋ</t>
         </is>
       </c>
       <c r="D1407" s="1" t="inlineStr">
@@ -45523,7 +45523,7 @@
       </c>
       <c r="B1410" s="1" t="inlineStr">
         <is>
-          <t>[abʃlʊsfaɪɐ] 开始；毕业典礼〈n.f.〉</t>
+          <t>[abʃlʊsfaɪɐ] 毕业典礼；闭幕式〈n.f.〉</t>
         </is>
       </c>
       <c r="C1410" s="1" t="inlineStr">
@@ -45533,7 +45533,7 @@
       </c>
       <c r="D1410" s="1" t="inlineStr">
         <is>
-          <t>开始；毕业典礼</t>
+          <t>毕业典礼；闭幕式</t>
         </is>
       </c>
       <c r="E1410" s="1" t="inlineStr">
@@ -45587,7 +45587,7 @@
       </c>
       <c r="B1412" s="1" t="inlineStr">
         <is>
-          <t>[ʃmiːʁə] 食堂；伙食；用膳〈n.f.〉</t>
+          <t>[ʃmiːʁə] 润滑油；油脂〈n.f.〉</t>
         </is>
       </c>
       <c r="C1412" s="1" t="inlineStr">
@@ -45597,7 +45597,7 @@
       </c>
       <c r="D1412" s="1" t="inlineStr">
         <is>
-          <t>食堂；伙食；用膳</t>
+          <t>润滑油；油脂</t>
         </is>
       </c>
       <c r="E1412" s="1" t="inlineStr">
@@ -46227,12 +46227,12 @@
       </c>
       <c r="B1432" s="1" t="inlineStr">
         <is>
-          <t>[mɛlbɔʊʁnə] 墨尔本〈n.〉</t>
+          <t>[mɛlbɔʁn] 墨尔本〈n.〉</t>
         </is>
       </c>
       <c r="C1432" s="1" t="inlineStr">
         <is>
-          <t>mɛlbɔʊʁnə</t>
+          <t>mɛlbɔʁn</t>
         </is>
       </c>
       <c r="D1432" s="1" t="inlineStr">
@@ -46579,7 +46579,7 @@
       </c>
       <c r="B1443" s="1" t="inlineStr">
         <is>
-          <t>[ʏblɪçəʁvaɪzə] 过去经常...；过去有规律地发生〈adv.〉</t>
+          <t>[ʏblɪçəʁvaɪzə] 通常；一般地〈adv.〉</t>
         </is>
       </c>
       <c r="C1443" s="1" t="inlineStr">
@@ -46589,7 +46589,7 @@
       </c>
       <c r="D1443" s="1" t="inlineStr">
         <is>
-          <t>过去经常...；过去有规律地发生</t>
+          <t>通常；一般地</t>
         </is>
       </c>
       <c r="E1443" s="1" t="inlineStr">
@@ -46643,7 +46643,7 @@
       </c>
       <c r="B1445" s="1" t="inlineStr">
         <is>
-          <t>[ɡɛldbœʁzə] 金钱；一笔款；财富〈n.f.〉</t>
+          <t>[ɡɛldbœʁzə] 钱包；皮夹〈n.f.〉</t>
         </is>
       </c>
       <c r="C1445" s="1" t="inlineStr">
@@ -46653,7 +46653,7 @@
       </c>
       <c r="D1445" s="1" t="inlineStr">
         <is>
-          <t>金钱；一笔款；财富</t>
+          <t>钱包；皮夹</t>
         </is>
       </c>
       <c r="E1445" s="1" t="inlineStr">
@@ -46675,7 +46675,7 @@
       </c>
       <c r="B1446" s="1" t="inlineStr">
         <is>
-          <t>[ʊntʁɔʏə] 裂口；违背；破坏〈n.f.〉</t>
+          <t>[ʊntʁɔʏə] 不忠；背信；不诚实〈n.f.〉</t>
         </is>
       </c>
       <c r="C1446" s="1" t="inlineStr">
@@ -46685,7 +46685,7 @@
       </c>
       <c r="D1446" s="1" t="inlineStr">
         <is>
-          <t>裂口；违背；破坏</t>
+          <t>不忠；背信；不诚实</t>
         </is>
       </c>
       <c r="E1446" s="1" t="inlineStr">
@@ -46771,7 +46771,7 @@
       </c>
       <c r="B1449" s="1" t="inlineStr">
         <is>
-          <t>[beːzɪçtɪɡən] 视野；风景；见解〈v.〉</t>
+          <t>[beːzɪçtɪɡən] 参观；游览；察看〈v.〉</t>
         </is>
       </c>
       <c r="C1449" s="1" t="inlineStr">
@@ -46781,7 +46781,7 @@
       </c>
       <c r="D1449" s="1" t="inlineStr">
         <is>
-          <t>视野；风景；见解</t>
+          <t>参观；游览；察看</t>
         </is>
       </c>
       <c r="E1449" s="1" t="inlineStr">
@@ -46899,7 +46899,7 @@
       </c>
       <c r="B1453" s="1" t="inlineStr">
         <is>
-          <t>[t͡suːʁʏkɡəbliːbən] 向后地；相反的；倒推〈adj.〉</t>
+          <t>[t͡suːʁʏkɡəbliːbən] 落后的；迟钝的〈adj.〉</t>
         </is>
       </c>
       <c r="C1453" s="1" t="inlineStr">
@@ -46909,7 +46909,7 @@
       </c>
       <c r="D1453" s="1" t="inlineStr">
         <is>
-          <t>向后地；相反的；倒推</t>
+          <t>落后的；迟钝的</t>
         </is>
       </c>
       <c r="E1453" s="1" t="inlineStr">
@@ -46963,7 +46963,7 @@
       </c>
       <c r="B1455" s="1" t="inlineStr">
         <is>
-          <t>[maːkəlɔs] 无瑕疵的；不锈的；不绣的；污染的〈adv.〉</t>
+          <t>[maːkəlɔs] 无瑕疵的；完美无缺的〈adv.〉</t>
         </is>
       </c>
       <c r="C1455" s="1" t="inlineStr">
@@ -46973,7 +46973,7 @@
       </c>
       <c r="D1455" s="1" t="inlineStr">
         <is>
-          <t>无瑕疵的；不锈的；不绣的；污染的</t>
+          <t>无瑕疵的；完美无缺的</t>
         </is>
       </c>
       <c r="E1455" s="1" t="inlineStr">
@@ -46995,7 +46995,7 @@
       </c>
       <c r="B1456" s="1" t="inlineStr">
         <is>
-          <t>[ʁɪndflaɪʃ] 牛肉；肌肉；养；宰；抱怨〈n.〉</t>
+          <t>[ʁɪndflaɪʃ] 牛肉〈n.〉</t>
         </is>
       </c>
       <c r="C1456" s="1" t="inlineStr">
@@ -47005,7 +47005,7 @@
       </c>
       <c r="D1456" s="1" t="inlineStr">
         <is>
-          <t>牛肉；肌肉；养；宰；抱怨</t>
+          <t>牛肉</t>
         </is>
       </c>
       <c r="E1456" s="1" t="inlineStr">
@@ -47027,7 +47027,7 @@
       </c>
       <c r="B1457" s="1" t="inlineStr">
         <is>
-          <t>[koːʁaːn] &lt;&lt;可兰经&gt;&gt;〈n.m.〉</t>
+          <t>[koːʁaːn] 《古兰经》〈n.m.〉</t>
         </is>
       </c>
       <c r="C1457" s="1" t="inlineStr">
@@ -47037,7 +47037,7 @@
       </c>
       <c r="D1457" s="1" t="inlineStr">
         <is>
-          <t>&lt;&lt;可兰经&gt;&gt;</t>
+          <t>《古兰经》</t>
         </is>
       </c>
       <c r="E1457" s="1" t="inlineStr">
@@ -47251,7 +47251,7 @@
       </c>
       <c r="B1464" s="1" t="inlineStr">
         <is>
-          <t>[vʊnt] 擦伤处；半成品；生的；未加工的〈adv.〉</t>
+          <t>[vʊnt] 疼痛的；擦伤的〈adv.〉</t>
         </is>
       </c>
       <c r="C1464" s="1" t="inlineStr">
@@ -47261,7 +47261,7 @@
       </c>
       <c r="D1464" s="1" t="inlineStr">
         <is>
-          <t>擦伤处；半成品；生的；未加工的</t>
+          <t>疼痛的；擦伤的</t>
         </is>
       </c>
       <c r="E1464" s="1" t="inlineStr">
@@ -47283,12 +47283,12 @@
       </c>
       <c r="B1465" s="1" t="inlineStr">
         <is>
-          <t>[ableːnʊnk] 拒绝；推却；优先决定权〈n.f.〉</t>
+          <t>[ableːnʊŋ] 拒绝；推却；优先决定权〈n.f.〉</t>
         </is>
       </c>
       <c r="C1465" s="1" t="inlineStr">
         <is>
-          <t>ableːnʊnk</t>
+          <t>ableːnʊŋ</t>
         </is>
       </c>
       <c r="D1465" s="1" t="inlineStr">
@@ -47315,7 +47315,7 @@
       </c>
       <c r="B1466" s="1" t="inlineStr">
         <is>
-          <t>[abvɪʃən] 温习；复习〈v.〉</t>
+          <t>[abvɪʃən] 擦去；擦净〈v.〉</t>
         </is>
       </c>
       <c r="C1466" s="1" t="inlineStr">
@@ -47325,7 +47325,7 @@
       </c>
       <c r="D1466" s="1" t="inlineStr">
         <is>
-          <t>温习；复习</t>
+          <t>擦去；擦净</t>
         </is>
       </c>
       <c r="E1466" s="1" t="inlineStr">
@@ -47411,7 +47411,7 @@
       </c>
       <c r="B1469" s="1" t="inlineStr">
         <is>
-          <t>[vɪnt͡sɪɡəs] 尘埃；微粒〈adv.〉</t>
+          <t>[vɪnt͡sɪɡəs] 微小的；极小的〈adv.〉</t>
         </is>
       </c>
       <c r="C1469" s="1" t="inlineStr">
@@ -47421,7 +47421,7 @@
       </c>
       <c r="D1469" s="1" t="inlineStr">
         <is>
-          <t>尘埃；微粒</t>
+          <t>微小的；极小的</t>
         </is>
       </c>
       <c r="E1469" s="1" t="inlineStr">
@@ -47539,7 +47539,7 @@
       </c>
       <c r="B1473" s="1" t="inlineStr">
         <is>
-          <t>[ʃmʏkən] 墓穴；坟墓；终结〈n.〉</t>
+          <t>[ʃmʏkən] 装饰；装扮〈n.〉</t>
         </is>
       </c>
       <c r="C1473" s="1" t="inlineStr">
@@ -47549,7 +47549,7 @@
       </c>
       <c r="D1473" s="1" t="inlineStr">
         <is>
-          <t>墓穴；坟墓；终结</t>
+          <t>装饰；装扮</t>
         </is>
       </c>
       <c r="E1473" s="1" t="inlineStr">
@@ -47731,7 +47731,7 @@
       </c>
       <c r="B1479" s="1" t="inlineStr">
         <is>
-          <t>[ʃaxmat] 击破；大败〈n.〉</t>
+          <t>[ʃaxmat] （国际象棋）将死；彻底失败〈n.〉</t>
         </is>
       </c>
       <c r="C1479" s="1" t="inlineStr">
@@ -47741,7 +47741,7 @@
       </c>
       <c r="D1479" s="1" t="inlineStr">
         <is>
-          <t>击破；大败</t>
+          <t>（国际象棋）将死；彻底失败</t>
         </is>
       </c>
       <c r="E1479" s="1" t="inlineStr">
@@ -47763,7 +47763,7 @@
       </c>
       <c r="B1480" s="1" t="inlineStr">
         <is>
-          <t>[tɛʁmɪnkaləndɐ] 约会；委任的职位；委派；任命〈n.m.〉</t>
+          <t>[tɛʁmɪnkaləndɐ] 日程表；日程簿〈n.m.〉</t>
         </is>
       </c>
       <c r="C1480" s="1" t="inlineStr">
@@ -47773,7 +47773,7 @@
       </c>
       <c r="D1480" s="1" t="inlineStr">
         <is>
-          <t>约会；委任的职位；委派；任命</t>
+          <t>日程表；日程簿</t>
         </is>
       </c>
       <c r="E1480" s="1" t="inlineStr">
@@ -48051,7 +48051,7 @@
       </c>
       <c r="B1489" s="1" t="inlineStr">
         <is>
-          <t>[poːlɪt͡saɪbəʁɪçt] 警察；警察当局〈n.m.〉</t>
+          <t>[poːlɪt͡saɪbəʁɪçt] 警方报告；警务报道〈n.m.〉</t>
         </is>
       </c>
       <c r="C1489" s="1" t="inlineStr">
@@ -48061,7 +48061,7 @@
       </c>
       <c r="D1489" s="1" t="inlineStr">
         <is>
-          <t>警察；警察当局</t>
+          <t>警方报告；警务报道</t>
         </is>
       </c>
       <c r="E1489" s="1" t="inlineStr">
@@ -48083,7 +48083,7 @@
       </c>
       <c r="B1490" s="1" t="inlineStr">
         <is>
-          <t>[maʁkɔs] 臭鼬；臭鼬皮〈n.〉</t>
+          <t>[maʁkɔs] 马科斯（男子名）〈n.〉</t>
         </is>
       </c>
       <c r="C1490" s="1" t="inlineStr">
@@ -48093,7 +48093,7 @@
       </c>
       <c r="D1490" s="1" t="inlineStr">
         <is>
-          <t>臭鼬；臭鼬皮</t>
+          <t>马科斯（男子名）</t>
         </is>
       </c>
       <c r="E1490" s="1" t="inlineStr">
@@ -48179,7 +48179,7 @@
       </c>
       <c r="B1493" s="1" t="inlineStr">
         <is>
-          <t>[aʊftʁaɡskɪlɐ] 合约；婚约〈n.m.〉</t>
+          <t>[aʊftʁaɡskɪlɐ] 职业杀手；雇佣杀手〈n.m.〉</t>
         </is>
       </c>
       <c r="C1493" s="1" t="inlineStr">
@@ -48189,7 +48189,7 @@
       </c>
       <c r="D1493" s="1" t="inlineStr">
         <is>
-          <t>合约；婚约</t>
+          <t>职业杀手；雇佣杀手</t>
         </is>
       </c>
       <c r="E1493" s="1" t="inlineStr">
@@ -48371,7 +48371,7 @@
       </c>
       <c r="B1499" s="1" t="inlineStr">
         <is>
-          <t>[deːmʏtɪɡənt] 抑制地\苦修地〈adv.〉</t>
+          <t>[deːmʏtɪɡənt] 羞辱的；使丢脸的〈adv.〉</t>
         </is>
       </c>
       <c r="C1499" s="1" t="inlineStr">
@@ -48381,7 +48381,7 @@
       </c>
       <c r="D1499" s="1" t="inlineStr">
         <is>
-          <t>抑制地\苦修地</t>
+          <t>羞辱的；使丢脸的</t>
         </is>
       </c>
       <c r="E1499" s="1" t="inlineStr">
@@ -48499,12 +48499,12 @@
       </c>
       <c r="B1503" s="1" t="inlineStr">
         <is>
-          <t>[diːfəʁzə] 各式各样的；杂的；各种〈adv.〉</t>
+          <t>[divɛʁzə] 各式各样的；杂的；各种〈adv.〉</t>
         </is>
       </c>
       <c r="C1503" s="1" t="inlineStr">
         <is>
-          <t>diːfəʁzə</t>
+          <t>divɛʁzə</t>
         </is>
       </c>
       <c r="D1503" s="1" t="inlineStr">
@@ -48627,7 +48627,7 @@
       </c>
       <c r="B1507" s="1" t="inlineStr">
         <is>
-          <t>[ʃlaɡt͡sɔʏk] 敲打；碰撞；叩击〈n.〉</t>
+          <t>[ʃlaɡt͡sɔʏk] 架子鼓；打击乐器〈n.〉</t>
         </is>
       </c>
       <c r="C1507" s="1" t="inlineStr">
@@ -48637,7 +48637,7 @@
       </c>
       <c r="D1507" s="1" t="inlineStr">
         <is>
-          <t>敲打；碰撞；叩击</t>
+          <t>架子鼓；打击乐器</t>
         </is>
       </c>
       <c r="E1507" s="1" t="inlineStr">
@@ -48787,7 +48787,7 @@
       </c>
       <c r="B1512" s="1" t="inlineStr">
         <is>
-          <t>[taʊɡən] 值得；有效〈v.〉</t>
+          <t>[taʊɡən] 有用；适合；有价值〈v.〉</t>
         </is>
       </c>
       <c r="C1512" s="1" t="inlineStr">
@@ -48797,7 +48797,7 @@
       </c>
       <c r="D1512" s="1" t="inlineStr">
         <is>
-          <t>值得；有效</t>
+          <t>有用；适合；有价值</t>
         </is>
       </c>
       <c r="E1512" s="1" t="inlineStr">
@@ -48819,7 +48819,7 @@
       </c>
       <c r="B1513" s="1" t="inlineStr">
         <is>
-          <t>[heːʁʏbɐ] 在这里〈adv.〉</t>
+          <t>[heːʁʏbɐ] 过来；越过〈adv.〉〈adv.〉</t>
         </is>
       </c>
       <c r="C1513" s="1" t="inlineStr">
@@ -48829,7 +48829,7 @@
       </c>
       <c r="D1513" s="1" t="inlineStr">
         <is>
-          <t>在这里</t>
+          <t>过来；越过〈adv.〉</t>
         </is>
       </c>
       <c r="E1513" s="1" t="inlineStr">
@@ -48915,7 +48915,7 @@
       </c>
       <c r="B1516" s="1" t="inlineStr">
         <is>
-          <t>[pɛʁzɔnalabtaɪlʊnk] 全体人员；工作班子；棍棒〈n.f.〉</t>
+          <t>[pɛʁzɔnalabtaɪlʊnk] 人事部；人事处〈n.f.〉</t>
         </is>
       </c>
       <c r="C1516" s="1" t="inlineStr">
@@ -48925,7 +48925,7 @@
       </c>
       <c r="D1516" s="1" t="inlineStr">
         <is>
-          <t>全体人员；工作班子；棍棒</t>
+          <t>人事部；人事处</t>
         </is>
       </c>
       <c r="E1516" s="1" t="inlineStr">
@@ -48947,7 +48947,7 @@
       </c>
       <c r="B1517" s="1" t="inlineStr">
         <is>
-          <t>[kʁiːmɪnalpɔlɪt͡saɪ] 罪犯；犯人〈n.f.〉</t>
+          <t>[kʁiːmɪnalpɔlɪt͡saɪ] 刑事警察；刑警〈n.f.〉</t>
         </is>
       </c>
       <c r="C1517" s="1" t="inlineStr">
@@ -48957,7 +48957,7 @@
       </c>
       <c r="D1517" s="1" t="inlineStr">
         <is>
-          <t>罪犯；犯人</t>
+          <t>刑事警察；刑警</t>
         </is>
       </c>
       <c r="E1517" s="1" t="inlineStr">
@@ -48979,7 +48979,7 @@
       </c>
       <c r="B1518" s="1" t="inlineStr">
         <is>
-          <t>[bʁiːtɪʃɐ] 英国英语〈adv.〉</t>
+          <t>[bʁiːtɪʃɐ] 英国的；英国人的〈adv.〉</t>
         </is>
       </c>
       <c r="C1518" s="1" t="inlineStr">
@@ -48989,7 +48989,7 @@
       </c>
       <c r="D1518" s="1" t="inlineStr">
         <is>
-          <t>英国英语</t>
+          <t>英国的；英国人的</t>
         </is>
       </c>
       <c r="E1518" s="1" t="inlineStr">
@@ -49043,7 +49043,7 @@
       </c>
       <c r="B1520" s="1" t="inlineStr">
         <is>
-          <t>[mɪsaxtən] 嘲笑；愚弄〈v.〉</t>
+          <t>[mɪsaxtən] 蔑视；无视；不尊重〈v.〉</t>
         </is>
       </c>
       <c r="C1520" s="1" t="inlineStr">
@@ -49053,7 +49053,7 @@
       </c>
       <c r="D1520" s="1" t="inlineStr">
         <is>
-          <t>嘲笑；愚弄</t>
+          <t>蔑视；无视；不尊重</t>
         </is>
       </c>
       <c r="E1520" s="1" t="inlineStr">
@@ -49171,7 +49171,7 @@
       </c>
       <c r="B1524" s="1" t="inlineStr">
         <is>
-          <t>[vaɪtəʁfyːʁən] 追赶；追踪；追随〈v.〉</t>
+          <t>[vaɪtəʁfyːʁən] 继续；引导〈v.〉</t>
         </is>
       </c>
       <c r="C1524" s="1" t="inlineStr">
@@ -49181,7 +49181,7 @@
       </c>
       <c r="D1524" s="1" t="inlineStr">
         <is>
-          <t>追赶；追踪；追随</t>
+          <t>继续；引导</t>
         </is>
       </c>
       <c r="E1524" s="1" t="inlineStr">
@@ -49235,7 +49235,7 @@
       </c>
       <c r="B1526" s="1" t="inlineStr">
         <is>
-          <t>[vaɪtəʁədən] 去；走；达到〈v.〉</t>
+          <t>[vaɪtəʁədən] 继续说；接着讲〈v.〉</t>
         </is>
       </c>
       <c r="C1526" s="1" t="inlineStr">
@@ -49245,7 +49245,7 @@
       </c>
       <c r="D1526" s="1" t="inlineStr">
         <is>
-          <t>去；走；达到</t>
+          <t>继续说；接着讲</t>
         </is>
       </c>
       <c r="E1526" s="1" t="inlineStr">
@@ -49299,7 +49299,7 @@
       </c>
       <c r="B1528" s="1" t="inlineStr">
         <is>
-          <t>[aɪnmɪʃʊnk] 闯入；侵扰；突入〈n.f.〉</t>
+          <t>[aɪnmɪʃʊnk] 干涉；干预；插手〈n.f.〉</t>
         </is>
       </c>
       <c r="C1528" s="1" t="inlineStr">
@@ -49309,7 +49309,7 @@
       </c>
       <c r="D1528" s="1" t="inlineStr">
         <is>
-          <t>闯入；侵扰；突入</t>
+          <t>干涉；干预；插手</t>
         </is>
       </c>
       <c r="E1528" s="1" t="inlineStr">
@@ -49363,7 +49363,7 @@
       </c>
       <c r="B1530" s="1" t="inlineStr">
         <is>
-          <t>[kʁaʊt] 树叶；花瓣〈n.〉</t>
+          <t>[kʁaʊt] 草本植物；药草；卷心菜〈n.〉</t>
         </is>
       </c>
       <c r="C1530" s="1" t="inlineStr">
@@ -49373,7 +49373,7 @@
       </c>
       <c r="D1530" s="1" t="inlineStr">
         <is>
-          <t>树叶；花瓣</t>
+          <t>草本植物；药草；卷心菜</t>
         </is>
       </c>
       <c r="E1530" s="1" t="inlineStr">
@@ -49523,7 +49523,7 @@
       </c>
       <c r="B1535" s="1" t="inlineStr">
         <is>
-          <t>[ʊnkoːl] 不；非；未〈adj.〉</t>
+          <t>[ʊnkoːl] 不酷的；不时髦的；不受欢迎的〈adj.〉</t>
         </is>
       </c>
       <c r="C1535" s="1" t="inlineStr">
@@ -49533,7 +49533,7 @@
       </c>
       <c r="D1535" s="1" t="inlineStr">
         <is>
-          <t>不；非；未</t>
+          <t>不酷的；不时髦的；不受欢迎的</t>
         </is>
       </c>
       <c r="E1535" s="1" t="inlineStr">
@@ -49619,7 +49619,7 @@
       </c>
       <c r="B1538" s="1" t="inlineStr">
         <is>
-          <t>[fɛʁhaɪʁatən] 对；夫妇〈v.〉</t>
+          <t>[fɛʁhaɪʁatən] 结婚；使成婚〈v.〉</t>
         </is>
       </c>
       <c r="C1538" s="1" t="inlineStr">
@@ -49629,7 +49629,7 @@
       </c>
       <c r="D1538" s="1" t="inlineStr">
         <is>
-          <t>对；夫妇</t>
+          <t>结婚；使成婚</t>
         </is>
       </c>
       <c r="E1538" s="1" t="inlineStr">
@@ -49651,7 +49651,7 @@
       </c>
       <c r="B1539" s="1" t="inlineStr">
         <is>
-          <t>[yːbəʁfyːʁt] 站立；站住；停顿〈adv.〉</t>
+          <t>[yːbəʁfyːʁt] 证明有罪；移送；转移〈adv.〉</t>
         </is>
       </c>
       <c r="C1539" s="1" t="inlineStr">
@@ -49661,7 +49661,7 @@
       </c>
       <c r="D1539" s="1" t="inlineStr">
         <is>
-          <t>站立；站住；停顿</t>
+          <t>证明有罪；移送；转移</t>
         </is>
       </c>
       <c r="E1539" s="1" t="inlineStr">
@@ -49779,7 +49779,7 @@
       </c>
       <c r="B1543" s="1" t="inlineStr">
         <is>
-          <t>[ɡeːbʊʁtstaɡskɪnt] 生日〈n.〉</t>
+          <t>[ɡeːbʊʁtstaɡskɪnt] 寿星；过生日的人〈n.〉</t>
         </is>
       </c>
       <c r="C1543" s="1" t="inlineStr">
@@ -49789,7 +49789,7 @@
       </c>
       <c r="D1543" s="1" t="inlineStr">
         <is>
-          <t>生日</t>
+          <t>寿星；过生日的人</t>
         </is>
       </c>
       <c r="E1543" s="1" t="inlineStr">
@@ -49811,7 +49811,7 @@
       </c>
       <c r="B1544" s="1" t="inlineStr">
         <is>
-          <t>[fɛʁbɔtənə] 共谋的〈adv.〉</t>
+          <t>[fɛʁbɔtənə] 被禁止的；违禁的〈adv.〉</t>
         </is>
       </c>
       <c r="C1544" s="1" t="inlineStr">
@@ -49821,7 +49821,7 @@
       </c>
       <c r="D1544" s="1" t="inlineStr">
         <is>
-          <t>共谋的</t>
+          <t>被禁止的；违禁的</t>
         </is>
       </c>
       <c r="E1544" s="1" t="inlineStr">
@@ -49939,7 +49939,7 @@
       </c>
       <c r="B1548" s="1" t="inlineStr">
         <is>
-          <t>[dʊʁkseːən] 熟读；精读；细读〈n.〉</t>
+          <t>[dʊʁkseːən] 查看；检查；浏览〈n.〉</t>
         </is>
       </c>
       <c r="C1548" s="1" t="inlineStr">
@@ -49949,7 +49949,7 @@
       </c>
       <c r="D1548" s="1" t="inlineStr">
         <is>
-          <t>熟读；精读；细读</t>
+          <t>查看；检查；浏览</t>
         </is>
       </c>
       <c r="E1548" s="1" t="inlineStr">
@@ -50163,12 +50163,12 @@
       </c>
       <c r="B1555" s="1" t="inlineStr">
         <is>
-          <t>[ɔʏʁɔpɛɪʃə] 欧洲人的〈adv.〉</t>
+          <t>[ɔʏʁopɛːɪʃə] 欧洲人的〈adv.〉</t>
         </is>
       </c>
       <c r="C1555" s="1" t="inlineStr">
         <is>
-          <t>ɔʏʁɔpɛɪʃə</t>
+          <t>ɔʏʁopɛːɪʃə</t>
         </is>
       </c>
       <c r="D1555" s="1" t="inlineStr">
@@ -50195,7 +50195,7 @@
       </c>
       <c r="B1556" s="1" t="inlineStr">
         <is>
-          <t>[ɡlaɪtən] 滑；滑道；山崩〈n.〉</t>
+          <t>[ɡlaɪtən] 滑动；滑行〈n.〉〈n.〉</t>
         </is>
       </c>
       <c r="C1556" s="1" t="inlineStr">
@@ -50205,7 +50205,7 @@
       </c>
       <c r="D1556" s="1" t="inlineStr">
         <is>
-          <t>滑；滑道；山崩</t>
+          <t>滑动；滑行〈n.〉</t>
         </is>
       </c>
       <c r="E1556" s="1" t="inlineStr">
@@ -50259,7 +50259,7 @@
       </c>
       <c r="B1558" s="1" t="inlineStr">
         <is>
-          <t>[faʊlɐ] 骗局；欺诈〈adv.〉</t>
+          <t>[faʊlɐ] 更懒惰的；更腐坏的〈adv.〉</t>
         </is>
       </c>
       <c r="C1558" s="1" t="inlineStr">
@@ -50269,7 +50269,7 @@
       </c>
       <c r="D1558" s="1" t="inlineStr">
         <is>
-          <t>骗局；欺诈</t>
+          <t>更懒惰的；更腐坏的</t>
         </is>
       </c>
       <c r="E1558" s="1" t="inlineStr">
@@ -50579,7 +50579,7 @@
       </c>
       <c r="B1568" s="1" t="inlineStr">
         <is>
-          <t>[fyːʁəndə] 矛尖；先锋队〈adv.〉</t>
+          <t>[fyːʁəndə] 领先的；主要的；领导的〈adv.〉</t>
         </is>
       </c>
       <c r="C1568" s="1" t="inlineStr">
@@ -50589,7 +50589,7 @@
       </c>
       <c r="D1568" s="1" t="inlineStr">
         <is>
-          <t>矛尖；先锋队</t>
+          <t>领先的；主要的；领导的</t>
         </is>
       </c>
       <c r="E1568" s="1" t="inlineStr">
@@ -50899,7 +50899,7 @@
       </c>
       <c r="B1578" s="1" t="inlineStr">
         <is>
-          <t>[maksɪmalə] 职业的〈adv.〉</t>
+          <t>[maksɪmalə] 最大的；最大限度的〈adv.〉</t>
         </is>
       </c>
       <c r="C1578" s="1" t="inlineStr">
@@ -50909,7 +50909,7 @@
       </c>
       <c r="D1578" s="1" t="inlineStr">
         <is>
-          <t>职业的</t>
+          <t>最大的；最大限度的</t>
         </is>
       </c>
       <c r="E1578" s="1" t="inlineStr">
@@ -51187,7 +51187,7 @@
       </c>
       <c r="B1587" s="1" t="inlineStr">
         <is>
-          <t>[zɛlbstbəvʊstzaɪn] 自我〈n.〉</t>
+          <t>[zɛlbstbəvʊstzaɪn] 自信；自我意识〈n.〉</t>
         </is>
       </c>
       <c r="C1587" s="1" t="inlineStr">
@@ -51197,7 +51197,7 @@
       </c>
       <c r="D1587" s="1" t="inlineStr">
         <is>
-          <t>自我</t>
+          <t>自信；自我意识</t>
         </is>
       </c>
       <c r="E1587" s="1" t="inlineStr">
@@ -51347,7 +51347,7 @@
       </c>
       <c r="B1592" s="1" t="inlineStr">
         <is>
-          <t>[ɡasɪ] 拿；取；抓〈n.〉</t>
+          <t>[ɡasɪ] 遛狗（口语，用于 Gassi gehen）〈n.〉</t>
         </is>
       </c>
       <c r="C1592" s="1" t="inlineStr">
@@ -51357,7 +51357,7 @@
       </c>
       <c r="D1592" s="1" t="inlineStr">
         <is>
-          <t>拿；取；抓</t>
+          <t>遛狗（口语，用于 Gassi gehen）</t>
         </is>
       </c>
       <c r="E1592" s="1" t="inlineStr">
@@ -51571,7 +51571,7 @@
       </c>
       <c r="B1599" s="1" t="inlineStr">
         <is>
-          <t>[ʊnfɔʁzɪçtɪç] 无远见的；浪费的〈adj.〉</t>
+          <t>[ʊnfɔʁzɪçtɪç] 不小心的；不谨慎的〈adj.〉</t>
         </is>
       </c>
       <c r="C1599" s="1" t="inlineStr">
@@ -51581,7 +51581,7 @@
       </c>
       <c r="D1599" s="1" t="inlineStr">
         <is>
-          <t>无远见的；浪费的</t>
+          <t>不小心的；不谨慎的</t>
         </is>
       </c>
       <c r="E1599" s="1" t="inlineStr">
@@ -51795,7 +51795,7 @@
       </c>
       <c r="B1606" s="1" t="inlineStr">
         <is>
-          <t>[abvəʁfən] 切断；除去；切除〈n.〉</t>
+          <t>[abvəʁfən] 抛下；投掷；脱落〈n.〉</t>
         </is>
       </c>
       <c r="C1606" s="1" t="inlineStr">
@@ -51805,7 +51805,7 @@
       </c>
       <c r="D1606" s="1" t="inlineStr">
         <is>
-          <t>切断；除去；切除</t>
+          <t>抛下；投掷；脱落</t>
         </is>
       </c>
       <c r="E1606" s="1" t="inlineStr">
@@ -51859,7 +51859,7 @@
       </c>
       <c r="B1608" s="1" t="inlineStr">
         <is>
-          <t>[fɛʁzøːnʊnk] 说服；安抚；抚慰〈n.f.〉</t>
+          <t>[fɛʁzøːnʊnk] 和解；调和〈n.f.〉</t>
         </is>
       </c>
       <c r="C1608" s="1" t="inlineStr">
@@ -51869,7 +51869,7 @@
       </c>
       <c r="D1608" s="1" t="inlineStr">
         <is>
-          <t>说服；安抚；抚慰</t>
+          <t>和解；调和</t>
         </is>
       </c>
       <c r="E1608" s="1" t="inlineStr">
@@ -51923,7 +51923,7 @@
       </c>
       <c r="B1610" s="1" t="inlineStr">
         <is>
-          <t>[fɔʁmalɪtɛtən] 庄严；严肃；庄重〈n.〉</t>
+          <t>[fɔʁmalɪtɛtən] 手续；形式〈n.〉</t>
         </is>
       </c>
       <c r="C1610" s="1" t="inlineStr">
@@ -51933,7 +51933,7 @@
       </c>
       <c r="D1610" s="1" t="inlineStr">
         <is>
-          <t>庄严；严肃；庄重</t>
+          <t>手续；形式</t>
         </is>
       </c>
       <c r="E1610" s="1" t="inlineStr">
@@ -51987,7 +51987,7 @@
       </c>
       <c r="B1612" s="1" t="inlineStr">
         <is>
-          <t>[fɔʁt͡saɪtɪç] 门闩；螺钉；筛子〈adj.〉</t>
+          <t>[fɔʁt͡saɪtɪç] 过早的；提前的〈adj.〉</t>
         </is>
       </c>
       <c r="C1612" s="1" t="inlineStr">
@@ -51997,7 +51997,7 @@
       </c>
       <c r="D1612" s="1" t="inlineStr">
         <is>
-          <t>门闩；螺钉；筛子</t>
+          <t>过早的；提前的</t>
         </is>
       </c>
       <c r="E1612" s="1" t="inlineStr">
@@ -52083,7 +52083,7 @@
       </c>
       <c r="B1615" s="1" t="inlineStr">
         <is>
-          <t>[fʁaɪɡəbən] 自由的；享受政治权力的；允许的〈v.〉</t>
+          <t>[fʁaɪɡəbən] 释放；放开；批准；公布〈v.〉</t>
         </is>
       </c>
       <c r="C1615" s="1" t="inlineStr">
@@ -52093,7 +52093,7 @@
       </c>
       <c r="D1615" s="1" t="inlineStr">
         <is>
-          <t>自由的；享受政治权力的；允许的</t>
+          <t>释放；放开；批准；公布</t>
         </is>
       </c>
       <c r="E1615" s="1" t="inlineStr">
@@ -52179,7 +52179,7 @@
       </c>
       <c r="B1618" s="1" t="inlineStr">
         <is>
-          <t>[abdəkən] 拆去屋顶〈v.〉</t>
+          <t>[abdəkən] 覆盖；遮盖；揭开（盖子）〈v.〉</t>
         </is>
       </c>
       <c r="C1618" s="1" t="inlineStr">
@@ -52189,7 +52189,7 @@
       </c>
       <c r="D1618" s="1" t="inlineStr">
         <is>
-          <t>拆去屋顶</t>
+          <t>覆盖；遮盖；揭开（盖子）</t>
         </is>
       </c>
       <c r="E1618" s="1" t="inlineStr">
@@ -52339,7 +52339,7 @@
       </c>
       <c r="B1623" s="1" t="inlineStr">
         <is>
-          <t>[dɪstant͡siːʁt] 沉默寡言的；自足的；完备的；自备的〈adj.〉</t>
+          <t>[dɪstant͡siːʁt] 冷淡的；疏远的；有距离感的〈adj.〉</t>
         </is>
       </c>
       <c r="C1623" s="1" t="inlineStr">
@@ -52349,7 +52349,7 @@
       </c>
       <c r="D1623" s="1" t="inlineStr">
         <is>
-          <t>沉默寡言的；自足的；完备的；自备的</t>
+          <t>冷淡的；疏远的；有距离感的</t>
         </is>
       </c>
       <c r="E1623" s="1" t="inlineStr">
@@ -52531,7 +52531,7 @@
       </c>
       <c r="B1629" s="1" t="inlineStr">
         <is>
-          <t>[bɛstəlʊnɡən] 有序化；定序；排序〈n.〉</t>
+          <t>[bɛstəlʊnɡən] 订单；订购；预约〈n.〉</t>
         </is>
       </c>
       <c r="C1629" s="1" t="inlineStr">
@@ -52541,7 +52541,7 @@
       </c>
       <c r="D1629" s="1" t="inlineStr">
         <is>
-          <t>有序化；定序；排序</t>
+          <t>订单；订购；预约</t>
         </is>
       </c>
       <c r="E1629" s="1" t="inlineStr">
@@ -52723,7 +52723,7 @@
       </c>
       <c r="B1635" s="1" t="inlineStr">
         <is>
-          <t>[bɛstək] 刺；刺痛感〈n.〉</t>
+          <t>[bɛstək] 餐具；成套用具；仪器〈n.〉</t>
         </is>
       </c>
       <c r="C1635" s="1" t="inlineStr">
@@ -52733,7 +52733,7 @@
       </c>
       <c r="D1635" s="1" t="inlineStr">
         <is>
-          <t>刺；刺痛感</t>
+          <t>餐具；成套用具；仪器</t>
         </is>
       </c>
       <c r="E1635" s="1" t="inlineStr">
@@ -52915,7 +52915,7 @@
       </c>
       <c r="B1641" s="1" t="inlineStr">
         <is>
-          <t>[ɡlœkçən] 补锅匠〈n.〉</t>
+          <t>[ɡlœkçən] 小铃铛；小钟〈n.〉〈n.〉</t>
         </is>
       </c>
       <c r="C1641" s="1" t="inlineStr">
@@ -52925,7 +52925,7 @@
       </c>
       <c r="D1641" s="1" t="inlineStr">
         <is>
-          <t>补锅匠</t>
+          <t>小铃铛；小钟〈n.〉</t>
         </is>
       </c>
       <c r="E1641" s="1" t="inlineStr">
@@ -53139,7 +53139,7 @@
       </c>
       <c r="B1648" s="1" t="inlineStr">
         <is>
-          <t>[ɡɛʃvɔʁənə] 陪审员；审查委员；陪审官〈n.〉</t>
+          <t>[ɡɛʃvɔʁənə] 陪审员；陪审官〈m.，按形容词变格：der Geschworene〉〈n.〉</t>
         </is>
       </c>
       <c r="C1648" s="1" t="inlineStr">
@@ -53149,7 +53149,7 @@
       </c>
       <c r="D1648" s="1" t="inlineStr">
         <is>
-          <t>陪审员；审查委员；陪审官</t>
+          <t>陪审员；陪审官〈m.，按形容词变格：der Geschworene〉</t>
         </is>
       </c>
       <c r="E1648" s="1" t="inlineStr">
@@ -53171,7 +53171,7 @@
       </c>
       <c r="B1649" s="1" t="inlineStr">
         <is>
-          <t>[hɛʁt͡sfʁəkvənt͡s] 心；心脏；中心〈n.f.〉</t>
+          <t>[hɛʁt͡sfʁəkvənt͡s] 心率〈n.f.〉</t>
         </is>
       </c>
       <c r="C1649" s="1" t="inlineStr">
@@ -53181,7 +53181,7 @@
       </c>
       <c r="D1649" s="1" t="inlineStr">
         <is>
-          <t>心；心脏；中心</t>
+          <t>心率</t>
         </is>
       </c>
       <c r="E1649" s="1" t="inlineStr">
@@ -53203,7 +53203,7 @@
       </c>
       <c r="B1650" s="1" t="inlineStr">
         <is>
-          <t>[ɛvɪɡɐ] 回转的；旋转的；旋转式的；循环〈adv.〉</t>
+          <t>[ɛvɪɡɐ] 永恒的；永久的〈adv.〉</t>
         </is>
       </c>
       <c r="C1650" s="1" t="inlineStr">
@@ -53213,7 +53213,7 @@
       </c>
       <c r="D1650" s="1" t="inlineStr">
         <is>
-          <t>回转的；旋转的；旋转式的；循环</t>
+          <t>永恒的；永久的</t>
         </is>
       </c>
       <c r="E1650" s="1" t="inlineStr">
@@ -53299,7 +53299,7 @@
       </c>
       <c r="B1653" s="1" t="inlineStr">
         <is>
-          <t>[paɪnlɪçə] 美好；准确；精密〈adv.〉</t>
+          <t>[paɪnlɪçə] 尴尬的；令人难堪的〈adv.〉</t>
         </is>
       </c>
       <c r="C1653" s="1" t="inlineStr">
@@ -53309,7 +53309,7 @@
       </c>
       <c r="D1653" s="1" t="inlineStr">
         <is>
-          <t>美好；准确；精密</t>
+          <t>尴尬的；令人难堪的</t>
         </is>
       </c>
       <c r="E1653" s="1" t="inlineStr">
@@ -53459,7 +53459,7 @@
       </c>
       <c r="B1658" s="1" t="inlineStr">
         <is>
-          <t>[baʁiːʁə] 弹幕〈n.f.〉</t>
+          <t>[baʁiːʁə] 障碍；屏障；障碍物〈n.f.〉</t>
         </is>
       </c>
       <c r="C1658" s="1" t="inlineStr">
@@ -53469,7 +53469,7 @@
       </c>
       <c r="D1658" s="1" t="inlineStr">
         <is>
-          <t>弹幕</t>
+          <t>障碍；屏障；障碍物</t>
         </is>
       </c>
       <c r="E1658" s="1" t="inlineStr">
@@ -53491,7 +53491,7 @@
       </c>
       <c r="B1659" s="1" t="inlineStr">
         <is>
-          <t>[diːmənzɪɔnən] 比例〈n.〉</t>
+          <t>[diːmənzɪɔnən] 尺寸；维度；范围〈n.〉</t>
         </is>
       </c>
       <c r="C1659" s="1" t="inlineStr">
@@ -53501,7 +53501,7 @@
       </c>
       <c r="D1659" s="1" t="inlineStr">
         <is>
-          <t>比例</t>
+          <t>尺寸；维度；范围</t>
         </is>
       </c>
       <c r="E1659" s="1" t="inlineStr">
@@ -53843,7 +53843,7 @@
       </c>
       <c r="B1670" s="1" t="inlineStr">
         <is>
-          <t>[aɪnvaɪzən] 火车；列车；行列〈v.〉</t>
+          <t>[aɪnvaɪzən] 指示；指引；把…送往（医院等）〈v.〉</t>
         </is>
       </c>
       <c r="C1670" s="1" t="inlineStr">
@@ -53853,7 +53853,7 @@
       </c>
       <c r="D1670" s="1" t="inlineStr">
         <is>
-          <t>火车；列车；行列</t>
+          <t>指示；指引；把…送往（医院等）</t>
         </is>
       </c>
       <c r="E1670" s="1" t="inlineStr">
@@ -53971,7 +53971,7 @@
       </c>
       <c r="B1674" s="1" t="inlineStr">
         <is>
-          <t>[ɡlʏkstʁɛːnə] 跑；赛跑；奔跑〈n.f.〉</t>
+          <t>[ɡlʏkstʁɛːnə] 连续的好运；幸运期〈n.f.〉〈n.f.〉</t>
         </is>
       </c>
       <c r="C1674" s="1" t="inlineStr">
@@ -53981,7 +53981,7 @@
       </c>
       <c r="D1674" s="1" t="inlineStr">
         <is>
-          <t>跑；赛跑；奔跑</t>
+          <t>连续的好运；幸运期〈n.f.〉</t>
         </is>
       </c>
       <c r="E1674" s="1" t="inlineStr">
@@ -54131,7 +54131,7 @@
       </c>
       <c r="B1679" s="1" t="inlineStr">
         <is>
-          <t>[ʃpaɪçɐn] 存储；储存；保全〈n.〉</t>
+          <t>[ʃpaɪçɐn] speichern 存储；储存〈v.〉（动词应小写）〈n.〉</t>
         </is>
       </c>
       <c r="C1679" s="1" t="inlineStr">
@@ -54141,7 +54141,7 @@
       </c>
       <c r="D1679" s="1" t="inlineStr">
         <is>
-          <t>存储；储存；保全</t>
+          <t>speichern 存储；储存〈v.〉（动词应小写）</t>
         </is>
       </c>
       <c r="E1679" s="1" t="inlineStr">
@@ -54291,7 +54291,7 @@
       </c>
       <c r="B1684" s="1" t="inlineStr">
         <is>
-          <t>[aɪnzaməln] 打扫；排除废气；在...中找有用之物〈v.〉</t>
+          <t>[aɪnzaməln] 收集；收取；捡拾〈v.〉</t>
         </is>
       </c>
       <c r="C1684" s="1" t="inlineStr">
@@ -54301,7 +54301,7 @@
       </c>
       <c r="D1684" s="1" t="inlineStr">
         <is>
-          <t>打扫；排除废气；在...中找有用之物</t>
+          <t>收集；收取；捡拾</t>
         </is>
       </c>
       <c r="E1684" s="1" t="inlineStr">
@@ -54547,7 +54547,7 @@
       </c>
       <c r="B1692" s="1" t="inlineStr">
         <is>
-          <t>[vɛstlɪçə] 灰色；灰色的〈adv.〉</t>
+          <t>[vɛstlɪçə] 西方的；西部的〈adv.〉</t>
         </is>
       </c>
       <c r="C1692" s="1" t="inlineStr">
@@ -54557,7 +54557,7 @@
       </c>
       <c r="D1692" s="1" t="inlineStr">
         <is>
-          <t>灰色；灰色的</t>
+          <t>西方的；西部的</t>
         </is>
       </c>
       <c r="E1692" s="1" t="inlineStr">
@@ -54611,7 +54611,7 @@
       </c>
       <c r="B1694" s="1" t="inlineStr">
         <is>
-          <t>[ɡeːnaʊəs] 手艺；技巧；制造工艺〈adv.〉</t>
+          <t>[ɡeːnaʊəs] 精确的；准确的〈adv.〉</t>
         </is>
       </c>
       <c r="C1694" s="1" t="inlineStr">
@@ -54621,7 +54621,7 @@
       </c>
       <c r="D1694" s="1" t="inlineStr">
         <is>
-          <t>手艺；技巧；制造工艺</t>
+          <t>精确的；准确的</t>
         </is>
       </c>
       <c r="E1694" s="1" t="inlineStr">
@@ -54643,7 +54643,7 @@
       </c>
       <c r="B1695" s="1" t="inlineStr">
         <is>
-          <t>[voːlfyːlən] 健康〈n.〉</t>
+          <t>[voːlfyːlən] 舒适感；惬意〈n.〉</t>
         </is>
       </c>
       <c r="C1695" s="1" t="inlineStr">
@@ -54653,7 +54653,7 @@
       </c>
       <c r="D1695" s="1" t="inlineStr">
         <is>
-          <t>健康</t>
+          <t>舒适感；惬意</t>
         </is>
       </c>
       <c r="E1695" s="1" t="inlineStr">
@@ -54867,7 +54867,7 @@
       </c>
       <c r="B1702" s="1" t="inlineStr">
         <is>
-          <t>[yːbəʁlɪstən] 周期；循环；自行车〈n.〉</t>
+          <t>[yːbəʁlɪstən] 智取；以计谋战胜〈n.〉</t>
         </is>
       </c>
       <c r="C1702" s="1" t="inlineStr">
@@ -54877,7 +54877,7 @@
       </c>
       <c r="D1702" s="1" t="inlineStr">
         <is>
-          <t>周期；循环；自行车</t>
+          <t>智取；以计谋战胜</t>
         </is>
       </c>
       <c r="E1702" s="1" t="inlineStr">
@@ -54899,7 +54899,7 @@
       </c>
       <c r="B1703" s="1" t="inlineStr">
         <is>
-          <t>[bʁiːftʁɛɡɐ] 邮递员；理财法庭的高级律师〈n.m.〉</t>
+          <t>[bʁiːftʁɛɡɐ] 邮递员〈n.m.〉</t>
         </is>
       </c>
       <c r="C1703" s="1" t="inlineStr">
@@ -54909,7 +54909,7 @@
       </c>
       <c r="D1703" s="1" t="inlineStr">
         <is>
-          <t>邮递员；理财法庭的高级律师</t>
+          <t>邮递员</t>
         </is>
       </c>
       <c r="E1703" s="1" t="inlineStr">
@@ -54931,7 +54931,7 @@
       </c>
       <c r="B1704" s="1" t="inlineStr">
         <is>
-          <t>[beːnədɪkt] 新婚男人〈n.m.〉</t>
+          <t>[beːnədɪkt] 本尼迪克特（男子名）〈n.m.〉</t>
         </is>
       </c>
       <c r="C1704" s="1" t="inlineStr">
@@ -54941,7 +54941,7 @@
       </c>
       <c r="D1704" s="1" t="inlineStr">
         <is>
-          <t>新婚男人</t>
+          <t>本尼迪克特（男子名）</t>
         </is>
       </c>
       <c r="E1704" s="1" t="inlineStr">
@@ -55059,7 +55059,7 @@
       </c>
       <c r="B1708" s="1" t="inlineStr">
         <is>
-          <t>[poːlɪt͡saɪfʊnk] 警察；警察当局〈n.m.〉</t>
+          <t>[poːlɪt͡saɪfʊnk] 警用无线电；警察电台〈n.m.〉</t>
         </is>
       </c>
       <c r="C1708" s="1" t="inlineStr">
@@ -55069,7 +55069,7 @@
       </c>
       <c r="D1708" s="1" t="inlineStr">
         <is>
-          <t>警察；警察当局</t>
+          <t>警用无线电；警察电台</t>
         </is>
       </c>
       <c r="E1708" s="1" t="inlineStr">
@@ -55251,7 +55251,7 @@
       </c>
       <c r="B1714" s="1" t="inlineStr">
         <is>
-          <t>[eːəfəʁtʁaːk] 婚姻；结婚；婚礼〈n.m.〉</t>
+          <t>[eːəfəʁtʁaːk] 婚前协议；婚约〈n.m.〉</t>
         </is>
       </c>
       <c r="C1714" s="1" t="inlineStr">
@@ -55261,7 +55261,7 @@
       </c>
       <c r="D1714" s="1" t="inlineStr">
         <is>
-          <t>婚姻；结婚；婚礼</t>
+          <t>婚前协议；婚约</t>
         </is>
       </c>
       <c r="E1714" s="1" t="inlineStr">
@@ -55283,7 +55283,7 @@
       </c>
       <c r="B1715" s="1" t="inlineStr">
         <is>
-          <t>[nɪkən] 点头；打盹；晃动〈n.〉</t>
+          <t>[nɪkən] 点头〈v.〉〈n.〉</t>
         </is>
       </c>
       <c r="C1715" s="1" t="inlineStr">
@@ -55293,7 +55293,7 @@
       </c>
       <c r="D1715" s="1" t="inlineStr">
         <is>
-          <t>点头；打盹；晃动</t>
+          <t>点头〈v.〉</t>
         </is>
       </c>
       <c r="E1715" s="1" t="inlineStr">
@@ -55571,12 +55571,12 @@
       </c>
       <c r="B1724" s="1" t="inlineStr">
         <is>
-          <t>[ɛʁnənən] 提名；任命〈v.〉</t>
+          <t>[ɛʁnɛnən] 提名；任命〈v.〉</t>
         </is>
       </c>
       <c r="C1724" s="1" t="inlineStr">
         <is>
-          <t>ɛʁnənən</t>
+          <t>ɛʁnɛnən</t>
         </is>
       </c>
       <c r="D1724" s="1" t="inlineStr">
@@ -55667,7 +55667,7 @@
       </c>
       <c r="B1727" s="1" t="inlineStr">
         <is>
-          <t>[dʏnaːmɪʃə] 冲击；冲突；影响〈adv.〉</t>
+          <t>[dʏnaːmɪʃə] 动态的；有活力的〈adv.〉</t>
         </is>
       </c>
       <c r="C1727" s="1" t="inlineStr">
@@ -55677,7 +55677,7 @@
       </c>
       <c r="D1727" s="1" t="inlineStr">
         <is>
-          <t>冲击；冲突；影响</t>
+          <t>动态的；有活力的</t>
         </is>
       </c>
       <c r="E1727" s="1" t="inlineStr">
@@ -55731,12 +55731,12 @@
       </c>
       <c r="B1729" s="1" t="inlineStr">
         <is>
-          <t>[dʊdlɛʏ] 达德利〈n.〉</t>
+          <t>[dʊdlɪ] 达德利〈n.〉</t>
         </is>
       </c>
       <c r="C1729" s="1" t="inlineStr">
         <is>
-          <t>dʊdlɛʏ</t>
+          <t>dʊdlɪ</t>
         </is>
       </c>
       <c r="D1729" s="1" t="inlineStr">
@@ -55923,7 +55923,7 @@
       </c>
       <c r="B1735" s="1" t="inlineStr">
         <is>
-          <t>[ʃœpfən] 铲子；勺子；穴〈n.〉</t>
+          <t>[ʃœpfən] 汲取；舀取；产生（希望、勇气等）〈n.〉</t>
         </is>
       </c>
       <c r="C1735" s="1" t="inlineStr">
@@ -55933,7 +55933,7 @@
       </c>
       <c r="D1735" s="1" t="inlineStr">
         <is>
-          <t>铲子；勺子；穴</t>
+          <t>汲取；舀取；产生（希望、勇气等）</t>
         </is>
       </c>
       <c r="E1735" s="1" t="inlineStr">
@@ -55955,12 +55955,12 @@
       </c>
       <c r="B1736" s="1" t="inlineStr">
         <is>
-          <t>[jɔʊʁnaːl] 每日的；日常地；日报〈n.〉</t>
+          <t>[ʒʊʁnaːl] 每日的；日常地；日报〈n.〉</t>
         </is>
       </c>
       <c r="C1736" s="1" t="inlineStr">
         <is>
-          <t>jɔʊʁnaːl</t>
+          <t>ʒʊʁnaːl</t>
         </is>
       </c>
       <c r="D1736" s="1" t="inlineStr">
@@ -56019,7 +56019,7 @@
       </c>
       <c r="B1738" s="1" t="inlineStr">
         <is>
-          <t>[tiːʁhaɪm] 动物〈n.〉</t>
+          <t>[tiːʁhaɪm] 动物收容所〈n.〉</t>
         </is>
       </c>
       <c r="C1738" s="1" t="inlineStr">
@@ -56029,7 +56029,7 @@
       </c>
       <c r="D1738" s="1" t="inlineStr">
         <is>
-          <t>动物</t>
+          <t>动物收容所</t>
         </is>
       </c>
       <c r="E1738" s="1" t="inlineStr">
@@ -56051,7 +56051,7 @@
       </c>
       <c r="B1739" s="1" t="inlineStr">
         <is>
-          <t>[pɔstamt] 柱；杆；准星〈n.〉</t>
+          <t>[pɔstamt] 邮局〈n.〉</t>
         </is>
       </c>
       <c r="C1739" s="1" t="inlineStr">
@@ -56061,7 +56061,7 @@
       </c>
       <c r="D1739" s="1" t="inlineStr">
         <is>
-          <t>柱；杆；准星</t>
+          <t>邮局</t>
         </is>
       </c>
       <c r="E1739" s="1" t="inlineStr">
@@ -56179,7 +56179,7 @@
       </c>
       <c r="B1743" s="1" t="inlineStr">
         <is>
-          <t>[yːbəʁlaʊfən] 背叛；缺乏；毛病；缺点〈n.〉</t>
+          <t>[yːbəʁlaʊfən] 叛逃；倒戈；溢出〈n.〉</t>
         </is>
       </c>
       <c r="C1743" s="1" t="inlineStr">
@@ -56189,7 +56189,7 @@
       </c>
       <c r="D1743" s="1" t="inlineStr">
         <is>
-          <t>背叛；缺乏；毛病；缺点</t>
+          <t>叛逃；倒戈；溢出</t>
         </is>
       </c>
       <c r="E1743" s="1" t="inlineStr">
@@ -56307,12 +56307,12 @@
       </c>
       <c r="B1747" s="1" t="inlineStr">
         <is>
-          <t>[dɔvntoːn] 唐顿（地名/庄园名）〈n.〉</t>
+          <t>[daʊntən] 唐顿（地名/庄园名）〈n.〉</t>
         </is>
       </c>
       <c r="C1747" s="1" t="inlineStr">
         <is>
-          <t>dɔvntoːn</t>
+          <t>daʊntən</t>
         </is>
       </c>
       <c r="D1747" s="1" t="inlineStr">
@@ -56499,7 +56499,7 @@
       </c>
       <c r="B1753" s="1" t="inlineStr">
         <is>
-          <t>[pfant] 安全；安全性；防护物〈n.〉</t>
+          <t>[pfant] 押金；抵押品〈n.〉</t>
         </is>
       </c>
       <c r="C1753" s="1" t="inlineStr">
@@ -56509,7 +56509,7 @@
       </c>
       <c r="D1753" s="1" t="inlineStr">
         <is>
-          <t>安全；安全性；防护物</t>
+          <t>押金；抵押品</t>
         </is>
       </c>
       <c r="E1753" s="1" t="inlineStr">
@@ -56531,7 +56531,7 @@
       </c>
       <c r="B1754" s="1" t="inlineStr">
         <is>
-          <t>[tʁyːbən] 暗淡的〈v.〉</t>
+          <t>[tʁyːbən] 使浑浊；使暗淡；使忧郁〈v.〉</t>
         </is>
       </c>
       <c r="C1754" s="1" t="inlineStr">
@@ -56541,7 +56541,7 @@
       </c>
       <c r="D1754" s="1" t="inlineStr">
         <is>
-          <t>暗淡的</t>
+          <t>使浑浊；使暗淡；使忧郁</t>
         </is>
       </c>
       <c r="E1754" s="1" t="inlineStr">
@@ -56915,7 +56915,7 @@
       </c>
       <c r="B1766" s="1" t="inlineStr">
         <is>
-          <t>[pʁaktɪʃə] 个别指导；论文；学习指南〈adv.〉</t>
+          <t>[pʁaktɪʃə] 实用的；实际的〈adv.〉</t>
         </is>
       </c>
       <c r="C1766" s="1" t="inlineStr">
@@ -56925,7 +56925,7 @@
       </c>
       <c r="D1766" s="1" t="inlineStr">
         <is>
-          <t>个别指导；论文；学习指南</t>
+          <t>实用的；实际的</t>
         </is>
       </c>
       <c r="E1766" s="1" t="inlineStr">
@@ -56947,7 +56947,7 @@
       </c>
       <c r="B1767" s="1" t="inlineStr">
         <is>
-          <t>[aʊfʁəçtəʁhaltən] 支持；遵守；袖手旁观〈v.〉</t>
+          <t>[aʊfʁəçtəʁhaltən] 维持；保持；维护〈v.〉</t>
         </is>
       </c>
       <c r="C1767" s="1" t="inlineStr">
@@ -56957,7 +56957,7 @@
       </c>
       <c r="D1767" s="1" t="inlineStr">
         <is>
-          <t>支持；遵守；袖手旁观</t>
+          <t>维持；保持；维护</t>
         </is>
       </c>
       <c r="E1767" s="1" t="inlineStr">
@@ -57011,7 +57011,7 @@
       </c>
       <c r="B1769" s="1" t="inlineStr">
         <is>
-          <t>[zeːnatɔʁən] 参议员（复数）〈n.〉</t>
+          <t>[zeːnatɔʁən] 参议员（复数）〈n.m.〉〈n.〉</t>
         </is>
       </c>
       <c r="C1769" s="1" t="inlineStr">
@@ -57021,7 +57021,7 @@
       </c>
       <c r="D1769" s="1" t="inlineStr">
         <is>
-          <t>参议员（复数）</t>
+          <t>参议员（复数）〈n.m.〉</t>
         </is>
       </c>
       <c r="E1769" s="1" t="inlineStr">
@@ -57075,7 +57075,7 @@
       </c>
       <c r="B1771" s="1" t="inlineStr">
         <is>
-          <t>[ʃpɔʁtliːç] 嬉戏地；闹着玩地〈adv.〉</t>
+          <t>[ʃpɔʁtliːç] 体育的；运动的；健壮的〈adv.〉</t>
         </is>
       </c>
       <c r="C1771" s="1" t="inlineStr">
@@ -57085,7 +57085,7 @@
       </c>
       <c r="D1771" s="1" t="inlineStr">
         <is>
-          <t>嬉戏地；闹着玩地</t>
+          <t>体育的；运动的；健壮的</t>
         </is>
       </c>
       <c r="E1771" s="1" t="inlineStr">
@@ -57139,7 +57139,7 @@
       </c>
       <c r="B1773" s="1" t="inlineStr">
         <is>
-          <t>[hɔʏl] 不要；禁忌〈n.〉</t>
+          <t>[hɔʏl] 嚎哭；哀嚎；嚎叫〈n.〉</t>
         </is>
       </c>
       <c r="C1773" s="1" t="inlineStr">
@@ -57149,7 +57149,7 @@
       </c>
       <c r="D1773" s="1" t="inlineStr">
         <is>
-          <t>不要；禁忌</t>
+          <t>嚎哭；哀嚎；嚎叫</t>
         </is>
       </c>
       <c r="E1773" s="1" t="inlineStr">
@@ -57171,7 +57171,7 @@
       </c>
       <c r="B1774" s="1" t="inlineStr">
         <is>
-          <t>[fɛʁziːɡəln] 印章；封条；海豹〈v.〉</t>
+          <t>[fɛʁziːɡəln] 密封；封缄〈v.〉</t>
         </is>
       </c>
       <c r="C1774" s="1" t="inlineStr">
@@ -57181,7 +57181,7 @@
       </c>
       <c r="D1774" s="1" t="inlineStr">
         <is>
-          <t>印章；封条；海豹</t>
+          <t>密封；封缄</t>
         </is>
       </c>
       <c r="E1774" s="1" t="inlineStr">
@@ -57267,12 +57267,12 @@
       </c>
       <c r="B1777" s="1" t="inlineStr">
         <is>
-          <t>[anvəndʊnk] 应用；申请；志愿书〈n.f.〉</t>
+          <t>[anvəndʊŋ] 应用；申请；志愿书〈n.f.〉</t>
         </is>
       </c>
       <c r="C1777" s="1" t="inlineStr">
         <is>
-          <t>anvəndʊnk</t>
+          <t>anvəndʊŋ</t>
         </is>
       </c>
       <c r="D1777" s="1" t="inlineStr">
@@ -57299,7 +57299,7 @@
       </c>
       <c r="B1778" s="1" t="inlineStr">
         <is>
-          <t>[fɔʁbaɪfaːʁən] 驾车；快车道；推进力〈v.〉</t>
+          <t>[fɔʁbaɪfaːʁən] 驶过；经过〈v.〉</t>
         </is>
       </c>
       <c r="C1778" s="1" t="inlineStr">
@@ -57309,7 +57309,7 @@
       </c>
       <c r="D1778" s="1" t="inlineStr">
         <is>
-          <t>驾车；快车道；推进力</t>
+          <t>驶过；经过</t>
         </is>
       </c>
       <c r="E1778" s="1" t="inlineStr">
@@ -57363,7 +57363,7 @@
       </c>
       <c r="B1780" s="1" t="inlineStr">
         <is>
-          <t>[naxlasən] 宽恕；豁免；免罪〈n.〉</t>
+          <t>[naxlasən] 减弱；减退；松懈〈v.〉〈n.〉</t>
         </is>
       </c>
       <c r="C1780" s="1" t="inlineStr">
@@ -57373,7 +57373,7 @@
       </c>
       <c r="D1780" s="1" t="inlineStr">
         <is>
-          <t>宽恕；豁免；免罪</t>
+          <t>减弱；减退；松懈〈v.〉</t>
         </is>
       </c>
       <c r="E1780" s="1" t="inlineStr">
@@ -57555,7 +57555,7 @@
       </c>
       <c r="B1786" s="1" t="inlineStr">
         <is>
-          <t>[ɪndɪʃə] 串；丛；群〈n.〉</t>
+          <t>[ɪndɪʃə] 印度人；印度的〈n.〉</t>
         </is>
       </c>
       <c r="C1786" s="1" t="inlineStr">
@@ -57565,7 +57565,7 @@
       </c>
       <c r="D1786" s="1" t="inlineStr">
         <is>
-          <t>串；丛；群</t>
+          <t>印度人；印度的</t>
         </is>
       </c>
       <c r="E1786" s="1" t="inlineStr">
@@ -57683,17 +57683,17 @@
       </c>
       <c r="B1790" s="1" t="inlineStr">
         <is>
-          <t>[aʊfasʊnk] 观念；概念；妊娠；受孕〈n.f.〉</t>
+          <t>[aʊfasʊŋ] 理解；见解；看法〈n.f.〉（“受孕”应为 Empfängnis）〈n.f.〉</t>
         </is>
       </c>
       <c r="C1790" s="1" t="inlineStr">
         <is>
-          <t>aʊfasʊnk</t>
+          <t>aʊfasʊŋ</t>
         </is>
       </c>
       <c r="D1790" s="1" t="inlineStr">
         <is>
-          <t>观念；概念；妊娠；受孕</t>
+          <t>理解；见解；看法〈n.f.〉（“受孕”应为 Empfängnis）</t>
         </is>
       </c>
       <c r="E1790" s="1" t="inlineStr">
@@ -57811,7 +57811,7 @@
       </c>
       <c r="B1794" s="1" t="inlineStr">
         <is>
-          <t>[moːp] 群氓；贱民；乌合之众〈n.m.〉</t>
+          <t>[moːp] 群氓；乌合之众〈n.m.〉〈n.m.〉</t>
         </is>
       </c>
       <c r="C1794" s="1" t="inlineStr">
@@ -57821,7 +57821,7 @@
       </c>
       <c r="D1794" s="1" t="inlineStr">
         <is>
-          <t>群氓；贱民；乌合之众</t>
+          <t>群氓；乌合之众〈n.m.〉</t>
         </is>
       </c>
       <c r="E1794" s="1" t="inlineStr">
@@ -57971,7 +57971,7 @@
       </c>
       <c r="B1799" s="1" t="inlineStr">
         <is>
-          <t>[baːzəbalʃlɛɡɐ] 棒球；棒球系统〈n.m.〉</t>
+          <t>[baːzəbalʃlɛɡɐ] 棒球棒〈n.m.〉</t>
         </is>
       </c>
       <c r="C1799" s="1" t="inlineStr">
@@ -57981,7 +57981,7 @@
       </c>
       <c r="D1799" s="1" t="inlineStr">
         <is>
-          <t>棒球；棒球系统</t>
+          <t>棒球棒</t>
         </is>
       </c>
       <c r="E1799" s="1" t="inlineStr">
@@ -58003,7 +58003,7 @@
       </c>
       <c r="B1800" s="1" t="inlineStr">
         <is>
-          <t>[fliːsənt] 漂浮的；浮动的；移动的〈adv.〉</t>
+          <t>[fliːsənt] 流动的；流利的；流畅的〈adv.〉</t>
         </is>
       </c>
       <c r="C1800" s="1" t="inlineStr">
@@ -58013,7 +58013,7 @@
       </c>
       <c r="D1800" s="1" t="inlineStr">
         <is>
-          <t>漂浮的；浮动的；移动的</t>
+          <t>流动的；流利的；流畅的</t>
         </is>
       </c>
       <c r="E1800" s="1" t="inlineStr">
@@ -58099,7 +58099,7 @@
       </c>
       <c r="B1803" s="1" t="inlineStr">
         <is>
-          <t>[lɛndəʁaɪən] 平原；平面〈n.〉</t>
+          <t>[lɛndəʁaɪən] 土地；地产；田产〈n.〉</t>
         </is>
       </c>
       <c r="C1803" s="1" t="inlineStr">
@@ -58109,7 +58109,7 @@
       </c>
       <c r="D1803" s="1" t="inlineStr">
         <is>
-          <t>平原；平面</t>
+          <t>土地；地产；田产</t>
         </is>
       </c>
       <c r="E1803" s="1" t="inlineStr">
@@ -58451,17 +58451,17 @@
       </c>
       <c r="B1814" s="1" t="inlineStr">
         <is>
-          <t>[aɪnvɪlɪɡʊnk] 附着；粘着；支持〈n.f.〉</t>
+          <t>[aɪnvɪlɪɡʊŋ] 同意；允诺〈n.f.〉</t>
         </is>
       </c>
       <c r="C1814" s="1" t="inlineStr">
         <is>
-          <t>aɪnvɪlɪɡʊnk</t>
+          <t>aɪnvɪlɪɡʊŋ</t>
         </is>
       </c>
       <c r="D1814" s="1" t="inlineStr">
         <is>
-          <t>附着；粘着；支持</t>
+          <t>同意；允诺</t>
         </is>
       </c>
       <c r="E1814" s="1" t="inlineStr">
@@ -58579,7 +58579,7 @@
       </c>
       <c r="B1818" s="1" t="inlineStr">
         <is>
-          <t>[ʁɛnfaːʁɐ] 赛马；赛车；空转；急转〈n.m.〉</t>
+          <t>[ʁɛnfaːʁɐ] 赛车手；赛车运动员〈n.m.〉</t>
         </is>
       </c>
       <c r="C1818" s="1" t="inlineStr">
@@ -58589,7 +58589,7 @@
       </c>
       <c r="D1818" s="1" t="inlineStr">
         <is>
-          <t>赛马；赛车；空转；急转</t>
+          <t>赛车手；赛车运动员</t>
         </is>
       </c>
       <c r="E1818" s="1" t="inlineStr">
@@ -58611,7 +58611,7 @@
       </c>
       <c r="B1819" s="1" t="inlineStr">
         <is>
-          <t>[ɡeːʁɪçtsbəʃlʊs] 法院；庭院〈n.m.〉</t>
+          <t>[ɡeːʁɪçtsbəʃlʊs] 法院裁定；法庭决议〈n.m.〉</t>
         </is>
       </c>
       <c r="C1819" s="1" t="inlineStr">
@@ -58621,7 +58621,7 @@
       </c>
       <c r="D1819" s="1" t="inlineStr">
         <is>
-          <t>法院；庭院</t>
+          <t>法院裁定；法庭决议</t>
         </is>
       </c>
       <c r="E1819" s="1" t="inlineStr">
@@ -58803,7 +58803,7 @@
       </c>
       <c r="B1825" s="1" t="inlineStr">
         <is>
-          <t>[ʃtɔfə] 流溢；面红；旺盛〈n.〉</t>
+          <t>[ʃtɔfə] 材料；布料；物质〈n.〉</t>
         </is>
       </c>
       <c r="C1825" s="1" t="inlineStr">
@@ -58813,7 +58813,7 @@
       </c>
       <c r="D1825" s="1" t="inlineStr">
         <is>
-          <t>流溢；面红；旺盛</t>
+          <t>材料；布料；物质</t>
         </is>
       </c>
       <c r="E1825" s="1" t="inlineStr">
@@ -59059,7 +59059,7 @@
       </c>
       <c r="B1833" s="1" t="inlineStr">
         <is>
-          <t>[hɪntəʁhɛltɪç] 蛇的；蛇一般的；弯弯曲曲的〈adj.〉</t>
+          <t>[hɪntəʁhɛltɪç] 阴险的；狡猾的；暗地里的〈adj.〉〈adj.〉</t>
         </is>
       </c>
       <c r="C1833" s="1" t="inlineStr">
@@ -59069,7 +59069,7 @@
       </c>
       <c r="D1833" s="1" t="inlineStr">
         <is>
-          <t>蛇的；蛇一般的；弯弯曲曲的</t>
+          <t>阴险的；狡猾的；暗地里的〈adj.〉</t>
         </is>
       </c>
       <c r="E1833" s="1" t="inlineStr">
@@ -59091,7 +59091,7 @@
       </c>
       <c r="B1834" s="1" t="inlineStr">
         <is>
-          <t>[ʊnɡʏltɪç] 病人；无效的〈adj.〉</t>
+          <t>[ʊnɡʏltɪç] 无效的〈adj.〉</t>
         </is>
       </c>
       <c r="C1834" s="1" t="inlineStr">
@@ -59101,7 +59101,7 @@
       </c>
       <c r="D1834" s="1" t="inlineStr">
         <is>
-          <t>病人；无效的</t>
+          <t>无效的</t>
         </is>
       </c>
       <c r="E1834" s="1" t="inlineStr">
@@ -59155,7 +59155,7 @@
       </c>
       <c r="B1836" s="1" t="inlineStr">
         <is>
-          <t>[ʁoːzɪnən] 有；怀有；拿〈n.〉</t>
+          <t>[ʁoːzɪnən] 葡萄干〈n.〉</t>
         </is>
       </c>
       <c r="C1836" s="1" t="inlineStr">
@@ -59165,7 +59165,7 @@
       </c>
       <c r="D1836" s="1" t="inlineStr">
         <is>
-          <t>有；怀有；拿</t>
+          <t>葡萄干</t>
         </is>
       </c>
       <c r="E1836" s="1" t="inlineStr">
@@ -59283,7 +59283,7 @@
       </c>
       <c r="B1840" s="1" t="inlineStr">
         <is>
-          <t>[fiːləʁlaɪ] 的；属于〈adv.〉</t>
+          <t>[fiːləʁlaɪ] 种种；多种多样的〈adv.〉</t>
         </is>
       </c>
       <c r="C1840" s="1" t="inlineStr">
@@ -59293,7 +59293,7 @@
       </c>
       <c r="D1840" s="1" t="inlineStr">
         <is>
-          <t>的；属于</t>
+          <t>种种；多种多样的</t>
         </is>
       </c>
       <c r="E1840" s="1" t="inlineStr">
@@ -59475,7 +59475,7 @@
       </c>
       <c r="B1846" s="1" t="inlineStr">
         <is>
-          <t>[tʊʁbʊlənt͡sən] 空气；旋律；态度；晾〈n.〉</t>
+          <t>[tʊʁbʊlənt͡sən] 湍流；动荡；骚乱〈n.〉</t>
         </is>
       </c>
       <c r="C1846" s="1" t="inlineStr">
@@ -59485,7 +59485,7 @@
       </c>
       <c r="D1846" s="1" t="inlineStr">
         <is>
-          <t>空气；旋律；态度；晾</t>
+          <t>湍流；动荡；骚乱</t>
         </is>
       </c>
       <c r="E1846" s="1" t="inlineStr">
@@ -59571,7 +59571,7 @@
       </c>
       <c r="B1849" s="1" t="inlineStr">
         <is>
-          <t>[aʊsɪçtslɔs] 孤独的；悲惨的；凄凉的〈adv.〉</t>
+          <t>[aʊsɪçtslɔs] 无望的；没有前途的〈adv.〉</t>
         </is>
       </c>
       <c r="C1849" s="1" t="inlineStr">
@@ -59581,7 +59581,7 @@
       </c>
       <c r="D1849" s="1" t="inlineStr">
         <is>
-          <t>孤独的；悲惨的；凄凉的</t>
+          <t>无望的；没有前途的</t>
         </is>
       </c>
       <c r="E1849" s="1" t="inlineStr">
@@ -59731,7 +59731,7 @@
       </c>
       <c r="B1854" s="1" t="inlineStr">
         <is>
-          <t>[bɛʁtʁaːm] 小白菊〈n.m.〉</t>
+          <t>[bɛʁtʁaːm] 贝特拉姆（男子名）〈n.m.〉</t>
         </is>
       </c>
       <c r="C1854" s="1" t="inlineStr">
@@ -59741,7 +59741,7 @@
       </c>
       <c r="D1854" s="1" t="inlineStr">
         <is>
-          <t>小白菊</t>
+          <t>贝特拉姆（男子名）</t>
         </is>
       </c>
       <c r="E1854" s="1" t="inlineStr">
@@ -59859,7 +59859,7 @@
       </c>
       <c r="B1858" s="1" t="inlineStr">
         <is>
-          <t>[haltəstələ] 停止点；爆炸点〈n.f.〉</t>
+          <t>[haltəstələ] 车站；停靠站〈n.f.〉</t>
         </is>
       </c>
       <c r="C1858" s="1" t="inlineStr">
@@ -59869,7 +59869,7 @@
       </c>
       <c r="D1858" s="1" t="inlineStr">
         <is>
-          <t>停止点；爆炸点</t>
+          <t>车站；停靠站</t>
         </is>
       </c>
       <c r="E1858" s="1" t="inlineStr">
@@ -59891,7 +59891,7 @@
       </c>
       <c r="B1859" s="1" t="inlineStr">
         <is>
-          <t>[baʊʊntəʁneːmɐ] 建筑物；建筑；营造〈n.m.〉</t>
+          <t>[baʊʊntəʁneːmɐ] 建筑承包商；营造商〈n.m.〉</t>
         </is>
       </c>
       <c r="C1859" s="1" t="inlineStr">
@@ -59901,7 +59901,7 @@
       </c>
       <c r="D1859" s="1" t="inlineStr">
         <is>
-          <t>建筑物；建筑；营造</t>
+          <t>建筑承包商；营造商</t>
         </is>
       </c>
       <c r="E1859" s="1" t="inlineStr">
@@ -60051,7 +60051,7 @@
       </c>
       <c r="B1864" s="1" t="inlineStr">
         <is>
-          <t>[ʃtaɪl] 急速上升；变焦摄影〈adv.〉</t>
+          <t>[ʃtaɪl] 陡峭的；急剧的〈adv.〉</t>
         </is>
       </c>
       <c r="C1864" s="1" t="inlineStr">
@@ -60061,7 +60061,7 @@
       </c>
       <c r="D1864" s="1" t="inlineStr">
         <is>
-          <t>急速上升；变焦摄影</t>
+          <t>陡峭的；急剧的</t>
         </is>
       </c>
       <c r="E1864" s="1" t="inlineStr">
@@ -60115,7 +60115,7 @@
       </c>
       <c r="B1866" s="1" t="inlineStr">
         <is>
-          <t>[kaːʁɔ] 检查；支票；阻止物〈n.〉</t>
+          <t>[kaːʁɔ] 方块（纸牌）；方格；菱形〈n.〉</t>
         </is>
       </c>
       <c r="C1866" s="1" t="inlineStr">
@@ -60125,7 +60125,7 @@
       </c>
       <c r="D1866" s="1" t="inlineStr">
         <is>
-          <t>检查；支票；阻止物</t>
+          <t>方块（纸牌）；方格；菱形</t>
         </is>
       </c>
       <c r="E1866" s="1" t="inlineStr">
@@ -60275,7 +60275,7 @@
       </c>
       <c r="B1871" s="1" t="inlineStr">
         <is>
-          <t>[ɡɔldənəs] 金门海峡〈adv.〉</t>
+          <t>[ɡɔldənəs] 金色的；金制的〈adj.〉〈adv.〉</t>
         </is>
       </c>
       <c r="C1871" s="1" t="inlineStr">
@@ -60285,7 +60285,7 @@
       </c>
       <c r="D1871" s="1" t="inlineStr">
         <is>
-          <t>金门海峡</t>
+          <t>金色的；金制的〈adj.〉</t>
         </is>
       </c>
       <c r="E1871" s="1" t="inlineStr">
@@ -60371,7 +60371,7 @@
       </c>
       <c r="B1874" s="1" t="inlineStr">
         <is>
-          <t>[dɪplɔmatɪʃə] 外交关系〈adv.〉</t>
+          <t>[dɪplɔmatɪʃə] 外交的；圆滑的；老练的〈adv.〉</t>
         </is>
       </c>
       <c r="C1874" s="1" t="inlineStr">
@@ -60381,7 +60381,7 @@
       </c>
       <c r="D1874" s="1" t="inlineStr">
         <is>
-          <t>外交关系</t>
+          <t>外交的；圆滑的；老练的</t>
         </is>
       </c>
       <c r="E1874" s="1" t="inlineStr">
@@ -60403,7 +60403,7 @@
       </c>
       <c r="B1875" s="1" t="inlineStr">
         <is>
-          <t>[aʊfkləbɐ] 屠夫；尖刀；刺〈n.m.〉</t>
+          <t>[aʊfkləbɐ] 贴纸；标签〈n.m.〉</t>
         </is>
       </c>
       <c r="C1875" s="1" t="inlineStr">
@@ -60413,7 +60413,7 @@
       </c>
       <c r="D1875" s="1" t="inlineStr">
         <is>
-          <t>屠夫；尖刀；刺</t>
+          <t>贴纸；标签</t>
         </is>
       </c>
       <c r="E1875" s="1" t="inlineStr">
@@ -60467,7 +60467,7 @@
       </c>
       <c r="B1877" s="1" t="inlineStr">
         <is>
-          <t>[aʊst͡suːaltən] 生活过得有价值的；过得去的；值得过的〈v.〉</t>
+          <t>[aʊst͡suːaltən] 忍受；经受住〈v.〉</t>
         </is>
       </c>
       <c r="C1877" s="1" t="inlineStr">
@@ -60477,7 +60477,7 @@
       </c>
       <c r="D1877" s="1" t="inlineStr">
         <is>
-          <t>生活过得有价值的；过得去的；值得过的</t>
+          <t>忍受；经受住</t>
         </is>
       </c>
       <c r="E1877" s="1" t="inlineStr">
@@ -60531,7 +60531,7 @@
       </c>
       <c r="B1879" s="1" t="inlineStr">
         <is>
-          <t>[fɛʁzʊkskanɪnçən] 天竺鼠〈n.〉</t>
+          <t>[fɛʁzʊkskanɪnçən] 实验豚鼠；试验品〈n.〉</t>
         </is>
       </c>
       <c r="C1879" s="1" t="inlineStr">
@@ -60541,7 +60541,7 @@
       </c>
       <c r="D1879" s="1" t="inlineStr">
         <is>
-          <t>天竺鼠</t>
+          <t>实验豚鼠；试验品</t>
         </is>
       </c>
       <c r="E1879" s="1" t="inlineStr">
@@ -60883,7 +60883,7 @@
       </c>
       <c r="B1890" s="1" t="inlineStr">
         <is>
-          <t>[fɛʁt͡suːk] 否定；否定语；负数〈n.m.〉</t>
+          <t>[fɛʁt͡suːk] 拖延；延误；迟延〈n.m.〉</t>
         </is>
       </c>
       <c r="C1890" s="1" t="inlineStr">
@@ -60893,7 +60893,7 @@
       </c>
       <c r="D1890" s="1" t="inlineStr">
         <is>
-          <t>否定；否定语；负数</t>
+          <t>拖延；延误；迟延</t>
         </is>
       </c>
       <c r="E1890" s="1" t="inlineStr">
@@ -60915,7 +60915,7 @@
       </c>
       <c r="B1891" s="1" t="inlineStr">
         <is>
-          <t>[afʁɪkanɪʃə] 非洲事物；非洲风格〈n.〉</t>
+          <t>[afʁɪkanɪʃə] 非洲的〈adj.〉（Afrikaner 才指非洲人）〈n.〉</t>
         </is>
       </c>
       <c r="C1891" s="1" t="inlineStr">
@@ -60925,7 +60925,7 @@
       </c>
       <c r="D1891" s="1" t="inlineStr">
         <is>
-          <t>非洲事物；非洲风格</t>
+          <t>非洲的〈adj.〉（Afrikaner 才指非洲人）</t>
         </is>
       </c>
       <c r="E1891" s="1" t="inlineStr">
@@ -60947,7 +60947,7 @@
       </c>
       <c r="B1892" s="1" t="inlineStr">
         <is>
-          <t>[pʊnʃ] 打洞器；钻孔机；冲压机〈n.m.〉</t>
+          <t>[pʊnʃ] 潘趣酒；热果酒〈n.m.〉</t>
         </is>
       </c>
       <c r="C1892" s="1" t="inlineStr">
@@ -60957,7 +60957,7 @@
       </c>
       <c r="D1892" s="1" t="inlineStr">
         <is>
-          <t>打洞器；钻孔机；冲压机</t>
+          <t>潘趣酒；热果酒</t>
         </is>
       </c>
       <c r="E1892" s="1" t="inlineStr">
@@ -61139,7 +61139,7 @@
       </c>
       <c r="B1898" s="1" t="inlineStr">
         <is>
-          <t>[vaʁtət͡sɪmɐ] 赌注；下赌注〈n.〉</t>
+          <t>[vaʁtət͡sɪmɐ] 等候室；候诊室〈n.〉</t>
         </is>
       </c>
       <c r="C1898" s="1" t="inlineStr">
@@ -61149,7 +61149,7 @@
       </c>
       <c r="D1898" s="1" t="inlineStr">
         <is>
-          <t>赌注；下赌注</t>
+          <t>等候室；候诊室</t>
         </is>
       </c>
       <c r="E1898" s="1" t="inlineStr">
@@ -61395,7 +61395,7 @@
       </c>
       <c r="B1906" s="1" t="inlineStr">
         <is>
-          <t>[ɡʁaʊɐ] 大瀑布；奔流；暴雨〈adv.〉</t>
+          <t>[ɡʁaʊɐ] 灰色的〈adj.〉〈adv.〉</t>
         </is>
       </c>
       <c r="C1906" s="1" t="inlineStr">
@@ -61405,7 +61405,7 @@
       </c>
       <c r="D1906" s="1" t="inlineStr">
         <is>
-          <t>大瀑布；奔流；暴雨</t>
+          <t>灰色的〈adj.〉</t>
         </is>
       </c>
       <c r="E1906" s="1" t="inlineStr">
@@ -61651,7 +61651,7 @@
       </c>
       <c r="B1914" s="1" t="inlineStr">
         <is>
-          <t>[vɪldəʁɐ] 偷猎者；侵入者；炖蛋锅〈n.m.〉</t>
+          <t>[vɪldəʁɐ] 偷猎者；盗猎者〈n.m.〉</t>
         </is>
       </c>
       <c r="C1914" s="1" t="inlineStr">
@@ -61661,7 +61661,7 @@
       </c>
       <c r="D1914" s="1" t="inlineStr">
         <is>
-          <t>偷猎者；侵入者；炖蛋锅</t>
+          <t>偷猎者；盗猎者</t>
         </is>
       </c>
       <c r="E1914" s="1" t="inlineStr">
@@ -61843,7 +61843,7 @@
       </c>
       <c r="B1920" s="1" t="inlineStr">
         <is>
-          <t>[knapə] 乡绅；大地主〈n.m.〉</t>
+          <t>[knapə] 侍从；见习骑士；矿工助手〈n.m.〉</t>
         </is>
       </c>
       <c r="C1920" s="1" t="inlineStr">
@@ -61853,7 +61853,7 @@
       </c>
       <c r="D1920" s="1" t="inlineStr">
         <is>
-          <t>乡绅；大地主</t>
+          <t>侍从；见习骑士；矿工助手</t>
         </is>
       </c>
       <c r="E1920" s="1" t="inlineStr">
@@ -62419,12 +62419,12 @@
       </c>
       <c r="B1938" s="1" t="inlineStr">
         <is>
-          <t>[bɛaxtʊnk] 注意〈n.f.〉</t>
+          <t>[bɛaxtʊŋ] 注意〈n.f.〉</t>
         </is>
       </c>
       <c r="C1938" s="1" t="inlineStr">
         <is>
-          <t>bɛaxtʊnk</t>
+          <t>bɛaxtʊŋ</t>
         </is>
       </c>
       <c r="D1938" s="1" t="inlineStr">
@@ -62483,7 +62483,7 @@
       </c>
       <c r="B1940" s="1" t="inlineStr">
         <is>
-          <t>[ʃtaɪnbʁuːx] 采石场；方形石；猎物〈n.m.〉</t>
+          <t>[ʃtaɪnbʁuːx] 采石场〈n.m.〉〈n.m.〉</t>
         </is>
       </c>
       <c r="C1940" s="1" t="inlineStr">
@@ -62493,7 +62493,7 @@
       </c>
       <c r="D1940" s="1" t="inlineStr">
         <is>
-          <t>采石场；方形石；猎物</t>
+          <t>采石场〈n.m.〉</t>
         </is>
       </c>
       <c r="E1940" s="1" t="inlineStr">
@@ -62739,7 +62739,7 @@
       </c>
       <c r="B1948" s="1" t="inlineStr">
         <is>
-          <t>[ʃmʊkstʏk] 块；片；篇〈n.〉</t>
+          <t>[ʃmʊkstʏk] 首饰；珠宝饰品〈n.〉</t>
         </is>
       </c>
       <c r="C1948" s="1" t="inlineStr">
@@ -62749,7 +62749,7 @@
       </c>
       <c r="D1948" s="1" t="inlineStr">
         <is>
-          <t>块；片；篇</t>
+          <t>首饰；珠宝饰品</t>
         </is>
       </c>
       <c r="E1948" s="1" t="inlineStr">
@@ -62899,7 +62899,7 @@
       </c>
       <c r="B1953" s="1" t="inlineStr">
         <is>
-          <t>[fɛʁɡʁœsəʁt] 肥大的；过度膨胀的；肥厚的〈adv.〉</t>
+          <t>[fɛʁɡʁœsəʁt] 扩大的；放大的〈adv.〉</t>
         </is>
       </c>
       <c r="C1953" s="1" t="inlineStr">
@@ -62909,7 +62909,7 @@
       </c>
       <c r="D1953" s="1" t="inlineStr">
         <is>
-          <t>肥大的；过度膨胀的；肥厚的</t>
+          <t>扩大的；放大的</t>
         </is>
       </c>
       <c r="E1953" s="1" t="inlineStr">
@@ -62931,7 +62931,7 @@
       </c>
       <c r="B1954" s="1" t="inlineStr">
         <is>
-          <t>[ɡeːzət͡sliːç] 所有者的；所有权的〈adj.〉</t>
+          <t>[ɡeːzət͡sliːç] 法定的；法律上的；合法的〈adj.〉</t>
         </is>
       </c>
       <c r="C1954" s="1" t="inlineStr">
@@ -62941,7 +62941,7 @@
       </c>
       <c r="D1954" s="1" t="inlineStr">
         <is>
-          <t>所有者的；所有权的</t>
+          <t>法定的；法律上的；合法的</t>
         </is>
       </c>
       <c r="E1954" s="1" t="inlineStr">
@@ -63251,7 +63251,7 @@
       </c>
       <c r="B1964" s="1" t="inlineStr">
         <is>
-          <t>[bʁʊxtaɪl] 滴；细流〈n.m.〉</t>
+          <t>[bʁʊxtaɪl] 一小部分；极小部分〈n.m.〉</t>
         </is>
       </c>
       <c r="C1964" s="1" t="inlineStr">
@@ -63261,7 +63261,7 @@
       </c>
       <c r="D1964" s="1" t="inlineStr">
         <is>
-          <t>滴；细流</t>
+          <t>一小部分；极小部分</t>
         </is>
       </c>
       <c r="E1964" s="1" t="inlineStr">
@@ -63443,7 +63443,7 @@
       </c>
       <c r="B1970" s="1" t="inlineStr">
         <is>
-          <t>[fɛʁʃlaɪɐn] 掩饰；装糊涂；虚伪；瞒病〈n.〉</t>
+          <t>[fɛʁʃlaɪɐn] 掩饰；遮掩〈v.〉〈n.〉</t>
         </is>
       </c>
       <c r="C1970" s="1" t="inlineStr">
@@ -63453,7 +63453,7 @@
       </c>
       <c r="D1970" s="1" t="inlineStr">
         <is>
-          <t>掩饰；装糊涂；虚伪；瞒病</t>
+          <t>掩饰；遮掩〈v.〉</t>
         </is>
       </c>
       <c r="E1970" s="1" t="inlineStr">
@@ -63667,7 +63667,7 @@
       </c>
       <c r="B1977" s="1" t="inlineStr">
         <is>
-          <t>[anhaltspʊnkt] 引导者；导游；指南〈n.m.〉</t>
+          <t>[anhaltspʊnkt] 依据；线索；论据〈n.m.〉</t>
         </is>
       </c>
       <c r="C1977" s="1" t="inlineStr">
@@ -63677,7 +63677,7 @@
       </c>
       <c r="D1977" s="1" t="inlineStr">
         <is>
-          <t>引导者；导游；指南</t>
+          <t>依据；线索；论据</t>
         </is>
       </c>
       <c r="E1977" s="1" t="inlineStr">
@@ -64051,7 +64051,7 @@
       </c>
       <c r="B1989" s="1" t="inlineStr">
         <is>
-          <t>[ɛʁəɡʊnk] 奋发；激励〈n.f.〉</t>
+          <t>[ɛʁəɡʊnk] 激动；兴奋；刺激〈n.f.〉</t>
         </is>
       </c>
       <c r="C1989" s="1" t="inlineStr">
@@ -64061,7 +64061,7 @@
       </c>
       <c r="D1989" s="1" t="inlineStr">
         <is>
-          <t>奋发；激励</t>
+          <t>激动；兴奋；刺激</t>
         </is>
       </c>
       <c r="E1989" s="1" t="inlineStr">
@@ -64275,12 +64275,12 @@
       </c>
       <c r="B1996" s="1" t="inlineStr">
         <is>
-          <t>[anstəlʊnk] 雇用；职业；工作〈n.f.〉</t>
+          <t>[anstəlʊŋ] 雇用；职业；工作〈n.f.〉</t>
         </is>
       </c>
       <c r="C1996" s="1" t="inlineStr">
         <is>
-          <t>anstəlʊnk</t>
+          <t>anstəlʊŋ</t>
         </is>
       </c>
       <c r="D1996" s="1" t="inlineStr">
@@ -64467,7 +64467,7 @@
       </c>
       <c r="B2002" s="1" t="inlineStr">
         <is>
-          <t>[ʃmɪnkə] 捏造〈n.f.〉</t>
+          <t>[ʃmɪnkə] 化妆品；脂粉〈n.f.〉</t>
         </is>
       </c>
       <c r="C2002" s="1" t="inlineStr">
@@ -64477,7 +64477,7 @@
       </c>
       <c r="D2002" s="1" t="inlineStr">
         <is>
-          <t>捏造</t>
+          <t>化妆品；脂粉</t>
         </is>
       </c>
       <c r="E2002" s="1" t="inlineStr">
@@ -64499,7 +64499,7 @@
       </c>
       <c r="B2003" s="1" t="inlineStr">
         <is>
-          <t>[ʃɪldkʁœtən] 乌龟〈n.〉</t>
+          <t>[ʃɪldkʁœtən] 乌龟〈n.f.〉（单数 Schildkröte，此处为复数形式）〈n.〉</t>
         </is>
       </c>
       <c r="C2003" s="1" t="inlineStr">
@@ -64509,7 +64509,7 @@
       </c>
       <c r="D2003" s="1" t="inlineStr">
         <is>
-          <t>乌龟</t>
+          <t>乌龟〈n.f.〉（单数 Schildkröte，此处为复数形式）</t>
         </is>
       </c>
       <c r="E2003" s="1" t="inlineStr">
@@ -64563,7 +64563,7 @@
       </c>
       <c r="B2005" s="1" t="inlineStr">
         <is>
-          <t>[halbt͡saɪt] 半工半薪；半日薪〈n.f.〉</t>
+          <t>[halbt͡saɪt] 中场休息；半场〈n.f.〉</t>
         </is>
       </c>
       <c r="C2005" s="1" t="inlineStr">
@@ -64573,7 +64573,7 @@
       </c>
       <c r="D2005" s="1" t="inlineStr">
         <is>
-          <t>半工半薪；半日薪</t>
+          <t>中场休息；半场</t>
         </is>
       </c>
       <c r="E2005" s="1" t="inlineStr">
@@ -64755,7 +64755,7 @@
       </c>
       <c r="B2011" s="1" t="inlineStr">
         <is>
-          <t>[dɪaləkt] 方言；地方话〈n.〉</t>
+          <t>[dɪaləkt] 方言；地方话〈n.m.〉〈n.〉</t>
         </is>
       </c>
       <c r="C2011" s="1" t="inlineStr">
@@ -64765,7 +64765,7 @@
       </c>
       <c r="D2011" s="1" t="inlineStr">
         <is>
-          <t>方言；地方话</t>
+          <t>方言；地方话〈n.m.〉</t>
         </is>
       </c>
       <c r="E2011" s="1" t="inlineStr">
@@ -64819,7 +64819,7 @@
       </c>
       <c r="B2013" s="1" t="inlineStr">
         <is>
-          <t>[t͡sapəln] 荷边装饰；挣扎〈v.〉</t>
+          <t>[t͡sapəln] 扭动；乱动；坐立不安〈v.〉</t>
         </is>
       </c>
       <c r="C2013" s="1" t="inlineStr">
@@ -64829,7 +64829,7 @@
       </c>
       <c r="D2013" s="1" t="inlineStr">
         <is>
-          <t>荷边装饰；挣扎</t>
+          <t>扭动；乱动；坐立不安</t>
         </is>
       </c>
       <c r="E2013" s="1" t="inlineStr">
@@ -65299,7 +65299,7 @@
       </c>
       <c r="B2028" s="1" t="inlineStr">
         <is>
-          <t>[kɔʁnflakəs] 玉蜀黍；谷类；谷粒〈n.〉</t>
+          <t>[kɔʁnflakəs] 玉米片〈n.〉</t>
         </is>
       </c>
       <c r="C2028" s="1" t="inlineStr">
@@ -65309,7 +65309,7 @@
       </c>
       <c r="D2028" s="1" t="inlineStr">
         <is>
-          <t>玉蜀黍；谷类；谷粒</t>
+          <t>玉米片</t>
         </is>
       </c>
       <c r="E2028" s="1" t="inlineStr">
@@ -65331,7 +65331,7 @@
       </c>
       <c r="B2029" s="1" t="inlineStr">
         <is>
-          <t>[beːtɔnt] 补药；声调的〈adj.〉</t>
+          <t>[beːtɔnt] 强调的；着重的；重读的〈adj.〉</t>
         </is>
       </c>
       <c r="C2029" s="1" t="inlineStr">
@@ -65341,7 +65341,7 @@
       </c>
       <c r="D2029" s="1" t="inlineStr">
         <is>
-          <t>补药；声调的</t>
+          <t>强调的；着重的；重读的</t>
         </is>
       </c>
       <c r="E2029" s="1" t="inlineStr">
@@ -65619,7 +65619,7 @@
       </c>
       <c r="B2038" s="1" t="inlineStr">
         <is>
-          <t>[dʁoːɡənfaːndʊnk] 药；麻药〈n.f.〉</t>
+          <t>[dʁoːɡənfaːndʊnk] 缉毒；毒品侦查〈n.f.〉</t>
         </is>
       </c>
       <c r="C2038" s="1" t="inlineStr">
@@ -65629,7 +65629,7 @@
       </c>
       <c r="D2038" s="1" t="inlineStr">
         <is>
-          <t>药；麻药</t>
+          <t>缉毒；毒品侦查</t>
         </is>
       </c>
       <c r="E2038" s="1" t="inlineStr">
@@ -65843,7 +65843,7 @@
       </c>
       <c r="B2045" s="1" t="inlineStr">
         <is>
-          <t>[bɛʃaɪsən] 螺旋；螺杆；螺钉〈v.〉</t>
+          <t>[bɛʃaɪsən] 欺骗；坑害〈v.〉</t>
         </is>
       </c>
       <c r="C2045" s="1" t="inlineStr">
@@ -65853,7 +65853,7 @@
       </c>
       <c r="D2045" s="1" t="inlineStr">
         <is>
-          <t>螺旋；螺杆；螺钉</t>
+          <t>欺骗；坑害</t>
         </is>
       </c>
       <c r="E2045" s="1" t="inlineStr">
@@ -65971,7 +65971,7 @@
       </c>
       <c r="B2049" s="1" t="inlineStr">
         <is>
-          <t>[fʊnkstɪlə] 无线电；收音机；无线电报〈n.f.〉</t>
+          <t>[fʊnkstɪlə] 无线电静默；通讯中断〈n.f.〉</t>
         </is>
       </c>
       <c r="C2049" s="1" t="inlineStr">
@@ -65981,7 +65981,7 @@
       </c>
       <c r="D2049" s="1" t="inlineStr">
         <is>
-          <t>无线电；收音机；无线电报</t>
+          <t>无线电静默；通讯中断</t>
         </is>
       </c>
       <c r="E2049" s="1" t="inlineStr">
@@ -66003,7 +66003,7 @@
       </c>
       <c r="B2050" s="1" t="inlineStr">
         <is>
-          <t>[poːpɔ] 建立基础〈n.m.〉</t>
+          <t>[poːpɔ] 屁股；臀部〈n.m.〉</t>
         </is>
       </c>
       <c r="C2050" s="1" t="inlineStr">
@@ -66013,7 +66013,7 @@
       </c>
       <c r="D2050" s="1" t="inlineStr">
         <is>
-          <t>建立基础</t>
+          <t>屁股；臀部</t>
         </is>
       </c>
       <c r="E2050" s="1" t="inlineStr">
@@ -66131,7 +66131,7 @@
       </c>
       <c r="B2054" s="1" t="inlineStr">
         <is>
-          <t>[haːʁfaʁbə] 头发；毛发；些微；毛〈n.f.〉</t>
+          <t>[haːʁfaʁbə] 发色；头发颜色〈n.f.〉</t>
         </is>
       </c>
       <c r="C2054" s="1" t="inlineStr">
@@ -66141,7 +66141,7 @@
       </c>
       <c r="D2054" s="1" t="inlineStr">
         <is>
-          <t>头发；毛发；些微；毛</t>
+          <t>发色；头发颜色</t>
         </is>
       </c>
       <c r="E2054" s="1" t="inlineStr">
@@ -66259,12 +66259,12 @@
       </c>
       <c r="B2058" s="1" t="inlineStr">
         <is>
-          <t>[anməldʊnk] 登记；挂号；注册〈n.f.〉</t>
+          <t>[anməldʊŋ] 登记；挂号；注册〈n.f.〉</t>
         </is>
       </c>
       <c r="C2058" s="1" t="inlineStr">
         <is>
-          <t>anməldʊnk</t>
+          <t>anməldʊŋ</t>
         </is>
       </c>
       <c r="D2058" s="1" t="inlineStr">
@@ -66387,7 +66387,7 @@
       </c>
       <c r="B2062" s="1" t="inlineStr">
         <is>
-          <t>[pʁɛːt͡sɪzɪoːn] 切断；简明；简洁〈n.f.〉</t>
+          <t>[pʁɛːt͡sɪzɪoːn] 精确；精密〈n.f.〉</t>
         </is>
       </c>
       <c r="C2062" s="1" t="inlineStr">
@@ -66397,7 +66397,7 @@
       </c>
       <c r="D2062" s="1" t="inlineStr">
         <is>
-          <t>切断；简明；简洁</t>
+          <t>精确；精密</t>
         </is>
       </c>
       <c r="E2062" s="1" t="inlineStr">
@@ -66547,7 +66547,7 @@
       </c>
       <c r="B2067" s="1" t="inlineStr">
         <is>
-          <t>[hɛmʊnɡən] 顾虑；心理障碍〈n.〉</t>
+          <t>[hɛmʊnɡən] 顾虑；心理障碍〈n.f.〉（单数 Hemmung）〈n.〉</t>
         </is>
       </c>
       <c r="C2067" s="1" t="inlineStr">
@@ -66557,7 +66557,7 @@
       </c>
       <c r="D2067" s="1" t="inlineStr">
         <is>
-          <t>顾虑；心理障碍</t>
+          <t>顾虑；心理障碍〈n.f.〉（单数 Hemmung）</t>
         </is>
       </c>
       <c r="E2067" s="1" t="inlineStr">
@@ -66611,7 +66611,7 @@
       </c>
       <c r="B2069" s="1" t="inlineStr">
         <is>
-          <t>[koːʁdɪniːʁən] 同等的人；坐标；同等的；并列的；协调〈v.〉</t>
+          <t>[koːʁdɪniːʁən] 协调；配合〈v.〉</t>
         </is>
       </c>
       <c r="C2069" s="1" t="inlineStr">
@@ -66621,7 +66621,7 @@
       </c>
       <c r="D2069" s="1" t="inlineStr">
         <is>
-          <t>同等的人；坐标；同等的；并列的；协调</t>
+          <t>协调；配合</t>
         </is>
       </c>
       <c r="E2069" s="1" t="inlineStr">
@@ -66803,7 +66803,7 @@
       </c>
       <c r="B2075" s="1" t="inlineStr">
         <is>
-          <t>[fɛʁʃʁaɪbən] 药物治疗；药物处理；医药；药疗法〈n.〉</t>
+          <t>[fɛʁʃʁaɪbən] 开处方；开药〈v.〉〈n.〉</t>
         </is>
       </c>
       <c r="C2075" s="1" t="inlineStr">
@@ -66813,7 +66813,7 @@
       </c>
       <c r="D2075" s="1" t="inlineStr">
         <is>
-          <t>药物治疗；药物处理；医药；药疗法</t>
+          <t>开处方；开药〈v.〉</t>
         </is>
       </c>
       <c r="E2075" s="1" t="inlineStr">
@@ -66931,7 +66931,7 @@
       </c>
       <c r="B2079" s="1" t="inlineStr">
         <is>
-          <t>[oːbəʁaʁt͡st] 助手；助理〈n.m.〉</t>
+          <t>[oːbəʁaʁt͡st] 主治医师；高级医师〈n.m.〉</t>
         </is>
       </c>
       <c r="C2079" s="1" t="inlineStr">
@@ -66941,7 +66941,7 @@
       </c>
       <c r="D2079" s="1" t="inlineStr">
         <is>
-          <t>助手；助理</t>
+          <t>主治医师；高级医师</t>
         </is>
       </c>
       <c r="E2079" s="1" t="inlineStr">
@@ -66995,7 +66995,7 @@
       </c>
       <c r="B2081" s="1" t="inlineStr">
         <is>
-          <t>[ʁaʊ] 粗糙的东西；毛坯；未加工品〈adv.〉</t>
+          <t>[ʁaʊ] 粗糙的；粗鲁的〈adv.〉</t>
         </is>
       </c>
       <c r="C2081" s="1" t="inlineStr">
@@ -67005,7 +67005,7 @@
       </c>
       <c r="D2081" s="1" t="inlineStr">
         <is>
-          <t>粗糙的东西；毛坯；未加工品</t>
+          <t>粗糙的；粗鲁的</t>
         </is>
       </c>
       <c r="E2081" s="1" t="inlineStr">
@@ -67219,7 +67219,7 @@
       </c>
       <c r="B2088" s="1" t="inlineStr">
         <is>
-          <t>[kloːnən] 无性系；代用件〈v.〉</t>
+          <t>[kloːnən] 克隆；无性繁殖〈v.〉</t>
         </is>
       </c>
       <c r="C2088" s="1" t="inlineStr">
@@ -67229,7 +67229,7 @@
       </c>
       <c r="D2088" s="1" t="inlineStr">
         <is>
-          <t>无性系；代用件</t>
+          <t>克隆；无性繁殖</t>
         </is>
       </c>
       <c r="E2088" s="1" t="inlineStr">
@@ -67347,7 +67347,7 @@
       </c>
       <c r="B2092" s="1" t="inlineStr">
         <is>
-          <t>[fɛʁflʊxən] 十六进制；巫婆〈v.〉</t>
+          <t>[fɛʁflʊxən] 诅咒；咒骂〈v.〉</t>
         </is>
       </c>
       <c r="C2092" s="1" t="inlineStr">
@@ -67357,7 +67357,7 @@
       </c>
       <c r="D2092" s="1" t="inlineStr">
         <is>
-          <t>十六进制；巫婆</t>
+          <t>诅咒；咒骂</t>
         </is>
       </c>
       <c r="E2092" s="1" t="inlineStr">
@@ -67379,7 +67379,7 @@
       </c>
       <c r="B2093" s="1" t="inlineStr">
         <is>
-          <t>[naːtʏʁlɪçəs] 白痴；自然的；自然界的；本能的〈adv.〉</t>
+          <t>[naːtʏʁlɪçəs] 自然的；天然的〈adv.〉</t>
         </is>
       </c>
       <c r="C2093" s="1" t="inlineStr">
@@ -67389,7 +67389,7 @@
       </c>
       <c r="D2093" s="1" t="inlineStr">
         <is>
-          <t>白痴；自然的；自然界的；本能的</t>
+          <t>自然的；天然的</t>
         </is>
       </c>
       <c r="E2093" s="1" t="inlineStr">
@@ -67443,7 +67443,7 @@
       </c>
       <c r="B2095" s="1" t="inlineStr">
         <is>
-          <t>[puːdɐ] 粉；粉末〈n.〉</t>
+          <t>[puːdɐ] 粉；粉末〈n.m.〉〈n.〉</t>
         </is>
       </c>
       <c r="C2095" s="1" t="inlineStr">
@@ -67453,7 +67453,7 @@
       </c>
       <c r="D2095" s="1" t="inlineStr">
         <is>
-          <t>粉；粉末</t>
+          <t>粉；粉末〈n.m.〉</t>
         </is>
       </c>
       <c r="E2095" s="1" t="inlineStr">
@@ -67475,7 +67475,7 @@
       </c>
       <c r="B2096" s="1" t="inlineStr">
         <is>
-          <t>[bɔshaɪt] 邪恶；魔界；恶魔研究〈n.f.〉</t>
+          <t>[bɔshaɪt] 恶意；恶毒；狠毒〈n.f.〉</t>
         </is>
       </c>
       <c r="C2096" s="1" t="inlineStr">
@@ -67485,7 +67485,7 @@
       </c>
       <c r="D2096" s="1" t="inlineStr">
         <is>
-          <t>邪恶；魔界；恶魔研究</t>
+          <t>恶意；恶毒；狠毒</t>
         </is>
       </c>
       <c r="E2096" s="1" t="inlineStr">
@@ -67571,7 +67571,7 @@
       </c>
       <c r="B2099" s="1" t="inlineStr">
         <is>
-          <t>[ɡʊt͡ʃaɪn] 证人；保证人；证明者〈n.m.〉</t>
+          <t>[ɡʊt͡ʃaɪn] 优惠券；代金券〈n.m.〉</t>
         </is>
       </c>
       <c r="C2099" s="1" t="inlineStr">
@@ -67581,7 +67581,7 @@
       </c>
       <c r="D2099" s="1" t="inlineStr">
         <is>
-          <t>证人；保证人；证明者</t>
+          <t>优惠券；代金券</t>
         </is>
       </c>
       <c r="E2099" s="1" t="inlineStr">
@@ -67603,7 +67603,7 @@
       </c>
       <c r="B2100" s="1" t="inlineStr">
         <is>
-          <t>[feːʁeːʁʊnk] 奉祀庙中；秘藏〈n.f.〉</t>
+          <t>[feːʁeːʁʊnk] 崇敬；敬仰；爱慕〈n.f.〉</t>
         </is>
       </c>
       <c r="C2100" s="1" t="inlineStr">
@@ -67613,7 +67613,7 @@
       </c>
       <c r="D2100" s="1" t="inlineStr">
         <is>
-          <t>奉祀庙中；秘藏</t>
+          <t>崇敬；敬仰；爱慕</t>
         </is>
       </c>
       <c r="E2100" s="1" t="inlineStr">
@@ -67891,7 +67891,7 @@
       </c>
       <c r="B2109" s="1" t="inlineStr">
         <is>
-          <t>[kaspɐ] 打洞器；钻孔机；冲压机〈n.m.〉</t>
+          <t>[kaspɐ] 木偶戏丑角；滑稽角色〈n.m.〉</t>
         </is>
       </c>
       <c r="C2109" s="1" t="inlineStr">
@@ -67901,7 +67901,7 @@
       </c>
       <c r="D2109" s="1" t="inlineStr">
         <is>
-          <t>打洞器；钻孔机；冲压机</t>
+          <t>木偶戏丑角；滑稽角色</t>
         </is>
       </c>
       <c r="E2109" s="1" t="inlineStr">
@@ -67987,7 +67987,7 @@
       </c>
       <c r="B2112" s="1" t="inlineStr">
         <is>
-          <t>[ɔʁdnɐ] 纸；文件；文章〈n.f.〉</t>
+          <t>[ɔʁdnɐ] 文件夹；活页夹〈n.f.〉</t>
         </is>
       </c>
       <c r="C2112" s="1" t="inlineStr">
@@ -67997,7 +67997,7 @@
       </c>
       <c r="D2112" s="1" t="inlineStr">
         <is>
-          <t>纸；文件；文章</t>
+          <t>文件夹；活页夹</t>
         </is>
       </c>
       <c r="E2112" s="1" t="inlineStr">
@@ -68115,7 +68115,7 @@
       </c>
       <c r="B2116" s="1" t="inlineStr">
         <is>
-          <t>[dɛalən] 心碌；挤；推〈v.〉</t>
+          <t>[dɛalən] 交易；买卖（尤指毒品）〈v.〉</t>
         </is>
       </c>
       <c r="C2116" s="1" t="inlineStr">
@@ -68125,7 +68125,7 @@
       </c>
       <c r="D2116" s="1" t="inlineStr">
         <is>
-          <t>心碌；挤；推</t>
+          <t>交易；买卖（尤指毒品）</t>
         </is>
       </c>
       <c r="E2116" s="1" t="inlineStr">
@@ -68243,7 +68243,7 @@
       </c>
       <c r="B2120" s="1" t="inlineStr">
         <is>
-          <t>[fɛʁɡlaɪçə] 授予；带来；协商〈adv.〉</t>
+          <t>[fɛʁɡlaɪçə] 比较；对比〈adv.〉</t>
         </is>
       </c>
       <c r="C2120" s="1" t="inlineStr">
@@ -68253,7 +68253,7 @@
       </c>
       <c r="D2120" s="1" t="inlineStr">
         <is>
-          <t>授予；带来；协商</t>
+          <t>比较；对比</t>
         </is>
       </c>
       <c r="E2120" s="1" t="inlineStr">
@@ -68307,7 +68307,7 @@
       </c>
       <c r="B2122" s="1" t="inlineStr">
         <is>
-          <t>[zuːpəʁɪntəndənt] 院长；学院院长〈n.m.〉</t>
+          <t>[zuːpəʁɪntəndənt] （新教）教区监督；主管人〈n.m.〉</t>
         </is>
       </c>
       <c r="C2122" s="1" t="inlineStr">
@@ -68317,7 +68317,7 @@
       </c>
       <c r="D2122" s="1" t="inlineStr">
         <is>
-          <t>院长；学院院长</t>
+          <t>（新教）教区监督；主管人</t>
         </is>
       </c>
       <c r="E2122" s="1" t="inlineStr">
@@ -68339,7 +68339,7 @@
       </c>
       <c r="B2123" s="1" t="inlineStr">
         <is>
-          <t>[fɛʁtaɪdɪɡʊnɡsmɪnɪstɐ] 部长；牧师；公使；服侍〈n.m.〉</t>
+          <t>[fɛʁtaɪdɪɡʊnɡsmɪnɪstɐ] 国防部长〈n.m.〉</t>
         </is>
       </c>
       <c r="C2123" s="1" t="inlineStr">
@@ -68349,7 +68349,7 @@
       </c>
       <c r="D2123" s="1" t="inlineStr">
         <is>
-          <t>部长；牧师；公使；服侍</t>
+          <t>国防部长</t>
         </is>
       </c>
       <c r="E2123" s="1" t="inlineStr">
@@ -68627,7 +68627,7 @@
       </c>
       <c r="B2132" s="1" t="inlineStr">
         <is>
-          <t>[hʊndəɡəbəl] 狗；坏蛋；跟踪；尾随〈n.〉</t>
+          <t>[hʊndəɡəbəl] 狗吠声；犬吠〈n.〉</t>
         </is>
       </c>
       <c r="C2132" s="1" t="inlineStr">
@@ -68637,7 +68637,7 @@
       </c>
       <c r="D2132" s="1" t="inlineStr">
         <is>
-          <t>狗；坏蛋；跟踪；尾随</t>
+          <t>狗吠声；犬吠</t>
         </is>
       </c>
       <c r="E2132" s="1" t="inlineStr">
@@ -68915,7 +68915,7 @@
       </c>
       <c r="B2141" s="1" t="inlineStr">
         <is>
-          <t>[ɡeːlaɡəʁt] 有；怀有；拿〈adv.〉</t>
+          <t>[ɡeːlaɡəʁt] 贮存的；存放的；位于〈adv.〉</t>
         </is>
       </c>
       <c r="C2141" s="1" t="inlineStr">
@@ -68925,7 +68925,7 @@
       </c>
       <c r="D2141" s="1" t="inlineStr">
         <is>
-          <t>有；怀有；拿</t>
+          <t>贮存的；存放的；位于</t>
         </is>
       </c>
       <c r="E2141" s="1" t="inlineStr">
@@ -69043,7 +69043,7 @@
       </c>
       <c r="B2145" s="1" t="inlineStr">
         <is>
-          <t>[kapən] 护盖；帽子 / 截短；切除〈n.〉</t>
+          <t>[kapən] 动词 kappen：截断；砍掉；切除〈v.〉（Kappen 亦为 Kappe 的复数）〈n.〉</t>
         </is>
       </c>
       <c r="C2145" s="1" t="inlineStr">
@@ -69053,7 +69053,7 @@
       </c>
       <c r="D2145" s="1" t="inlineStr">
         <is>
-          <t>护盖；帽子 / 截短；切除</t>
+          <t>动词 kappen：截断；砍掉；切除〈v.〉（Kappen 亦为 Kappe 的复数）</t>
         </is>
       </c>
       <c r="E2145" s="1" t="inlineStr">
@@ -69235,12 +69235,12 @@
       </c>
       <c r="B2151" s="1" t="inlineStr">
         <is>
-          <t>[piːnɔkçɪɔ] 童话中的主角〈n.m.〉</t>
+          <t>[piːnɔkjo] 童话中的主角〈n.m.〉</t>
         </is>
       </c>
       <c r="C2151" s="1" t="inlineStr">
         <is>
-          <t>piːnɔkçɪɔ</t>
+          <t>piːnɔkjo</t>
         </is>
       </c>
       <c r="D2151" s="1" t="inlineStr">
@@ -69267,12 +69267,12 @@
       </c>
       <c r="B2152" s="1" t="inlineStr">
         <is>
-          <t>[vʏoːmɪnk] 怀俄明〈n.〉</t>
+          <t>[vʏoːmɪŋ] 怀俄明〈n.〉</t>
         </is>
       </c>
       <c r="C2152" s="1" t="inlineStr">
         <is>
-          <t>vʏoːmɪnk</t>
+          <t>vʏoːmɪŋ</t>
         </is>
       </c>
       <c r="D2152" s="1" t="inlineStr">
@@ -69491,7 +69491,7 @@
       </c>
       <c r="B2159" s="1" t="inlineStr">
         <is>
-          <t>[fɛstnaɡəln] 长钉；鞋钉；钉状物〈v.〉</t>
+          <t>[fɛstnaɡəln] 用钉子钉牢；钉住〈v.〉</t>
         </is>
       </c>
       <c r="C2159" s="1" t="inlineStr">
@@ -69501,7 +69501,7 @@
       </c>
       <c r="D2159" s="1" t="inlineStr">
         <is>
-          <t>长钉；鞋钉；钉状物</t>
+          <t>用钉子钉牢；钉住</t>
         </is>
       </c>
       <c r="E2159" s="1" t="inlineStr">
@@ -69523,7 +69523,7 @@
       </c>
       <c r="B2160" s="1" t="inlineStr">
         <is>
-          <t>[ʁɛalɪziːʁən] 工具；器具；手段；实现〈v.〉</t>
+          <t>[ʁɛalɪziːʁən] 实现；认识到〈v.〉</t>
         </is>
       </c>
       <c r="C2160" s="1" t="inlineStr">
@@ -69533,7 +69533,7 @@
       </c>
       <c r="D2160" s="1" t="inlineStr">
         <is>
-          <t>工具；器具；手段；实现</t>
+          <t>实现；认识到</t>
         </is>
       </c>
       <c r="E2160" s="1" t="inlineStr">
@@ -69619,7 +69619,7 @@
       </c>
       <c r="B2163" s="1" t="inlineStr">
         <is>
-          <t>[fɔlɡliːç] 如此；因此；到如此程度；乳香〈adv.〉</t>
+          <t>[fɔlɡliːç] 因此；所以；由此〈adv.〉</t>
         </is>
       </c>
       <c r="C2163" s="1" t="inlineStr">
@@ -69629,7 +69629,7 @@
       </c>
       <c r="D2163" s="1" t="inlineStr">
         <is>
-          <t>如此；因此；到如此程度；乳香</t>
+          <t>因此；所以；由此</t>
         </is>
       </c>
       <c r="E2163" s="1" t="inlineStr">
@@ -69843,7 +69843,7 @@
       </c>
       <c r="B2170" s="1" t="inlineStr">
         <is>
-          <t>[ɔbɡlaɪç] 然而〈adv.〉</t>
+          <t>[ɔbɡlaɪç] 虽然；尽管〈adv.〉</t>
         </is>
       </c>
       <c r="C2170" s="1" t="inlineStr">
@@ -69853,7 +69853,7 @@
       </c>
       <c r="D2170" s="1" t="inlineStr">
         <is>
-          <t>然而</t>
+          <t>虽然；尽管</t>
         </is>
       </c>
       <c r="E2170" s="1" t="inlineStr">
@@ -69971,7 +69971,7 @@
       </c>
       <c r="B2174" s="1" t="inlineStr">
         <is>
-          <t>[faʊxən] 唾液；唾吐；小雨〈v.〉</t>
+          <t>[faʊxən] 嘶嘶叫；哈气；发出嘶声〈v.〉</t>
         </is>
       </c>
       <c r="C2174" s="1" t="inlineStr">
@@ -69981,7 +69981,7 @@
       </c>
       <c r="D2174" s="1" t="inlineStr">
         <is>
-          <t>唾液；唾吐；小雨</t>
+          <t>嘶嘶叫；哈气；发出嘶声</t>
         </is>
       </c>
       <c r="E2174" s="1" t="inlineStr">
